--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="游戏任务" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0">
+    <comment ref="O3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -63,7 +63,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>_id</t>
   </si>
@@ -71,33 +74,39 @@
     <t>GroupId</t>
   </si>
   <si>
+    <t>ConType</t>
+  </si>
+  <si>
+    <t>ConRequire</t>
+  </si>
+  <si>
+    <t>RewardGold</t>
+  </si>
+  <si>
+    <t>RewardExp</t>
+  </si>
+  <si>
+    <t>RewardTypeList</t>
+  </si>
+  <si>
+    <t>RewardIdList</t>
+  </si>
+  <si>
+    <t>NumberList</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>RewardText</t>
+  </si>
+  <si>
+    <t>Sort</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
-    <t>Condition</t>
-  </si>
-  <si>
-    <t>RewardGold</t>
-  </si>
-  <si>
-    <t>RewardExp</t>
-  </si>
-  <si>
-    <t>RewardIdList</t>
-  </si>
-  <si>
-    <t>RewardTypeList</t>
-  </si>
-  <si>
-    <t>QuanlityList</t>
-  </si>
-  <si>
-    <t>Memo</t>
-  </si>
-  <si>
-    <t>Sort</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -113,70 +122,46 @@
     <t>string</t>
   </si>
   <si>
-    <t>闯过第2关</t>
+    <t>击杀10个怪物</t>
+  </si>
+  <si>
+    <t>奖励1个新手武器</t>
   </si>
   <si>
     <t>穿戴一件装备</t>
   </si>
   <si>
-    <t>闯过5关</t>
-  </si>
-  <si>
-    <t>闯过第10关</t>
+    <t>奖励1万金币</t>
   </si>
   <si>
     <t>强化一次</t>
   </si>
   <si>
-    <t>挑战一次副本</t>
-  </si>
-  <si>
-    <t>包裹界面设置回收</t>
-  </si>
-  <si>
-    <t>学习技能</t>
-  </si>
-  <si>
-    <t>闯过第100关</t>
-  </si>
-  <si>
-    <t>闯过第200关</t>
-  </si>
-  <si>
-    <t>闯过第500关</t>
+    <t>奖励100精炼石</t>
+  </si>
+  <si>
+    <t>精炼一次</t>
+  </si>
+  <si>
+    <t>奖励1本1阶技能</t>
+  </si>
+  <si>
+    <t>学习一个技能</t>
+  </si>
+  <si>
+    <t>奖励一个宠物</t>
+  </si>
+  <si>
+    <t>上阵一个宠物</t>
+  </si>
+  <si>
+    <t>奖励十万金币</t>
+  </si>
+  <si>
+    <t>设置自动回收</t>
   </si>
   <si>
     <t>闯过1w关</t>
-  </si>
-  <si>
-    <t>闯过2w关</t>
-  </si>
-  <si>
-    <t>闯过3w关</t>
-  </si>
-  <si>
-    <t>闯过4w关</t>
-  </si>
-  <si>
-    <t>闯过5w关</t>
-  </si>
-  <si>
-    <t>闯过6w关</t>
-  </si>
-  <si>
-    <t>闯过7w关</t>
-  </si>
-  <si>
-    <t>闯过8w关</t>
-  </si>
-  <si>
-    <t>闯过9w关</t>
-  </si>
-  <si>
-    <t>闯过10w关</t>
-  </si>
-  <si>
-    <t>设置-其他界面，绑定帐号并且存档</t>
   </si>
 </sst>
 </file>
@@ -1145,163 +1130,192 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:M27"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="13.5833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1"/>
+    <col min="6" max="6" width="15.8333333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="20.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.75" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.4166666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="1" customWidth="1"/>
+    <col min="10" max="11" width="13.75" style="1" customWidth="1"/>
     <col min="12" max="12" width="19.8333333333333" style="1" customWidth="1"/>
-    <col min="13" max="13" width="19.625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="13" max="13" width="21.4166666666667" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19.625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5833333333333" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" customHeight="1" spans="3:13">
+    <row r="1" customHeight="1" spans="1:15">
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:15">
+      <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:15">
       <c r="C3" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:15">
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="M4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="2"/>
     </row>
-    <row r="4" customHeight="1" spans="3:13">
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="2" t="s">
+    <row r="5" customHeight="1" spans="1:15">
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:15">
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>301</v>
+      </c>
+      <c r="F6" s="1">
         <v>10</v>
       </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>20</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2"/>
     </row>
-    <row r="5" customHeight="1" spans="3:13">
-      <c r="C5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:13">
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
-      <c r="G6" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H6" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
-      <c r="J6" s="1">
-        <v>2</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:13">
+    <row r="7" customHeight="1" spans="1:15">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1309,7 +1323,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -1318,16 +1332,20 @@
         <v>10000</v>
       </c>
       <c r="H7" s="1">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M7" s="1">
+        <v>21</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="1">
         <v>2</v>
       </c>
+      <c r="O7" s="2"/>
     </row>
-    <row r="8" customHeight="1" spans="3:13">
+    <row r="8" customHeight="1" spans="1:15">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1335,34 +1353,38 @@
         <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
         <v>5</v>
       </c>
-      <c r="G8" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H8" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I8" s="1">
-        <v>2</v>
-      </c>
       <c r="J8" s="1">
-        <v>2</v>
+        <v>5001</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M8" s="1">
+        <v>23</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="1">
         <v>3</v>
       </c>
+      <c r="O8" s="2"/>
     </row>
-    <row r="9" customHeight="1" spans="3:13">
+    <row r="9" customHeight="1" spans="1:15">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1370,34 +1392,38 @@
         <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>1</v>
+        <v>202</v>
       </c>
       <c r="F9" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>401</v>
+        <v>4</v>
       </c>
       <c r="J9" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M9" s="1">
+        <v>25</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" s="1">
         <v>4</v>
       </c>
+      <c r="O9" s="2"/>
     </row>
-    <row r="10" customHeight="1" spans="3:13">
+    <row r="10" customHeight="1" spans="1:15">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1405,53 +1431,70 @@
         <v>1</v>
       </c>
       <c r="E10" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>10000</v>
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>4</v>
+      </c>
+      <c r="J10" s="1">
+        <v>10</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" s="1">
+        <v>27</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N10" s="1">
         <v>5</v>
       </c>
+      <c r="O10" s="2"/>
     </row>
-    <row r="11" customHeight="1" spans="3:13">
+    <row r="11" customHeight="1" spans="1:15">
       <c r="C11" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
       </c>
       <c r="E11" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="F11" s="1">
         <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="H11" s="1">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" s="1">
-        <v>6</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N11" s="1">
+        <v>10</v>
+      </c>
+      <c r="O11" s="2"/>
     </row>
-    <row r="12" customHeight="1" spans="3:13">
+    <row r="12" customHeight="1" spans="1:15">
       <c r="C12" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
@@ -1460,549 +1503,84 @@
         <v>5</v>
       </c>
       <c r="F12" s="1">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="G12" s="1">
+        <v>100000</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N12" s="1">
+        <v>11</v>
+      </c>
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:15">
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:15">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1">
+        <v>101</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
         <v>10000</v>
       </c>
-      <c r="H12" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I12" s="1">
-        <v>2001</v>
-      </c>
-      <c r="J12" s="1">
-        <v>3</v>
-      </c>
-      <c r="K12" s="1">
-        <v>1</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" s="1">
-        <v>7</v>
-      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>9</v>
+      </c>
+      <c r="J14" s="1">
+        <v>4003</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N14" s="1">
+        <v>13</v>
+      </c>
+      <c r="O14" s="2"/>
     </row>
-    <row r="13" customHeight="1" spans="3:13">
-      <c r="C13" s="1">
-        <v>8</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1">
-        <v>6</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="1">
-        <v>10000</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M13" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:13">
-      <c r="C14" s="1">
-        <v>9</v>
-      </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1">
-        <v>100</v>
-      </c>
-      <c r="G14" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I14" s="1">
-        <v>2002</v>
-      </c>
-      <c r="J14" s="1">
-        <v>3</v>
-      </c>
-      <c r="K14" s="1">
-        <v>1</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M14" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:13">
-      <c r="C15" s="1">
-        <v>10</v>
-      </c>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="F15" s="1">
-        <v>200</v>
-      </c>
-      <c r="G15" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I15" s="1">
-        <v>2003</v>
-      </c>
-      <c r="J15" s="1">
-        <v>3</v>
-      </c>
-      <c r="K15" s="1">
-        <v>1</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:13">
-      <c r="C16" s="1">
-        <v>11</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1">
-        <v>500</v>
-      </c>
-      <c r="G16" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H16" s="1">
-        <v>10000</v>
-      </c>
-      <c r="I16" s="1">
-        <v>3003</v>
-      </c>
-      <c r="J16" s="1">
-        <v>3</v>
-      </c>
-      <c r="K16" s="1">
-        <v>1</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M16" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:13">
-      <c r="C17" s="1">
-        <v>12</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2</v>
-      </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="F17" s="1">
-        <v>10000</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1">
-        <v>4003</v>
-      </c>
-      <c r="J17" s="1">
-        <v>9</v>
-      </c>
-      <c r="K17" s="1">
-        <v>100</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M17" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:13">
-      <c r="C18" s="1">
-        <v>13</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2</v>
-      </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1">
-        <v>20000</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
-        <v>0</v>
-      </c>
-      <c r="I18" s="1">
-        <v>4003</v>
-      </c>
-      <c r="J18" s="1">
-        <v>9</v>
-      </c>
-      <c r="K18" s="1">
-        <v>100</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M18" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:13">
-      <c r="C19" s="1">
-        <v>14</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
-      <c r="I19" s="1">
-        <v>4003</v>
-      </c>
-      <c r="J19" s="1">
-        <v>9</v>
-      </c>
-      <c r="K19" s="1">
-        <v>100</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M19" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:13">
-      <c r="C20" s="1">
-        <v>15</v>
-      </c>
-      <c r="D20" s="1">
-        <v>2</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1">
-        <v>40000</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-      <c r="I20" s="1">
-        <v>4003</v>
-      </c>
-      <c r="J20" s="1">
-        <v>9</v>
-      </c>
-      <c r="K20" s="1">
-        <v>100</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M20" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:13">
-      <c r="C21" s="1">
-        <v>16</v>
-      </c>
-      <c r="D21" s="1">
-        <v>2</v>
-      </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1">
-        <v>50000</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="1">
-        <v>4003</v>
-      </c>
-      <c r="J21" s="1">
-        <v>9</v>
-      </c>
-      <c r="K21" s="1">
-        <v>100</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M21" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:13">
-      <c r="C22" s="1">
-        <v>17</v>
-      </c>
-      <c r="D22" s="1">
-        <v>2</v>
-      </c>
-      <c r="E22" s="1">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1">
-        <v>60000</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
-      <c r="I22" s="1">
-        <v>4003</v>
-      </c>
-      <c r="J22" s="1">
-        <v>9</v>
-      </c>
-      <c r="K22" s="1">
-        <v>100</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M22" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:13">
-      <c r="C23" s="1">
-        <v>18</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1">
-        <v>70000</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1">
-        <v>4003</v>
-      </c>
-      <c r="J23" s="1">
-        <v>9</v>
-      </c>
-      <c r="K23" s="1">
-        <v>100</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M23" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:13">
-      <c r="C24" s="1">
-        <v>19</v>
-      </c>
-      <c r="D24" s="1">
-        <v>2</v>
-      </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="1">
-        <v>80000</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="1">
-        <v>4003</v>
-      </c>
-      <c r="J24" s="1">
-        <v>9</v>
-      </c>
-      <c r="K24" s="1">
-        <v>100</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M24" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:13">
-      <c r="C25" s="1">
-        <v>20</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2</v>
-      </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1">
-        <v>90000</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1">
-        <v>4003</v>
-      </c>
-      <c r="J25" s="1">
-        <v>9</v>
-      </c>
-      <c r="K25" s="1">
-        <v>100</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M25" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:13">
-      <c r="C26" s="1">
-        <v>21</v>
-      </c>
-      <c r="D26" s="1">
-        <v>2</v>
-      </c>
-      <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1">
-        <v>100000</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="I26" s="1">
-        <v>4003</v>
-      </c>
-      <c r="J26" s="1">
-        <v>9</v>
-      </c>
-      <c r="K26" s="1">
-        <v>100</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M26" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:13">
-      <c r="C27" s="1">
-        <v>22</v>
-      </c>
-      <c r="D27" s="1">
-        <v>2</v>
-      </c>
-      <c r="E27" s="1">
-        <v>7</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0</v>
-      </c>
-      <c r="H27" s="1">
-        <v>0</v>
-      </c>
-      <c r="I27" s="1">
-        <v>4003</v>
-      </c>
-      <c r="J27" s="1">
-        <v>9</v>
-      </c>
-      <c r="K27" s="1">
-        <v>100</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M27" s="1">
-        <v>12</v>
+    <row r="28" customHeight="1" spans="1:3">
+      <c r="A28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="1">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O14 C3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="35">
   <si>
     <t>#</t>
   </si>
@@ -131,13 +131,13 @@
     <t>穿戴一件装备</t>
   </si>
   <si>
-    <t>奖励1万金币</t>
+    <t>奖励1万金币，1000铁矿石</t>
   </si>
   <si>
     <t>强化一次</t>
   </si>
   <si>
-    <t>奖励100精炼石</t>
+    <t>奖励1万金币，1000黑铁石</t>
   </si>
   <si>
     <t>精炼一次</t>
@@ -149,13 +149,19 @@
     <t>学习一个技能</t>
   </si>
   <si>
-    <t>奖励一个宠物</t>
+    <t>奖励一个新手宠物</t>
   </si>
   <si>
     <t>上阵一个宠物</t>
   </si>
   <si>
     <t>奖励十万金币</t>
+  </si>
+  <si>
+    <t>击杀100个怪物</t>
+  </si>
+  <si>
+    <t>奖励1本2阶技能</t>
   </si>
   <si>
     <t>设置自动回收</t>
@@ -340,12 +346,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1130,8 +1136,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
+  <dimension ref="A1:O39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="13.5833333333333" style="1" customWidth="1"/>
@@ -1147,17 +1153,17 @@
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:15">
+    <row r="1" customHeight="1" spans="3:15">
       <c r="O1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:15">
+    <row r="2" customHeight="1" spans="3:15">
       <c r="O2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:15">
+    <row r="3" customHeight="1" spans="3:15">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1198,7 +1204,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:15">
+    <row r="4" customHeight="1" spans="3:15">
       <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1237,7 +1243,7 @@
       </c>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" customHeight="1" spans="1:15">
+    <row r="5" customHeight="1" spans="3:15">
       <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
@@ -1276,7 +1282,7 @@
       </c>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" customHeight="1" spans="1:15">
+    <row r="6" customHeight="1" spans="3:15">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1315,7 +1321,7 @@
       </c>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" customHeight="1" spans="1:15">
+    <row r="7" customHeight="1" spans="3:15">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1334,6 +1340,15 @@
       <c r="H7" s="1">
         <v>0</v>
       </c>
+      <c r="I7" s="1">
+        <v>5</v>
+      </c>
+      <c r="J7" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K7" s="1">
+        <v>10</v>
+      </c>
       <c r="L7" s="1" t="s">
         <v>21</v>
       </c>
@@ -1345,7 +1360,7 @@
       </c>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" customHeight="1" spans="1:15">
+    <row r="8" customHeight="1" spans="3:15">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1359,7 +1374,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -1368,7 +1383,7 @@
         <v>5</v>
       </c>
       <c r="J8" s="1">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
@@ -1384,7 +1399,7 @@
       </c>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" customHeight="1" spans="1:15">
+    <row r="9" customHeight="1" spans="3:15">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1404,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J9" s="1">
         <v>1</v>
@@ -1423,7 +1438,7 @@
       </c>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" customHeight="1" spans="1:15">
+    <row r="10" customHeight="1" spans="3:15">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1443,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J10" s="1">
         <v>10</v>
@@ -1462,7 +1477,7 @@
       </c>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" customHeight="1" spans="1:15">
+    <row r="11" customHeight="1" spans="3:15">
       <c r="C11" s="1">
         <v>7</v>
       </c>
@@ -1488,11 +1503,11 @@
         <v>30</v>
       </c>
       <c r="N11" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" customHeight="1" spans="1:15">
+    <row r="12" customHeight="1" spans="3:15">
       <c r="C12" s="1">
         <v>8</v>
       </c>
@@ -1500,87 +1515,156 @@
         <v>1</v>
       </c>
       <c r="E12" s="1">
-        <v>5</v>
+        <v>301</v>
       </c>
       <c r="F12" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G12" s="1">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
         <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>7</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>31</v>
       </c>
       <c r="M12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" s="1">
+        <v>7</v>
+      </c>
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" customHeight="1" spans="3:15">
+      <c r="C13" s="1">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>5</v>
+      </c>
+      <c r="F13" s="1">
+        <v>500</v>
+      </c>
+      <c r="G13" s="1">
+        <v>100000</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N12" s="1">
-        <v>11</v>
-      </c>
-      <c r="O12" s="2"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:15">
+      <c r="N13" s="1">
+        <v>8</v>
+      </c>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" customHeight="1" spans="1:15">
-      <c r="A14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="1">
+    <row r="14" customHeight="1" spans="3:15">
+      <c r="O14" s="2"/>
+    </row>
+    <row r="15" customHeight="1" spans="3:15">
+      <c r="O15" s="2"/>
+    </row>
+    <row r="16" customHeight="1" spans="3:15">
+      <c r="O16" s="2"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:15">
+      <c r="O17" s="2"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:15">
+      <c r="O18" s="2"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:15">
+      <c r="O19" s="2"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:15">
+      <c r="O20" s="2"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:15">
+      <c r="O21" s="2"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:15">
+      <c r="O22" s="2"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:15">
+      <c r="O23" s="2"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:15">
+      <c r="O24" s="2"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:15">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1">
         <v>101</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D25" s="1">
         <v>2</v>
       </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1">
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
         <v>10000</v>
       </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
         <v>9</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J25" s="1">
         <v>4003</v>
       </c>
-      <c r="K14" s="1">
+      <c r="K25" s="1">
         <v>100</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N14" s="1">
+      <c r="L25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N25" s="1">
         <v>13</v>
       </c>
-      <c r="O14" s="2"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:3">
-      <c r="A28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C28" s="1">
+      <c r="O25" s="2"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:3">
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="1">
         <v>201</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O14 C3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O25 C3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -346,12 +346,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1335,7 +1335,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -1374,7 +1374,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>5002</v>
       </c>
       <c r="K8" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>23</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
   <si>
     <t>#</t>
   </si>
@@ -128,43 +128,58 @@
     <t>奖励1个新手武器</t>
   </si>
   <si>
-    <t>穿戴一件装备</t>
-  </si>
-  <si>
-    <t>奖励1万金币，1000铁矿石</t>
-  </si>
-  <si>
-    <t>强化一次</t>
-  </si>
-  <si>
-    <t>奖励1万金币，1000黑铁石</t>
-  </si>
-  <si>
-    <t>精炼一次</t>
-  </si>
-  <si>
-    <t>奖励1本1阶技能</t>
+    <t>穿戴1件装备</t>
+  </si>
+  <si>
+    <t>奖励1个新手衣服</t>
+  </si>
+  <si>
+    <t>穿戴2件装备</t>
+  </si>
+  <si>
+    <t>奖励1万金币，10铜矿石</t>
+  </si>
+  <si>
+    <t>强化1次</t>
+  </si>
+  <si>
+    <t>奖励1万金币，10黑铁矿</t>
+  </si>
+  <si>
+    <t>精炼1次</t>
+  </si>
+  <si>
+    <t>奖励1本1阶技能自选</t>
   </si>
   <si>
     <t>学习一个技能</t>
   </si>
   <si>
-    <t>奖励一个新手宠物</t>
+    <t>奖励1个新手宠物自选</t>
   </si>
   <si>
     <t>上阵一个宠物</t>
   </si>
   <si>
-    <t>奖励十万金币</t>
+    <t>奖励10万金币</t>
   </si>
   <si>
     <t>击杀100个怪物</t>
   </si>
   <si>
-    <t>奖励1本2阶技能</t>
-  </si>
-  <si>
-    <t>设置自动回收</t>
+    <t>奖励1本2阶技能自选</t>
+  </si>
+  <si>
+    <t>设置1次自动回收</t>
+  </si>
+  <si>
+    <t>奖励10万金币，100铜矿石</t>
+  </si>
+  <si>
+    <t>回收100件道具</t>
+  </si>
+  <si>
+    <t>奖励20万金币，100黑铁矿</t>
   </si>
   <si>
     <t>闯过1w关</t>
@@ -1136,7 +1151,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1323,7 +1338,7 @@
     </row>
     <row r="7" customHeight="1" spans="3:15">
       <c r="C7" s="1">
-        <v>2</v>
+        <v>222</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -1335,19 +1350,19 @@
         <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J7" s="1">
-        <v>5001</v>
+        <v>2</v>
       </c>
       <c r="K7" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>21</v>
@@ -1368,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>203</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
@@ -1383,7 +1398,7 @@
         <v>5</v>
       </c>
       <c r="J8" s="1">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="K8" s="1">
         <v>10</v>
@@ -1393,9 +1408,6 @@
       </c>
       <c r="M8" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="N8" s="1">
-        <v>3</v>
       </c>
       <c r="O8" s="2"/>
     </row>
@@ -1407,25 +1419,25 @@
         <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J9" s="1">
-        <v>1</v>
+        <v>5002</v>
       </c>
       <c r="K9" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>25</v>
@@ -1434,7 +1446,7 @@
         <v>26</v>
       </c>
       <c r="N9" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O9" s="2"/>
     </row>
@@ -1446,7 +1458,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1">
-        <v>10</v>
+        <v>202</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
@@ -1461,7 +1473,7 @@
         <v>7</v>
       </c>
       <c r="J10" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
@@ -1473,28 +1485,37 @@
         <v>28</v>
       </c>
       <c r="N10" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O10" s="2"/>
     </row>
     <row r="11" customHeight="1" spans="3:15">
       <c r="C11" s="1">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>10</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
         <v>7</v>
       </c>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1">
-        <v>100</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1">
-        <v>100000</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
+      <c r="J11" s="1">
+        <v>10</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>29</v>
@@ -1503,37 +1524,28 @@
         <v>30</v>
       </c>
       <c r="N11" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O11" s="2"/>
     </row>
     <row r="12" customHeight="1" spans="3:15">
       <c r="C12" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
       </c>
       <c r="E12" s="1">
-        <v>301</v>
+        <v>100</v>
       </c>
       <c r="F12" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H12" s="1">
         <v>0</v>
-      </c>
-      <c r="I12" s="1">
-        <v>7</v>
-      </c>
-      <c r="J12" s="1">
-        <v>2</v>
-      </c>
-      <c r="K12" s="1">
-        <v>1</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>31</v>
@@ -1542,44 +1554,122 @@
         <v>32</v>
       </c>
       <c r="N12" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O12" s="2"/>
     </row>
     <row r="13" customHeight="1" spans="3:15">
       <c r="C13" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
       </c>
       <c r="E13" s="1">
-        <v>5</v>
+        <v>301</v>
       </c>
       <c r="F13" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G13" s="1">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1">
         <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>7</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>33</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N13" s="1">
+        <v>7</v>
+      </c>
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" customHeight="1" spans="3:15">
+      <c r="C14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>5</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>100000</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K14" s="1">
+        <v>100</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N14" s="1">
         <v>8</v>
       </c>
-      <c r="O13" s="2"/>
-    </row>
-    <row r="14" customHeight="1" spans="3:15">
       <c r="O14" s="2"/>
     </row>
     <row r="15" customHeight="1" spans="3:15">
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>6</v>
+      </c>
+      <c r="F15" s="1">
+        <v>100</v>
+      </c>
+      <c r="G15" s="1">
+        <v>200000</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>5</v>
+      </c>
+      <c r="J15" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K15" s="1">
+        <v>100</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N15" s="1">
+        <v>9</v>
+      </c>
       <c r="O15" s="2"/>
     </row>
     <row r="16" customHeight="1" spans="3:15">
@@ -1610,61 +1700,64 @@
       <c r="O24" s="2"/>
     </row>
     <row r="25" customHeight="1" spans="1:15">
-      <c r="A25" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C25" s="1">
+      <c r="O25" s="2"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:15">
+      <c r="A26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1">
         <v>101</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D26" s="1">
         <v>2</v>
       </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1">
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
         <v>10000</v>
       </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1">
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
         <v>9</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J26" s="1">
         <v>4003</v>
       </c>
-      <c r="K25" s="1">
+      <c r="K26" s="1">
         <v>100</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N25" s="1">
+      <c r="L26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N26" s="1">
         <v>13</v>
       </c>
-      <c r="O25" s="2"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:3">
-      <c r="A39" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="1">
+      <c r="O26" s="2"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:3">
+      <c r="A40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="1">
         <v>201</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O25 C3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O26 C3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="39">
   <si>
     <t>#</t>
   </si>
@@ -134,7 +134,7 @@
     <t>奖励1个新手衣服</t>
   </si>
   <si>
-    <t>穿戴2件装备</t>
+    <t>击杀100个怪物</t>
   </si>
   <si>
     <t>奖励1万金币，10铜矿石</t>
@@ -162,9 +162,6 @@
   </si>
   <si>
     <t>奖励10万金币</t>
-  </si>
-  <si>
-    <t>击杀100个怪物</t>
   </si>
   <si>
     <t>奖励1本2阶技能自选</t>
@@ -1338,7 +1335,7 @@
     </row>
     <row r="7" customHeight="1" spans="3:15">
       <c r="C7" s="1">
-        <v>222</v>
+        <v>2</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -1383,10 +1380,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>4</v>
+        <v>301</v>
       </c>
       <c r="F8" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G8" s="1">
         <v>20000</v>
@@ -1408,6 +1405,9 @@
       </c>
       <c r="M8" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="N8" s="1">
+        <v>3</v>
       </c>
       <c r="O8" s="2"/>
     </row>
@@ -1446,7 +1446,7 @@
         <v>26</v>
       </c>
       <c r="N9" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" s="2"/>
     </row>
@@ -1470,7 +1470,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J10" s="1">
         <v>1</v>
@@ -1485,7 +1485,7 @@
         <v>28</v>
       </c>
       <c r="N10" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O10" s="2"/>
     </row>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" s="1">
         <v>10</v>
@@ -1524,7 +1524,7 @@
         <v>30</v>
       </c>
       <c r="N11" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11" s="2"/>
     </row>
@@ -1554,7 +1554,7 @@
         <v>32</v>
       </c>
       <c r="N12" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O12" s="2"/>
     </row>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J13" s="1">
         <v>2</v>
@@ -1587,13 +1587,13 @@
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="N13" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O13" s="2"/>
     </row>
@@ -1623,13 +1623,13 @@
         <v>100</v>
       </c>
       <c r="L14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="N14" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O14" s="2"/>
     </row>
@@ -1662,13 +1662,13 @@
         <v>100</v>
       </c>
       <c r="L15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="M15" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="N15" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O15" s="2"/>
     </row>
@@ -1737,7 +1737,7 @@
         <v>100</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N26" s="1">
         <v>13</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="38">
   <si>
     <t>#</t>
   </si>
@@ -161,16 +161,13 @@
     <t>上阵一个宠物</t>
   </si>
   <si>
-    <t>奖励10万金币</t>
+    <t>奖励10万金币，100铜矿石</t>
   </si>
   <si>
     <t>奖励1本2阶技能自选</t>
   </si>
   <si>
     <t>设置1次自动回收</t>
-  </si>
-  <si>
-    <t>奖励10万金币，100铜矿石</t>
   </si>
   <si>
     <t>回收100件道具</t>
@@ -1547,6 +1544,15 @@
       <c r="H12" s="1">
         <v>0</v>
       </c>
+      <c r="I12" s="1">
+        <v>5</v>
+      </c>
+      <c r="J12" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
       <c r="L12" s="1" t="s">
         <v>31</v>
       </c>
@@ -1616,6 +1622,9 @@
       <c r="H14" s="1">
         <v>0</v>
       </c>
+      <c r="I14" s="1">
+        <v>5</v>
+      </c>
       <c r="J14" s="1">
         <v>5001</v>
       </c>
@@ -1626,7 +1635,7 @@
         <v>34</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="N14" s="1">
         <v>9</v>
@@ -1662,10 +1671,10 @@
         <v>100</v>
       </c>
       <c r="L15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M15" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="N15" s="1">
         <v>10</v>
@@ -1737,7 +1746,7 @@
         <v>100</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N26" s="1">
         <v>13</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -170,7 +170,7 @@
     <t>设置1次自动回收</t>
   </si>
   <si>
-    <t>回收100件道具</t>
+    <t>自动回收100件装备</t>
   </si>
   <si>
     <t>奖励20万金币，100黑铁矿</t>
@@ -355,12 +355,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -137,13 +137,13 @@
     <t>击杀100个怪物</t>
   </si>
   <si>
-    <t>奖励1万金币，10铜矿石</t>
+    <t>奖励1万金币，100铜矿石</t>
   </si>
   <si>
     <t>强化1次</t>
   </si>
   <si>
-    <t>奖励1万金币，10黑铁矿</t>
+    <t>奖励1万金币，100黑铁矿</t>
   </si>
   <si>
     <t>精炼1次</t>
@@ -161,7 +161,7 @@
     <t>上阵一个宠物</t>
   </si>
   <si>
-    <t>奖励10万金币，100铜矿石</t>
+    <t>奖励100万金币，1000铜矿石</t>
   </si>
   <si>
     <t>奖励1本2阶技能自选</t>
@@ -173,7 +173,7 @@
     <t>自动回收100件装备</t>
   </si>
   <si>
-    <t>奖励20万金币，100黑铁矿</t>
+    <t>奖励200万金币，1000黑铁矿</t>
   </si>
   <si>
     <t>闯过1w关</t>
@@ -355,12 +355,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1383,7 +1383,7 @@
         <v>100</v>
       </c>
       <c r="G8" s="1">
-        <v>20000</v>
+        <v>200000</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -1395,7 +1395,7 @@
         <v>5001</v>
       </c>
       <c r="K8" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>23</v>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>20000</v>
+        <v>200000</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -1434,7 +1434,7 @@
         <v>5002</v>
       </c>
       <c r="K9" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>25</v>
@@ -1539,7 +1539,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="H12" s="1">
         <v>0</v>
@@ -1551,7 +1551,7 @@
         <v>5001</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>31</v>
@@ -1617,7 +1617,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
       <c r="H14" s="1">
         <v>0</v>
@@ -1629,7 +1629,7 @@
         <v>5001</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>34</v>
@@ -1656,7 +1656,7 @@
         <v>100</v>
       </c>
       <c r="G15" s="1">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
@@ -1668,7 +1668,7 @@
         <v>5002</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>35</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="39">
   <si>
     <t>#</t>
   </si>
@@ -122,7 +122,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>击杀10个怪物</t>
+    <t>击杀2个怪物</t>
   </si>
   <si>
     <t>奖励1个新手武器</t>
@@ -134,34 +134,37 @@
     <t>奖励1个新手衣服</t>
   </si>
   <si>
+    <t>击杀30个怪物</t>
+  </si>
+  <si>
+    <t>奖励20万金币，100铜矿石</t>
+  </si>
+  <si>
+    <t>强化1次</t>
+  </si>
+  <si>
+    <t>奖励20万金币，100黑铁矿</t>
+  </si>
+  <si>
+    <t>精炼1次</t>
+  </si>
+  <si>
+    <t>奖励1本1阶技能自选</t>
+  </si>
+  <si>
+    <t>学习一个技能</t>
+  </si>
+  <si>
+    <t>奖励1个新手宠物自选</t>
+  </si>
+  <si>
+    <t>上阵一个宠物</t>
+  </si>
+  <si>
+    <t>奖励100万金币，1000铜矿石</t>
+  </si>
+  <si>
     <t>击杀100个怪物</t>
-  </si>
-  <si>
-    <t>奖励1万金币，100铜矿石</t>
-  </si>
-  <si>
-    <t>强化1次</t>
-  </si>
-  <si>
-    <t>奖励1万金币，100黑铁矿</t>
-  </si>
-  <si>
-    <t>精炼1次</t>
-  </si>
-  <si>
-    <t>奖励1本1阶技能自选</t>
-  </si>
-  <si>
-    <t>学习一个技能</t>
-  </si>
-  <si>
-    <t>奖励1个新手宠物自选</t>
-  </si>
-  <si>
-    <t>上阵一个宠物</t>
-  </si>
-  <si>
-    <t>奖励100万金币，1000铜矿石</t>
   </si>
   <si>
     <t>奖励1本2阶技能自选</t>
@@ -1302,7 +1305,7 @@
         <v>301</v>
       </c>
       <c r="F6" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -1380,7 +1383,7 @@
         <v>301</v>
       </c>
       <c r="F8" s="1">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1">
         <v>200000</v>
@@ -1593,10 +1596,10 @@
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N13" s="1">
         <v>8</v>
@@ -1632,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>32</v>
@@ -1671,10 +1674,10 @@
         <v>1000</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N15" s="1">
         <v>10</v>
@@ -1746,7 +1749,7 @@
         <v>100</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N26" s="1">
         <v>13</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="41">
   <si>
     <t>#</t>
   </si>
@@ -143,7 +143,7 @@
     <t>强化1次</t>
   </si>
   <si>
-    <t>奖励20万金币，100黑铁矿</t>
+    <t>奖励20万金币，10黑铁矿</t>
   </si>
   <si>
     <t>精炼1次</t>
@@ -173,10 +173,16 @@
     <t>设置1次自动回收</t>
   </si>
   <si>
-    <t>自动回收100件装备</t>
-  </si>
-  <si>
-    <t>奖励200万金币，1000黑铁矿</t>
+    <t>自动回收50件装备</t>
+  </si>
+  <si>
+    <t>奖励200万金币，100黑铁矿</t>
+  </si>
+  <si>
+    <t>通过第2关</t>
+  </si>
+  <si>
+    <t>奖励1本3阶技能自选</t>
   </si>
   <si>
     <t>闯过1w关</t>
@@ -1437,7 +1443,7 @@
         <v>5002</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>25</v>
@@ -1656,7 +1662,7 @@
         <v>6</v>
       </c>
       <c r="F15" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G15" s="1">
         <v>2000000</v>
@@ -1671,7 +1677,7 @@
         <v>5002</v>
       </c>
       <c r="K15" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>36</v>
@@ -1685,6 +1691,42 @@
       <c r="O15" s="2"/>
     </row>
     <row r="16" customHeight="1" spans="3:15">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>300</v>
+      </c>
+      <c r="F16" s="1">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>8</v>
+      </c>
+      <c r="J16" s="1">
+        <v>3</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N16" s="1">
+        <v>10</v>
+      </c>
       <c r="O16" s="2"/>
     </row>
     <row r="17" customHeight="1" spans="1:15">
@@ -1749,7 +1791,7 @@
         <v>100</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N26" s="1">
         <v>13</v>
@@ -1769,7 +1811,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O26 C3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O15 O16 O6:O14 O17:O26 C3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
   <si>
     <t>#</t>
   </si>
@@ -183,6 +183,21 @@
   </si>
   <si>
     <t>奖励1本3阶技能自选</t>
+  </si>
+  <si>
+    <t>击杀1000个怪物</t>
+  </si>
+  <si>
+    <t>奖励200万金币，1000铜矿石</t>
+  </si>
+  <si>
+    <t>通过第3关</t>
+  </si>
+  <si>
+    <t>奖励1本4阶技能自选</t>
+  </si>
+  <si>
+    <t>击杀3000个怪物</t>
   </si>
   <si>
     <t>闯过1w关</t>
@@ -364,12 +379,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1154,7 +1169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1725,17 +1740,125 @@
         <v>39</v>
       </c>
       <c r="N16" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O16" s="2"/>
     </row>
     <row r="17" customHeight="1" spans="1:15">
+      <c r="C17" s="1">
+        <v>13</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>301</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2000000</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>5</v>
+      </c>
+      <c r="J17" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N17" s="1">
+        <v>12</v>
+      </c>
       <c r="O17" s="2"/>
     </row>
     <row r="18" customHeight="1" spans="1:15">
+      <c r="C18" s="1">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>300</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>8</v>
+      </c>
+      <c r="J18" s="1">
+        <v>4</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N18" s="1">
+        <v>13</v>
+      </c>
       <c r="O18" s="2"/>
     </row>
     <row r="19" customHeight="1" spans="1:15">
+      <c r="C19" s="1">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>301</v>
+      </c>
+      <c r="F19" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2000000</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>5</v>
+      </c>
+      <c r="J19" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K19" s="1">
+        <v>100</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N19" s="1">
+        <v>12</v>
+      </c>
       <c r="O19" s="2"/>
     </row>
     <row r="20" customHeight="1" spans="1:15">
@@ -1754,64 +1877,61 @@
       <c r="O24" s="2"/>
     </row>
     <row r="25" customHeight="1" spans="1:15">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1">
+        <v>101</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1">
+        <v>10000</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
+        <v>9</v>
+      </c>
+      <c r="J25" s="1">
+        <v>4003</v>
+      </c>
+      <c r="K25" s="1">
+        <v>100</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N25" s="1">
+        <v>13</v>
+      </c>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" customHeight="1" spans="1:15">
-      <c r="A26" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C26" s="1">
-        <v>101</v>
-      </c>
-      <c r="D26" s="1">
-        <v>2</v>
-      </c>
-      <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1">
-        <v>10000</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="I26" s="1">
-        <v>9</v>
-      </c>
-      <c r="J26" s="1">
-        <v>4003</v>
-      </c>
-      <c r="K26" s="1">
-        <v>100</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N26" s="1">
-        <v>13</v>
-      </c>
-      <c r="O26" s="2"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:3">
-      <c r="A40" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C40" s="1">
+    <row r="39" customHeight="1" spans="1:3">
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="1">
         <v>201</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O15 O16 O6:O14 O17:O26 C3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O16 O17:O25 C3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="53">
   <si>
     <t>#</t>
   </si>
@@ -173,7 +173,7 @@
     <t>设置1次自动回收</t>
   </si>
   <si>
-    <t>自动回收50件装备</t>
+    <t>获得50件装备</t>
   </si>
   <si>
     <t>奖励200万金币，100黑铁矿</t>
@@ -200,7 +200,28 @@
     <t>击杀3000个怪物</t>
   </si>
   <si>
-    <t>闯过1w关</t>
+    <t>强化{0}次</t>
+  </si>
+  <si>
+    <t>奖励{0}金币，{1}铜矿石</t>
+  </si>
+  <si>
+    <t>精炼{0}次</t>
+  </si>
+  <si>
+    <t>奖励{0}金币，{1}黑铁矿</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物</t>
+  </si>
+  <si>
+    <t>奖励{0}金币，{1}组四格碎片</t>
+  </si>
+  <si>
+    <t>自动回收{0}件装备</t>
+  </si>
+  <si>
+    <t>获得{0}个宠物</t>
   </si>
 </sst>
 </file>
@@ -379,23 +400,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -720,7 +747,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -744,16 +771,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -762,92 +789,93 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1169,769 +1197,1417 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O39"/>
+  <dimension ref="C1:O43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="13.5833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.8333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.4166666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5" style="1" customWidth="1"/>
-    <col min="10" max="11" width="13.75" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19.8333333333333" style="1" customWidth="1"/>
-    <col min="13" max="13" width="21.4166666666667" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19.625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5833333333333" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="1" max="4" width="9" style="2"/>
+    <col min="5" max="5" width="13.5833333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.8333333333333" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.4166666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="2" customWidth="1"/>
+    <col min="10" max="11" width="13.75" style="2" customWidth="1"/>
+    <col min="12" max="12" width="19.8333333333333" style="2" customWidth="1"/>
+    <col min="13" max="13" width="21.4166666666667" style="2" customWidth="1"/>
+    <col min="14" max="14" width="19.625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="12.5833333333333" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="3:15">
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="3:15">
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="3:15">
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="G3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="3:15">
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="D4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="G4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="2"/>
+      <c r="O4" s="3"/>
     </row>
     <row r="5" customHeight="1" spans="3:15">
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="O5" s="2"/>
+      <c r="O5" s="3"/>
     </row>
     <row r="6" customHeight="1" spans="3:15">
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
         <v>301</v>
       </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="F6" s="2">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
         <v>20</v>
       </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1" t="s">
+      <c r="J6" s="2">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="M6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N6" s="1">
-        <v>1</v>
-      </c>
-      <c r="O6" s="2"/>
+      <c r="N6" s="2">
+        <v>1</v>
+      </c>
+      <c r="O6" s="3"/>
     </row>
     <row r="7" customHeight="1" spans="3:15">
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
         <v>4</v>
       </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
         <v>20</v>
       </c>
-      <c r="J7" s="1">
-        <v>2</v>
-      </c>
-      <c r="K7" s="1">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1" t="s">
+      <c r="J7" s="2">
+        <v>2</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="1">
-        <v>2</v>
-      </c>
-      <c r="O7" s="2"/>
+      <c r="N7" s="2">
+        <v>2</v>
+      </c>
+      <c r="O7" s="3"/>
     </row>
     <row r="8" customHeight="1" spans="3:15">
-      <c r="C8" s="1">
+      <c r="C8" s="2">
         <v>3</v>
       </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
         <v>301</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <v>30</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="2">
         <v>200000</v>
       </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>5</v>
-      </c>
-      <c r="J8" s="1">
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>5</v>
+      </c>
+      <c r="J8" s="2">
         <v>5001</v>
       </c>
-      <c r="K8" s="1">
+      <c r="K8" s="2">
         <v>100</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N8" s="1">
+      <c r="N8" s="2">
         <v>3</v>
       </c>
-      <c r="O8" s="2"/>
+      <c r="O8" s="3"/>
     </row>
     <row r="9" customHeight="1" spans="3:15">
-      <c r="C9" s="1">
+      <c r="C9" s="2">
         <v>4</v>
       </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1">
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
         <v>203</v>
       </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1">
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
         <v>200000</v>
       </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1">
-        <v>5</v>
-      </c>
-      <c r="J9" s="1">
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>5</v>
+      </c>
+      <c r="J9" s="2">
         <v>5002</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="2">
         <v>10</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9" s="2">
         <v>4</v>
       </c>
-      <c r="O9" s="2"/>
+      <c r="O9" s="3"/>
     </row>
     <row r="10" customHeight="1" spans="3:15">
-      <c r="C10" s="1">
-        <v>5</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="C10" s="2">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
         <v>202</v>
       </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
         <v>8</v>
       </c>
-      <c r="J10" s="1">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1">
-        <v>1</v>
-      </c>
-      <c r="L10" s="1" t="s">
+      <c r="J10" s="2">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="M10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="N10" s="1">
-        <v>5</v>
-      </c>
-      <c r="O10" s="2"/>
+      <c r="N10" s="2">
+        <v>5</v>
+      </c>
+      <c r="O10" s="3"/>
     </row>
     <row r="11" customHeight="1" spans="3:15">
-      <c r="C11" s="1">
+      <c r="C11" s="2">
         <v>6</v>
       </c>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
         <v>10</v>
       </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
         <v>8</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="2">
         <v>10</v>
       </c>
-      <c r="K11" s="1">
-        <v>1</v>
-      </c>
-      <c r="L11" s="1" t="s">
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="M11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N11" s="2">
         <v>6</v>
       </c>
-      <c r="O11" s="2"/>
+      <c r="O11" s="3"/>
     </row>
     <row r="12" customHeight="1" spans="3:15">
-      <c r="C12" s="1">
+      <c r="C12" s="2">
         <v>7</v>
       </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1">
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
         <v>100</v>
       </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1">
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
         <v>1000000</v>
       </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1">
-        <v>5</v>
-      </c>
-      <c r="J12" s="1">
+      <c r="H12" s="2">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>5</v>
+      </c>
+      <c r="J12" s="2">
         <v>5001</v>
       </c>
-      <c r="K12" s="1">
+      <c r="K12" s="2">
         <v>1000</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="L12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="M12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N12" s="2">
         <v>7</v>
       </c>
-      <c r="O12" s="2"/>
+      <c r="O12" s="3"/>
     </row>
     <row r="13" customHeight="1" spans="3:15">
-      <c r="C13" s="1">
+      <c r="C13" s="2">
         <v>8</v>
       </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1">
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2">
         <v>301</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="2">
         <v>100</v>
       </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1">
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
         <v>8</v>
       </c>
-      <c r="J13" s="1">
-        <v>2</v>
-      </c>
-      <c r="K13" s="1">
-        <v>1</v>
-      </c>
-      <c r="L13" s="1" t="s">
+      <c r="J13" s="2">
+        <v>2</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="M13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="N13" s="1">
+      <c r="N13" s="2">
         <v>8</v>
       </c>
-      <c r="O13" s="2"/>
+      <c r="O13" s="3"/>
     </row>
     <row r="14" customHeight="1" spans="3:15">
-      <c r="C14" s="1">
+      <c r="C14" s="2">
         <v>9</v>
       </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1">
-        <v>5</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" s="1">
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>5</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
         <v>1000000</v>
       </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
-        <v>5</v>
-      </c>
-      <c r="J14" s="1">
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>5</v>
+      </c>
+      <c r="J14" s="2">
         <v>5001</v>
       </c>
-      <c r="K14" s="1">
+      <c r="K14" s="2">
         <v>1000</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="L14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="M14" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N14" s="1">
+      <c r="N14" s="2">
         <v>9</v>
       </c>
-      <c r="O14" s="2"/>
+      <c r="O14" s="3"/>
     </row>
     <row r="15" customHeight="1" spans="3:15">
-      <c r="C15" s="1">
+      <c r="C15" s="2">
         <v>10</v>
       </c>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1">
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2">
+        <v>201</v>
+      </c>
+      <c r="F15" s="2">
+        <v>50</v>
+      </c>
+      <c r="G15" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>5</v>
+      </c>
+      <c r="J15" s="2">
+        <v>5002</v>
+      </c>
+      <c r="K15" s="2">
+        <v>100</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N15" s="2">
+        <v>10</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" customHeight="1" spans="3:15">
+      <c r="C16" s="2">
+        <v>11</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2">
+        <v>300</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>8</v>
+      </c>
+      <c r="J16" s="2">
+        <v>3</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N16" s="2">
+        <v>11</v>
+      </c>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" customHeight="1" spans="3:15">
+      <c r="C17" s="2">
+        <v>13</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2">
+        <v>301</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>5</v>
+      </c>
+      <c r="J17" s="2">
+        <v>5001</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N17" s="2">
+        <v>12</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" customHeight="1" spans="3:15">
+      <c r="C18" s="2">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2">
+        <v>300</v>
+      </c>
+      <c r="F18" s="2">
+        <v>3</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2">
+        <v>4</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N18" s="2">
+        <v>13</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" customHeight="1" spans="3:15">
+      <c r="C19" s="2">
+        <v>14</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2">
+        <v>301</v>
+      </c>
+      <c r="F19" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G19" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>5</v>
+      </c>
+      <c r="J19" s="2">
+        <v>5002</v>
+      </c>
+      <c r="K19" s="2">
+        <v>100</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N19" s="2">
+        <v>14</v>
+      </c>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" customHeight="1" spans="3:15">
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" customHeight="1" spans="3:15">
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" customHeight="1" spans="3:15">
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" customHeight="1" spans="3:15">
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" customHeight="1" spans="3:15">
+      <c r="C24" s="2">
+        <v>1001</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2</v>
+      </c>
+      <c r="E24" s="2">
+        <v>203</v>
+      </c>
+      <c r="F24" s="2">
+        <v>10</v>
+      </c>
+      <c r="G24" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>5</v>
+      </c>
+      <c r="J24" s="2">
+        <v>5001</v>
+      </c>
+      <c r="K24" s="2">
+        <v>2000</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N24" s="2">
+        <v>13</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" customHeight="1" spans="3:15">
+      <c r="C25" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D25" s="2">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2">
+        <v>202</v>
+      </c>
+      <c r="F25" s="2">
+        <v>3</v>
+      </c>
+      <c r="G25" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <v>5</v>
+      </c>
+      <c r="J25" s="2">
+        <v>5002</v>
+      </c>
+      <c r="K25" s="2">
+        <v>200</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:15">
+      <c r="C26" s="2">
+        <v>1003</v>
+      </c>
+      <c r="D26" s="2">
+        <v>2</v>
+      </c>
+      <c r="E26" s="2">
+        <v>301</v>
+      </c>
+      <c r="F26" s="2">
+        <v>2000</v>
+      </c>
+      <c r="G26" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>5</v>
+      </c>
+      <c r="J26" s="2">
+        <v>5001</v>
+      </c>
+      <c r="K26" s="2">
+        <v>50</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:15">
+      <c r="C27" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2">
+        <v>201</v>
+      </c>
+      <c r="F27" s="2">
+        <v>100</v>
+      </c>
+      <c r="G27" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <v>5</v>
+      </c>
+      <c r="J27" s="2">
+        <v>5002</v>
+      </c>
+      <c r="K27" s="2">
+        <v>2000</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:15">
+      <c r="C28" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D28" s="2">
+        <v>2</v>
+      </c>
+      <c r="E28" s="2">
+        <v>101</v>
+      </c>
+      <c r="F28" s="2">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
+        <v>5</v>
+      </c>
+      <c r="J28" s="2">
+        <v>5002</v>
+      </c>
+      <c r="K28" s="2">
+        <v>200</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C29" s="1">
+        <v>1006</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1">
+        <v>203</v>
+      </c>
+      <c r="F29" s="1">
+        <v>30</v>
+      </c>
+      <c r="G29" s="1">
+        <v>4000000</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1">
+        <v>5</v>
+      </c>
+      <c r="J29" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K29" s="1">
+        <v>3000</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:15">
+      <c r="C30" s="2">
+        <v>1007</v>
+      </c>
+      <c r="D30" s="2">
+        <v>2</v>
+      </c>
+      <c r="E30" s="2">
+        <v>202</v>
+      </c>
+      <c r="F30" s="2">
         <v>6</v>
       </c>
-      <c r="F15" s="1">
+      <c r="G30" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="H30" s="2">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>5</v>
+      </c>
+      <c r="J30" s="2">
+        <v>5002</v>
+      </c>
+      <c r="K30" s="2">
+        <v>300</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:15">
+      <c r="C31" s="2">
+        <v>1008</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2</v>
+      </c>
+      <c r="E31" s="2">
+        <v>301</v>
+      </c>
+      <c r="F31" s="2">
+        <v>6000</v>
+      </c>
+      <c r="G31" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>5</v>
+      </c>
+      <c r="J31" s="2">
+        <v>5001</v>
+      </c>
+      <c r="K31" s="2">
         <v>50</v>
       </c>
-      <c r="G15" s="1">
-        <v>2000000</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1">
-        <v>5</v>
-      </c>
-      <c r="J15" s="1">
+      <c r="L31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:15">
+      <c r="C32" s="2">
+        <v>1009</v>
+      </c>
+      <c r="D32" s="2">
+        <v>2</v>
+      </c>
+      <c r="E32" s="2">
+        <v>201</v>
+      </c>
+      <c r="F32" s="2">
+        <v>800</v>
+      </c>
+      <c r="G32" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
+        <v>5</v>
+      </c>
+      <c r="J32" s="2">
         <v>5002</v>
       </c>
-      <c r="K15" s="1">
-        <v>100</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="N15" s="1">
-        <v>10</v>
-      </c>
-      <c r="O15" s="2"/>
-    </row>
-    <row r="16" customHeight="1" spans="3:15">
-      <c r="C16" s="1">
-        <v>11</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1">
+      <c r="K32" s="2">
         <v>300</v>
       </c>
-      <c r="F16" s="1">
-        <v>2</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1">
-        <v>8</v>
-      </c>
-      <c r="J16" s="1">
-        <v>3</v>
-      </c>
-      <c r="K16" s="1">
-        <v>1</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N16" s="1">
-        <v>11</v>
-      </c>
-      <c r="O16" s="2"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:15">
-      <c r="C17" s="1">
-        <v>13</v>
-      </c>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1">
+      <c r="L32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:13">
+      <c r="C33" s="2">
+        <v>1010</v>
+      </c>
+      <c r="D33" s="2">
+        <v>2</v>
+      </c>
+      <c r="E33" s="2">
+        <v>101</v>
+      </c>
+      <c r="F33" s="2">
+        <v>20</v>
+      </c>
+      <c r="G33" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="H33" s="2">
+        <v>0</v>
+      </c>
+      <c r="I33" s="2">
+        <v>5</v>
+      </c>
+      <c r="J33" s="2">
+        <v>5002</v>
+      </c>
+      <c r="K33" s="2">
+        <v>300</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C34" s="1">
+        <v>1011</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2</v>
+      </c>
+      <c r="E34" s="1">
+        <v>203</v>
+      </c>
+      <c r="F34" s="1">
+        <v>50</v>
+      </c>
+      <c r="G34" s="1">
+        <v>5000000</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="1">
+        <v>5</v>
+      </c>
+      <c r="J34" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K34" s="1">
+        <v>4000</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:13">
+      <c r="C35" s="2">
+        <v>1012</v>
+      </c>
+      <c r="D35" s="2">
+        <v>2</v>
+      </c>
+      <c r="E35" s="2">
+        <v>202</v>
+      </c>
+      <c r="F35" s="2">
+        <v>9</v>
+      </c>
+      <c r="G35" s="1">
+        <v>5000000</v>
+      </c>
+      <c r="H35" s="2">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2">
+        <v>5</v>
+      </c>
+      <c r="J35" s="2">
+        <v>5002</v>
+      </c>
+      <c r="K35" s="2">
+        <v>400</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:13">
+      <c r="C36" s="2">
+        <v>1013</v>
+      </c>
+      <c r="D36" s="2">
+        <v>2</v>
+      </c>
+      <c r="E36" s="2">
         <v>301</v>
       </c>
-      <c r="F17" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G17" s="1">
-        <v>2000000</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1">
-        <v>5</v>
-      </c>
-      <c r="J17" s="1">
+      <c r="F36" s="2">
+        <v>20000</v>
+      </c>
+      <c r="G36" s="1">
+        <v>5000000</v>
+      </c>
+      <c r="H36" s="2">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2">
+        <v>5</v>
+      </c>
+      <c r="J36" s="2">
         <v>5001</v>
       </c>
-      <c r="K17" s="1">
-        <v>1000</v>
-      </c>
-      <c r="L17" s="1" t="s">
+      <c r="K36" s="2">
+        <v>50</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:13">
+      <c r="C37" s="2">
+        <v>1014</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2</v>
+      </c>
+      <c r="E37" s="2">
+        <v>201</v>
+      </c>
+      <c r="F37" s="2">
+        <v>2000</v>
+      </c>
+      <c r="G37" s="1">
+        <v>5000000</v>
+      </c>
+      <c r="H37" s="2">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2">
+        <v>5</v>
+      </c>
+      <c r="J37" s="2">
+        <v>5002</v>
+      </c>
+      <c r="K37" s="2">
+        <v>400</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:13">
+      <c r="C38" s="2">
+        <v>1015</v>
+      </c>
+      <c r="D38" s="2">
+        <v>2</v>
+      </c>
+      <c r="E38" s="2">
+        <v>101</v>
+      </c>
+      <c r="F38" s="2">
+        <v>30</v>
+      </c>
+      <c r="G38" s="1">
+        <v>5000000</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2">
+        <v>5</v>
+      </c>
+      <c r="J38" s="2">
+        <v>5002</v>
+      </c>
+      <c r="K38" s="2">
+        <v>400</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C39" s="1">
+        <v>1016</v>
+      </c>
+      <c r="D39" s="1">
+        <v>2</v>
+      </c>
+      <c r="E39" s="1">
+        <v>203</v>
+      </c>
+      <c r="F39" s="1">
+        <v>80</v>
+      </c>
+      <c r="G39" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1">
+        <v>5</v>
+      </c>
+      <c r="J39" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K39" s="1">
+        <v>5000</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:13">
+      <c r="C40" s="2">
+        <v>1017</v>
+      </c>
+      <c r="D40" s="2">
+        <v>2</v>
+      </c>
+      <c r="E40" s="2">
+        <v>202</v>
+      </c>
+      <c r="F40" s="2">
+        <v>12</v>
+      </c>
+      <c r="G40" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="H40" s="2">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2">
+        <v>5</v>
+      </c>
+      <c r="J40" s="2">
+        <v>5002</v>
+      </c>
+      <c r="K40" s="2">
+        <v>500</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:13">
+      <c r="C41" s="2">
+        <v>1018</v>
+      </c>
+      <c r="D41" s="2">
+        <v>2</v>
+      </c>
+      <c r="E41" s="2">
+        <v>301</v>
+      </c>
+      <c r="F41" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G41" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="H41" s="2">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2">
+        <v>5</v>
+      </c>
+      <c r="J41" s="2">
+        <v>5001</v>
+      </c>
+      <c r="K41" s="2">
+        <v>50</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:13">
+      <c r="C42" s="2">
+        <v>1019</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2</v>
+      </c>
+      <c r="E42" s="2">
+        <v>201</v>
+      </c>
+      <c r="F42" s="2">
+        <v>6000</v>
+      </c>
+      <c r="G42" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="H42" s="2">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2">
+        <v>5</v>
+      </c>
+      <c r="J42" s="2">
+        <v>5002</v>
+      </c>
+      <c r="K42" s="2">
+        <v>500</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:13">
+      <c r="C43" s="2">
+        <v>1020</v>
+      </c>
+      <c r="D43" s="2">
+        <v>2</v>
+      </c>
+      <c r="E43" s="2">
+        <v>101</v>
+      </c>
+      <c r="F43" s="2">
         <v>40</v>
       </c>
-      <c r="M17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N17" s="1">
-        <v>12</v>
-      </c>
-      <c r="O17" s="2"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:15">
-      <c r="C18" s="1">
-        <v>12</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1">
-        <v>300</v>
-      </c>
-      <c r="F18" s="1">
-        <v>3</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
-        <v>0</v>
-      </c>
-      <c r="I18" s="1">
-        <v>8</v>
-      </c>
-      <c r="J18" s="1">
-        <v>4</v>
-      </c>
-      <c r="K18" s="1">
-        <v>1</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N18" s="1">
-        <v>13</v>
-      </c>
-      <c r="O18" s="2"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:15">
-      <c r="C19" s="1">
-        <v>14</v>
-      </c>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1">
-        <v>301</v>
-      </c>
-      <c r="F19" s="1">
-        <v>3000</v>
-      </c>
-      <c r="G19" s="1">
-        <v>2000000</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
-      <c r="I19" s="1">
-        <v>5</v>
-      </c>
-      <c r="J19" s="1">
+      <c r="G43" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="H43" s="2">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2">
+        <v>5</v>
+      </c>
+      <c r="J43" s="2">
         <v>5002</v>
       </c>
-      <c r="K19" s="1">
-        <v>100</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="N19" s="1">
-        <v>12</v>
-      </c>
-      <c r="O19" s="2"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:15">
-      <c r="O20" s="2"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:15">
-      <c r="O21" s="2"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:15">
-      <c r="O22" s="2"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:15">
-      <c r="O23" s="2"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:15">
-      <c r="O24" s="2"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:15">
-      <c r="A25" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C25" s="1">
-        <v>101</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2</v>
-      </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1">
-        <v>10000</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1">
-        <v>9</v>
-      </c>
-      <c r="J25" s="1">
-        <v>4003</v>
-      </c>
-      <c r="K25" s="1">
-        <v>100</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N25" s="1">
-        <v>13</v>
-      </c>
-      <c r="O25" s="2"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:3">
-      <c r="A39" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="1">
-        <v>201</v>
+      <c r="K43" s="2">
+        <v>500</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O16 O17:O25 C3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O19 O20:O24 C3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -1936,7 +1936,7 @@
         <v>46</v>
       </c>
       <c r="N24" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="O24" s="3"/>
     </row>
@@ -1974,6 +1974,9 @@
       <c r="M25" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="N25" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="26" customHeight="1" spans="3:15">
       <c r="C26" s="2">
@@ -2009,6 +2012,9 @@
       <c r="M26" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="N26" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="27" customHeight="1" spans="3:15">
       <c r="C27" s="2">
@@ -2044,6 +2050,9 @@
       <c r="M27" s="2" t="s">
         <v>46</v>
       </c>
+      <c r="N27" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="28" customHeight="1" spans="3:15">
       <c r="C28" s="2">
@@ -2079,6 +2088,9 @@
       <c r="M28" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="N28" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C29" s="1">
@@ -2114,6 +2126,9 @@
       <c r="M29" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="N29" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="30" customHeight="1" spans="3:15">
       <c r="C30" s="2">
@@ -2149,6 +2164,9 @@
       <c r="M30" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="N30" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="31" customHeight="1" spans="3:15">
       <c r="C31" s="2">
@@ -2184,6 +2202,9 @@
       <c r="M31" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="N31" s="2">
+        <v>8</v>
+      </c>
     </row>
     <row r="32" customHeight="1" spans="3:15">
       <c r="C32" s="2">
@@ -2211,7 +2232,7 @@
         <v>5002</v>
       </c>
       <c r="K32" s="2">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>51</v>
@@ -2219,8 +2240,11 @@
       <c r="M32" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:13">
+      <c r="N32" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:14">
       <c r="C33" s="2">
         <v>1010</v>
       </c>
@@ -2254,8 +2278,11 @@
       <c r="M33" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N33" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C34" s="1">
         <v>1011</v>
       </c>
@@ -2289,8 +2316,11 @@
       <c r="M34" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:13">
+      <c r="N34" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:14">
       <c r="C35" s="2">
         <v>1012</v>
       </c>
@@ -2324,8 +2354,11 @@
       <c r="M35" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:13">
+      <c r="N35" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:14">
       <c r="C36" s="2">
         <v>1013</v>
       </c>
@@ -2359,8 +2392,11 @@
       <c r="M36" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:13">
+      <c r="N36" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:14">
       <c r="C37" s="2">
         <v>1014</v>
       </c>
@@ -2386,7 +2422,7 @@
         <v>5002</v>
       </c>
       <c r="K37" s="2">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>51</v>
@@ -2394,8 +2430,11 @@
       <c r="M37" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:13">
+      <c r="N37" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:14">
       <c r="C38" s="2">
         <v>1015</v>
       </c>
@@ -2429,8 +2468,11 @@
       <c r="M38" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="N38" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C39" s="1">
         <v>1016</v>
       </c>
@@ -2464,8 +2506,11 @@
       <c r="M39" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:13">
+      <c r="N39" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:14">
       <c r="C40" s="2">
         <v>1017</v>
       </c>
@@ -2499,8 +2544,11 @@
       <c r="M40" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:13">
+      <c r="N40" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:14">
       <c r="C41" s="2">
         <v>1018</v>
       </c>
@@ -2534,8 +2582,11 @@
       <c r="M41" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:13">
+      <c r="N41" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:14">
       <c r="C42" s="2">
         <v>1019</v>
       </c>
@@ -2561,7 +2612,7 @@
         <v>5002</v>
       </c>
       <c r="K42" s="2">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>51</v>
@@ -2569,8 +2620,11 @@
       <c r="M42" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:13">
+      <c r="N42" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:14">
       <c r="C43" s="2">
         <v>1020</v>
       </c>
@@ -2604,10 +2658,13 @@
       <c r="M43" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="N43" s="2">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O19 O20:O24 C3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O24 C3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J26" s="2">
-        <v>5001</v>
+        <v>11</v>
       </c>
       <c r="K26" s="2">
         <v>50</v>
@@ -2188,10 +2188,10 @@
         <v>0</v>
       </c>
       <c r="I31" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J31" s="2">
-        <v>5001</v>
+        <v>11</v>
       </c>
       <c r="K31" s="2">
         <v>50</v>
@@ -2378,10 +2378,10 @@
         <v>0</v>
       </c>
       <c r="I36" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J36" s="2">
-        <v>5001</v>
+        <v>11</v>
       </c>
       <c r="K36" s="2">
         <v>50</v>
@@ -2568,10 +2568,10 @@
         <v>0</v>
       </c>
       <c r="I41" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J41" s="2">
-        <v>5001</v>
+        <v>11</v>
       </c>
       <c r="K41" s="2">
         <v>50</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -2004,7 +2004,7 @@
         <v>11</v>
       </c>
       <c r="K26" s="2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>49</v>
@@ -2194,7 +2194,7 @@
         <v>11</v>
       </c>
       <c r="K31" s="2">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>49</v>
@@ -2384,7 +2384,7 @@
         <v>11</v>
       </c>
       <c r="K36" s="2">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>49</v>
@@ -2574,7 +2574,7 @@
         <v>11</v>
       </c>
       <c r="K41" s="2">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>49</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -400,12 +400,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J26" s="2">
         <v>11</v>
@@ -2188,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J31" s="2">
         <v>11</v>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J36" s="2">
         <v>11</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J41" s="2">
         <v>11</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="48">
   <si>
     <t>#</t>
   </si>
@@ -137,13 +137,13 @@
     <t>击杀30个怪物</t>
   </si>
   <si>
-    <t>奖励20万金币，100铜矿石</t>
+    <t>奖励{0}金币，{1}铜矿石</t>
   </si>
   <si>
     <t>强化1次</t>
   </si>
   <si>
-    <t>奖励20万金币，10黑铁矿</t>
+    <t>奖励{0}金币，{1}黑铁矿</t>
   </si>
   <si>
     <t>精炼1次</t>
@@ -161,9 +161,6 @@
     <t>上阵一个宠物</t>
   </si>
   <si>
-    <t>奖励100万金币，1000铜矿石</t>
-  </si>
-  <si>
     <t>击杀100个怪物</t>
   </si>
   <si>
@@ -176,9 +173,6 @@
     <t>获得50件装备</t>
   </si>
   <si>
-    <t>奖励200万金币，100黑铁矿</t>
-  </si>
-  <si>
     <t>通过第2关</t>
   </si>
   <si>
@@ -188,9 +182,6 @@
     <t>击杀1000个怪物</t>
   </si>
   <si>
-    <t>奖励200万金币，1000铜矿石</t>
-  </si>
-  <si>
     <t>通过第3关</t>
   </si>
   <si>
@@ -200,19 +191,13 @@
     <t>击杀3000个怪物</t>
   </si>
   <si>
+    <t>击杀{0}个怪物</t>
+  </si>
+  <si>
     <t>强化{0}次</t>
   </si>
   <si>
-    <t>奖励{0}金币，{1}铜矿石</t>
-  </si>
-  <si>
     <t>精炼{0}次</t>
-  </si>
-  <si>
-    <t>奖励{0}金币，{1}黑铁矿</t>
-  </si>
-  <si>
-    <t>击杀{0}个怪物</t>
   </si>
   <si>
     <t>奖励{0}金币，{1}组四格碎片</t>
@@ -400,12 +385,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1447,7 +1432,7 @@
         <v>5001</v>
       </c>
       <c r="K8" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>23</v>
@@ -1603,13 +1588,13 @@
         <v>5001</v>
       </c>
       <c r="K12" s="2">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>31</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="N12" s="2">
         <v>7</v>
@@ -1645,10 +1630,10 @@
         <v>1</v>
       </c>
       <c r="L13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="N13" s="2">
         <v>8</v>
@@ -1684,10 +1669,10 @@
         <v>1000</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="N14" s="2">
         <v>9</v>
@@ -1720,13 +1705,13 @@
         <v>5002</v>
       </c>
       <c r="K15" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N15" s="2">
         <v>10</v>
@@ -1762,10 +1747,10 @@
         <v>1</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N16" s="2">
         <v>11</v>
@@ -1798,13 +1783,13 @@
         <v>5001</v>
       </c>
       <c r="K17" s="2">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="N17" s="2">
         <v>12</v>
@@ -1840,10 +1825,10 @@
         <v>1</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N18" s="2">
         <v>13</v>
@@ -1876,13 +1861,13 @@
         <v>5002</v>
       </c>
       <c r="K19" s="2">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N19" s="2">
         <v>14</v>
@@ -1899,11 +1884,46 @@
       <c r="O22" s="3"/>
     </row>
     <row r="23" customHeight="1" spans="3:15">
-      <c r="O23" s="3"/>
+      <c r="C23" s="2">
+        <v>1001</v>
+      </c>
+      <c r="D23" s="2">
+        <v>2</v>
+      </c>
+      <c r="E23" s="2">
+        <v>301</v>
+      </c>
+      <c r="F23" s="2">
+        <v>500</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>5</v>
+      </c>
+      <c r="J23" s="2">
+        <v>5001</v>
+      </c>
+      <c r="K23" s="2">
+        <v>1000</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N23" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" customHeight="1" spans="3:15">
       <c r="C24" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D24" s="2">
         <v>2</v>
@@ -1930,19 +1950,19 @@
         <v>2000</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="N24" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" s="3"/>
     </row>
     <row r="25" customHeight="1" spans="3:15">
       <c r="C25" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D25" s="2">
         <v>2</v>
@@ -1969,18 +1989,18 @@
         <v>200</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="N25" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:15">
       <c r="C26" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D26" s="2">
         <v>2</v>
@@ -2007,18 +2027,18 @@
         <v>10</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N26" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:15">
       <c r="C27" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D27" s="2">
         <v>2</v>
@@ -2045,18 +2065,18 @@
         <v>2000</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="N27" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:15">
       <c r="C28" s="2">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D28" s="2">
         <v>2</v>
@@ -2083,18 +2103,18 @@
         <v>200</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C29" s="1">
-        <v>1006</v>
+      <c r="C29" s="2">
+        <v>1007</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
@@ -2121,18 +2141,18 @@
         <v>3000</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="N29" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:15">
       <c r="C30" s="2">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D30" s="2">
         <v>2</v>
@@ -2159,18 +2179,18 @@
         <v>300</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="N30" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:15">
       <c r="C31" s="2">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D31" s="2">
         <v>2</v>
@@ -2197,18 +2217,18 @@
         <v>15</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N31" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:15">
       <c r="C32" s="2">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D32" s="2">
         <v>2</v>
@@ -2235,18 +2255,18 @@
         <v>3000</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="N32" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:14">
       <c r="C33" s="2">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D33" s="2">
         <v>2</v>
@@ -2273,18 +2293,18 @@
         <v>300</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="N33" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C34" s="1">
-        <v>1011</v>
+      <c r="C34" s="2">
+        <v>1012</v>
       </c>
       <c r="D34" s="1">
         <v>2</v>
@@ -2311,18 +2331,18 @@
         <v>4000</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="N34" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:14">
       <c r="C35" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D35" s="2">
         <v>2</v>
@@ -2349,18 +2369,18 @@
         <v>400</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="N35" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:14">
       <c r="C36" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D36" s="2">
         <v>2</v>
@@ -2387,18 +2407,18 @@
         <v>20</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N36" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:14">
       <c r="C37" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D37" s="2">
         <v>2</v>
@@ -2425,18 +2445,18 @@
         <v>4000</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="N37" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:14">
       <c r="C38" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D38" s="2">
         <v>2</v>
@@ -2463,18 +2483,18 @@
         <v>400</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="N38" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C39" s="1">
-        <v>1016</v>
+      <c r="C39" s="2">
+        <v>1017</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
@@ -2501,18 +2521,18 @@
         <v>5000</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="N39" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:14">
       <c r="C40" s="2">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="D40" s="2">
         <v>2</v>
@@ -2539,18 +2559,18 @@
         <v>500</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="N40" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:14">
       <c r="C41" s="2">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D41" s="2">
         <v>2</v>
@@ -2577,18 +2597,18 @@
         <v>25</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N41" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:14">
       <c r="C42" s="2">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D42" s="2">
         <v>2</v>
@@ -2615,18 +2635,18 @@
         <v>5000</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="N42" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:14">
       <c r="C43" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="D43" s="2">
         <v>2</v>
@@ -2653,18 +2673,18 @@
         <v>500</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="N43" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O24 C3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O24 O6:O22 C3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -1986,7 +1986,7 @@
         <v>5002</v>
       </c>
       <c r="K25" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>44</v>
@@ -2059,7 +2059,7 @@
         <v>5</v>
       </c>
       <c r="J27" s="2">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="K27" s="2">
         <v>2000</v>
@@ -2100,7 +2100,7 @@
         <v>5002</v>
       </c>
       <c r="K28" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>47</v>
@@ -2134,7 +2134,7 @@
       <c r="I29" s="1">
         <v>5</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J29" s="2">
         <v>5001</v>
       </c>
       <c r="K29" s="1">
@@ -2176,7 +2176,7 @@
         <v>5002</v>
       </c>
       <c r="K30" s="2">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>44</v>
@@ -2249,7 +2249,7 @@
         <v>5</v>
       </c>
       <c r="J32" s="2">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="K32" s="2">
         <v>3000</v>
@@ -2290,7 +2290,7 @@
         <v>5002</v>
       </c>
       <c r="K33" s="2">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>47</v>
@@ -2324,7 +2324,7 @@
       <c r="I34" s="1">
         <v>5</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34" s="2">
         <v>5001</v>
       </c>
       <c r="K34" s="1">
@@ -2366,7 +2366,7 @@
         <v>5002</v>
       </c>
       <c r="K35" s="2">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>44</v>
@@ -2439,7 +2439,7 @@
         <v>5</v>
       </c>
       <c r="J37" s="2">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="K37" s="2">
         <v>4000</v>
@@ -2480,7 +2480,7 @@
         <v>5002</v>
       </c>
       <c r="K38" s="2">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>47</v>
@@ -2514,7 +2514,7 @@
       <c r="I39" s="1">
         <v>5</v>
       </c>
-      <c r="J39" s="1">
+      <c r="J39" s="2">
         <v>5001</v>
       </c>
       <c r="K39" s="1">
@@ -2556,7 +2556,7 @@
         <v>5002</v>
       </c>
       <c r="K40" s="2">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>44</v>
@@ -2629,7 +2629,7 @@
         <v>5</v>
       </c>
       <c r="J42" s="2">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="K42" s="2">
         <v>5000</v>
@@ -2670,7 +2670,7 @@
         <v>5002</v>
       </c>
       <c r="K43" s="2">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>47</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="48">
   <si>
     <t>#</t>
   </si>
@@ -856,13 +856,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1182,7 +1183,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O43"/>
+  <dimension ref="C1:O53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="2"/>
@@ -1935,7 +1936,7 @@
         <v>10</v>
       </c>
       <c r="G24" s="2">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="H24" s="2">
         <v>0</v>
@@ -1974,7 +1975,7 @@
         <v>3</v>
       </c>
       <c r="G25" s="2">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="H25" s="2">
         <v>0</v>
@@ -2012,7 +2013,7 @@
         <v>2000</v>
       </c>
       <c r="G26" s="2">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="H26" s="2">
         <v>0</v>
@@ -2050,7 +2051,7 @@
         <v>100</v>
       </c>
       <c r="G27" s="2">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="H27" s="2">
         <v>0</v>
@@ -2088,7 +2089,7 @@
         <v>10</v>
       </c>
       <c r="G28" s="2">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="H28" s="2">
         <v>0</v>
@@ -2125,8 +2126,8 @@
       <c r="F29" s="1">
         <v>30</v>
       </c>
-      <c r="G29" s="1">
-        <v>4000000</v>
+      <c r="G29" s="2">
+        <v>1500000</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -2164,7 +2165,7 @@
         <v>6</v>
       </c>
       <c r="G30" s="2">
-        <v>4000000</v>
+        <v>1500000</v>
       </c>
       <c r="H30" s="2">
         <v>0</v>
@@ -2202,7 +2203,7 @@
         <v>6000</v>
       </c>
       <c r="G31" s="2">
-        <v>4000000</v>
+        <v>1500000</v>
       </c>
       <c r="H31" s="2">
         <v>0</v>
@@ -2240,7 +2241,7 @@
         <v>800</v>
       </c>
       <c r="G32" s="2">
-        <v>4000000</v>
+        <v>1500000</v>
       </c>
       <c r="H32" s="2">
         <v>0</v>
@@ -2278,7 +2279,7 @@
         <v>20</v>
       </c>
       <c r="G33" s="2">
-        <v>4000000</v>
+        <v>1500000</v>
       </c>
       <c r="H33" s="2">
         <v>0</v>
@@ -2315,8 +2316,8 @@
       <c r="F34" s="1">
         <v>50</v>
       </c>
-      <c r="G34" s="1">
-        <v>5000000</v>
+      <c r="G34" s="2">
+        <v>1500000</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
@@ -2353,8 +2354,8 @@
       <c r="F35" s="2">
         <v>9</v>
       </c>
-      <c r="G35" s="1">
-        <v>5000000</v>
+      <c r="G35" s="2">
+        <v>1500000</v>
       </c>
       <c r="H35" s="2">
         <v>0</v>
@@ -2391,8 +2392,8 @@
       <c r="F36" s="2">
         <v>20000</v>
       </c>
-      <c r="G36" s="1">
-        <v>5000000</v>
+      <c r="G36" s="2">
+        <v>1500000</v>
       </c>
       <c r="H36" s="2">
         <v>0</v>
@@ -2429,8 +2430,8 @@
       <c r="F37" s="2">
         <v>2000</v>
       </c>
-      <c r="G37" s="1">
-        <v>5000000</v>
+      <c r="G37" s="2">
+        <v>1500000</v>
       </c>
       <c r="H37" s="2">
         <v>0</v>
@@ -2467,8 +2468,8 @@
       <c r="F38" s="2">
         <v>30</v>
       </c>
-      <c r="G38" s="1">
-        <v>5000000</v>
+      <c r="G38" s="2">
+        <v>1500000</v>
       </c>
       <c r="H38" s="2">
         <v>0</v>
@@ -2505,8 +2506,8 @@
       <c r="F39" s="1">
         <v>80</v>
       </c>
-      <c r="G39" s="1">
-        <v>6000000</v>
+      <c r="G39" s="2">
+        <v>1500000</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
@@ -2543,8 +2544,8 @@
       <c r="F40" s="2">
         <v>12</v>
       </c>
-      <c r="G40" s="1">
-        <v>6000000</v>
+      <c r="G40" s="4">
+        <v>2000000</v>
       </c>
       <c r="H40" s="2">
         <v>0</v>
@@ -2581,8 +2582,8 @@
       <c r="F41" s="2">
         <v>100000</v>
       </c>
-      <c r="G41" s="1">
-        <v>6000000</v>
+      <c r="G41" s="4">
+        <v>2000000</v>
       </c>
       <c r="H41" s="2">
         <v>0</v>
@@ -2619,8 +2620,8 @@
       <c r="F42" s="2">
         <v>6000</v>
       </c>
-      <c r="G42" s="1">
-        <v>6000000</v>
+      <c r="G42" s="4">
+        <v>2000000</v>
       </c>
       <c r="H42" s="2">
         <v>0</v>
@@ -2657,8 +2658,8 @@
       <c r="F43" s="2">
         <v>40</v>
       </c>
-      <c r="G43" s="1">
-        <v>6000000</v>
+      <c r="G43" s="4">
+        <v>2000000</v>
       </c>
       <c r="H43" s="2">
         <v>0</v>
@@ -2679,6 +2680,386 @@
         <v>26</v>
       </c>
       <c r="N43" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:14">
+      <c r="C44" s="2">
+        <v>1022</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1">
+        <v>203</v>
+      </c>
+      <c r="F44" s="1">
+        <v>100</v>
+      </c>
+      <c r="G44" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1">
+        <v>5</v>
+      </c>
+      <c r="J44" s="2">
+        <v>5001</v>
+      </c>
+      <c r="K44" s="1">
+        <v>6000</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N44" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:14">
+      <c r="C45" s="2">
+        <v>1023</v>
+      </c>
+      <c r="D45" s="2">
+        <v>2</v>
+      </c>
+      <c r="E45" s="2">
+        <v>202</v>
+      </c>
+      <c r="F45" s="2">
+        <v>12</v>
+      </c>
+      <c r="G45" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H45" s="2">
+        <v>0</v>
+      </c>
+      <c r="I45" s="2">
+        <v>5</v>
+      </c>
+      <c r="J45" s="2">
+        <v>5002</v>
+      </c>
+      <c r="K45" s="2">
+        <v>50</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:14">
+      <c r="C46" s="2">
+        <v>1024</v>
+      </c>
+      <c r="D46" s="2">
+        <v>2</v>
+      </c>
+      <c r="E46" s="2">
+        <v>301</v>
+      </c>
+      <c r="F46" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G46" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H46" s="2">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2">
+        <v>8</v>
+      </c>
+      <c r="J46" s="2">
+        <v>11</v>
+      </c>
+      <c r="K46" s="2">
+        <v>30</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N46" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:14">
+      <c r="C47" s="2">
+        <v>1025</v>
+      </c>
+      <c r="D47" s="2">
+        <v>2</v>
+      </c>
+      <c r="E47" s="2">
+        <v>201</v>
+      </c>
+      <c r="F47" s="2">
+        <v>6000</v>
+      </c>
+      <c r="G47" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H47" s="2">
+        <v>0</v>
+      </c>
+      <c r="I47" s="2">
+        <v>5</v>
+      </c>
+      <c r="J47" s="2">
+        <v>5001</v>
+      </c>
+      <c r="K47" s="2">
+        <v>6000</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N47" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:14">
+      <c r="C48" s="2">
+        <v>1026</v>
+      </c>
+      <c r="D48" s="2">
+        <v>2</v>
+      </c>
+      <c r="E48" s="2">
+        <v>101</v>
+      </c>
+      <c r="F48" s="2">
+        <v>40</v>
+      </c>
+      <c r="G48" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H48" s="2">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2">
+        <v>5</v>
+      </c>
+      <c r="J48" s="2">
+        <v>5002</v>
+      </c>
+      <c r="K48" s="2">
+        <v>50</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N48" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:14">
+      <c r="C49" s="2">
+        <v>1027</v>
+      </c>
+      <c r="D49" s="1">
+        <v>2</v>
+      </c>
+      <c r="E49" s="1">
+        <v>203</v>
+      </c>
+      <c r="F49" s="1">
+        <v>120</v>
+      </c>
+      <c r="G49" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="1">
+        <v>5</v>
+      </c>
+      <c r="J49" s="2">
+        <v>5001</v>
+      </c>
+      <c r="K49" s="1">
+        <v>7000</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N49" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:14">
+      <c r="C50" s="2">
+        <v>1028</v>
+      </c>
+      <c r="D50" s="2">
+        <v>2</v>
+      </c>
+      <c r="E50" s="2">
+        <v>202</v>
+      </c>
+      <c r="F50" s="2">
+        <v>12</v>
+      </c>
+      <c r="G50" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H50" s="2">
+        <v>0</v>
+      </c>
+      <c r="I50" s="2">
+        <v>5</v>
+      </c>
+      <c r="J50" s="2">
+        <v>5002</v>
+      </c>
+      <c r="K50" s="2">
+        <v>50</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N50" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:14">
+      <c r="C51" s="2">
+        <v>1029</v>
+      </c>
+      <c r="D51" s="2">
+        <v>2</v>
+      </c>
+      <c r="E51" s="2">
+        <v>301</v>
+      </c>
+      <c r="F51" s="2">
+        <v>100000</v>
+      </c>
+      <c r="G51" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H51" s="2">
+        <v>0</v>
+      </c>
+      <c r="I51" s="2">
+        <v>8</v>
+      </c>
+      <c r="J51" s="2">
+        <v>11</v>
+      </c>
+      <c r="K51" s="2">
+        <v>35</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N51" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:14">
+      <c r="C52" s="2">
+        <v>1030</v>
+      </c>
+      <c r="D52" s="2">
+        <v>2</v>
+      </c>
+      <c r="E52" s="2">
+        <v>201</v>
+      </c>
+      <c r="F52" s="2">
+        <v>6000</v>
+      </c>
+      <c r="G52" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H52" s="2">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2">
+        <v>5</v>
+      </c>
+      <c r="J52" s="2">
+        <v>5001</v>
+      </c>
+      <c r="K52" s="2">
+        <v>7000</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N52" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:14">
+      <c r="C53" s="2">
+        <v>1031</v>
+      </c>
+      <c r="D53" s="2">
+        <v>2</v>
+      </c>
+      <c r="E53" s="2">
+        <v>101</v>
+      </c>
+      <c r="F53" s="2">
+        <v>40</v>
+      </c>
+      <c r="G53" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H53" s="2">
+        <v>0</v>
+      </c>
+      <c r="I53" s="2">
+        <v>5</v>
+      </c>
+      <c r="J53" s="2">
+        <v>5002</v>
+      </c>
+      <c r="K53" s="2">
+        <v>50</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N53" s="2">
         <v>21</v>
       </c>
     </row>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -1972,7 +1972,7 @@
         <v>202</v>
       </c>
       <c r="F25" s="2">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G25" s="2">
         <v>1000000</v>
@@ -2086,7 +2086,7 @@
         <v>101</v>
       </c>
       <c r="F28" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G28" s="2">
         <v>1000000</v>
@@ -2162,7 +2162,7 @@
         <v>202</v>
       </c>
       <c r="F30" s="2">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="G30" s="2">
         <v>1500000</v>
@@ -2276,7 +2276,7 @@
         <v>101</v>
       </c>
       <c r="F33" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G33" s="2">
         <v>1500000</v>
@@ -2314,7 +2314,7 @@
         <v>203</v>
       </c>
       <c r="F34" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G34" s="2">
         <v>1500000</v>
@@ -2352,7 +2352,7 @@
         <v>202</v>
       </c>
       <c r="F35" s="2">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="G35" s="2">
         <v>1500000</v>
@@ -2466,7 +2466,7 @@
         <v>101</v>
       </c>
       <c r="F38" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G38" s="2">
         <v>1500000</v>
@@ -2504,7 +2504,7 @@
         <v>203</v>
       </c>
       <c r="F39" s="1">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G39" s="2">
         <v>1500000</v>
@@ -2542,7 +2542,7 @@
         <v>202</v>
       </c>
       <c r="F40" s="2">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="G40" s="4">
         <v>2000000</v>
@@ -2656,7 +2656,7 @@
         <v>101</v>
       </c>
       <c r="F43" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G43" s="4">
         <v>2000000</v>
@@ -2694,7 +2694,7 @@
         <v>203</v>
       </c>
       <c r="F44" s="1">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G44" s="4">
         <v>2000000</v>
@@ -2732,7 +2732,7 @@
         <v>202</v>
       </c>
       <c r="F45" s="2">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="G45" s="4">
         <v>2000000</v>
@@ -2846,7 +2846,7 @@
         <v>101</v>
       </c>
       <c r="F48" s="2">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G48" s="4">
         <v>2000000</v>
@@ -2884,7 +2884,7 @@
         <v>203</v>
       </c>
       <c r="F49" s="1">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="G49" s="4">
         <v>2000000</v>
@@ -2922,7 +2922,7 @@
         <v>202</v>
       </c>
       <c r="F50" s="2">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="G50" s="4">
         <v>2000000</v>
@@ -3036,7 +3036,7 @@
         <v>101</v>
       </c>
       <c r="F53" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G53" s="4">
         <v>2000000</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="游戏任务" sheetId="1" r:id="rId1"/>
+    <sheet name="指引任务" sheetId="1" r:id="rId1"/>
+    <sheet name="新手任务" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,8 +63,44 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="O3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 闯关层数
+2 穿戴装备
+3 强化装备
+4 挑战副本
+5 设置回收</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="48">
   <si>
     <t>#</t>
   </si>
@@ -858,8 +895,8 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1186,27 +1223,27 @@
   <dimension ref="C1:O53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="9" style="2"/>
-    <col min="5" max="5" width="13.5833333333333" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.8333333333333" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.4166666666667" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.5" style="2" customWidth="1"/>
-    <col min="10" max="11" width="13.75" style="2" customWidth="1"/>
-    <col min="12" max="12" width="19.8333333333333" style="2" customWidth="1"/>
-    <col min="13" max="13" width="21.4166666666667" style="2" customWidth="1"/>
-    <col min="14" max="14" width="19.625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="12.5833333333333" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="13.5833333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.8333333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.4166666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="1" customWidth="1"/>
+    <col min="10" max="11" width="13.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.8333333333333" style="1" customWidth="1"/>
+    <col min="13" max="13" width="21.4166666666667" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19.625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5833333333333" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="3:15">
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="3:15">
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1330,547 +1367,547 @@
       <c r="O5" s="3"/>
     </row>
     <row r="6" customHeight="1" spans="3:15">
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>301</v>
       </c>
-      <c r="F6" s="2">
-        <v>2</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
+      <c r="F6" s="1">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
         <v>20</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <v>1</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="1">
         <v>1</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="1">
         <v>1</v>
       </c>
       <c r="O6" s="3"/>
     </row>
     <row r="7" customHeight="1" spans="3:15">
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
         <v>1</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>4</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="1">
         <v>1</v>
       </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
         <v>20</v>
       </c>
-      <c r="J7" s="2">
-        <v>2</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="J7" s="1">
+        <v>2</v>
+      </c>
+      <c r="K7" s="1">
         <v>1</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="1">
         <v>2</v>
       </c>
       <c r="O7" s="3"/>
     </row>
     <row r="8" customHeight="1" spans="3:15">
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>301</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>30</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="1">
         <v>200000</v>
       </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>5</v>
-      </c>
-      <c r="J8" s="2">
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>5</v>
+      </c>
+      <c r="J8" s="1">
         <v>5001</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="1">
         <v>200</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8" s="1">
         <v>3</v>
       </c>
       <c r="O8" s="3"/>
     </row>
     <row r="9" customHeight="1" spans="3:15">
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>203</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>1</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="1">
         <v>200000</v>
       </c>
-      <c r="H9" s="2">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2">
-        <v>5</v>
-      </c>
-      <c r="J9" s="2">
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>5</v>
+      </c>
+      <c r="J9" s="1">
         <v>5002</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="1">
         <v>10</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="L9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="1">
         <v>4</v>
       </c>
       <c r="O9" s="3"/>
     </row>
     <row r="10" customHeight="1" spans="3:15">
-      <c r="C10" s="2">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2">
+      <c r="C10" s="1">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>202</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="1">
         <v>1</v>
       </c>
-      <c r="G10" s="2">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2">
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
         <v>8</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="1">
         <v>1</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="1">
         <v>1</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="L10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="1">
         <v>5</v>
       </c>
       <c r="O10" s="3"/>
     </row>
     <row r="11" customHeight="1" spans="3:15">
-      <c r="C11" s="2">
+      <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>10</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <v>1</v>
       </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
         <v>8</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <v>10</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="1">
         <v>1</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="L11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="1">
         <v>6</v>
       </c>
       <c r="O11" s="3"/>
     </row>
     <row r="12" customHeight="1" spans="3:15">
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>100</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="1">
         <v>1</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="1">
         <v>1000000</v>
       </c>
-      <c r="H12" s="2">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2">
-        <v>5</v>
-      </c>
-      <c r="J12" s="2">
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>5</v>
+      </c>
+      <c r="J12" s="1">
         <v>5001</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="1">
         <v>500</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="L12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="M12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="1">
         <v>7</v>
       </c>
       <c r="O12" s="3"/>
     </row>
     <row r="13" customHeight="1" spans="3:15">
-      <c r="C13" s="2">
+      <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>301</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>100</v>
       </c>
-      <c r="G13" s="2">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2">
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
         <v>8</v>
       </c>
-      <c r="J13" s="2">
-        <v>2</v>
-      </c>
-      <c r="K13" s="2">
+      <c r="J13" s="1">
+        <v>2</v>
+      </c>
+      <c r="K13" s="1">
         <v>1</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="L13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="M13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N13" s="2">
+      <c r="N13" s="1">
         <v>8</v>
       </c>
       <c r="O13" s="3"/>
     </row>
     <row r="14" customHeight="1" spans="3:15">
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>1</v>
       </c>
-      <c r="E14" s="2">
-        <v>5</v>
-      </c>
-      <c r="F14" s="2">
+      <c r="E14" s="1">
+        <v>5</v>
+      </c>
+      <c r="F14" s="1">
         <v>1</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="1">
         <v>1000000</v>
       </c>
-      <c r="H14" s="2">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2">
-        <v>5</v>
-      </c>
-      <c r="J14" s="2">
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>5</v>
+      </c>
+      <c r="J14" s="1">
         <v>5001</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" s="1">
         <v>1000</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="L14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="M14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N14" s="2">
+      <c r="N14" s="1">
         <v>9</v>
       </c>
       <c r="O14" s="3"/>
     </row>
     <row r="15" customHeight="1" spans="3:15">
-      <c r="C15" s="2">
+      <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>1</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>201</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="1">
         <v>50</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="1">
         <v>2000000</v>
       </c>
-      <c r="H15" s="2">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2">
-        <v>5</v>
-      </c>
-      <c r="J15" s="2">
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>5</v>
+      </c>
+      <c r="J15" s="1">
         <v>5002</v>
       </c>
-      <c r="K15" s="2">
+      <c r="K15" s="1">
         <v>20</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="L15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="M15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N15" s="2">
+      <c r="N15" s="1">
         <v>10</v>
       </c>
       <c r="O15" s="3"/>
     </row>
     <row r="16" customHeight="1" spans="3:15">
-      <c r="C16" s="2">
+      <c r="C16" s="1">
         <v>11</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="1">
         <v>1</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="1">
         <v>300</v>
       </c>
-      <c r="F16" s="2">
-        <v>2</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
+      <c r="F16" s="1">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
         <v>8</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="1">
         <v>3</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16" s="1">
         <v>1</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="L16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="M16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N16" s="2">
+      <c r="N16" s="1">
         <v>11</v>
       </c>
       <c r="O16" s="3"/>
     </row>
     <row r="17" customHeight="1" spans="3:15">
-      <c r="C17" s="2">
+      <c r="C17" s="1">
         <v>13</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="1">
         <v>1</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="1">
         <v>301</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="1">
         <v>1000</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="1">
         <v>2000000</v>
       </c>
-      <c r="H17" s="2">
-        <v>0</v>
-      </c>
-      <c r="I17" s="2">
-        <v>5</v>
-      </c>
-      <c r="J17" s="2">
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>5</v>
+      </c>
+      <c r="J17" s="1">
         <v>5001</v>
       </c>
-      <c r="K17" s="2">
+      <c r="K17" s="1">
         <v>2000</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="L17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="M17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N17" s="2">
+      <c r="N17" s="1">
         <v>12</v>
       </c>
       <c r="O17" s="3"/>
     </row>
     <row r="18" customHeight="1" spans="3:15">
-      <c r="C18" s="2">
+      <c r="C18" s="1">
         <v>12</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="1">
         <v>1</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="1">
         <v>300</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="1">
         <v>3</v>
       </c>
-      <c r="G18" s="2">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2">
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
         <v>8</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="1">
         <v>4</v>
       </c>
-      <c r="K18" s="2">
+      <c r="K18" s="1">
         <v>1</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="L18" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="M18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N18" s="2">
+      <c r="N18" s="1">
         <v>13</v>
       </c>
       <c r="O18" s="3"/>
     </row>
     <row r="19" customHeight="1" spans="3:15">
-      <c r="C19" s="2">
+      <c r="C19" s="1">
         <v>14</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="1">
         <v>1</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="1">
         <v>301</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="1">
         <v>3000</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="1">
         <v>2000000</v>
       </c>
-      <c r="H19" s="2">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2">
-        <v>5</v>
-      </c>
-      <c r="J19" s="2">
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>5</v>
+      </c>
+      <c r="J19" s="1">
         <v>5002</v>
       </c>
-      <c r="K19" s="2">
+      <c r="K19" s="1">
         <v>30</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="L19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="M19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N19" s="2">
+      <c r="N19" s="1">
         <v>14</v>
       </c>
       <c r="O19" s="3"/>
@@ -1884,1188 +1921,40 @@
     <row r="22" customHeight="1" spans="3:15">
       <c r="O22" s="3"/>
     </row>
-    <row r="23" customHeight="1" spans="3:15">
-      <c r="C23" s="2">
-        <v>1001</v>
-      </c>
-      <c r="D23" s="2">
-        <v>2</v>
-      </c>
-      <c r="E23" s="2">
-        <v>301</v>
-      </c>
-      <c r="F23" s="2">
-        <v>500</v>
-      </c>
-      <c r="G23" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="H23" s="2">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2">
-        <v>5</v>
-      </c>
-      <c r="J23" s="2">
-        <v>5001</v>
-      </c>
-      <c r="K23" s="2">
-        <v>1000</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N23" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:15">
-      <c r="C24" s="2">
-        <v>1002</v>
-      </c>
-      <c r="D24" s="2">
-        <v>2</v>
-      </c>
-      <c r="E24" s="2">
-        <v>203</v>
-      </c>
-      <c r="F24" s="2">
-        <v>10</v>
-      </c>
-      <c r="G24" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="H24" s="2">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2">
-        <v>5</v>
-      </c>
-      <c r="J24" s="2">
-        <v>5001</v>
-      </c>
-      <c r="K24" s="2">
-        <v>2000</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N24" s="2">
-        <v>2</v>
-      </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" customHeight="1" spans="3:15">
-      <c r="C25" s="2">
-        <v>1003</v>
-      </c>
-      <c r="D25" s="2">
-        <v>2</v>
-      </c>
-      <c r="E25" s="2">
-        <v>202</v>
-      </c>
-      <c r="F25" s="2">
-        <v>20</v>
-      </c>
-      <c r="G25" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="H25" s="2">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2">
-        <v>5</v>
-      </c>
-      <c r="J25" s="2">
-        <v>5002</v>
-      </c>
-      <c r="K25" s="2">
-        <v>20</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:15">
-      <c r="C26" s="2">
-        <v>1004</v>
-      </c>
-      <c r="D26" s="2">
-        <v>2</v>
-      </c>
-      <c r="E26" s="2">
-        <v>301</v>
-      </c>
-      <c r="F26" s="2">
-        <v>2000</v>
-      </c>
-      <c r="G26" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="H26" s="2">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
-        <v>8</v>
-      </c>
-      <c r="J26" s="2">
-        <v>11</v>
-      </c>
-      <c r="K26" s="2">
-        <v>10</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N26" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:15">
-      <c r="C27" s="2">
-        <v>1005</v>
-      </c>
-      <c r="D27" s="2">
-        <v>2</v>
-      </c>
-      <c r="E27" s="2">
-        <v>201</v>
-      </c>
-      <c r="F27" s="2">
-        <v>100</v>
-      </c>
-      <c r="G27" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="H27" s="2">
-        <v>0</v>
-      </c>
-      <c r="I27" s="2">
-        <v>5</v>
-      </c>
-      <c r="J27" s="2">
-        <v>5001</v>
-      </c>
-      <c r="K27" s="2">
-        <v>2000</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N27" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:15">
-      <c r="C28" s="2">
-        <v>1006</v>
-      </c>
-      <c r="D28" s="2">
-        <v>2</v>
-      </c>
-      <c r="E28" s="2">
-        <v>101</v>
-      </c>
-      <c r="F28" s="2">
-        <v>5</v>
-      </c>
-      <c r="G28" s="2">
-        <v>1000000</v>
-      </c>
-      <c r="H28" s="2">
-        <v>0</v>
-      </c>
-      <c r="I28" s="2">
-        <v>5</v>
-      </c>
-      <c r="J28" s="2">
-        <v>5002</v>
-      </c>
-      <c r="K28" s="2">
-        <v>20</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N28" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C29" s="2">
-        <v>1007</v>
-      </c>
-      <c r="D29" s="1">
-        <v>2</v>
-      </c>
-      <c r="E29" s="1">
-        <v>203</v>
-      </c>
-      <c r="F29" s="1">
-        <v>30</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1500000</v>
-      </c>
-      <c r="H29" s="1">
-        <v>0</v>
-      </c>
-      <c r="I29" s="1">
-        <v>5</v>
-      </c>
-      <c r="J29" s="2">
-        <v>5001</v>
-      </c>
-      <c r="K29" s="1">
-        <v>3000</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N29" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:15">
-      <c r="C30" s="2">
-        <v>1008</v>
-      </c>
-      <c r="D30" s="2">
-        <v>2</v>
-      </c>
-      <c r="E30" s="2">
-        <v>202</v>
-      </c>
-      <c r="F30" s="2">
-        <v>60</v>
-      </c>
-      <c r="G30" s="2">
-        <v>1500000</v>
-      </c>
-      <c r="H30" s="2">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2">
-        <v>5</v>
-      </c>
-      <c r="J30" s="2">
-        <v>5002</v>
-      </c>
-      <c r="K30" s="2">
-        <v>30</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N30" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:15">
-      <c r="C31" s="2">
-        <v>1009</v>
-      </c>
-      <c r="D31" s="2">
-        <v>2</v>
-      </c>
-      <c r="E31" s="2">
-        <v>301</v>
-      </c>
-      <c r="F31" s="2">
-        <v>6000</v>
-      </c>
-      <c r="G31" s="2">
-        <v>1500000</v>
-      </c>
-      <c r="H31" s="2">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2">
-        <v>8</v>
-      </c>
-      <c r="J31" s="2">
-        <v>11</v>
-      </c>
-      <c r="K31" s="2">
-        <v>15</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N31" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:15">
-      <c r="C32" s="2">
-        <v>1010</v>
-      </c>
-      <c r="D32" s="2">
-        <v>2</v>
-      </c>
-      <c r="E32" s="2">
-        <v>201</v>
-      </c>
-      <c r="F32" s="2">
-        <v>800</v>
-      </c>
-      <c r="G32" s="2">
-        <v>1500000</v>
-      </c>
-      <c r="H32" s="2">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2">
-        <v>5</v>
-      </c>
-      <c r="J32" s="2">
-        <v>5001</v>
-      </c>
-      <c r="K32" s="2">
-        <v>3000</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N32" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:14">
-      <c r="C33" s="2">
-        <v>1011</v>
-      </c>
-      <c r="D33" s="2">
-        <v>2</v>
-      </c>
-      <c r="E33" s="2">
-        <v>101</v>
-      </c>
-      <c r="F33" s="2">
-        <v>10</v>
-      </c>
-      <c r="G33" s="2">
-        <v>1500000</v>
-      </c>
-      <c r="H33" s="2">
-        <v>0</v>
-      </c>
-      <c r="I33" s="2">
-        <v>5</v>
-      </c>
-      <c r="J33" s="2">
-        <v>5002</v>
-      </c>
-      <c r="K33" s="2">
-        <v>30</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C34" s="2">
-        <v>1012</v>
-      </c>
-      <c r="D34" s="1">
-        <v>2</v>
-      </c>
-      <c r="E34" s="1">
-        <v>203</v>
-      </c>
-      <c r="F34" s="1">
-        <v>40</v>
-      </c>
-      <c r="G34" s="2">
-        <v>1500000</v>
-      </c>
-      <c r="H34" s="1">
-        <v>0</v>
-      </c>
-      <c r="I34" s="1">
-        <v>5</v>
-      </c>
-      <c r="J34" s="2">
-        <v>5001</v>
-      </c>
-      <c r="K34" s="1">
-        <v>4000</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N34" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:14">
-      <c r="C35" s="2">
-        <v>1013</v>
-      </c>
-      <c r="D35" s="2">
-        <v>2</v>
-      </c>
-      <c r="E35" s="2">
-        <v>202</v>
-      </c>
-      <c r="F35" s="2">
-        <v>40</v>
-      </c>
-      <c r="G35" s="2">
-        <v>1500000</v>
-      </c>
-      <c r="H35" s="2">
-        <v>0</v>
-      </c>
-      <c r="I35" s="2">
-        <v>5</v>
-      </c>
-      <c r="J35" s="2">
-        <v>5002</v>
-      </c>
-      <c r="K35" s="2">
-        <v>40</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:14">
-      <c r="C36" s="2">
-        <v>1014</v>
-      </c>
-      <c r="D36" s="2">
-        <v>2</v>
-      </c>
-      <c r="E36" s="2">
-        <v>301</v>
-      </c>
-      <c r="F36" s="2">
-        <v>20000</v>
-      </c>
-      <c r="G36" s="2">
-        <v>1500000</v>
-      </c>
-      <c r="H36" s="2">
-        <v>0</v>
-      </c>
-      <c r="I36" s="2">
-        <v>8</v>
-      </c>
-      <c r="J36" s="2">
-        <v>11</v>
-      </c>
-      <c r="K36" s="2">
-        <v>20</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N36" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:14">
-      <c r="C37" s="2">
-        <v>1015</v>
-      </c>
-      <c r="D37" s="2">
-        <v>2</v>
-      </c>
-      <c r="E37" s="2">
-        <v>201</v>
-      </c>
-      <c r="F37" s="2">
-        <v>2000</v>
-      </c>
-      <c r="G37" s="2">
-        <v>1500000</v>
-      </c>
-      <c r="H37" s="2">
-        <v>0</v>
-      </c>
-      <c r="I37" s="2">
-        <v>5</v>
-      </c>
-      <c r="J37" s="2">
-        <v>5001</v>
-      </c>
-      <c r="K37" s="2">
-        <v>4000</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N37" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:14">
-      <c r="C38" s="2">
-        <v>1016</v>
-      </c>
-      <c r="D38" s="2">
-        <v>2</v>
-      </c>
-      <c r="E38" s="2">
-        <v>101</v>
-      </c>
-      <c r="F38" s="2">
-        <v>15</v>
-      </c>
-      <c r="G38" s="2">
-        <v>1500000</v>
-      </c>
-      <c r="H38" s="2">
-        <v>0</v>
-      </c>
-      <c r="I38" s="2">
-        <v>5</v>
-      </c>
-      <c r="J38" s="2">
-        <v>5002</v>
-      </c>
-      <c r="K38" s="2">
-        <v>40</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N38" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C39" s="2">
-        <v>1017</v>
-      </c>
-      <c r="D39" s="1">
-        <v>2</v>
-      </c>
-      <c r="E39" s="1">
-        <v>203</v>
-      </c>
-      <c r="F39" s="1">
-        <v>50</v>
-      </c>
-      <c r="G39" s="2">
-        <v>1500000</v>
-      </c>
-      <c r="H39" s="1">
-        <v>0</v>
-      </c>
-      <c r="I39" s="1">
-        <v>5</v>
-      </c>
-      <c r="J39" s="2">
-        <v>5001</v>
-      </c>
-      <c r="K39" s="1">
-        <v>5000</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N39" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:14">
-      <c r="C40" s="2">
-        <v>1018</v>
-      </c>
-      <c r="D40" s="2">
-        <v>2</v>
-      </c>
-      <c r="E40" s="2">
-        <v>202</v>
-      </c>
-      <c r="F40" s="2">
-        <v>50</v>
-      </c>
-      <c r="G40" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="H40" s="2">
-        <v>0</v>
-      </c>
-      <c r="I40" s="2">
-        <v>5</v>
-      </c>
-      <c r="J40" s="2">
-        <v>5002</v>
-      </c>
-      <c r="K40" s="2">
-        <v>50</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N40" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:14">
-      <c r="C41" s="2">
-        <v>1019</v>
-      </c>
-      <c r="D41" s="2">
-        <v>2</v>
-      </c>
-      <c r="E41" s="2">
-        <v>301</v>
-      </c>
-      <c r="F41" s="2">
-        <v>100000</v>
-      </c>
-      <c r="G41" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="H41" s="2">
-        <v>0</v>
-      </c>
-      <c r="I41" s="2">
-        <v>8</v>
-      </c>
-      <c r="J41" s="2">
-        <v>11</v>
-      </c>
-      <c r="K41" s="2">
-        <v>25</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N41" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:14">
-      <c r="C42" s="2">
-        <v>1020</v>
-      </c>
-      <c r="D42" s="2">
-        <v>2</v>
-      </c>
-      <c r="E42" s="2">
-        <v>201</v>
-      </c>
-      <c r="F42" s="2">
-        <v>6000</v>
-      </c>
-      <c r="G42" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="H42" s="2">
-        <v>0</v>
-      </c>
-      <c r="I42" s="2">
-        <v>5</v>
-      </c>
-      <c r="J42" s="2">
-        <v>5001</v>
-      </c>
-      <c r="K42" s="2">
-        <v>5000</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N42" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:14">
-      <c r="C43" s="2">
-        <v>1021</v>
-      </c>
-      <c r="D43" s="2">
-        <v>2</v>
-      </c>
-      <c r="E43" s="2">
-        <v>101</v>
-      </c>
-      <c r="F43" s="2">
-        <v>20</v>
-      </c>
-      <c r="G43" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="H43" s="2">
-        <v>0</v>
-      </c>
-      <c r="I43" s="2">
-        <v>5</v>
-      </c>
-      <c r="J43" s="2">
-        <v>5002</v>
-      </c>
-      <c r="K43" s="2">
-        <v>50</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M43" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N43" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:14">
-      <c r="C44" s="2">
-        <v>1022</v>
-      </c>
-      <c r="D44" s="1">
-        <v>2</v>
-      </c>
-      <c r="E44" s="1">
-        <v>203</v>
-      </c>
-      <c r="F44" s="1">
-        <v>60</v>
-      </c>
-      <c r="G44" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="H44" s="1">
-        <v>0</v>
-      </c>
-      <c r="I44" s="1">
-        <v>5</v>
-      </c>
-      <c r="J44" s="2">
-        <v>5001</v>
-      </c>
-      <c r="K44" s="1">
-        <v>6000</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N44" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:14">
-      <c r="C45" s="2">
-        <v>1023</v>
-      </c>
-      <c r="D45" s="2">
-        <v>2</v>
-      </c>
-      <c r="E45" s="2">
-        <v>202</v>
-      </c>
-      <c r="F45" s="2">
-        <v>60</v>
-      </c>
-      <c r="G45" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="H45" s="2">
-        <v>0</v>
-      </c>
-      <c r="I45" s="2">
-        <v>5</v>
-      </c>
-      <c r="J45" s="2">
-        <v>5002</v>
-      </c>
-      <c r="K45" s="2">
-        <v>50</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:14">
-      <c r="C46" s="2">
-        <v>1024</v>
-      </c>
-      <c r="D46" s="2">
-        <v>2</v>
-      </c>
-      <c r="E46" s="2">
-        <v>301</v>
-      </c>
-      <c r="F46" s="2">
-        <v>100000</v>
-      </c>
-      <c r="G46" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="H46" s="2">
-        <v>0</v>
-      </c>
-      <c r="I46" s="2">
-        <v>8</v>
-      </c>
-      <c r="J46" s="2">
-        <v>11</v>
-      </c>
-      <c r="K46" s="2">
-        <v>30</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M46" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N46" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:14">
-      <c r="C47" s="2">
-        <v>1025</v>
-      </c>
-      <c r="D47" s="2">
-        <v>2</v>
-      </c>
-      <c r="E47" s="2">
-        <v>201</v>
-      </c>
-      <c r="F47" s="2">
-        <v>6000</v>
-      </c>
-      <c r="G47" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="H47" s="2">
-        <v>0</v>
-      </c>
-      <c r="I47" s="2">
-        <v>5</v>
-      </c>
-      <c r="J47" s="2">
-        <v>5001</v>
-      </c>
-      <c r="K47" s="2">
-        <v>6000</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M47" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N47" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:14">
-      <c r="C48" s="2">
-        <v>1026</v>
-      </c>
-      <c r="D48" s="2">
-        <v>2</v>
-      </c>
-      <c r="E48" s="2">
-        <v>101</v>
-      </c>
-      <c r="F48" s="2">
-        <v>25</v>
-      </c>
-      <c r="G48" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="H48" s="2">
-        <v>0</v>
-      </c>
-      <c r="I48" s="2">
-        <v>5</v>
-      </c>
-      <c r="J48" s="2">
-        <v>5002</v>
-      </c>
-      <c r="K48" s="2">
-        <v>50</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N48" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:14">
-      <c r="C49" s="2">
-        <v>1027</v>
-      </c>
-      <c r="D49" s="1">
-        <v>2</v>
-      </c>
-      <c r="E49" s="1">
-        <v>203</v>
-      </c>
-      <c r="F49" s="1">
-        <v>70</v>
-      </c>
-      <c r="G49" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="H49" s="1">
-        <v>0</v>
-      </c>
-      <c r="I49" s="1">
-        <v>5</v>
-      </c>
-      <c r="J49" s="2">
-        <v>5001</v>
-      </c>
-      <c r="K49" s="1">
-        <v>7000</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M49" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N49" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:14">
-      <c r="C50" s="2">
-        <v>1028</v>
-      </c>
-      <c r="D50" s="2">
-        <v>2</v>
-      </c>
-      <c r="E50" s="2">
-        <v>202</v>
-      </c>
-      <c r="F50" s="2">
-        <v>70</v>
-      </c>
-      <c r="G50" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="H50" s="2">
-        <v>0</v>
-      </c>
-      <c r="I50" s="2">
-        <v>5</v>
-      </c>
-      <c r="J50" s="2">
-        <v>5002</v>
-      </c>
-      <c r="K50" s="2">
-        <v>50</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M50" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N50" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:14">
-      <c r="C51" s="2">
-        <v>1029</v>
-      </c>
-      <c r="D51" s="2">
-        <v>2</v>
-      </c>
-      <c r="E51" s="2">
-        <v>301</v>
-      </c>
-      <c r="F51" s="2">
-        <v>100000</v>
-      </c>
-      <c r="G51" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="H51" s="2">
-        <v>0</v>
-      </c>
-      <c r="I51" s="2">
-        <v>8</v>
-      </c>
-      <c r="J51" s="2">
-        <v>11</v>
-      </c>
-      <c r="K51" s="2">
-        <v>35</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N51" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:14">
-      <c r="C52" s="2">
-        <v>1030</v>
-      </c>
-      <c r="D52" s="2">
-        <v>2</v>
-      </c>
-      <c r="E52" s="2">
-        <v>201</v>
-      </c>
-      <c r="F52" s="2">
-        <v>6000</v>
-      </c>
-      <c r="G52" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="H52" s="2">
-        <v>0</v>
-      </c>
-      <c r="I52" s="2">
-        <v>5</v>
-      </c>
-      <c r="J52" s="2">
-        <v>5001</v>
-      </c>
-      <c r="K52" s="2">
-        <v>7000</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M52" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N52" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:14">
-      <c r="C53" s="2">
-        <v>1031</v>
-      </c>
-      <c r="D53" s="2">
-        <v>2</v>
-      </c>
-      <c r="E53" s="2">
-        <v>101</v>
-      </c>
-      <c r="F53" s="2">
-        <v>30</v>
-      </c>
-      <c r="G53" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="H53" s="2">
-        <v>0</v>
-      </c>
-      <c r="I53" s="2">
-        <v>5</v>
-      </c>
-      <c r="J53" s="2">
-        <v>5002</v>
-      </c>
-      <c r="K53" s="2">
-        <v>50</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N53" s="2">
-        <v>21</v>
-      </c>
-    </row>
+    <row r="23" customFormat="1" customHeight="1"/>
+    <row r="24" customFormat="1" customHeight="1"/>
+    <row r="25" customFormat="1" customHeight="1"/>
+    <row r="26" customFormat="1" customHeight="1"/>
+    <row r="27" customFormat="1" customHeight="1"/>
+    <row r="28" customFormat="1" customHeight="1"/>
+    <row r="29" customFormat="1" customHeight="1"/>
+    <row r="30" customFormat="1" customHeight="1"/>
+    <row r="31" customFormat="1" customHeight="1"/>
+    <row r="32" customFormat="1" customHeight="1"/>
+    <row r="33" customFormat="1" customHeight="1"/>
+    <row r="34" customFormat="1" customHeight="1"/>
+    <row r="35" customFormat="1" customHeight="1"/>
+    <row r="36" customFormat="1" customHeight="1"/>
+    <row r="37" customFormat="1" customHeight="1"/>
+    <row r="38" customFormat="1" customHeight="1"/>
+    <row r="39" customFormat="1" customHeight="1"/>
+    <row r="40" customFormat="1" customHeight="1"/>
+    <row r="41" customFormat="1" customHeight="1"/>
+    <row r="42" customFormat="1" customHeight="1"/>
+    <row r="43" customFormat="1" customHeight="1"/>
+    <row r="44" customFormat="1" customHeight="1"/>
+    <row r="45" customFormat="1" customHeight="1"/>
+    <row r="46" customFormat="1" customHeight="1"/>
+    <row r="47" customFormat="1" customHeight="1"/>
+    <row r="48" customFormat="1" customHeight="1"/>
+    <row r="49" customFormat="1" customHeight="1"/>
+    <row r="50" customFormat="1" customHeight="1"/>
+    <row r="51" customFormat="1" customHeight="1"/>
+    <row r="52" customFormat="1" customHeight="1"/>
+    <row r="53" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O24 O6:O22 C3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O22 C3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -3073,4 +1962,2056 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C1:O55"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="13" max="13" width="23.9166666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C6" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1">
+        <v>301</v>
+      </c>
+      <c r="F6" s="1">
+        <v>500</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>5</v>
+      </c>
+      <c r="J6" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C7" s="1">
+        <v>1002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1">
+        <v>301</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>5</v>
+      </c>
+      <c r="J7" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C8" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1">
+        <v>301</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>5</v>
+      </c>
+      <c r="J8" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C9" s="1">
+        <v>1004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="1">
+        <v>301</v>
+      </c>
+      <c r="F9" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>5</v>
+      </c>
+      <c r="J9" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N9" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C10" s="1">
+        <v>1005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1">
+        <v>301</v>
+      </c>
+      <c r="F10" s="1">
+        <v>5000</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>5</v>
+      </c>
+      <c r="J10" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N10" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C11" s="1">
+        <v>1006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1">
+        <v>203</v>
+      </c>
+      <c r="F11" s="1">
+        <v>10</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>5</v>
+      </c>
+      <c r="J11" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K11" s="1">
+        <v>2000</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N11" s="1">
+        <v>6</v>
+      </c>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C12" s="1">
+        <v>1007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1">
+        <v>202</v>
+      </c>
+      <c r="F12" s="1">
+        <v>10</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>5</v>
+      </c>
+      <c r="J12" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K12" s="1">
+        <v>20</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C13" s="1">
+        <v>1008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2</v>
+      </c>
+      <c r="E13" s="1">
+        <v>301</v>
+      </c>
+      <c r="F13" s="1">
+        <v>7000</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>8</v>
+      </c>
+      <c r="J13" s="1">
+        <v>11</v>
+      </c>
+      <c r="K13" s="1">
+        <v>10</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N13" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C14" s="1">
+        <v>1009</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1">
+        <v>201</v>
+      </c>
+      <c r="F14" s="1">
+        <v>100</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>5</v>
+      </c>
+      <c r="J14" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K14" s="1">
+        <v>2000</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N14" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C15" s="1">
+        <v>1010</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1">
+        <v>101</v>
+      </c>
+      <c r="F15" s="1">
+        <v>5</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>5</v>
+      </c>
+      <c r="J15" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K15" s="1">
+        <v>20</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C16" s="1">
+        <v>1011</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2">
+        <v>203</v>
+      </c>
+      <c r="F16" s="2">
+        <v>20</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1500000</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>5</v>
+      </c>
+      <c r="J16" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K16" s="2">
+        <v>3000</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N16" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C17" s="1">
+        <v>1012</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>202</v>
+      </c>
+      <c r="F17" s="1">
+        <v>20</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1500000</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>5</v>
+      </c>
+      <c r="J17" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K17" s="1">
+        <v>30</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C18" s="1">
+        <v>1013</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1">
+        <v>301</v>
+      </c>
+      <c r="F18" s="1">
+        <v>10000</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1500000</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>8</v>
+      </c>
+      <c r="J18" s="1">
+        <v>11</v>
+      </c>
+      <c r="K18" s="1">
+        <v>15</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N18" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C19" s="1">
+        <v>1014</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1">
+        <v>201</v>
+      </c>
+      <c r="F19" s="1">
+        <v>800</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1500000</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>5</v>
+      </c>
+      <c r="J19" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K19" s="1">
+        <v>3000</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N19" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C20" s="1">
+        <v>1015</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1">
+        <v>101</v>
+      </c>
+      <c r="F20" s="1">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1500000</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1">
+        <v>5</v>
+      </c>
+      <c r="J20" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K20" s="1">
+        <v>30</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C21" s="1">
+        <v>1016</v>
+      </c>
+      <c r="D21" s="2">
+        <v>2</v>
+      </c>
+      <c r="E21" s="2">
+        <v>203</v>
+      </c>
+      <c r="F21" s="2">
+        <v>35</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1500000</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>5</v>
+      </c>
+      <c r="J21" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K21" s="2">
+        <v>4000</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N21" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C22" s="1">
+        <v>1017</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1">
+        <v>202</v>
+      </c>
+      <c r="F22" s="1">
+        <v>35</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1500000</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1">
+        <v>5</v>
+      </c>
+      <c r="J22" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K22" s="1">
+        <v>40</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N22" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C23" s="1">
+        <v>1018</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1">
+        <v>301</v>
+      </c>
+      <c r="F23" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1500000</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1">
+        <v>8</v>
+      </c>
+      <c r="J23" s="1">
+        <v>11</v>
+      </c>
+      <c r="K23" s="1">
+        <v>20</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N23" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C24" s="1">
+        <v>1019</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1">
+        <v>201</v>
+      </c>
+      <c r="F24" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1500000</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="1">
+        <v>5</v>
+      </c>
+      <c r="J24" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K24" s="1">
+        <v>4000</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N24" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C25" s="1">
+        <v>1020</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1">
+        <v>101</v>
+      </c>
+      <c r="F25" s="1">
+        <v>15</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1500000</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
+        <v>5</v>
+      </c>
+      <c r="J25" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K25" s="1">
+        <v>40</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C26" s="1">
+        <v>1021</v>
+      </c>
+      <c r="D26" s="2">
+        <v>2</v>
+      </c>
+      <c r="E26" s="2">
+        <v>203</v>
+      </c>
+      <c r="F26" s="2">
+        <v>55</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1500000</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>5</v>
+      </c>
+      <c r="J26" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K26" s="2">
+        <v>5000</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N26" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C27" s="1">
+        <v>1022</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
+      <c r="E27" s="1">
+        <v>202</v>
+      </c>
+      <c r="F27" s="1">
+        <v>55</v>
+      </c>
+      <c r="G27" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1">
+        <v>5</v>
+      </c>
+      <c r="J27" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K27" s="1">
+        <v>50</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N27" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C28" s="1">
+        <v>1023</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2</v>
+      </c>
+      <c r="E28" s="1">
+        <v>301</v>
+      </c>
+      <c r="F28" s="1">
+        <v>50000</v>
+      </c>
+      <c r="G28" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1">
+        <v>8</v>
+      </c>
+      <c r="J28" s="1">
+        <v>11</v>
+      </c>
+      <c r="K28" s="1">
+        <v>25</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N28" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C29" s="1">
+        <v>1024</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1">
+        <v>201</v>
+      </c>
+      <c r="F29" s="1">
+        <v>5000</v>
+      </c>
+      <c r="G29" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1">
+        <v>5</v>
+      </c>
+      <c r="J29" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K29" s="1">
+        <v>5000</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N29" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C30" s="1">
+        <v>1025</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2</v>
+      </c>
+      <c r="E30" s="1">
+        <v>101</v>
+      </c>
+      <c r="F30" s="1">
+        <v>20</v>
+      </c>
+      <c r="G30" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1">
+        <v>5</v>
+      </c>
+      <c r="J30" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K30" s="1">
+        <v>50</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N30" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C31" s="1">
+        <v>1026</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2</v>
+      </c>
+      <c r="E31" s="2">
+        <v>203</v>
+      </c>
+      <c r="F31" s="2">
+        <v>85</v>
+      </c>
+      <c r="G31" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>5</v>
+      </c>
+      <c r="J31" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K31" s="2">
+        <v>6000</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N31" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C32" s="1">
+        <v>1027</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
+      <c r="E32" s="1">
+        <v>202</v>
+      </c>
+      <c r="F32" s="2">
+        <v>85</v>
+      </c>
+      <c r="G32" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1">
+        <v>5</v>
+      </c>
+      <c r="J32" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K32" s="1">
+        <v>50</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N32" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C33" s="1">
+        <v>1028</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1">
+        <v>301</v>
+      </c>
+      <c r="F33" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G33" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1">
+        <v>8</v>
+      </c>
+      <c r="J33" s="1">
+        <v>11</v>
+      </c>
+      <c r="K33" s="1">
+        <v>30</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N33" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C34" s="1">
+        <v>1029</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2</v>
+      </c>
+      <c r="E34" s="1">
+        <v>201</v>
+      </c>
+      <c r="F34" s="1">
+        <v>10000</v>
+      </c>
+      <c r="G34" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="1">
+        <v>5</v>
+      </c>
+      <c r="J34" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K34" s="1">
+        <v>6000</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N34" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C35" s="1">
+        <v>1030</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" s="1">
+        <v>101</v>
+      </c>
+      <c r="F35" s="1">
+        <v>25</v>
+      </c>
+      <c r="G35" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1">
+        <v>5</v>
+      </c>
+      <c r="J35" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K35" s="1">
+        <v>50</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C36" s="1">
+        <v>1031</v>
+      </c>
+      <c r="D36" s="2">
+        <v>2</v>
+      </c>
+      <c r="E36" s="2">
+        <v>203</v>
+      </c>
+      <c r="F36" s="2">
+        <v>120</v>
+      </c>
+      <c r="G36" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H36" s="2">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2">
+        <v>5</v>
+      </c>
+      <c r="J36" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K36" s="2">
+        <v>7000</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N36" s="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C37" s="1">
+        <v>1032</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37" s="1">
+        <v>202</v>
+      </c>
+      <c r="F37" s="1">
+        <v>120</v>
+      </c>
+      <c r="G37" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1">
+        <v>5</v>
+      </c>
+      <c r="J37" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K37" s="1">
+        <v>50</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C38" s="1">
+        <v>1033</v>
+      </c>
+      <c r="D38" s="1">
+        <v>2</v>
+      </c>
+      <c r="E38" s="1">
+        <v>301</v>
+      </c>
+      <c r="F38" s="1">
+        <v>200000</v>
+      </c>
+      <c r="G38" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1">
+        <v>8</v>
+      </c>
+      <c r="J38" s="1">
+        <v>11</v>
+      </c>
+      <c r="K38" s="1">
+        <v>35</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N38" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C39" s="1">
+        <v>1034</v>
+      </c>
+      <c r="D39" s="1">
+        <v>2</v>
+      </c>
+      <c r="E39" s="1">
+        <v>201</v>
+      </c>
+      <c r="F39" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G39" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1">
+        <v>5</v>
+      </c>
+      <c r="J39" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K39" s="1">
+        <v>7000</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N39" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C40" s="1">
+        <v>1035</v>
+      </c>
+      <c r="D40" s="1">
+        <v>2</v>
+      </c>
+      <c r="E40" s="1">
+        <v>101</v>
+      </c>
+      <c r="F40" s="1">
+        <v>50</v>
+      </c>
+      <c r="G40" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="1">
+        <v>5</v>
+      </c>
+      <c r="J40" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K40" s="1">
+        <v>50</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N40" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:14">
+      <c r="C41" s="1">
+        <v>1036</v>
+      </c>
+      <c r="D41" s="2">
+        <v>2</v>
+      </c>
+      <c r="E41" s="2">
+        <v>203</v>
+      </c>
+      <c r="F41" s="2">
+        <v>160</v>
+      </c>
+      <c r="G41" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H41" s="2">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2">
+        <v>5</v>
+      </c>
+      <c r="J41" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K41" s="2">
+        <v>7000</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N41" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:14">
+      <c r="C42" s="1">
+        <v>1037</v>
+      </c>
+      <c r="D42" s="1">
+        <v>2</v>
+      </c>
+      <c r="E42" s="1">
+        <v>202</v>
+      </c>
+      <c r="F42" s="1">
+        <v>160</v>
+      </c>
+      <c r="G42" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1">
+        <v>5</v>
+      </c>
+      <c r="J42" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K42" s="1">
+        <v>50</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N42" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:14">
+      <c r="C43" s="1">
+        <v>1038</v>
+      </c>
+      <c r="D43" s="1">
+        <v>2</v>
+      </c>
+      <c r="E43" s="1">
+        <v>301</v>
+      </c>
+      <c r="F43" s="1">
+        <v>350000</v>
+      </c>
+      <c r="G43" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="1">
+        <v>8</v>
+      </c>
+      <c r="J43" s="1">
+        <v>11</v>
+      </c>
+      <c r="K43" s="1">
+        <v>35</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N43" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:14">
+      <c r="C44" s="1">
+        <v>1039</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1">
+        <v>201</v>
+      </c>
+      <c r="F44" s="1">
+        <v>3500</v>
+      </c>
+      <c r="G44" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1">
+        <v>5</v>
+      </c>
+      <c r="J44" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K44" s="1">
+        <v>7000</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N44" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:14">
+      <c r="C45" s="1">
+        <v>1040</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2</v>
+      </c>
+      <c r="E45" s="1">
+        <v>101</v>
+      </c>
+      <c r="F45" s="1">
+        <v>100</v>
+      </c>
+      <c r="G45" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1">
+        <v>5</v>
+      </c>
+      <c r="J45" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K45" s="1">
+        <v>50</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:14">
+      <c r="C46" s="1">
+        <v>1041</v>
+      </c>
+      <c r="D46" s="2">
+        <v>2</v>
+      </c>
+      <c r="E46" s="2">
+        <v>203</v>
+      </c>
+      <c r="F46" s="2">
+        <v>200</v>
+      </c>
+      <c r="G46" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H46" s="2">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2">
+        <v>5</v>
+      </c>
+      <c r="J46" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K46" s="2">
+        <v>7000</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N46" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:14">
+      <c r="C47" s="1">
+        <v>1042</v>
+      </c>
+      <c r="D47" s="1">
+        <v>2</v>
+      </c>
+      <c r="E47" s="1">
+        <v>202</v>
+      </c>
+      <c r="F47" s="1">
+        <v>200</v>
+      </c>
+      <c r="G47" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1">
+        <v>5</v>
+      </c>
+      <c r="J47" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K47" s="1">
+        <v>50</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:14">
+      <c r="C48" s="1">
+        <v>1043</v>
+      </c>
+      <c r="D48" s="1">
+        <v>2</v>
+      </c>
+      <c r="E48" s="1">
+        <v>301</v>
+      </c>
+      <c r="F48" s="1">
+        <v>550000</v>
+      </c>
+      <c r="G48" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="1">
+        <v>8</v>
+      </c>
+      <c r="J48" s="1">
+        <v>11</v>
+      </c>
+      <c r="K48" s="1">
+        <v>35</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N48" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:14">
+      <c r="C49" s="1">
+        <v>1044</v>
+      </c>
+      <c r="D49" s="1">
+        <v>2</v>
+      </c>
+      <c r="E49" s="1">
+        <v>201</v>
+      </c>
+      <c r="F49" s="1">
+        <v>55000</v>
+      </c>
+      <c r="G49" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="1">
+        <v>5</v>
+      </c>
+      <c r="J49" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K49" s="1">
+        <v>7000</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N49" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:14">
+      <c r="C50" s="1">
+        <v>1045</v>
+      </c>
+      <c r="D50" s="1">
+        <v>2</v>
+      </c>
+      <c r="E50" s="1">
+        <v>101</v>
+      </c>
+      <c r="F50" s="1">
+        <v>200</v>
+      </c>
+      <c r="G50" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="1">
+        <v>5</v>
+      </c>
+      <c r="J50" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K50" s="1">
+        <v>50</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N50" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:14">
+      <c r="C51" s="1">
+        <v>1046</v>
+      </c>
+      <c r="D51" s="2">
+        <v>2</v>
+      </c>
+      <c r="E51" s="2">
+        <v>203</v>
+      </c>
+      <c r="F51" s="2">
+        <v>240</v>
+      </c>
+      <c r="G51" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H51" s="2">
+        <v>0</v>
+      </c>
+      <c r="I51" s="2">
+        <v>5</v>
+      </c>
+      <c r="J51" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K51" s="2">
+        <v>7000</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N51" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:14">
+      <c r="C52" s="1">
+        <v>1047</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2</v>
+      </c>
+      <c r="E52" s="1">
+        <v>202</v>
+      </c>
+      <c r="F52" s="1">
+        <v>240</v>
+      </c>
+      <c r="G52" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="1">
+        <v>5</v>
+      </c>
+      <c r="J52" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K52" s="1">
+        <v>50</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N52" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:14">
+      <c r="C53" s="1">
+        <v>1048</v>
+      </c>
+      <c r="D53" s="1">
+        <v>2</v>
+      </c>
+      <c r="E53" s="1">
+        <v>301</v>
+      </c>
+      <c r="F53" s="1">
+        <v>800000</v>
+      </c>
+      <c r="G53" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="1">
+        <v>8</v>
+      </c>
+      <c r="J53" s="1">
+        <v>11</v>
+      </c>
+      <c r="K53" s="1">
+        <v>35</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N53" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:14">
+      <c r="C54" s="1">
+        <v>1049</v>
+      </c>
+      <c r="D54" s="1">
+        <v>2</v>
+      </c>
+      <c r="E54" s="1">
+        <v>201</v>
+      </c>
+      <c r="F54" s="1">
+        <v>80000</v>
+      </c>
+      <c r="G54" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" s="1">
+        <v>5</v>
+      </c>
+      <c r="J54" s="1">
+        <v>5001</v>
+      </c>
+      <c r="K54" s="1">
+        <v>7000</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N54" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:14">
+      <c r="C55" s="1">
+        <v>1050</v>
+      </c>
+      <c r="D55" s="1">
+        <v>2</v>
+      </c>
+      <c r="E55" s="1">
+        <v>101</v>
+      </c>
+      <c r="F55" s="1">
+        <v>300</v>
+      </c>
+      <c r="G55" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" s="1">
+        <v>5</v>
+      </c>
+      <c r="J55" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K55" s="1">
+        <v>50</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" s="1">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O11 C3:O5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="指引任务" sheetId="1" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="49">
   <si>
     <t>#</t>
   </si>
@@ -196,6 +196,9 @@
   </si>
   <si>
     <t>上阵一个宠物</t>
+  </si>
+  <si>
+    <t>出战一个宠物，出战后需要切换地图才会生效</t>
   </si>
   <si>
     <t>击杀100个怪物</t>
@@ -1220,7 +1223,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O53"/>
+  <dimension ref="C1:O54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1230,7 +1233,7 @@
     <col min="8" max="8" width="15.4166666666667" style="1" customWidth="1"/>
     <col min="9" max="9" width="13.5" style="1" customWidth="1"/>
     <col min="10" max="11" width="13.75" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19.8333333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="42.75" style="1" customWidth="1"/>
     <col min="13" max="13" width="21.4166666666667" style="1" customWidth="1"/>
     <col min="14" max="14" width="19.625" style="1" customWidth="1"/>
     <col min="15" max="15" width="12.5833333333333" style="1" customWidth="1"/>
@@ -1614,7 +1617,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="H12" s="1">
         <v>0</v>
@@ -1647,31 +1650,31 @@
         <v>1</v>
       </c>
       <c r="E13" s="1">
-        <v>301</v>
+        <v>102</v>
       </c>
       <c r="F13" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="H13" s="1">
         <v>0</v>
       </c>
       <c r="I13" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J13" s="1">
-        <v>2</v>
+        <v>5001</v>
       </c>
       <c r="K13" s="1">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="N13" s="1">
         <v>8</v>
@@ -1686,31 +1689,31 @@
         <v>1</v>
       </c>
       <c r="E14" s="1">
-        <v>5</v>
+        <v>301</v>
       </c>
       <c r="F14" s="1">
+        <v>100</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>8</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2</v>
+      </c>
+      <c r="K14" s="1">
         <v>1</v>
       </c>
-      <c r="G14" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
-        <v>5</v>
-      </c>
-      <c r="J14" s="1">
-        <v>5001</v>
-      </c>
-      <c r="K14" s="1">
-        <v>1000</v>
-      </c>
       <c r="L14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="N14" s="1">
         <v>9</v>
@@ -1725,13 +1728,13 @@
         <v>1</v>
       </c>
       <c r="E15" s="1">
-        <v>201</v>
+        <v>5</v>
       </c>
       <c r="F15" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
@@ -1740,16 +1743,16 @@
         <v>5</v>
       </c>
       <c r="J15" s="1">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="K15" s="1">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>35</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N15" s="1">
         <v>10</v>
@@ -1764,31 +1767,31 @@
         <v>1</v>
       </c>
       <c r="E16" s="1">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="F16" s="1">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
       </c>
       <c r="I16" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J16" s="1">
-        <v>3</v>
+        <v>5002</v>
       </c>
       <c r="K16" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>36</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N16" s="1">
         <v>11</v>
@@ -1797,37 +1800,37 @@
     </row>
     <row r="17" customHeight="1" spans="3:15">
       <c r="C17" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
       </c>
       <c r="E17" s="1">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F17" s="1">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J17" s="1">
-        <v>5001</v>
+        <v>3</v>
       </c>
       <c r="K17" s="1">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="L17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M17" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="N17" s="1">
         <v>12</v>
@@ -1836,37 +1839,37 @@
     </row>
     <row r="18" customHeight="1" spans="3:15">
       <c r="C18" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
       </c>
       <c r="E18" s="1">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F18" s="1">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
       </c>
       <c r="I18" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J18" s="1">
-        <v>4</v>
+        <v>5001</v>
       </c>
       <c r="K18" s="1">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>39</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="N18" s="1">
         <v>13</v>
@@ -1881,31 +1884,31 @@
         <v>1</v>
       </c>
       <c r="E19" s="1">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F19" s="1">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
       </c>
       <c r="I19" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J19" s="1">
-        <v>5002</v>
+        <v>4</v>
       </c>
       <c r="K19" s="1">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M19" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="N19" s="1">
         <v>14</v>
@@ -1913,6 +1916,42 @@
       <c r="O19" s="3"/>
     </row>
     <row r="20" customHeight="1" spans="3:15">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>301</v>
+      </c>
+      <c r="F20" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1">
+        <v>5</v>
+      </c>
+      <c r="J20" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K20" s="1">
+        <v>30</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" s="1">
+        <v>15</v>
+      </c>
       <c r="O20" s="3"/>
     </row>
     <row r="21" customHeight="1" spans="3:15">
@@ -1921,7 +1960,9 @@
     <row r="22" customHeight="1" spans="3:15">
       <c r="O22" s="3"/>
     </row>
-    <row r="23" customFormat="1" customHeight="1"/>
+    <row r="23" customHeight="1" spans="3:15">
+      <c r="O23" s="3"/>
+    </row>
     <row r="24" customFormat="1" customHeight="1"/>
     <row r="25" customFormat="1" customHeight="1"/>
     <row r="26" customFormat="1" customHeight="1"/>
@@ -1952,9 +1993,10 @@
     <row r="51" customFormat="1" customHeight="1"/>
     <row r="52" customFormat="1" customHeight="1"/>
     <row r="53" customFormat="1" customHeight="1"/>
+    <row r="54" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O22 C3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O23 C3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -2132,7 +2174,7 @@
         <v>1000</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>24</v>
@@ -2170,7 +2212,7 @@
         <v>1000</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>24</v>
@@ -2208,7 +2250,7 @@
         <v>1000</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>24</v>
@@ -2246,7 +2288,7 @@
         <v>1000</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>24</v>
@@ -2284,7 +2326,7 @@
         <v>1000</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>24</v>
@@ -2322,7 +2364,7 @@
         <v>2000</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>24</v>
@@ -2361,7 +2403,7 @@
         <v>20</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>26</v>
@@ -2399,10 +2441,10 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N13" s="1">
         <v>8</v>
@@ -2437,7 +2479,7 @@
         <v>2000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>24</v>
@@ -2475,7 +2517,7 @@
         <v>20</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>26</v>
@@ -2513,7 +2555,7 @@
         <v>3000</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>24</v>
@@ -2551,7 +2593,7 @@
         <v>30</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>26</v>
@@ -2589,10 +2631,10 @@
         <v>15</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N18" s="1">
         <v>13</v>
@@ -2627,7 +2669,7 @@
         <v>3000</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>24</v>
@@ -2665,7 +2707,7 @@
         <v>30</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>26</v>
@@ -2703,7 +2745,7 @@
         <v>4000</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>24</v>
@@ -2741,7 +2783,7 @@
         <v>40</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>26</v>
@@ -2779,10 +2821,10 @@
         <v>20</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N23" s="1">
         <v>18</v>
@@ -2817,7 +2859,7 @@
         <v>4000</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>24</v>
@@ -2855,7 +2897,7 @@
         <v>40</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>26</v>
@@ -2893,7 +2935,7 @@
         <v>5000</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>24</v>
@@ -2931,7 +2973,7 @@
         <v>50</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>26</v>
@@ -2969,10 +3011,10 @@
         <v>25</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N28" s="1">
         <v>23</v>
@@ -3007,7 +3049,7 @@
         <v>5000</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>24</v>
@@ -3045,7 +3087,7 @@
         <v>50</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>26</v>
@@ -3083,7 +3125,7 @@
         <v>6000</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>24</v>
@@ -3121,7 +3163,7 @@
         <v>50</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>26</v>
@@ -3159,10 +3201,10 @@
         <v>30</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N33" s="1">
         <v>28</v>
@@ -3197,7 +3239,7 @@
         <v>6000</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>24</v>
@@ -3235,7 +3277,7 @@
         <v>50</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>26</v>
@@ -3273,7 +3315,7 @@
         <v>7000</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>24</v>
@@ -3311,7 +3353,7 @@
         <v>50</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>26</v>
@@ -3349,10 +3391,10 @@
         <v>35</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N38" s="1">
         <v>33</v>
@@ -3387,7 +3429,7 @@
         <v>7000</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>24</v>
@@ -3425,7 +3467,7 @@
         <v>50</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>26</v>
@@ -3463,7 +3505,7 @@
         <v>7000</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>24</v>
@@ -3501,7 +3543,7 @@
         <v>50</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>26</v>
@@ -3539,10 +3581,10 @@
         <v>35</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N43" s="1">
         <v>38</v>
@@ -3577,7 +3619,7 @@
         <v>7000</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>24</v>
@@ -3615,7 +3657,7 @@
         <v>50</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>26</v>
@@ -3653,7 +3695,7 @@
         <v>7000</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>24</v>
@@ -3691,7 +3733,7 @@
         <v>50</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>26</v>
@@ -3729,10 +3771,10 @@
         <v>35</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N48" s="1">
         <v>43</v>
@@ -3767,7 +3809,7 @@
         <v>7000</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>24</v>
@@ -3805,7 +3847,7 @@
         <v>50</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>26</v>
@@ -3843,7 +3885,7 @@
         <v>7000</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>24</v>
@@ -3881,7 +3923,7 @@
         <v>50</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M52" s="1" t="s">
         <v>26</v>
@@ -3919,10 +3961,10 @@
         <v>35</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N53" s="1">
         <v>48</v>
@@ -3957,7 +3999,7 @@
         <v>7000</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>24</v>
@@ -3995,7 +4037,7 @@
         <v>50</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>26</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="54">
   <si>
     <t>#</t>
   </si>
@@ -213,15 +213,18 @@
     <t>获得50件装备</t>
   </si>
   <si>
+    <t>通过第1关</t>
+  </si>
+  <si>
+    <t>击杀1000个怪物</t>
+  </si>
+  <si>
     <t>通过第2关</t>
   </si>
   <si>
     <t>奖励1本3阶技能自选</t>
   </si>
   <si>
-    <t>击杀1000个怪物</t>
-  </si>
-  <si>
     <t>通过第3关</t>
   </si>
   <si>
@@ -229,6 +232,18 @@
   </si>
   <si>
     <t>击杀3000个怪物</t>
+  </si>
+  <si>
+    <t>击杀5000个怪物</t>
+  </si>
+  <si>
+    <t>击杀10000个怪物</t>
+  </si>
+  <si>
+    <t>击杀15000个怪物</t>
+  </si>
+  <si>
+    <t>击杀20000个怪物</t>
   </si>
   <si>
     <t>击杀{0}个怪物</t>
@@ -1223,7 +1238,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O54"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1798,7 +1813,7 @@
       </c>
       <c r="O16" s="3"/>
     </row>
-    <row r="17" customHeight="1" spans="3:15">
+    <row r="17" customHeight="1" spans="1:15">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1809,7 +1824,7 @@
         <v>300</v>
       </c>
       <c r="F17" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -1818,26 +1833,26 @@
         <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J17" s="1">
-        <v>3</v>
+        <v>5002</v>
       </c>
       <c r="K17" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>37</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N17" s="1">
         <v>12</v>
       </c>
       <c r="O17" s="3"/>
     </row>
-    <row r="18" customHeight="1" spans="3:15">
+    <row r="18" customHeight="1" spans="1:15">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1848,7 +1863,7 @@
         <v>301</v>
       </c>
       <c r="F18" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G18" s="1">
         <v>1000000</v>
@@ -1866,7 +1881,7 @@
         <v>2000</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>24</v>
@@ -1876,7 +1891,7 @@
       </c>
       <c r="O18" s="3"/>
     </row>
-    <row r="19" customHeight="1" spans="3:15">
+    <row r="19" customHeight="1" spans="1:15">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -1887,7 +1902,7 @@
         <v>300</v>
       </c>
       <c r="F19" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -1899,23 +1914,23 @@
         <v>8</v>
       </c>
       <c r="J19" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19" s="1">
         <v>1</v>
       </c>
       <c r="L19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M19" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="N19" s="1">
         <v>14</v>
       </c>
       <c r="O19" s="3"/>
     </row>
-    <row r="20" customHeight="1" spans="3:15">
+    <row r="20" customHeight="1" spans="1:15">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -1926,7 +1941,7 @@
         <v>301</v>
       </c>
       <c r="F20" s="1">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="G20" s="1">
         <v>1000000</v>
@@ -1938,34 +1953,258 @@
         <v>5</v>
       </c>
       <c r="J20" s="1">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="K20" s="1">
-        <v>30</v>
+        <v>2000</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N20" s="1">
         <v>15</v>
       </c>
       <c r="O20" s="3"/>
     </row>
-    <row r="21" customHeight="1" spans="3:15">
+    <row r="21" customHeight="1" spans="1:15">
+      <c r="C21" s="1">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>300</v>
+      </c>
+      <c r="F21" s="1">
+        <v>3</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1">
+        <v>8</v>
+      </c>
+      <c r="J21" s="1">
+        <v>4</v>
+      </c>
+      <c r="K21" s="1">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N21" s="1">
+        <v>16</v>
+      </c>
       <c r="O21" s="3"/>
     </row>
-    <row r="22" customHeight="1" spans="3:15">
+    <row r="22" customHeight="1" spans="1:15">
+      <c r="C22" s="1">
+        <v>17</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>301</v>
+      </c>
+      <c r="F22" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1">
+        <v>5</v>
+      </c>
+      <c r="J22" s="1">
+        <v>5002</v>
+      </c>
+      <c r="K22" s="1">
+        <v>40</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N22" s="1">
+        <v>17</v>
+      </c>
       <c r="O22" s="3"/>
     </row>
-    <row r="23" customHeight="1" spans="3:15">
+    <row r="23" customHeight="1" spans="1:15">
+      <c r="C23" s="1">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>301</v>
+      </c>
+      <c r="F23" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1">
+        <v>8</v>
+      </c>
+      <c r="J23" s="1">
+        <v>2</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N23" s="1">
+        <v>18</v>
+      </c>
       <c r="O23" s="3"/>
     </row>
-    <row r="24" customFormat="1" customHeight="1"/>
-    <row r="25" customFormat="1" customHeight="1"/>
-    <row r="26" customFormat="1" customHeight="1"/>
+    <row r="24" customHeight="1" spans="1:15">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
+        <v>301</v>
+      </c>
+      <c r="F24" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24" s="1">
+        <v>8</v>
+      </c>
+      <c r="J24" s="1">
+        <v>3</v>
+      </c>
+      <c r="K24" s="1">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N24" s="1">
+        <v>19</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:15">
+      <c r="C25" s="1">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1">
+        <v>301</v>
+      </c>
+      <c r="F25" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
+        <v>8</v>
+      </c>
+      <c r="J25" s="1">
+        <v>2</v>
+      </c>
+      <c r="K25" s="1">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N25" s="1">
+        <v>20</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1">
+        <v>21</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>301</v>
+      </c>
+      <c r="F26" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
+        <v>8</v>
+      </c>
+      <c r="J26" s="1">
+        <v>3</v>
+      </c>
+      <c r="K26" s="1">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N26" s="1">
+        <v>21</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
     <row r="27" customFormat="1" customHeight="1"/>
     <row r="28" customFormat="1" customHeight="1"/>
     <row r="29" customFormat="1" customHeight="1"/>
@@ -1994,9 +2233,11 @@
     <row r="52" customFormat="1" customHeight="1"/>
     <row r="53" customFormat="1" customHeight="1"/>
     <row r="54" customFormat="1" customHeight="1"/>
+    <row r="55" customFormat="1" customHeight="1"/>
+    <row r="56" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O23 C3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O22 O23 O24 O25 O26 O6:O21 C3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -2174,7 +2415,7 @@
         <v>1000</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>24</v>
@@ -2212,7 +2453,7 @@
         <v>1000</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>24</v>
@@ -2250,7 +2491,7 @@
         <v>1000</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>24</v>
@@ -2288,7 +2529,7 @@
         <v>1000</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>24</v>
@@ -2326,7 +2567,7 @@
         <v>1000</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>24</v>
@@ -2364,7 +2605,7 @@
         <v>2000</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>24</v>
@@ -2403,7 +2644,7 @@
         <v>20</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>26</v>
@@ -2441,10 +2682,10 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N13" s="1">
         <v>8</v>
@@ -2479,7 +2720,7 @@
         <v>2000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>24</v>
@@ -2517,7 +2758,7 @@
         <v>20</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>26</v>
@@ -2555,7 +2796,7 @@
         <v>3000</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>24</v>
@@ -2593,7 +2834,7 @@
         <v>30</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>26</v>
@@ -2631,10 +2872,10 @@
         <v>15</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N18" s="1">
         <v>13</v>
@@ -2669,7 +2910,7 @@
         <v>3000</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>24</v>
@@ -2707,7 +2948,7 @@
         <v>30</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>26</v>
@@ -2745,7 +2986,7 @@
         <v>4000</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>24</v>
@@ -2783,7 +3024,7 @@
         <v>40</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>26</v>
@@ -2821,10 +3062,10 @@
         <v>20</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N23" s="1">
         <v>18</v>
@@ -2859,7 +3100,7 @@
         <v>4000</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>24</v>
@@ -2897,7 +3138,7 @@
         <v>40</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>26</v>
@@ -2935,7 +3176,7 @@
         <v>5000</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>24</v>
@@ -2973,7 +3214,7 @@
         <v>50</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>26</v>
@@ -3011,10 +3252,10 @@
         <v>25</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N28" s="1">
         <v>23</v>
@@ -3049,7 +3290,7 @@
         <v>5000</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>24</v>
@@ -3087,7 +3328,7 @@
         <v>50</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>26</v>
@@ -3125,7 +3366,7 @@
         <v>6000</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>24</v>
@@ -3163,7 +3404,7 @@
         <v>50</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>26</v>
@@ -3201,10 +3442,10 @@
         <v>30</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N33" s="1">
         <v>28</v>
@@ -3239,7 +3480,7 @@
         <v>6000</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>24</v>
@@ -3277,7 +3518,7 @@
         <v>50</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>26</v>
@@ -3315,7 +3556,7 @@
         <v>7000</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>24</v>
@@ -3353,7 +3594,7 @@
         <v>50</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>26</v>
@@ -3391,10 +3632,10 @@
         <v>35</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N38" s="1">
         <v>33</v>
@@ -3429,7 +3670,7 @@
         <v>7000</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>24</v>
@@ -3467,7 +3708,7 @@
         <v>50</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>26</v>
@@ -3505,7 +3746,7 @@
         <v>7000</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>24</v>
@@ -3543,7 +3784,7 @@
         <v>50</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>26</v>
@@ -3581,10 +3822,10 @@
         <v>35</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N43" s="1">
         <v>38</v>
@@ -3619,7 +3860,7 @@
         <v>7000</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>24</v>
@@ -3657,7 +3898,7 @@
         <v>50</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>26</v>
@@ -3695,7 +3936,7 @@
         <v>7000</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>24</v>
@@ -3733,7 +3974,7 @@
         <v>50</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>26</v>
@@ -3771,10 +4012,10 @@
         <v>35</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N48" s="1">
         <v>43</v>
@@ -3809,7 +4050,7 @@
         <v>7000</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>24</v>
@@ -3847,7 +4088,7 @@
         <v>50</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>26</v>
@@ -3885,7 +4126,7 @@
         <v>7000</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>24</v>
@@ -3923,7 +4164,7 @@
         <v>50</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M52" s="1" t="s">
         <v>26</v>
@@ -3961,10 +4202,10 @@
         <v>35</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N53" s="1">
         <v>48</v>
@@ -3999,7 +4240,7 @@
         <v>7000</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>24</v>
@@ -4037,7 +4278,7 @@
         <v>50</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>26</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -100,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="56">
   <si>
     <t>#</t>
   </si>
@@ -234,16 +239,22 @@
     <t>击杀3000个怪物</t>
   </si>
   <si>
-    <t>击杀5000个怪物</t>
-  </si>
-  <si>
     <t>击杀10000个怪物</t>
   </si>
   <si>
-    <t>击杀15000个怪物</t>
-  </si>
-  <si>
     <t>击杀20000个怪物</t>
+  </si>
+  <si>
+    <t>击杀30000个怪物</t>
+  </si>
+  <si>
+    <t>击杀50000个怪物</t>
+  </si>
+  <si>
+    <t>击杀100000个怪物</t>
+  </si>
+  <si>
+    <t>击杀150000个怪物</t>
   </si>
   <si>
     <t>击杀{0}个怪物</t>
@@ -1238,7 +1249,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -2058,7 +2069,7 @@
         <v>301</v>
       </c>
       <c r="F23" s="1">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
@@ -2097,7 +2108,7 @@
         <v>301</v>
       </c>
       <c r="F24" s="1">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
@@ -2136,7 +2147,7 @@
         <v>301</v>
       </c>
       <c r="F25" s="1">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
@@ -2148,7 +2159,7 @@
         <v>8</v>
       </c>
       <c r="J25" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K25" s="1">
         <v>1</v>
@@ -2157,16 +2168,14 @@
         <v>46</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="N25" s="1">
         <v>20</v>
       </c>
       <c r="O25" s="3"/>
     </row>
-    <row r="26" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
+    <row r="26" customHeight="1" spans="1:15">
       <c r="C26" s="1">
         <v>21</v>
       </c>
@@ -2177,7 +2186,7 @@
         <v>301</v>
       </c>
       <c r="F26" s="1">
-        <v>3000</v>
+        <v>50000</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
@@ -2189,7 +2198,7 @@
         <v>8</v>
       </c>
       <c r="J26" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" s="1">
         <v>1</v>
@@ -2198,15 +2207,92 @@
         <v>47</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="N26" s="1">
         <v>21</v>
       </c>
       <c r="O26" s="3"/>
     </row>
-    <row r="27" customFormat="1" customHeight="1"/>
-    <row r="28" customFormat="1" customHeight="1"/>
+    <row r="27" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>301</v>
+      </c>
+      <c r="F27" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1">
+        <v>8</v>
+      </c>
+      <c r="J27" s="1">
+        <v>3</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N27" s="1">
+        <v>22</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>301</v>
+      </c>
+      <c r="F28" s="1">
+        <v>150000</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1">
+        <v>8</v>
+      </c>
+      <c r="J28" s="1">
+        <v>4</v>
+      </c>
+      <c r="K28" s="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N28" s="1">
+        <v>23</v>
+      </c>
+    </row>
     <row r="29" customFormat="1" customHeight="1"/>
     <row r="30" customFormat="1" customHeight="1"/>
     <row r="31" customFormat="1" customHeight="1"/>
@@ -2235,9 +2321,10 @@
     <row r="54" customFormat="1" customHeight="1"/>
     <row r="55" customFormat="1" customHeight="1"/>
     <row r="56" customFormat="1" customHeight="1"/>
+    <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O22 O23 O24 O25 O26 O6:O21 C3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O25 O6:O24 O26:O27 C3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -2415,7 +2502,7 @@
         <v>1000</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>24</v>
@@ -2453,7 +2540,7 @@
         <v>1000</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>24</v>
@@ -2491,7 +2578,7 @@
         <v>1000</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>24</v>
@@ -2529,7 +2616,7 @@
         <v>1000</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>24</v>
@@ -2567,7 +2654,7 @@
         <v>1000</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>24</v>
@@ -2605,7 +2692,7 @@
         <v>2000</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>24</v>
@@ -2644,7 +2731,7 @@
         <v>20</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>26</v>
@@ -2682,10 +2769,10 @@
         <v>10</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N13" s="1">
         <v>8</v>
@@ -2720,7 +2807,7 @@
         <v>2000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>24</v>
@@ -2758,7 +2845,7 @@
         <v>20</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>26</v>
@@ -2796,7 +2883,7 @@
         <v>3000</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>24</v>
@@ -2834,7 +2921,7 @@
         <v>30</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>26</v>
@@ -2872,10 +2959,10 @@
         <v>15</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N18" s="1">
         <v>13</v>
@@ -2910,7 +2997,7 @@
         <v>3000</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>24</v>
@@ -2948,7 +3035,7 @@
         <v>30</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>26</v>
@@ -2986,7 +3073,7 @@
         <v>4000</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>24</v>
@@ -3024,7 +3111,7 @@
         <v>40</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>26</v>
@@ -3062,10 +3149,10 @@
         <v>20</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N23" s="1">
         <v>18</v>
@@ -3100,7 +3187,7 @@
         <v>4000</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>24</v>
@@ -3138,7 +3225,7 @@
         <v>40</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>26</v>
@@ -3176,7 +3263,7 @@
         <v>5000</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>24</v>
@@ -3214,7 +3301,7 @@
         <v>50</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>26</v>
@@ -3252,10 +3339,10 @@
         <v>25</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N28" s="1">
         <v>23</v>
@@ -3290,7 +3377,7 @@
         <v>5000</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>24</v>
@@ -3328,7 +3415,7 @@
         <v>50</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>26</v>
@@ -3366,7 +3453,7 @@
         <v>6000</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>24</v>
@@ -3404,7 +3491,7 @@
         <v>50</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>26</v>
@@ -3442,10 +3529,10 @@
         <v>30</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N33" s="1">
         <v>28</v>
@@ -3480,7 +3567,7 @@
         <v>6000</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>24</v>
@@ -3518,7 +3605,7 @@
         <v>50</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>26</v>
@@ -3556,7 +3643,7 @@
         <v>7000</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>24</v>
@@ -3594,7 +3681,7 @@
         <v>50</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>26</v>
@@ -3632,10 +3719,10 @@
         <v>35</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N38" s="1">
         <v>33</v>
@@ -3670,7 +3757,7 @@
         <v>7000</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>24</v>
@@ -3708,7 +3795,7 @@
         <v>50</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>26</v>
@@ -3746,7 +3833,7 @@
         <v>7000</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>24</v>
@@ -3784,7 +3871,7 @@
         <v>50</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>26</v>
@@ -3822,10 +3909,10 @@
         <v>35</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N43" s="1">
         <v>38</v>
@@ -3860,7 +3947,7 @@
         <v>7000</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>24</v>
@@ -3898,7 +3985,7 @@
         <v>50</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>26</v>
@@ -3936,7 +4023,7 @@
         <v>7000</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>24</v>
@@ -3974,7 +4061,7 @@
         <v>50</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>26</v>
@@ -4012,10 +4099,10 @@
         <v>35</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N48" s="1">
         <v>43</v>
@@ -4050,7 +4137,7 @@
         <v>7000</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>24</v>
@@ -4088,7 +4175,7 @@
         <v>50</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>26</v>
@@ -4126,7 +4213,7 @@
         <v>7000</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>24</v>
@@ -4164,7 +4251,7 @@
         <v>50</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M52" s="1" t="s">
         <v>26</v>
@@ -4202,10 +4289,10 @@
         <v>35</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N53" s="1">
         <v>48</v>
@@ -4240,7 +4327,7 @@
         <v>7000</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>24</v>
@@ -4278,7 +4365,7 @@
         <v>50</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>26</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="指引任务" sheetId="1" r:id="rId1"/>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="57">
   <si>
     <t>#</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>自动回收{0}件装备</t>
+  </si>
+  <si>
+    <t>四格总阶数{0}阶</t>
   </si>
   <si>
     <t>获得{0}个宠物</t>
@@ -451,12 +454,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -922,12 +925,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
@@ -2324,7 +2330,7 @@
     <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O25 O6:O24 O26:O27 C3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O27 C3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -2824,10 +2830,10 @@
         <v>2</v>
       </c>
       <c r="E15" s="1">
-        <v>101</v>
+        <v>205</v>
       </c>
       <c r="F15" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
         <v>1000000</v>
@@ -2844,7 +2850,7 @@
       <c r="K15" s="1">
         <v>20</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="L15" s="4" t="s">
         <v>55</v>
       </c>
       <c r="M15" s="1" t="s">
@@ -3017,7 +3023,7 @@
         <v>101</v>
       </c>
       <c r="F20" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G20" s="1">
         <v>1500000</v>
@@ -3035,7 +3041,7 @@
         <v>30</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>26</v>
@@ -3204,13 +3210,13 @@
         <v>2</v>
       </c>
       <c r="E25" s="1">
-        <v>101</v>
+        <v>205</v>
       </c>
       <c r="F25" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G25" s="1">
-        <v>1500000</v>
+        <v>1000000</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -3224,7 +3230,7 @@
       <c r="K25" s="1">
         <v>40</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="L25" s="4" t="s">
         <v>55</v>
       </c>
       <c r="M25" s="1" t="s">
@@ -3285,7 +3291,7 @@
       <c r="F27" s="1">
         <v>55</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G27" s="5">
         <v>2000000</v>
       </c>
       <c r="H27" s="1">
@@ -3323,7 +3329,7 @@
       <c r="F28" s="1">
         <v>50000</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G28" s="5">
         <v>2000000</v>
       </c>
       <c r="H28" s="1">
@@ -3361,7 +3367,7 @@
       <c r="F29" s="1">
         <v>5000</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29" s="5">
         <v>2000000</v>
       </c>
       <c r="H29" s="1">
@@ -3397,9 +3403,9 @@
         <v>101</v>
       </c>
       <c r="F30" s="1">
-        <v>20</v>
-      </c>
-      <c r="G30" s="4">
+        <v>10</v>
+      </c>
+      <c r="G30" s="5">
         <v>2000000</v>
       </c>
       <c r="H30" s="1">
@@ -3415,7 +3421,7 @@
         <v>50</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>26</v>
@@ -3437,7 +3443,7 @@
       <c r="F31" s="2">
         <v>85</v>
       </c>
-      <c r="G31" s="4">
+      <c r="G31" s="5">
         <v>2000000</v>
       </c>
       <c r="H31" s="2">
@@ -3475,7 +3481,7 @@
       <c r="F32" s="2">
         <v>85</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G32" s="5">
         <v>2000000</v>
       </c>
       <c r="H32" s="1">
@@ -3513,7 +3519,7 @@
       <c r="F33" s="1">
         <v>100000</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G33" s="5">
         <v>2000000</v>
       </c>
       <c r="H33" s="1">
@@ -3551,7 +3557,7 @@
       <c r="F34" s="1">
         <v>10000</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G34" s="5">
         <v>2000000</v>
       </c>
       <c r="H34" s="1">
@@ -3584,13 +3590,13 @@
         <v>2</v>
       </c>
       <c r="E35" s="1">
-        <v>101</v>
+        <v>205</v>
       </c>
       <c r="F35" s="1">
-        <v>25</v>
-      </c>
-      <c r="G35" s="4">
-        <v>2000000</v>
+        <v>9</v>
+      </c>
+      <c r="G35" s="1">
+        <v>1000000</v>
       </c>
       <c r="H35" s="1">
         <v>0</v>
@@ -3604,7 +3610,7 @@
       <c r="K35" s="1">
         <v>50</v>
       </c>
-      <c r="L35" s="1" t="s">
+      <c r="L35" s="4" t="s">
         <v>55</v>
       </c>
       <c r="M35" s="1" t="s">
@@ -3627,7 +3633,7 @@
       <c r="F36" s="2">
         <v>120</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G36" s="5">
         <v>2000000</v>
       </c>
       <c r="H36" s="2">
@@ -3665,7 +3671,7 @@
       <c r="F37" s="1">
         <v>120</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G37" s="5">
         <v>2000000</v>
       </c>
       <c r="H37" s="1">
@@ -3703,7 +3709,7 @@
       <c r="F38" s="1">
         <v>200000</v>
       </c>
-      <c r="G38" s="4">
+      <c r="G38" s="5">
         <v>2000000</v>
       </c>
       <c r="H38" s="1">
@@ -3741,7 +3747,7 @@
       <c r="F39" s="1">
         <v>20000</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G39" s="5">
         <v>2000000</v>
       </c>
       <c r="H39" s="1">
@@ -3779,7 +3785,7 @@
       <c r="F40" s="1">
         <v>50</v>
       </c>
-      <c r="G40" s="4">
+      <c r="G40" s="5">
         <v>2000000</v>
       </c>
       <c r="H40" s="1">
@@ -3795,7 +3801,7 @@
         <v>50</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>26</v>
@@ -3817,7 +3823,7 @@
       <c r="F41" s="2">
         <v>160</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G41" s="5">
         <v>2000000</v>
       </c>
       <c r="H41" s="2">
@@ -3855,7 +3861,7 @@
       <c r="F42" s="1">
         <v>160</v>
       </c>
-      <c r="G42" s="4">
+      <c r="G42" s="5">
         <v>2000000</v>
       </c>
       <c r="H42" s="1">
@@ -3893,7 +3899,7 @@
       <c r="F43" s="1">
         <v>350000</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G43" s="5">
         <v>2000000</v>
       </c>
       <c r="H43" s="1">
@@ -3931,7 +3937,7 @@
       <c r="F44" s="1">
         <v>3500</v>
       </c>
-      <c r="G44" s="4">
+      <c r="G44" s="5">
         <v>2000000</v>
       </c>
       <c r="H44" s="1">
@@ -3964,13 +3970,13 @@
         <v>2</v>
       </c>
       <c r="E45" s="1">
-        <v>101</v>
+        <v>205</v>
       </c>
       <c r="F45" s="1">
-        <v>100</v>
-      </c>
-      <c r="G45" s="4">
-        <v>2000000</v>
+        <v>13</v>
+      </c>
+      <c r="G45" s="1">
+        <v>1000000</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -3984,7 +3990,7 @@
       <c r="K45" s="1">
         <v>50</v>
       </c>
-      <c r="L45" s="1" t="s">
+      <c r="L45" s="4" t="s">
         <v>55</v>
       </c>
       <c r="M45" s="1" t="s">
@@ -4007,7 +4013,7 @@
       <c r="F46" s="2">
         <v>200</v>
       </c>
-      <c r="G46" s="4">
+      <c r="G46" s="5">
         <v>2000000</v>
       </c>
       <c r="H46" s="2">
@@ -4045,7 +4051,7 @@
       <c r="F47" s="1">
         <v>200</v>
       </c>
-      <c r="G47" s="4">
+      <c r="G47" s="5">
         <v>2000000</v>
       </c>
       <c r="H47" s="1">
@@ -4083,7 +4089,7 @@
       <c r="F48" s="1">
         <v>550000</v>
       </c>
-      <c r="G48" s="4">
+      <c r="G48" s="5">
         <v>2000000</v>
       </c>
       <c r="H48" s="1">
@@ -4121,7 +4127,7 @@
       <c r="F49" s="1">
         <v>55000</v>
       </c>
-      <c r="G49" s="4">
+      <c r="G49" s="5">
         <v>2000000</v>
       </c>
       <c r="H49" s="1">
@@ -4159,7 +4165,7 @@
       <c r="F50" s="1">
         <v>200</v>
       </c>
-      <c r="G50" s="4">
+      <c r="G50" s="5">
         <v>2000000</v>
       </c>
       <c r="H50" s="1">
@@ -4175,7 +4181,7 @@
         <v>50</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>26</v>
@@ -4197,7 +4203,7 @@
       <c r="F51" s="2">
         <v>240</v>
       </c>
-      <c r="G51" s="4">
+      <c r="G51" s="5">
         <v>2000000</v>
       </c>
       <c r="H51" s="2">
@@ -4235,7 +4241,7 @@
       <c r="F52" s="1">
         <v>240</v>
       </c>
-      <c r="G52" s="4">
+      <c r="G52" s="5">
         <v>2000000</v>
       </c>
       <c r="H52" s="1">
@@ -4273,7 +4279,7 @@
       <c r="F53" s="1">
         <v>800000</v>
       </c>
-      <c r="G53" s="4">
+      <c r="G53" s="5">
         <v>2000000</v>
       </c>
       <c r="H53" s="1">
@@ -4311,7 +4317,7 @@
       <c r="F54" s="1">
         <v>80000</v>
       </c>
-      <c r="G54" s="4">
+      <c r="G54" s="5">
         <v>2000000</v>
       </c>
       <c r="H54" s="1">
@@ -4349,7 +4355,7 @@
       <c r="F55" s="1">
         <v>300</v>
       </c>
-      <c r="G55" s="4">
+      <c r="G55" s="5">
         <v>2000000</v>
       </c>
       <c r="H55" s="1">
@@ -4365,7 +4371,7 @@
         <v>50</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>26</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -454,12 +454,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3213,7 +3213,7 @@
         <v>205</v>
       </c>
       <c r="F25" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G25" s="1">
         <v>1000000</v>
@@ -3593,7 +3593,7 @@
         <v>205</v>
       </c>
       <c r="F35" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G35" s="1">
         <v>1000000</v>
@@ -3973,7 +3973,7 @@
         <v>205</v>
       </c>
       <c r="F45" s="1">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G45" s="1">
         <v>1000000</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,11 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="指引任务" sheetId="1" r:id="rId1"/>
     <sheet name="新手任务" sheetId="2" r:id="rId2"/>
+    <sheet name="福利任务" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -104,8 +105,44 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="O3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 闯关层数
+2 穿戴装备
+3 强化装备
+4 挑战副本
+5 设置回收</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="60">
   <si>
     <t>#</t>
   </si>
@@ -276,6 +313,15 @@
   </si>
   <si>
     <t>获得{0}个宠物</t>
+  </si>
+  <si>
+    <t>奖励1个多重宠物</t>
+  </si>
+  <si>
+    <t>击杀200个区域boss</t>
+  </si>
+  <si>
+    <t>奖励1个天下无双皮肤</t>
   </si>
 </sst>
 </file>
@@ -474,13 +520,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -928,10 +974,10 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1283,123 +1329,123 @@
       </c>
     </row>
     <row r="3" customHeight="1" spans="3:15">
-      <c r="C3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="3:15">
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="G4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="3"/>
+      <c r="O4" s="2"/>
     </row>
     <row r="5" customHeight="1" spans="3:15">
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="N5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O5" s="3"/>
+      <c r="O5" s="2"/>
     </row>
     <row r="6" customHeight="1" spans="3:15">
       <c r="C6" s="1">
@@ -1438,7 +1484,7 @@
       <c r="N6" s="1">
         <v>1</v>
       </c>
-      <c r="O6" s="3"/>
+      <c r="O6" s="2"/>
     </row>
     <row r="7" customHeight="1" spans="3:15">
       <c r="C7" s="1">
@@ -1477,7 +1523,7 @@
       <c r="N7" s="1">
         <v>2</v>
       </c>
-      <c r="O7" s="3"/>
+      <c r="O7" s="2"/>
     </row>
     <row r="8" customHeight="1" spans="3:15">
       <c r="C8" s="1">
@@ -1516,7 +1562,7 @@
       <c r="N8" s="1">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
+      <c r="O8" s="2"/>
     </row>
     <row r="9" customHeight="1" spans="3:15">
       <c r="C9" s="1">
@@ -1555,7 +1601,7 @@
       <c r="N9" s="1">
         <v>4</v>
       </c>
-      <c r="O9" s="3"/>
+      <c r="O9" s="2"/>
     </row>
     <row r="10" customHeight="1" spans="3:15">
       <c r="C10" s="1">
@@ -1594,7 +1640,7 @@
       <c r="N10" s="1">
         <v>5</v>
       </c>
-      <c r="O10" s="3"/>
+      <c r="O10" s="2"/>
     </row>
     <row r="11" customHeight="1" spans="3:15">
       <c r="C11" s="1">
@@ -1633,7 +1679,7 @@
       <c r="N11" s="1">
         <v>6</v>
       </c>
-      <c r="O11" s="3"/>
+      <c r="O11" s="2"/>
     </row>
     <row r="12" customHeight="1" spans="3:15">
       <c r="C12" s="1">
@@ -1672,7 +1718,7 @@
       <c r="N12" s="1">
         <v>7</v>
       </c>
-      <c r="O12" s="3"/>
+      <c r="O12" s="2"/>
     </row>
     <row r="13" customHeight="1" spans="3:15">
       <c r="C13" s="1">
@@ -1711,7 +1757,7 @@
       <c r="N13" s="1">
         <v>8</v>
       </c>
-      <c r="O13" s="3"/>
+      <c r="O13" s="2"/>
     </row>
     <row r="14" customHeight="1" spans="3:15">
       <c r="C14" s="1">
@@ -1750,7 +1796,7 @@
       <c r="N14" s="1">
         <v>9</v>
       </c>
-      <c r="O14" s="3"/>
+      <c r="O14" s="2"/>
     </row>
     <row r="15" customHeight="1" spans="3:15">
       <c r="C15" s="1">
@@ -1789,7 +1835,7 @@
       <c r="N15" s="1">
         <v>10</v>
       </c>
-      <c r="O15" s="3"/>
+      <c r="O15" s="2"/>
     </row>
     <row r="16" customHeight="1" spans="3:15">
       <c r="C16" s="1">
@@ -1828,7 +1874,7 @@
       <c r="N16" s="1">
         <v>11</v>
       </c>
-      <c r="O16" s="3"/>
+      <c r="O16" s="2"/>
     </row>
     <row r="17" customHeight="1" spans="1:15">
       <c r="C17" s="1">
@@ -1867,7 +1913,7 @@
       <c r="N17" s="1">
         <v>12</v>
       </c>
-      <c r="O17" s="3"/>
+      <c r="O17" s="2"/>
     </row>
     <row r="18" customHeight="1" spans="1:15">
       <c r="C18" s="1">
@@ -1906,7 +1952,7 @@
       <c r="N18" s="1">
         <v>13</v>
       </c>
-      <c r="O18" s="3"/>
+      <c r="O18" s="2"/>
     </row>
     <row r="19" customHeight="1" spans="1:15">
       <c r="C19" s="1">
@@ -1945,7 +1991,7 @@
       <c r="N19" s="1">
         <v>14</v>
       </c>
-      <c r="O19" s="3"/>
+      <c r="O19" s="2"/>
     </row>
     <row r="20" customHeight="1" spans="1:15">
       <c r="C20" s="1">
@@ -1984,7 +2030,7 @@
       <c r="N20" s="1">
         <v>15</v>
       </c>
-      <c r="O20" s="3"/>
+      <c r="O20" s="2"/>
     </row>
     <row r="21" customHeight="1" spans="1:15">
       <c r="C21" s="1">
@@ -2023,7 +2069,7 @@
       <c r="N21" s="1">
         <v>16</v>
       </c>
-      <c r="O21" s="3"/>
+      <c r="O21" s="2"/>
     </row>
     <row r="22" customHeight="1" spans="1:15">
       <c r="C22" s="1">
@@ -2062,7 +2108,7 @@
       <c r="N22" s="1">
         <v>17</v>
       </c>
-      <c r="O22" s="3"/>
+      <c r="O22" s="2"/>
     </row>
     <row r="23" customHeight="1" spans="1:15">
       <c r="C23" s="1">
@@ -2101,7 +2147,7 @@
       <c r="N23" s="1">
         <v>18</v>
       </c>
-      <c r="O23" s="3"/>
+      <c r="O23" s="2"/>
     </row>
     <row r="24" customHeight="1" spans="1:15">
       <c r="C24" s="1">
@@ -2140,7 +2186,7 @@
       <c r="N24" s="1">
         <v>19</v>
       </c>
-      <c r="O24" s="3"/>
+      <c r="O24" s="2"/>
     </row>
     <row r="25" customHeight="1" spans="1:15">
       <c r="C25" s="1">
@@ -2179,7 +2225,7 @@
       <c r="N25" s="1">
         <v>20</v>
       </c>
-      <c r="O25" s="3"/>
+      <c r="O25" s="2"/>
     </row>
     <row r="26" customHeight="1" spans="1:15">
       <c r="C26" s="1">
@@ -2218,7 +2264,7 @@
       <c r="N26" s="1">
         <v>21</v>
       </c>
-      <c r="O26" s="3"/>
+      <c r="O26" s="2"/>
     </row>
     <row r="27" customFormat="1" customHeight="1" spans="1:15">
       <c r="A27" s="1"/>
@@ -2259,7 +2305,7 @@
       <c r="N27" s="1">
         <v>22</v>
       </c>
-      <c r="O27" s="3"/>
+      <c r="O27" s="2"/>
     </row>
     <row r="28" customFormat="1" customHeight="1" spans="1:15">
       <c r="C28" s="1">
@@ -2361,123 +2407,123 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="G4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="3"/>
+      <c r="O4" s="2"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="N5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O5" s="3"/>
+      <c r="O5" s="2"/>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C6" s="1">
@@ -2706,7 +2752,7 @@
       <c r="N11" s="1">
         <v>6</v>
       </c>
-      <c r="O11" s="3"/>
+      <c r="O11" s="2"/>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C12" s="1">
@@ -2860,38 +2906,38 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:15">
+    <row r="16" s="3" customFormat="1" customHeight="1" spans="3:15">
       <c r="C16" s="1">
         <v>1011</v>
       </c>
-      <c r="D16" s="2">
-        <v>2</v>
-      </c>
-      <c r="E16" s="2">
+      <c r="D16" s="3">
+        <v>2</v>
+      </c>
+      <c r="E16" s="3">
         <v>203</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="3">
         <v>20</v>
       </c>
       <c r="G16" s="1">
         <v>1500000</v>
       </c>
-      <c r="H16" s="2">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
+      <c r="H16" s="3">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
         <v>5</v>
       </c>
       <c r="J16" s="1">
         <v>5001</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16" s="3">
         <v>3000</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="L16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="M16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="N16" s="1">
@@ -3050,38 +3096,38 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:14">
+    <row r="21" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C21" s="1">
         <v>1016</v>
       </c>
-      <c r="D21" s="2">
-        <v>2</v>
-      </c>
-      <c r="E21" s="2">
+      <c r="D21" s="3">
+        <v>2</v>
+      </c>
+      <c r="E21" s="3">
         <v>203</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="3">
         <v>35</v>
       </c>
       <c r="G21" s="1">
         <v>1500000</v>
       </c>
-      <c r="H21" s="2">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2">
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>5</v>
       </c>
       <c r="J21" s="1">
         <v>5001</v>
       </c>
-      <c r="K21" s="2">
+      <c r="K21" s="3">
         <v>4000</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="L21" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="M21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="N21" s="1">
@@ -3240,38 +3286,38 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:14">
+    <row r="26" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C26" s="1">
         <v>1021</v>
       </c>
-      <c r="D26" s="2">
-        <v>2</v>
-      </c>
-      <c r="E26" s="2">
+      <c r="D26" s="3">
+        <v>2</v>
+      </c>
+      <c r="E26" s="3">
         <v>203</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="3">
         <v>55</v>
       </c>
       <c r="G26" s="1">
         <v>1500000</v>
       </c>
-      <c r="H26" s="2">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
+      <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>5</v>
       </c>
       <c r="J26" s="1">
         <v>5001</v>
       </c>
-      <c r="K26" s="2">
+      <c r="K26" s="3">
         <v>5000</v>
       </c>
-      <c r="L26" s="2" t="s">
+      <c r="L26" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="M26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="N26" s="1">
@@ -3434,34 +3480,34 @@
       <c r="C31" s="1">
         <v>1026</v>
       </c>
-      <c r="D31" s="2">
-        <v>2</v>
-      </c>
-      <c r="E31" s="2">
+      <c r="D31" s="3">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3">
         <v>203</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
         <v>85</v>
       </c>
       <c r="G31" s="5">
         <v>2000000</v>
       </c>
-      <c r="H31" s="2">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2">
+      <c r="H31" s="3">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3">
         <v>5</v>
       </c>
       <c r="J31" s="1">
         <v>5001</v>
       </c>
-      <c r="K31" s="2">
+      <c r="K31" s="3">
         <v>6000</v>
       </c>
-      <c r="L31" s="2" t="s">
+      <c r="L31" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="M31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="N31" s="1">
@@ -3478,7 +3524,7 @@
       <c r="E32" s="1">
         <v>202</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="3">
         <v>85</v>
       </c>
       <c r="G32" s="5">
@@ -3624,34 +3670,34 @@
       <c r="C36" s="1">
         <v>1031</v>
       </c>
-      <c r="D36" s="2">
-        <v>2</v>
-      </c>
-      <c r="E36" s="2">
+      <c r="D36" s="3">
+        <v>2</v>
+      </c>
+      <c r="E36" s="3">
         <v>203</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="3">
         <v>120</v>
       </c>
       <c r="G36" s="5">
         <v>2000000</v>
       </c>
-      <c r="H36" s="2">
-        <v>0</v>
-      </c>
-      <c r="I36" s="2">
+      <c r="H36" s="3">
+        <v>0</v>
+      </c>
+      <c r="I36" s="3">
         <v>5</v>
       </c>
       <c r="J36" s="1">
         <v>5001</v>
       </c>
-      <c r="K36" s="2">
+      <c r="K36" s="3">
         <v>7000</v>
       </c>
-      <c r="L36" s="2" t="s">
+      <c r="L36" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="M36" s="3" t="s">
         <v>24</v>
       </c>
       <c r="N36" s="1">
@@ -3814,34 +3860,34 @@
       <c r="C41" s="1">
         <v>1036</v>
       </c>
-      <c r="D41" s="2">
-        <v>2</v>
-      </c>
-      <c r="E41" s="2">
+      <c r="D41" s="3">
+        <v>2</v>
+      </c>
+      <c r="E41" s="3">
         <v>203</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="3">
         <v>160</v>
       </c>
       <c r="G41" s="5">
         <v>2000000</v>
       </c>
-      <c r="H41" s="2">
-        <v>0</v>
-      </c>
-      <c r="I41" s="2">
+      <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
         <v>5</v>
       </c>
       <c r="J41" s="1">
         <v>5001</v>
       </c>
-      <c r="K41" s="2">
+      <c r="K41" s="3">
         <v>7000</v>
       </c>
-      <c r="L41" s="2" t="s">
+      <c r="L41" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="M41" s="2" t="s">
+      <c r="M41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="N41" s="1">
@@ -4004,34 +4050,34 @@
       <c r="C46" s="1">
         <v>1041</v>
       </c>
-      <c r="D46" s="2">
-        <v>2</v>
-      </c>
-      <c r="E46" s="2">
+      <c r="D46" s="3">
+        <v>2</v>
+      </c>
+      <c r="E46" s="3">
         <v>203</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="3">
         <v>200</v>
       </c>
       <c r="G46" s="5">
         <v>2000000</v>
       </c>
-      <c r="H46" s="2">
-        <v>0</v>
-      </c>
-      <c r="I46" s="2">
+      <c r="H46" s="3">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3">
         <v>5</v>
       </c>
       <c r="J46" s="1">
         <v>5001</v>
       </c>
-      <c r="K46" s="2">
+      <c r="K46" s="3">
         <v>7000</v>
       </c>
-      <c r="L46" s="2" t="s">
+      <c r="L46" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="M46" s="3" t="s">
         <v>24</v>
       </c>
       <c r="N46" s="1">
@@ -4194,34 +4240,34 @@
       <c r="C51" s="1">
         <v>1046</v>
       </c>
-      <c r="D51" s="2">
-        <v>2</v>
-      </c>
-      <c r="E51" s="2">
+      <c r="D51" s="3">
+        <v>2</v>
+      </c>
+      <c r="E51" s="3">
         <v>203</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="3">
         <v>240</v>
       </c>
       <c r="G51" s="5">
         <v>2000000</v>
       </c>
-      <c r="H51" s="2">
-        <v>0</v>
-      </c>
-      <c r="I51" s="2">
+      <c r="H51" s="3">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3">
         <v>5</v>
       </c>
       <c r="J51" s="1">
         <v>5001</v>
       </c>
-      <c r="K51" s="2">
+      <c r="K51" s="3">
         <v>7000</v>
       </c>
-      <c r="L51" s="2" t="s">
+      <c r="L51" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="M51" s="2" t="s">
+      <c r="M51" s="3" t="s">
         <v>24</v>
       </c>
       <c r="N51" s="1">
@@ -4390,4 +4436,360 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O57"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="13.5833333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.8333333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.4166666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="1" customWidth="1"/>
+    <col min="10" max="11" width="13.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="42.75" style="1" customWidth="1"/>
+    <col min="13" max="13" width="21.4166666666667" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19.625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5833333333333" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C6" s="1">
+        <v>3001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>301</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>8</v>
+      </c>
+      <c r="J6" s="1">
+        <v>14</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2"/>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C7" s="1">
+        <v>3002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>307</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>5</v>
+      </c>
+      <c r="J7" s="1">
+        <v>10004</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" s="1">
+        <v>2</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O14" s="2"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O15" s="2"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O16" s="2"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O17" s="2"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O18" s="2"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O19" s="2"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O20" s="2"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O21" s="2"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O22" s="2"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O23" s="2"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O24" s="2"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O25" s="2"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O26" s="2"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="2"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+    </row>
+    <row r="29" customFormat="1" customHeight="1"/>
+    <row r="30" customFormat="1" customHeight="1"/>
+    <row r="31" customFormat="1" customHeight="1"/>
+    <row r="32" customFormat="1" customHeight="1"/>
+    <row r="33" customFormat="1" customHeight="1"/>
+    <row r="34" customFormat="1" customHeight="1"/>
+    <row r="35" customFormat="1" customHeight="1"/>
+    <row r="36" customFormat="1" customHeight="1"/>
+    <row r="37" customFormat="1" customHeight="1"/>
+    <row r="38" customFormat="1" customHeight="1"/>
+    <row r="39" customFormat="1" customHeight="1"/>
+    <row r="40" customFormat="1" customHeight="1"/>
+    <row r="41" customFormat="1" customHeight="1"/>
+    <row r="42" customFormat="1" customHeight="1"/>
+    <row r="43" customFormat="1" customHeight="1"/>
+    <row r="44" customFormat="1" customHeight="1"/>
+    <row r="45" customFormat="1" customHeight="1"/>
+    <row r="46" customFormat="1" customHeight="1"/>
+    <row r="47" customFormat="1" customHeight="1"/>
+    <row r="48" customFormat="1" customHeight="1"/>
+    <row r="49" customFormat="1" customHeight="1"/>
+    <row r="50" customFormat="1" customHeight="1"/>
+    <row r="51" customFormat="1" customHeight="1"/>
+    <row r="52" customFormat="1" customHeight="1"/>
+    <row r="53" customFormat="1" customHeight="1"/>
+    <row r="54" customFormat="1" customHeight="1"/>
+    <row r="55" customFormat="1" customHeight="1"/>
+    <row r="56" customFormat="1" customHeight="1"/>
+    <row r="57" customFormat="1" customHeight="1"/>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O27 C3:O5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="61">
   <si>
     <t>#</t>
   </si>
@@ -315,10 +315,13 @@
     <t>获得{0}个宠物</t>
   </si>
   <si>
+    <t>击杀1万个怪物</t>
+  </si>
+  <si>
     <t>奖励1个多重宠物</t>
   </si>
   <si>
-    <t>击杀200个区域boss</t>
+    <t>击杀10万个怪物</t>
   </si>
   <si>
     <t>奖励1个天下无双皮肤</t>
@@ -4598,7 +4601,7 @@
         <v>301</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -4616,10 +4619,10 @@
         <v>1</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N6" s="1">
         <v>1</v>
@@ -4637,7 +4640,7 @@
         <v>307</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -4655,10 +4658,10 @@
         <v>1</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N7" s="1">
         <v>2</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="66">
   <si>
     <t>#</t>
   </si>
@@ -325,6 +325,21 @@
   </si>
   <si>
     <t>奖励1个天下无双皮肤</t>
+  </si>
+  <si>
+    <t>奖励{1}个狼毛</t>
+  </si>
+  <si>
+    <t>奖励{1}个蛛丝</t>
+  </si>
+  <si>
+    <t>奖励{1}个雄狮利爪</t>
+  </si>
+  <si>
+    <t>奖励{1}个蛇皮</t>
+  </si>
+  <si>
+    <t>奖励{1}个巨鳄之泪</t>
   </si>
 </sst>
 </file>
@@ -503,12 +518,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4490,8 +4505,8 @@
       <c r="H3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>7</v>
+      <c r="I3" s="2">
+        <v>5</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>8</v>
@@ -4637,7 +4652,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="1">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="F7" s="1">
         <v>100000</v>
@@ -4669,21 +4684,219 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C8" s="1">
+        <v>3003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>301</v>
+      </c>
+      <c r="F8" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>5</v>
+      </c>
+      <c r="J8" s="1">
+        <v>40000001</v>
+      </c>
+      <c r="K8" s="1">
+        <v>25</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="O8" s="2"/>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C9" s="1">
+        <v>3004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>3</v>
+      </c>
+      <c r="E9" s="1">
+        <v>301</v>
+      </c>
+      <c r="F9" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>5</v>
+      </c>
+      <c r="J9" s="1">
+        <v>40000002</v>
+      </c>
+      <c r="K9" s="1">
+        <v>5</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="O9" s="2"/>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C10" s="1">
+        <v>3005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1">
+        <v>301</v>
+      </c>
+      <c r="F10" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>5</v>
+      </c>
+      <c r="J10" s="1">
+        <v>40000003</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="O10" s="2"/>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C11" s="1">
+        <v>3006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>301</v>
+      </c>
+      <c r="F11" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>5</v>
+      </c>
+      <c r="J11" s="1">
+        <v>40000004</v>
+      </c>
+      <c r="K11" s="1">
+        <v>25</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="O11" s="2"/>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C12" s="1">
+        <v>3007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1">
+        <v>301</v>
+      </c>
+      <c r="F12" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>5</v>
+      </c>
+      <c r="J12" s="1">
+        <v>40000005</v>
+      </c>
+      <c r="K12" s="1">
+        <v>6</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="O12" s="2"/>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C13" s="1">
+        <v>3008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1">
+        <v>301</v>
+      </c>
+      <c r="F13" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>5</v>
+      </c>
+      <c r="J13" s="1">
+        <v>40000006</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="O13" s="2"/>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -518,12 +518,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4745,7 +4745,7 @@
         <v>40000002</v>
       </c>
       <c r="K9" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>59</v>
@@ -4853,7 +4853,7 @@
         <v>40000005</v>
       </c>
       <c r="K12" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>59</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -4694,7 +4694,7 @@
         <v>301</v>
       </c>
       <c r="F8" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -4716,6 +4716,9 @@
       </c>
       <c r="M8" s="1" t="s">
         <v>61</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
       </c>
       <c r="O8" s="2"/>
     </row>
@@ -4730,7 +4733,7 @@
         <v>301</v>
       </c>
       <c r="F9" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -4752,6 +4755,9 @@
       </c>
       <c r="M9" s="1" t="s">
         <v>62</v>
+      </c>
+      <c r="N9" s="1">
+        <v>4</v>
       </c>
       <c r="O9" s="2"/>
     </row>
@@ -4766,7 +4772,7 @@
         <v>301</v>
       </c>
       <c r="F10" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -4788,6 +4794,9 @@
       </c>
       <c r="M10" s="1" t="s">
         <v>63</v>
+      </c>
+      <c r="N10" s="1">
+        <v>5</v>
       </c>
       <c r="O10" s="2"/>
     </row>
@@ -4802,7 +4811,7 @@
         <v>301</v>
       </c>
       <c r="F11" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -4824,6 +4833,9 @@
       </c>
       <c r="M11" s="1" t="s">
         <v>64</v>
+      </c>
+      <c r="N11" s="1">
+        <v>6</v>
       </c>
       <c r="O11" s="2"/>
     </row>
@@ -4838,7 +4850,7 @@
         <v>301</v>
       </c>
       <c r="F12" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -4860,6 +4872,9 @@
       </c>
       <c r="M12" s="1" t="s">
         <v>61</v>
+      </c>
+      <c r="N12" s="1">
+        <v>7</v>
       </c>
       <c r="O12" s="2"/>
     </row>
@@ -4874,7 +4889,7 @@
         <v>301</v>
       </c>
       <c r="F13" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -4896,6 +4911,9 @@
       </c>
       <c r="M13" s="1" t="s">
         <v>65</v>
+      </c>
+      <c r="N13" s="1">
+        <v>8</v>
       </c>
       <c r="O13" s="2"/>
     </row>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,12 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="指引任务" sheetId="1" r:id="rId1"/>
-    <sheet name="新手任务" sheetId="2" r:id="rId2"/>
-    <sheet name="福利任务" sheetId="3" r:id="rId3"/>
+    <sheet name="新入世界" sheetId="1" r:id="rId1"/>
+    <sheet name="小试牛刀" sheetId="2" r:id="rId2"/>
+    <sheet name="初露锋芒" sheetId="3" r:id="rId3"/>
+    <sheet name="每日任务" sheetId="4" r:id="rId4"/>
+    <sheet name="福利任务" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="O3" authorId="0">
+    <comment ref="P3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -75,7 +77,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="O3" authorId="0">
+    <comment ref="P3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -111,7 +113,79 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="O3" authorId="0">
+    <comment ref="P3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 闯关层数
+2 穿戴装备
+3 强化装备
+4 挑战副本
+5 设置回收</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="P3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 闯关层数
+2 穿戴装备
+3 强化装备
+4 挑战副本
+5 设置回收</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="P3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -142,7 +216,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="71">
   <si>
     <t>#</t>
   </si>
@@ -153,6 +227,9 @@
     <t>GroupId</t>
   </si>
   <si>
+    <t>CalId</t>
+  </si>
+  <si>
     <t>ConType</t>
   </si>
   <si>
@@ -327,6 +404,9 @@
     <t>奖励1个天下无双皮肤</t>
   </si>
   <si>
+    <t>击杀5万个怪物</t>
+  </si>
+  <si>
     <t>奖励{1}个狼毛</t>
   </si>
   <si>
@@ -340,6 +420,15 @@
   </si>
   <si>
     <t>奖励{1}个巨鳄之泪</t>
+  </si>
+  <si>
+    <t>击杀1万个怪物，每日刷新</t>
+  </si>
+  <si>
+    <t>奖励10次抽奖次数</t>
+  </si>
+  <si>
+    <t>奖励5次抽奖次数</t>
   </si>
 </sst>
 </file>
@@ -1319,34 +1408,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="13.5833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.8333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.4166666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5" style="1" customWidth="1"/>
-    <col min="10" max="11" width="13.75" style="1" customWidth="1"/>
-    <col min="12" max="12" width="42.75" style="1" customWidth="1"/>
-    <col min="13" max="13" width="21.4166666666667" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19.625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5833333333333" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5833333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.8333333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.4166666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5" style="1" customWidth="1"/>
+    <col min="11" max="12" width="13.75" style="1" customWidth="1"/>
+    <col min="13" max="13" width="42.75" style="1" customWidth="1"/>
+    <col min="14" max="14" width="21.4166666666667" style="1" customWidth="1"/>
+    <col min="15" max="15" width="19.625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5833333333333" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:15">
-      <c r="O1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:15">
-      <c r="O2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="3:15">
+    <row r="1" customHeight="1" spans="3:16">
+      <c r="P1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:16">
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="3:16">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1386,10 +1476,13 @@
       <c r="O3" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="3:15">
+      <c r="P3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="3:16">
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -1424,48 +1517,54 @@
       <c r="N4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="2"/>
-    </row>
-    <row r="5" customHeight="1" spans="3:15">
+      <c r="O4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="2"/>
+    </row>
+    <row r="5" customHeight="1" spans="3:16">
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O5" s="2"/>
-    </row>
-    <row r="6" customHeight="1" spans="3:15">
+        <v>19</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P5" s="2"/>
+    </row>
+    <row r="6" customHeight="1" spans="3:16">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1473,38 +1572,41 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
         <v>301</v>
       </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
         <v>20</v>
       </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
       <c r="K6" s="1">
         <v>1</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>19</v>
+      <c r="L6" s="1">
+        <v>1</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N6" s="1">
-        <v>1</v>
-      </c>
-      <c r="O6" s="2"/>
-    </row>
-    <row r="7" customHeight="1" spans="3:15">
+      <c r="N6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2"/>
+    </row>
+    <row r="7" customHeight="1" spans="3:16">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1512,38 +1614,41 @@
         <v>1</v>
       </c>
       <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
         <v>4</v>
       </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
       <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
         <v>20</v>
       </c>
-      <c r="J7" s="1">
-        <v>2</v>
-      </c>
       <c r="K7" s="1">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="1">
-        <v>2</v>
-      </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" customHeight="1" spans="3:15">
+      <c r="N7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" s="1">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" customHeight="1" spans="3:16">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1551,38 +1656,41 @@
         <v>1</v>
       </c>
       <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
         <v>301</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>30</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>200000</v>
       </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
       <c r="I8" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1">
+        <v>5</v>
+      </c>
+      <c r="K8" s="1">
         <v>5001</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>200</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N8" s="1">
+      <c r="N8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O8" s="1">
         <v>3</v>
       </c>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" customHeight="1" spans="3:15">
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" customHeight="1" spans="3:16">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1590,38 +1698,41 @@
         <v>1</v>
       </c>
       <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
         <v>203</v>
       </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
       <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
         <v>200000</v>
       </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
       <c r="I9" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J9" s="1">
+        <v>5</v>
+      </c>
+      <c r="K9" s="1">
         <v>5002</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>10</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="1">
         <v>4</v>
       </c>
-      <c r="O9" s="2"/>
-    </row>
-    <row r="10" customHeight="1" spans="3:15">
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" customHeight="1" spans="3:16">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1629,38 +1740,41 @@
         <v>1</v>
       </c>
       <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
         <v>202</v>
       </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
       </c>
       <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
         <v>8</v>
       </c>
-      <c r="J10" s="1">
-        <v>1</v>
-      </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>27</v>
+      <c r="L10" s="1">
+        <v>1</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N10" s="1">
-        <v>5</v>
-      </c>
-      <c r="O10" s="2"/>
-    </row>
-    <row r="11" customHeight="1" spans="3:15">
+      <c r="N10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10" s="1">
+        <v>5</v>
+      </c>
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" customHeight="1" spans="3:16">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1668,38 +1782,41 @@
         <v>1</v>
       </c>
       <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
         <v>10</v>
       </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
       </c>
       <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
         <v>8</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>10</v>
       </c>
-      <c r="K11" s="1">
-        <v>1</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>29</v>
+      <c r="L11" s="1">
+        <v>1</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O11" s="1">
         <v>6</v>
       </c>
-      <c r="O11" s="2"/>
-    </row>
-    <row r="12" customHeight="1" spans="3:15">
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" customHeight="1" spans="3:16">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1707,38 +1824,41 @@
         <v>1</v>
       </c>
       <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
         <v>100</v>
       </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
       <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1">
         <v>500000</v>
       </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
       <c r="I12" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J12" s="1">
+        <v>5</v>
+      </c>
+      <c r="K12" s="1">
         <v>5001</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>500</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="M12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N12" s="1">
+        <v>32</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O12" s="1">
         <v>7</v>
       </c>
-      <c r="O12" s="2"/>
-    </row>
-    <row r="13" customHeight="1" spans="3:15">
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" customHeight="1" spans="3:16">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1746,38 +1866,41 @@
         <v>1</v>
       </c>
       <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
         <v>102</v>
       </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
       <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1">
         <v>500000</v>
       </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
       <c r="I13" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J13" s="1">
+        <v>5</v>
+      </c>
+      <c r="K13" s="1">
         <v>5001</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>500</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="M13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N13" s="1">
+        <v>33</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O13" s="1">
         <v>8</v>
       </c>
-      <c r="O13" s="2"/>
-    </row>
-    <row r="14" customHeight="1" spans="3:15">
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" customHeight="1" spans="3:16">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1785,38 +1908,41 @@
         <v>1</v>
       </c>
       <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
         <v>301</v>
       </c>
-      <c r="F14" s="1">
+      <c r="G14" s="1">
         <v>100</v>
       </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
       <c r="H14" s="1">
         <v>0</v>
       </c>
       <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
         <v>8</v>
       </c>
-      <c r="J14" s="1">
-        <v>2</v>
-      </c>
       <c r="K14" s="1">
-        <v>1</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>33</v>
+        <v>2</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N14" s="1">
+      <c r="N14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O14" s="1">
         <v>9</v>
       </c>
-      <c r="O14" s="2"/>
-    </row>
-    <row r="15" customHeight="1" spans="3:15">
+      <c r="P14" s="2"/>
+    </row>
+    <row r="15" customHeight="1" spans="3:16">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1824,38 +1950,41 @@
         <v>1</v>
       </c>
       <c r="E15" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
         <v>500000</v>
       </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
       <c r="I15" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J15" s="1">
+        <v>5</v>
+      </c>
+      <c r="K15" s="1">
         <v>5001</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>1000</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="M15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N15" s="1">
+        <v>36</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O15" s="1">
         <v>10</v>
       </c>
-      <c r="O15" s="2"/>
-    </row>
-    <row r="16" customHeight="1" spans="3:15">
+      <c r="P15" s="2"/>
+    </row>
+    <row r="16" customHeight="1" spans="3:16">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1863,38 +1992,41 @@
         <v>1</v>
       </c>
       <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
         <v>201</v>
       </c>
-      <c r="F16" s="1">
+      <c r="G16" s="1">
         <v>50</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>1000000</v>
       </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
       <c r="I16" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J16" s="1">
+        <v>5</v>
+      </c>
+      <c r="K16" s="1">
         <v>5002</v>
       </c>
-      <c r="K16" s="1">
+      <c r="L16" s="1">
         <v>20</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="M16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N16" s="1">
+        <v>37</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="1">
         <v>11</v>
       </c>
-      <c r="O16" s="2"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:15">
+      <c r="P16" s="2"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:16">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1902,38 +2034,41 @@
         <v>1</v>
       </c>
       <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
         <v>300</v>
       </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J17" s="1">
+        <v>5</v>
+      </c>
+      <c r="K17" s="1">
         <v>5002</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <v>30</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="M17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N17" s="1">
+        <v>38</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" s="1">
         <v>12</v>
       </c>
-      <c r="O17" s="2"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:15">
+      <c r="P17" s="2"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:16">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1941,38 +2076,41 @@
         <v>1</v>
       </c>
       <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1">
         <v>301</v>
       </c>
-      <c r="F18" s="1">
+      <c r="G18" s="1">
         <v>500</v>
       </c>
-      <c r="G18" s="1">
+      <c r="H18" s="1">
         <v>1000000</v>
       </c>
-      <c r="H18" s="1">
-        <v>0</v>
-      </c>
       <c r="I18" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="1">
+        <v>5</v>
+      </c>
+      <c r="K18" s="1">
         <v>5001</v>
       </c>
-      <c r="K18" s="1">
+      <c r="L18" s="1">
         <v>2000</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="M18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N18" s="1">
+        <v>39</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O18" s="1">
         <v>13</v>
       </c>
-      <c r="O18" s="2"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:15">
+      <c r="P18" s="2"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:16">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -1980,38 +2118,41 @@
         <v>1</v>
       </c>
       <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
         <v>300</v>
       </c>
-      <c r="F19" s="1">
-        <v>2</v>
-      </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
       </c>
       <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
         <v>8</v>
       </c>
-      <c r="J19" s="1">
+      <c r="K19" s="1">
         <v>3</v>
       </c>
-      <c r="K19" s="1">
-        <v>1</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>39</v>
+      <c r="L19" s="1">
+        <v>1</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="N19" s="1">
+      <c r="N19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O19" s="1">
         <v>14</v>
       </c>
-      <c r="O19" s="2"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:15">
+      <c r="P19" s="2"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:16">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -2019,38 +2160,41 @@
         <v>1</v>
       </c>
       <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1">
         <v>301</v>
       </c>
-      <c r="F20" s="1">
+      <c r="G20" s="1">
         <v>1000</v>
       </c>
-      <c r="G20" s="1">
+      <c r="H20" s="1">
         <v>1000000</v>
       </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
       <c r="I20" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J20" s="1">
+        <v>5</v>
+      </c>
+      <c r="K20" s="1">
         <v>5001</v>
       </c>
-      <c r="K20" s="1">
+      <c r="L20" s="1">
         <v>2000</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="M20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N20" s="1">
+        <v>39</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O20" s="1">
         <v>15</v>
       </c>
-      <c r="O20" s="2"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:15">
+      <c r="P20" s="2"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:16">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -2058,38 +2202,41 @@
         <v>1</v>
       </c>
       <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
         <v>300</v>
       </c>
-      <c r="F21" s="1">
+      <c r="G21" s="1">
         <v>3</v>
       </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
       <c r="H21" s="1">
         <v>0</v>
       </c>
       <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
         <v>8</v>
       </c>
-      <c r="J21" s="1">
+      <c r="K21" s="1">
         <v>4</v>
       </c>
-      <c r="K21" s="1">
-        <v>1</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>41</v>
+      <c r="L21" s="1">
+        <v>1</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N21" s="1">
+      <c r="N21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O21" s="1">
         <v>16</v>
       </c>
-      <c r="O21" s="2"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:15">
+      <c r="P21" s="2"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:16">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -2097,38 +2244,41 @@
         <v>1</v>
       </c>
       <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1">
         <v>301</v>
       </c>
-      <c r="F22" s="1">
+      <c r="G22" s="1">
         <v>3000</v>
       </c>
-      <c r="G22" s="1">
+      <c r="H22" s="1">
         <v>1000000</v>
       </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
       <c r="I22" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J22" s="1">
+        <v>5</v>
+      </c>
+      <c r="K22" s="1">
         <v>5002</v>
       </c>
-      <c r="K22" s="1">
+      <c r="L22" s="1">
         <v>40</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N22" s="1">
+        <v>44</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" s="1">
         <v>17</v>
       </c>
-      <c r="O22" s="2"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:15">
+      <c r="P22" s="2"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:16">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -2136,38 +2286,41 @@
         <v>1</v>
       </c>
       <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1">
         <v>301</v>
       </c>
-      <c r="F23" s="1">
+      <c r="G23" s="1">
         <v>10000</v>
       </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
       <c r="H23" s="1">
         <v>0</v>
       </c>
       <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
         <v>8</v>
       </c>
-      <c r="J23" s="1">
-        <v>2</v>
-      </c>
       <c r="K23" s="1">
-        <v>1</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>44</v>
+        <v>2</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N23" s="1">
+        <v>45</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O23" s="1">
         <v>18</v>
       </c>
-      <c r="O23" s="2"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:15">
+      <c r="P23" s="2"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:16">
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -2175,38 +2328,41 @@
         <v>1</v>
       </c>
       <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1">
         <v>301</v>
       </c>
-      <c r="F24" s="1">
+      <c r="G24" s="1">
         <v>20000</v>
       </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
       <c r="H24" s="1">
         <v>0</v>
       </c>
       <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
         <v>8</v>
       </c>
-      <c r="J24" s="1">
+      <c r="K24" s="1">
         <v>3</v>
       </c>
-      <c r="K24" s="1">
-        <v>1</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>45</v>
+      <c r="L24" s="1">
+        <v>1</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N24" s="1">
+        <v>46</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O24" s="1">
         <v>19</v>
       </c>
-      <c r="O24" s="2"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:15">
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:16">
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -2214,38 +2370,41 @@
         <v>1</v>
       </c>
       <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1">
         <v>301</v>
       </c>
-      <c r="F25" s="1">
+      <c r="G25" s="1">
         <v>30000</v>
       </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
       <c r="H25" s="1">
         <v>0</v>
       </c>
       <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
         <v>8</v>
       </c>
-      <c r="J25" s="1">
+      <c r="K25" s="1">
         <v>4</v>
       </c>
-      <c r="K25" s="1">
-        <v>1</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>46</v>
+      <c r="L25" s="1">
+        <v>1</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N25" s="1">
+        <v>47</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O25" s="1">
         <v>20</v>
       </c>
-      <c r="O25" s="2"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:15">
+      <c r="P25" s="2"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:16">
       <c r="C26" s="1">
         <v>21</v>
       </c>
@@ -2253,38 +2412,41 @@
         <v>1</v>
       </c>
       <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1">
         <v>301</v>
       </c>
-      <c r="F26" s="1">
+      <c r="G26" s="1">
         <v>50000</v>
       </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
       <c r="H26" s="1">
         <v>0</v>
       </c>
       <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
         <v>8</v>
       </c>
-      <c r="J26" s="1">
-        <v>2</v>
-      </c>
       <c r="K26" s="1">
-        <v>1</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>47</v>
+        <v>2</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N26" s="1">
+        <v>48</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O26" s="1">
         <v>21</v>
       </c>
-      <c r="O26" s="2"/>
-    </row>
-    <row r="27" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P26" s="2"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="1:16">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1">
@@ -2294,38 +2456,41 @@
         <v>1</v>
       </c>
       <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1">
         <v>301</v>
       </c>
-      <c r="F27" s="1">
+      <c r="G27" s="1">
         <v>100000</v>
       </c>
-      <c r="G27" s="1">
-        <v>0</v>
-      </c>
       <c r="H27" s="1">
         <v>0</v>
       </c>
       <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
         <v>8</v>
       </c>
-      <c r="J27" s="1">
+      <c r="K27" s="1">
         <v>3</v>
       </c>
-      <c r="K27" s="1">
-        <v>1</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>48</v>
+      <c r="L27" s="1">
+        <v>1</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N27" s="1">
+        <v>49</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O27" s="1">
         <v>22</v>
       </c>
-      <c r="O27" s="2"/>
-    </row>
-    <row r="28" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P27" s="2"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="1:16">
       <c r="C28" s="1">
         <v>23</v>
       </c>
@@ -2333,33 +2498,36 @@
         <v>1</v>
       </c>
       <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1">
         <v>301</v>
       </c>
-      <c r="F28" s="1">
+      <c r="G28" s="1">
         <v>150000</v>
       </c>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
       <c r="H28" s="1">
         <v>0</v>
       </c>
       <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
         <v>8</v>
       </c>
-      <c r="J28" s="1">
+      <c r="K28" s="1">
         <v>4</v>
       </c>
-      <c r="K28" s="1">
-        <v>1</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>49</v>
+      <c r="L28" s="1">
+        <v>1</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N28" s="1">
+        <v>50</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O28" s="1">
         <v>23</v>
       </c>
     </row>
@@ -2394,7 +2562,7 @@
     <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O27 C3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 P6:P27 C3:D5 F3:P5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -2407,24 +2575,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O55"/>
+  <dimension ref="C1:P57"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="12" max="12" width="14.5" customWidth="1"/>
-    <col min="13" max="13" width="23.9166666666667" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5" customWidth="1"/>
+    <col min="14" max="14" width="23.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="O1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="O2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -2464,10 +2633,13 @@
       <c r="O3" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -2502,48 +2674,54 @@
       <c r="N4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="2"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="2"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O5" s="2"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:15">
+        <v>19</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -2551,37 +2729,40 @@
         <v>2</v>
       </c>
       <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
         <v>301</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>500</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>1000000</v>
       </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
       <c r="I6" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1">
+        <v>5</v>
+      </c>
+      <c r="K6" s="1">
         <v>5001</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>1000</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="M6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:15">
+        <v>51</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -2589,37 +2770,40 @@
         <v>2</v>
       </c>
       <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
         <v>301</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>1000</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>1000000</v>
       </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
       <c r="I7" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J7" s="1">
+        <v>5</v>
+      </c>
+      <c r="K7" s="1">
         <v>5001</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>1000</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="M7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N7" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
+        <v>51</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -2627,37 +2811,40 @@
         <v>2</v>
       </c>
       <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
         <v>301</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>2000</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>1000000</v>
       </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
       <c r="I8" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1">
+        <v>5</v>
+      </c>
+      <c r="K8" s="1">
         <v>5001</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>1000</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="M8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N8" s="1">
+        <v>51</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O8" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -2665,37 +2852,40 @@
         <v>2</v>
       </c>
       <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
         <v>301</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>3000</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>1000000</v>
       </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
       <c r="I9" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J9" s="1">
+        <v>5</v>
+      </c>
+      <c r="K9" s="1">
         <v>5001</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>1000</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="M9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N9" s="1">
+        <v>51</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O9" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
@@ -2703,37 +2893,40 @@
         <v>2</v>
       </c>
       <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
         <v>301</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>5000</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>1000000</v>
       </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
       <c r="I10" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J10" s="1">
+        <v>5</v>
+      </c>
+      <c r="K10" s="1">
         <v>5001</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>1000</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="M10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N10" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
+        <v>51</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O10" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
@@ -2741,38 +2934,41 @@
         <v>2</v>
       </c>
       <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
         <v>203</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
         <v>10</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>1000000</v>
       </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
       <c r="I11" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J11" s="1">
+        <v>5</v>
+      </c>
+      <c r="K11" s="1">
         <v>5001</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>2000</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="M11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N11" s="1">
+        <v>52</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O11" s="1">
         <v>6</v>
       </c>
-      <c r="O11" s="2"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
@@ -2780,37 +2976,40 @@
         <v>2</v>
       </c>
       <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
         <v>202</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G12" s="1">
         <v>10</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>1000000</v>
       </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
       <c r="I12" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J12" s="1">
+        <v>5</v>
+      </c>
+      <c r="K12" s="1">
         <v>5002</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>20</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="M12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N12" s="1">
+        <v>53</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C13" s="1">
         <v>1008</v>
       </c>
@@ -2818,37 +3017,40 @@
         <v>2</v>
       </c>
       <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
         <v>301</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13" s="1">
         <v>7000</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>1000000</v>
       </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
       <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
         <v>8</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>11</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>10</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="M13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N13" s="1">
+        <v>51</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O13" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C14" s="1">
         <v>1009</v>
       </c>
@@ -2856,37 +3058,40 @@
         <v>2</v>
       </c>
       <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
         <v>201</v>
       </c>
-      <c r="F14" s="1">
+      <c r="G14" s="1">
         <v>100</v>
       </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1">
         <v>1000000</v>
       </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
       <c r="I14" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J14" s="1">
+        <v>5</v>
+      </c>
+      <c r="K14" s="1">
         <v>5001</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <v>2000</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="M14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N14" s="1">
+        <v>55</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O14" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C15" s="1">
         <v>1010</v>
       </c>
@@ -2894,75 +3099,81 @@
         <v>2</v>
       </c>
       <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
         <v>205</v>
       </c>
-      <c r="F15" s="1">
-        <v>1</v>
-      </c>
       <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
         <v>1000000</v>
       </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
       <c r="I15" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J15" s="1">
+        <v>5</v>
+      </c>
+      <c r="K15" s="1">
         <v>5002</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>20</v>
       </c>
-      <c r="L15" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N15" s="1">
+      <c r="M15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O15" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="16" s="3" customFormat="1" customHeight="1" spans="3:15">
+    <row r="16" s="3" customFormat="1" customHeight="1" spans="3:16">
       <c r="C16" s="1">
         <v>1011</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
         <v>203</v>
       </c>
-      <c r="F16" s="3">
+      <c r="G16" s="3">
         <v>20</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>1500000</v>
       </c>
-      <c r="H16" s="3">
-        <v>0</v>
-      </c>
       <c r="I16" s="3">
-        <v>5</v>
-      </c>
-      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3">
+        <v>5</v>
+      </c>
+      <c r="K16" s="1">
         <v>5001</v>
       </c>
-      <c r="K16" s="3">
+      <c r="L16" s="3">
         <v>3000</v>
       </c>
-      <c r="L16" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="M16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N16" s="1">
+        <v>52</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O16" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C17" s="1">
         <v>1012</v>
       </c>
@@ -2970,37 +3181,40 @@
         <v>2</v>
       </c>
       <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
         <v>202</v>
       </c>
-      <c r="F17" s="1">
+      <c r="G17" s="1">
         <v>20</v>
       </c>
-      <c r="G17" s="1">
+      <c r="H17" s="1">
         <v>1500000</v>
       </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
       <c r="I17" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J17" s="1">
+        <v>5</v>
+      </c>
+      <c r="K17" s="1">
         <v>5002</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <v>30</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="M17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N17" s="1">
+        <v>53</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C18" s="1">
         <v>1013</v>
       </c>
@@ -3008,37 +3222,40 @@
         <v>2</v>
       </c>
       <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1">
         <v>301</v>
       </c>
-      <c r="F18" s="1">
+      <c r="G18" s="1">
         <v>10000</v>
       </c>
-      <c r="G18" s="1">
+      <c r="H18" s="1">
         <v>1500000</v>
       </c>
-      <c r="H18" s="1">
-        <v>0</v>
-      </c>
       <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
         <v>8</v>
       </c>
-      <c r="J18" s="1">
+      <c r="K18" s="1">
         <v>11</v>
       </c>
-      <c r="K18" s="1">
+      <c r="L18" s="1">
         <v>15</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="M18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N18" s="1">
+        <v>51</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O18" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C19" s="1">
         <v>1014</v>
       </c>
@@ -3046,37 +3263,40 @@
         <v>2</v>
       </c>
       <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
         <v>201</v>
       </c>
-      <c r="F19" s="1">
+      <c r="G19" s="1">
         <v>800</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>1500000</v>
       </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
       <c r="I19" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J19" s="1">
+        <v>5</v>
+      </c>
+      <c r="K19" s="1">
         <v>5001</v>
       </c>
-      <c r="K19" s="1">
+      <c r="L19" s="1">
         <v>3000</v>
       </c>
-      <c r="L19" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="M19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N19" s="1">
+        <v>55</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O19" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C20" s="1">
         <v>1015</v>
       </c>
@@ -3084,75 +3304,81 @@
         <v>2</v>
       </c>
       <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1">
         <v>101</v>
       </c>
-      <c r="F20" s="1">
-        <v>5</v>
-      </c>
       <c r="G20" s="1">
+        <v>5</v>
+      </c>
+      <c r="H20" s="1">
         <v>1500000</v>
       </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
       <c r="I20" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J20" s="1">
+        <v>5</v>
+      </c>
+      <c r="K20" s="1">
         <v>5002</v>
       </c>
-      <c r="K20" s="1">
+      <c r="L20" s="1">
         <v>30</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="M20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N20" s="1">
+        <v>57</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="21" s="3" customFormat="1" customHeight="1" spans="3:14">
+    <row r="21" s="3" customFormat="1" customHeight="1" spans="3:15">
       <c r="C21" s="1">
         <v>1016</v>
       </c>
       <c r="D21" s="3">
         <v>2</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>203</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>35</v>
       </c>
-      <c r="G21" s="1">
+      <c r="H21" s="1">
         <v>1500000</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
       <c r="I21" s="3">
-        <v>5</v>
-      </c>
-      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>5</v>
+      </c>
+      <c r="K21" s="1">
         <v>5001</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="M21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N21" s="1">
+        <v>52</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O21" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C22" s="1">
         <v>1017</v>
       </c>
@@ -3160,37 +3386,40 @@
         <v>2</v>
       </c>
       <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1">
         <v>202</v>
       </c>
-      <c r="F22" s="1">
+      <c r="G22" s="1">
         <v>35</v>
       </c>
-      <c r="G22" s="1">
+      <c r="H22" s="1">
         <v>1500000</v>
       </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
       <c r="I22" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J22" s="1">
+        <v>5</v>
+      </c>
+      <c r="K22" s="1">
         <v>5002</v>
       </c>
-      <c r="K22" s="1">
+      <c r="L22" s="1">
         <v>40</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="M22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N22" s="1">
+        <v>53</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C23" s="1">
         <v>1018</v>
       </c>
@@ -3198,37 +3427,40 @@
         <v>2</v>
       </c>
       <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1">
         <v>301</v>
       </c>
-      <c r="F23" s="1">
+      <c r="G23" s="1">
         <v>20000</v>
       </c>
-      <c r="G23" s="1">
+      <c r="H23" s="1">
         <v>1500000</v>
       </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
       <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
         <v>8</v>
       </c>
-      <c r="J23" s="1">
+      <c r="K23" s="1">
         <v>11</v>
       </c>
-      <c r="K23" s="1">
+      <c r="L23" s="1">
         <v>20</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="M23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N23" s="1">
+        <v>51</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O23" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C24" s="1">
         <v>1019</v>
       </c>
@@ -3236,37 +3468,40 @@
         <v>2</v>
       </c>
       <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1">
         <v>201</v>
       </c>
-      <c r="F24" s="1">
+      <c r="G24" s="1">
         <v>2000</v>
       </c>
-      <c r="G24" s="1">
+      <c r="H24" s="1">
         <v>1500000</v>
       </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
       <c r="I24" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J24" s="1">
+        <v>5</v>
+      </c>
+      <c r="K24" s="1">
         <v>5001</v>
       </c>
-      <c r="K24" s="1">
+      <c r="L24" s="1">
         <v>4000</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="M24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N24" s="1">
+        <v>55</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O24" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C25" s="1">
         <v>1020</v>
       </c>
@@ -3274,75 +3509,81 @@
         <v>2</v>
       </c>
       <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1">
         <v>205</v>
       </c>
-      <c r="F25" s="1">
+      <c r="G25" s="1">
         <v>3</v>
       </c>
-      <c r="G25" s="1">
+      <c r="H25" s="1">
         <v>1000000</v>
       </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
       <c r="I25" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J25" s="1">
+        <v>5</v>
+      </c>
+      <c r="K25" s="1">
         <v>5002</v>
       </c>
-      <c r="K25" s="1">
+      <c r="L25" s="1">
         <v>40</v>
       </c>
-      <c r="L25" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" s="1">
+      <c r="M25" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O25" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="26" s="3" customFormat="1" customHeight="1" spans="3:14">
+    <row r="26" s="3" customFormat="1" customHeight="1" spans="3:15">
       <c r="C26" s="1">
         <v>1021</v>
       </c>
       <c r="D26" s="3">
         <v>2</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>203</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>55</v>
       </c>
-      <c r="G26" s="1">
+      <c r="H26" s="1">
         <v>1500000</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
       <c r="I26" s="3">
-        <v>5</v>
-      </c>
-      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>5</v>
+      </c>
+      <c r="K26" s="1">
         <v>5001</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5000</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="M26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N26" s="1">
+        <v>52</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O26" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C27" s="1">
         <v>1022</v>
       </c>
@@ -3350,37 +3591,40 @@
         <v>2</v>
       </c>
       <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1">
         <v>202</v>
       </c>
-      <c r="F27" s="1">
+      <c r="G27" s="1">
         <v>55</v>
       </c>
-      <c r="G27" s="5">
+      <c r="H27" s="5">
         <v>2000000</v>
       </c>
-      <c r="H27" s="1">
-        <v>0</v>
-      </c>
       <c r="I27" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J27" s="1">
+        <v>5</v>
+      </c>
+      <c r="K27" s="1">
         <v>5002</v>
       </c>
-      <c r="K27" s="1">
+      <c r="L27" s="1">
         <v>50</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="M27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N27" s="1">
+        <v>53</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O27" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C28" s="1">
         <v>1023</v>
       </c>
@@ -3388,1065 +3632,1101 @@
         <v>2</v>
       </c>
       <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1">
         <v>301</v>
       </c>
-      <c r="F28" s="1">
+      <c r="G28" s="1">
         <v>50000</v>
       </c>
-      <c r="G28" s="5">
+      <c r="H28" s="5">
         <v>2000000</v>
       </c>
-      <c r="H28" s="1">
-        <v>0</v>
-      </c>
       <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
         <v>8</v>
       </c>
-      <c r="J28" s="1">
+      <c r="K28" s="1">
         <v>11</v>
       </c>
-      <c r="K28" s="1">
+      <c r="L28" s="1">
         <v>25</v>
       </c>
-      <c r="L28" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="M28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N28" s="1">
+        <v>51</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O28" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C29" s="1">
         <v>1024</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29"/>
+      <c r="F29" s="1">
         <v>201</v>
       </c>
-      <c r="F29" s="1">
+      <c r="G29" s="1">
         <v>5000</v>
       </c>
-      <c r="G29" s="5">
+      <c r="H29" s="5">
         <v>2000000</v>
       </c>
-      <c r="H29" s="1">
-        <v>0</v>
-      </c>
       <c r="I29" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J29" s="1">
+        <v>5</v>
+      </c>
+      <c r="K29" s="1">
         <v>5001</v>
       </c>
-      <c r="K29" s="1">
+      <c r="L29" s="1">
         <v>5000</v>
       </c>
-      <c r="L29" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="M29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O29" s="1">
         <v>24</v>
       </c>
-      <c r="N29" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:14">
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C30" s="1">
         <v>1025</v>
       </c>
       <c r="D30" s="1">
         <v>2</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30"/>
+      <c r="F30" s="1">
         <v>101</v>
       </c>
-      <c r="F30" s="1">
+      <c r="G30" s="1">
         <v>10</v>
       </c>
-      <c r="G30" s="5">
+      <c r="H30" s="5">
         <v>2000000</v>
       </c>
-      <c r="H30" s="1">
-        <v>0</v>
-      </c>
       <c r="I30" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J30" s="1">
+        <v>5</v>
+      </c>
+      <c r="K30" s="1">
         <v>5002</v>
       </c>
-      <c r="K30" s="1">
+      <c r="L30" s="1">
         <v>50</v>
       </c>
-      <c r="L30" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="M30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N30" s="1">
+        <v>57</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O30" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C31" s="1">
         <v>1026</v>
       </c>
       <c r="D31" s="3">
         <v>2</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31"/>
+      <c r="F31" s="3">
         <v>203</v>
       </c>
-      <c r="F31" s="3">
+      <c r="G31" s="3">
         <v>85</v>
       </c>
-      <c r="G31" s="5">
+      <c r="H31" s="5">
         <v>2000000</v>
       </c>
-      <c r="H31" s="3">
-        <v>0</v>
-      </c>
       <c r="I31" s="3">
-        <v>5</v>
-      </c>
-      <c r="J31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3">
+        <v>5</v>
+      </c>
+      <c r="K31" s="1">
         <v>5001</v>
       </c>
-      <c r="K31" s="3">
+      <c r="L31" s="3">
         <v>6000</v>
       </c>
-      <c r="L31" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="M31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N31" s="1">
+        <v>52</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O31" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C32" s="1">
         <v>1027</v>
       </c>
       <c r="D32" s="1">
         <v>2</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32"/>
+      <c r="F32" s="1">
         <v>202</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>85</v>
       </c>
-      <c r="G32" s="5">
+      <c r="H32" s="5">
         <v>2000000</v>
       </c>
-      <c r="H32" s="1">
-        <v>0</v>
-      </c>
       <c r="I32" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J32" s="1">
+        <v>5</v>
+      </c>
+      <c r="K32" s="1">
         <v>5002</v>
       </c>
-      <c r="K32" s="1">
+      <c r="L32" s="1">
         <v>50</v>
       </c>
-      <c r="L32" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="M32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N32" s="1">
+        <v>53</v>
+      </c>
+      <c r="N32" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O32" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C33" s="1">
         <v>1028</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33"/>
+      <c r="F33" s="1">
         <v>301</v>
       </c>
-      <c r="F33" s="1">
+      <c r="G33" s="1">
         <v>100000</v>
       </c>
-      <c r="G33" s="5">
+      <c r="H33" s="5">
         <v>2000000</v>
       </c>
-      <c r="H33" s="1">
-        <v>0</v>
-      </c>
       <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1">
         <v>8</v>
       </c>
-      <c r="J33" s="1">
+      <c r="K33" s="1">
         <v>11</v>
       </c>
-      <c r="K33" s="1">
+      <c r="L33" s="1">
         <v>30</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="M33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N33" s="1">
+        <v>51</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O33" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C34" s="1">
         <v>1029</v>
       </c>
       <c r="D34" s="1">
         <v>2</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34"/>
+      <c r="F34" s="1">
         <v>201</v>
       </c>
-      <c r="F34" s="1">
+      <c r="G34" s="1">
         <v>10000</v>
       </c>
-      <c r="G34" s="5">
+      <c r="H34" s="5">
         <v>2000000</v>
       </c>
-      <c r="H34" s="1">
-        <v>0</v>
-      </c>
       <c r="I34" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J34" s="1">
+        <v>5</v>
+      </c>
+      <c r="K34" s="1">
         <v>5001</v>
       </c>
-      <c r="K34" s="1">
+      <c r="L34" s="1">
         <v>6000</v>
       </c>
-      <c r="L34" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="M34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N34" s="1">
+        <v>55</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O34" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C35" s="1">
         <v>1030</v>
       </c>
       <c r="D35" s="1">
         <v>2</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35"/>
+      <c r="F35" s="1">
         <v>205</v>
       </c>
-      <c r="F35" s="1">
-        <v>5</v>
-      </c>
       <c r="G35" s="1">
+        <v>5</v>
+      </c>
+      <c r="H35" s="1">
         <v>1000000</v>
       </c>
-      <c r="H35" s="1">
-        <v>0</v>
-      </c>
       <c r="I35" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J35" s="1">
+        <v>5</v>
+      </c>
+      <c r="K35" s="1">
         <v>5002</v>
       </c>
-      <c r="K35" s="1">
+      <c r="L35" s="1">
         <v>50</v>
       </c>
-      <c r="L35" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" s="1">
+      <c r="M35" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O35" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C36" s="1">
         <v>1031</v>
       </c>
       <c r="D36" s="3">
         <v>2</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36"/>
+      <c r="F36" s="3">
         <v>203</v>
       </c>
-      <c r="F36" s="3">
+      <c r="G36" s="3">
         <v>120</v>
       </c>
-      <c r="G36" s="5">
+      <c r="H36" s="5">
         <v>2000000</v>
       </c>
-      <c r="H36" s="3">
-        <v>0</v>
-      </c>
       <c r="I36" s="3">
-        <v>5</v>
-      </c>
-      <c r="J36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3">
+        <v>5</v>
+      </c>
+      <c r="K36" s="1">
         <v>5001</v>
       </c>
-      <c r="K36" s="3">
+      <c r="L36" s="3">
         <v>7000</v>
       </c>
-      <c r="L36" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="M36" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N36" s="1">
+        <v>52</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O36" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C37" s="1">
         <v>1032</v>
       </c>
       <c r="D37" s="1">
         <v>2</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37"/>
+      <c r="F37" s="1">
         <v>202</v>
       </c>
-      <c r="F37" s="1">
+      <c r="G37" s="1">
         <v>120</v>
       </c>
-      <c r="G37" s="5">
+      <c r="H37" s="5">
         <v>2000000</v>
       </c>
-      <c r="H37" s="1">
-        <v>0</v>
-      </c>
       <c r="I37" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J37" s="1">
+        <v>5</v>
+      </c>
+      <c r="K37" s="1">
         <v>5002</v>
       </c>
-      <c r="K37" s="1">
+      <c r="L37" s="1">
         <v>50</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="M37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N37" s="1">
+        <v>53</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O37" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C38" s="1">
         <v>1033</v>
       </c>
       <c r="D38" s="1">
         <v>2</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38"/>
+      <c r="F38" s="1">
         <v>301</v>
       </c>
-      <c r="F38" s="1">
+      <c r="G38" s="1">
         <v>200000</v>
       </c>
-      <c r="G38" s="5">
+      <c r="H38" s="5">
         <v>2000000</v>
       </c>
-      <c r="H38" s="1">
-        <v>0</v>
-      </c>
       <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1">
         <v>8</v>
       </c>
-      <c r="J38" s="1">
+      <c r="K38" s="1">
         <v>11</v>
       </c>
-      <c r="K38" s="1">
+      <c r="L38" s="1">
         <v>35</v>
       </c>
-      <c r="L38" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="M38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N38" s="1">
+        <v>51</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O38" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C39" s="1">
         <v>1034</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39"/>
+      <c r="F39" s="1">
         <v>201</v>
       </c>
-      <c r="F39" s="1">
+      <c r="G39" s="1">
         <v>20000</v>
       </c>
-      <c r="G39" s="5">
+      <c r="H39" s="5">
         <v>2000000</v>
       </c>
-      <c r="H39" s="1">
-        <v>0</v>
-      </c>
       <c r="I39" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J39" s="1">
+        <v>5</v>
+      </c>
+      <c r="K39" s="1">
         <v>5001</v>
       </c>
-      <c r="K39" s="1">
+      <c r="L39" s="1">
         <v>7000</v>
       </c>
-      <c r="L39" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="M39" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N39" s="1">
+        <v>55</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O39" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C40" s="1">
         <v>1035</v>
       </c>
       <c r="D40" s="1">
         <v>2</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40"/>
+      <c r="F40" s="1">
         <v>101</v>
       </c>
-      <c r="F40" s="1">
+      <c r="G40" s="1">
         <v>50</v>
       </c>
-      <c r="G40" s="5">
+      <c r="H40" s="5">
         <v>2000000</v>
       </c>
-      <c r="H40" s="1">
-        <v>0</v>
-      </c>
       <c r="I40" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J40" s="1">
+        <v>5</v>
+      </c>
+      <c r="K40" s="1">
         <v>5002</v>
       </c>
-      <c r="K40" s="1">
+      <c r="L40" s="1">
         <v>50</v>
       </c>
-      <c r="L40" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="M40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N40" s="1">
+        <v>57</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O40" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="3:14">
+    <row r="41" customHeight="1" spans="3:15">
       <c r="C41" s="1">
         <v>1036</v>
       </c>
       <c r="D41" s="3">
         <v>2</v>
       </c>
-      <c r="E41" s="3">
+      <c r="E41"/>
+      <c r="F41" s="3">
         <v>203</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>160</v>
       </c>
-      <c r="G41" s="5">
+      <c r="H41" s="5">
         <v>2000000</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
       <c r="I41" s="3">
-        <v>5</v>
-      </c>
-      <c r="J41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
+        <v>5</v>
+      </c>
+      <c r="K41" s="1">
         <v>5001</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7000</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="M41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N41" s="1">
+        <v>52</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O41" s="1">
         <v>36</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="3:14">
+    <row r="42" customHeight="1" spans="3:15">
       <c r="C42" s="1">
         <v>1037</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42"/>
+      <c r="F42" s="1">
         <v>202</v>
       </c>
-      <c r="F42" s="1">
+      <c r="G42" s="1">
         <v>160</v>
       </c>
-      <c r="G42" s="5">
+      <c r="H42" s="5">
         <v>2000000</v>
       </c>
-      <c r="H42" s="1">
-        <v>0</v>
-      </c>
       <c r="I42" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J42" s="1">
+        <v>5</v>
+      </c>
+      <c r="K42" s="1">
         <v>5002</v>
       </c>
-      <c r="K42" s="1">
+      <c r="L42" s="1">
         <v>50</v>
       </c>
-      <c r="L42" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="M42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N42" s="1">
+        <v>53</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O42" s="1">
         <v>37</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="3:14">
+    <row r="43" customHeight="1" spans="3:15">
       <c r="C43" s="1">
         <v>1038</v>
       </c>
       <c r="D43" s="1">
         <v>2</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43"/>
+      <c r="F43" s="1">
         <v>301</v>
       </c>
-      <c r="F43" s="1">
+      <c r="G43" s="1">
         <v>350000</v>
       </c>
-      <c r="G43" s="5">
+      <c r="H43" s="5">
         <v>2000000</v>
       </c>
-      <c r="H43" s="1">
-        <v>0</v>
-      </c>
       <c r="I43" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
         <v>8</v>
       </c>
-      <c r="J43" s="1">
+      <c r="K43" s="1">
         <v>11</v>
       </c>
-      <c r="K43" s="1">
+      <c r="L43" s="1">
         <v>35</v>
       </c>
-      <c r="L43" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="M43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N43" s="1">
+        <v>51</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O43" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="3:14">
+    <row r="44" customHeight="1" spans="3:15">
       <c r="C44" s="1">
         <v>1039</v>
       </c>
       <c r="D44" s="1">
         <v>2</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44"/>
+      <c r="F44" s="1">
         <v>201</v>
       </c>
-      <c r="F44" s="1">
+      <c r="G44" s="1">
         <v>3500</v>
       </c>
-      <c r="G44" s="5">
+      <c r="H44" s="5">
         <v>2000000</v>
       </c>
-      <c r="H44" s="1">
-        <v>0</v>
-      </c>
       <c r="I44" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J44" s="1">
+        <v>5</v>
+      </c>
+      <c r="K44" s="1">
         <v>5001</v>
       </c>
-      <c r="K44" s="1">
+      <c r="L44" s="1">
         <v>7000</v>
       </c>
-      <c r="L44" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="M44" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N44" s="1">
+        <v>55</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O44" s="1">
         <v>39</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="3:14">
+    <row r="45" customHeight="1" spans="3:15">
       <c r="C45" s="1">
         <v>1040</v>
       </c>
       <c r="D45" s="1">
         <v>2</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45"/>
+      <c r="F45" s="1">
         <v>205</v>
       </c>
-      <c r="F45" s="1">
+      <c r="G45" s="1">
         <v>7</v>
       </c>
-      <c r="G45" s="1">
+      <c r="H45" s="1">
         <v>1000000</v>
       </c>
-      <c r="H45" s="1">
-        <v>0</v>
-      </c>
       <c r="I45" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J45" s="1">
+        <v>5</v>
+      </c>
+      <c r="K45" s="1">
         <v>5002</v>
       </c>
-      <c r="K45" s="1">
+      <c r="L45" s="1">
         <v>50</v>
       </c>
-      <c r="L45" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" s="1">
+      <c r="M45" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O45" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="3:14">
+    <row r="46" customHeight="1" spans="3:15">
       <c r="C46" s="1">
         <v>1041</v>
       </c>
       <c r="D46" s="3">
         <v>2</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46"/>
+      <c r="F46" s="3">
         <v>203</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>200</v>
       </c>
-      <c r="G46" s="5">
+      <c r="H46" s="5">
         <v>2000000</v>
       </c>
-      <c r="H46" s="3">
-        <v>0</v>
-      </c>
       <c r="I46" s="3">
-        <v>5</v>
-      </c>
-      <c r="J46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3">
+        <v>5</v>
+      </c>
+      <c r="K46" s="1">
         <v>5001</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="M46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N46" s="1">
+        <v>52</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O46" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="3:14">
+    <row r="47" customHeight="1" spans="3:15">
       <c r="C47" s="1">
         <v>1042</v>
       </c>
       <c r="D47" s="1">
         <v>2</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47"/>
+      <c r="F47" s="1">
         <v>202</v>
       </c>
-      <c r="F47" s="1">
+      <c r="G47" s="1">
         <v>200</v>
       </c>
-      <c r="G47" s="5">
+      <c r="H47" s="5">
         <v>2000000</v>
       </c>
-      <c r="H47" s="1">
-        <v>0</v>
-      </c>
       <c r="I47" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J47" s="1">
+        <v>5</v>
+      </c>
+      <c r="K47" s="1">
         <v>5002</v>
       </c>
-      <c r="K47" s="1">
+      <c r="L47" s="1">
         <v>50</v>
       </c>
-      <c r="L47" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="M47" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N47" s="1">
+        <v>53</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O47" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="3:14">
+    <row r="48" customHeight="1" spans="3:15">
       <c r="C48" s="1">
         <v>1043</v>
       </c>
       <c r="D48" s="1">
         <v>2</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48"/>
+      <c r="F48" s="1">
         <v>301</v>
       </c>
-      <c r="F48" s="1">
+      <c r="G48" s="1">
         <v>550000</v>
       </c>
-      <c r="G48" s="5">
+      <c r="H48" s="5">
         <v>2000000</v>
       </c>
-      <c r="H48" s="1">
-        <v>0</v>
-      </c>
       <c r="I48" s="1">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1">
         <v>8</v>
       </c>
-      <c r="J48" s="1">
+      <c r="K48" s="1">
         <v>11</v>
       </c>
-      <c r="K48" s="1">
+      <c r="L48" s="1">
         <v>35</v>
       </c>
-      <c r="L48" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="M48" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N48" s="1">
+        <v>51</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O48" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="3:14">
+    <row r="49" customHeight="1" spans="3:15">
       <c r="C49" s="1">
         <v>1044</v>
       </c>
       <c r="D49" s="1">
         <v>2</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49"/>
+      <c r="F49" s="1">
         <v>201</v>
       </c>
-      <c r="F49" s="1">
+      <c r="G49" s="1">
         <v>55000</v>
       </c>
-      <c r="G49" s="5">
+      <c r="H49" s="5">
         <v>2000000</v>
       </c>
-      <c r="H49" s="1">
-        <v>0</v>
-      </c>
       <c r="I49" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J49" s="1">
+        <v>5</v>
+      </c>
+      <c r="K49" s="1">
         <v>5001</v>
       </c>
-      <c r="K49" s="1">
+      <c r="L49" s="1">
         <v>7000</v>
       </c>
-      <c r="L49" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="M49" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N49" s="1">
+        <v>55</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O49" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="3:14">
+    <row r="50" customHeight="1" spans="3:15">
       <c r="C50" s="1">
         <v>1045</v>
       </c>
       <c r="D50" s="1">
         <v>2</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50"/>
+      <c r="F50" s="1">
         <v>101</v>
       </c>
-      <c r="F50" s="1">
+      <c r="G50" s="1">
         <v>200</v>
       </c>
-      <c r="G50" s="5">
+      <c r="H50" s="5">
         <v>2000000</v>
       </c>
-      <c r="H50" s="1">
-        <v>0</v>
-      </c>
       <c r="I50" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J50" s="1">
+        <v>5</v>
+      </c>
+      <c r="K50" s="1">
         <v>5002</v>
       </c>
-      <c r="K50" s="1">
+      <c r="L50" s="1">
         <v>50</v>
       </c>
-      <c r="L50" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="M50" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N50" s="1">
+        <v>57</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O50" s="1">
         <v>45</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="3:14">
+    <row r="51" customHeight="1" spans="3:15">
       <c r="C51" s="1">
         <v>1046</v>
       </c>
       <c r="D51" s="3">
         <v>2</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51"/>
+      <c r="F51" s="3">
         <v>203</v>
       </c>
-      <c r="F51" s="3">
+      <c r="G51" s="3">
         <v>240</v>
       </c>
-      <c r="G51" s="5">
+      <c r="H51" s="5">
         <v>2000000</v>
       </c>
-      <c r="H51" s="3">
-        <v>0</v>
-      </c>
       <c r="I51" s="3">
-        <v>5</v>
-      </c>
-      <c r="J51" s="1">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3">
+        <v>5</v>
+      </c>
+      <c r="K51" s="1">
         <v>5001</v>
       </c>
-      <c r="K51" s="3">
+      <c r="L51" s="3">
         <v>7000</v>
       </c>
-      <c r="L51" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="M51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N51" s="1">
+        <v>52</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O51" s="1">
         <v>46</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="3:14">
+    <row r="52" customHeight="1" spans="3:15">
       <c r="C52" s="1">
         <v>1047</v>
       </c>
       <c r="D52" s="1">
         <v>2</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E52"/>
+      <c r="F52" s="1">
         <v>202</v>
       </c>
-      <c r="F52" s="1">
+      <c r="G52" s="1">
         <v>240</v>
       </c>
-      <c r="G52" s="5">
+      <c r="H52" s="5">
         <v>2000000</v>
       </c>
-      <c r="H52" s="1">
-        <v>0</v>
-      </c>
       <c r="I52" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J52" s="1">
+        <v>5</v>
+      </c>
+      <c r="K52" s="1">
         <v>5002</v>
       </c>
-      <c r="K52" s="1">
+      <c r="L52" s="1">
         <v>50</v>
       </c>
-      <c r="L52" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="M52" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N52" s="1">
+        <v>53</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O52" s="1">
         <v>47</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="3:14">
+    <row r="53" customHeight="1" spans="3:15">
       <c r="C53" s="1">
         <v>1048</v>
       </c>
       <c r="D53" s="1">
         <v>2</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53"/>
+      <c r="F53" s="1">
         <v>301</v>
       </c>
-      <c r="F53" s="1">
+      <c r="G53" s="1">
         <v>800000</v>
       </c>
-      <c r="G53" s="5">
+      <c r="H53" s="5">
         <v>2000000</v>
       </c>
-      <c r="H53" s="1">
-        <v>0</v>
-      </c>
       <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1">
         <v>8</v>
       </c>
-      <c r="J53" s="1">
+      <c r="K53" s="1">
         <v>11</v>
       </c>
-      <c r="K53" s="1">
+      <c r="L53" s="1">
         <v>35</v>
       </c>
-      <c r="L53" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="M53" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N53" s="1">
+        <v>51</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O53" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="3:14">
+    <row r="54" customHeight="1" spans="3:15">
       <c r="C54" s="1">
         <v>1049</v>
       </c>
       <c r="D54" s="1">
         <v>2</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E54"/>
+      <c r="F54" s="1">
         <v>201</v>
       </c>
-      <c r="F54" s="1">
+      <c r="G54" s="1">
         <v>80000</v>
       </c>
-      <c r="G54" s="5">
+      <c r="H54" s="5">
         <v>2000000</v>
       </c>
-      <c r="H54" s="1">
-        <v>0</v>
-      </c>
       <c r="I54" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J54" s="1">
+        <v>5</v>
+      </c>
+      <c r="K54" s="1">
         <v>5001</v>
       </c>
-      <c r="K54" s="1">
+      <c r="L54" s="1">
         <v>7000</v>
       </c>
-      <c r="L54" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="M54" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N54" s="1">
+        <v>55</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O54" s="1">
         <v>49</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="3:14">
+    <row r="55" customHeight="1" spans="3:15">
       <c r="C55" s="1">
         <v>1050</v>
       </c>
       <c r="D55" s="1">
         <v>2</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E55"/>
+      <c r="F55" s="1">
         <v>101</v>
       </c>
-      <c r="F55" s="1">
+      <c r="G55" s="1">
         <v>300</v>
       </c>
-      <c r="G55" s="5">
+      <c r="H55" s="5">
         <v>2000000</v>
       </c>
-      <c r="H55" s="1">
-        <v>0</v>
-      </c>
       <c r="I55" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J55" s="1">
+        <v>5</v>
+      </c>
+      <c r="K55" s="1">
         <v>5002</v>
       </c>
-      <c r="K55" s="1">
+      <c r="L55" s="1">
         <v>50</v>
       </c>
-      <c r="L55" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="M55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N55" s="1">
+        <v>57</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O55" s="1">
         <v>50</v>
       </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:15">
+      <c r="E56"/>
+    </row>
+    <row r="57" customHeight="1" spans="3:15">
+      <c r="E57"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O11 C3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 P11 C3:D5 F3:P5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -4459,34 +4739,35 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="13.5833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.8333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.4166666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5" style="1" customWidth="1"/>
-    <col min="10" max="11" width="13.75" style="1" customWidth="1"/>
-    <col min="12" max="12" width="42.75" style="1" customWidth="1"/>
-    <col min="13" max="13" width="21.4166666666667" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19.625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5833333333333" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5833333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.8333333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.4166666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5" style="1" customWidth="1"/>
+    <col min="11" max="12" width="13.75" style="1" customWidth="1"/>
+    <col min="13" max="13" width="42.75" style="1" customWidth="1"/>
+    <col min="14" max="14" width="21.4166666666667" style="1" customWidth="1"/>
+    <col min="15" max="15" width="19.625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5833333333333" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="O1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="O2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -4505,11 +4786,11 @@
       <c r="H3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="2">
-        <v>5</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>8</v>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="2">
+        <v>5</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>9</v>
@@ -4526,10 +4807,13 @@
       <c r="O3" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -4564,48 +4848,54 @@
       <c r="N4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="2"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="2"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O5" s="2"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:15">
+        <v>19</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C6" s="1">
         <v>3001</v>
       </c>
@@ -4613,38 +4903,41 @@
         <v>3</v>
       </c>
       <c r="E6" s="1">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1">
         <v>301</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>10000</v>
       </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
         <v>8</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>14</v>
       </c>
-      <c r="K6" s="1">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>57</v>
+      <c r="L6" s="1">
+        <v>1</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="N6" s="1">
-        <v>1</v>
-      </c>
-      <c r="O6" s="2"/>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2"/>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C7" s="1">
         <v>3002</v>
       </c>
@@ -4652,38 +4945,41 @@
         <v>3</v>
       </c>
       <c r="E7" s="1">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1">
         <v>301</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>100000</v>
       </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J7" s="1">
+        <v>5</v>
+      </c>
+      <c r="K7" s="1">
         <v>10004</v>
       </c>
-      <c r="K7" s="1">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>59</v>
+      <c r="L7" s="1">
+        <v>1</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="N7" s="1">
-        <v>2</v>
-      </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="N7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O7" s="1">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C8" s="1">
         <v>3003</v>
       </c>
@@ -4691,38 +4987,41 @@
         <v>3</v>
       </c>
       <c r="E8" s="1">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1">
         <v>301</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>50000</v>
       </c>
-      <c r="G8" s="1">
-        <v>0</v>
-      </c>
       <c r="H8" s="1">
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1">
+        <v>5</v>
+      </c>
+      <c r="K8" s="1">
         <v>40000001</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>25</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="M8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="N8" s="1">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
+        <v>62</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O8" s="1">
+        <v>3</v>
+      </c>
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C9" s="1">
         <v>3004</v>
       </c>
@@ -4730,38 +5029,41 @@
         <v>3</v>
       </c>
       <c r="E9" s="1">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1">
         <v>301</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>50000</v>
       </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
       <c r="H9" s="1">
         <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J9" s="1">
+        <v>5</v>
+      </c>
+      <c r="K9" s="1">
         <v>40000002</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>3</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O9" s="1">
         <v>4</v>
       </c>
-      <c r="O9" s="2"/>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C10" s="1">
         <v>3005</v>
       </c>
@@ -4769,38 +5071,41 @@
         <v>3</v>
       </c>
       <c r="E10" s="1">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1">
         <v>301</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>50000</v>
       </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
       <c r="H10" s="1">
         <v>0</v>
       </c>
       <c r="I10" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J10" s="1">
+        <v>5</v>
+      </c>
+      <c r="K10" s="1">
         <v>40000003</v>
       </c>
-      <c r="K10" s="1">
-        <v>1</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>59</v>
+      <c r="L10" s="1">
+        <v>1</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="N10" s="1">
-        <v>5</v>
-      </c>
-      <c r="O10" s="2"/>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:15">
+        <v>62</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O10" s="1">
+        <v>5</v>
+      </c>
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C11" s="1">
         <v>3006</v>
       </c>
@@ -4808,38 +5113,41 @@
         <v>3</v>
       </c>
       <c r="E11" s="1">
+        <v>3</v>
+      </c>
+      <c r="F11" s="1">
         <v>301</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
         <v>50000</v>
       </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
       <c r="H11" s="1">
         <v>0</v>
       </c>
       <c r="I11" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J11" s="1">
+        <v>5</v>
+      </c>
+      <c r="K11" s="1">
         <v>40000004</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>25</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="M11" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="N11" s="1">
+        <v>62</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O11" s="1">
         <v>6</v>
       </c>
-      <c r="O11" s="2"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C12" s="1">
         <v>3007</v>
       </c>
@@ -4847,38 +5155,41 @@
         <v>3</v>
       </c>
       <c r="E12" s="1">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1">
         <v>301</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G12" s="1">
         <v>50000</v>
       </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
       <c r="H12" s="1">
         <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J12" s="1">
+        <v>5</v>
+      </c>
+      <c r="K12" s="1">
         <v>40000005</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>3</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="M12" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="N12" s="1">
+        <v>62</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O12" s="1">
         <v>7</v>
       </c>
-      <c r="O12" s="2"/>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
       <c r="C13" s="1">
         <v>3008</v>
       </c>
@@ -4886,77 +5197,80 @@
         <v>3</v>
       </c>
       <c r="E13" s="1">
+        <v>3</v>
+      </c>
+      <c r="F13" s="1">
         <v>301</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13" s="1">
         <v>50000</v>
       </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
       <c r="H13" s="1">
         <v>0</v>
       </c>
       <c r="I13" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J13" s="1">
+        <v>5</v>
+      </c>
+      <c r="K13" s="1">
         <v>40000006</v>
       </c>
-      <c r="K13" s="1">
-        <v>1</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>59</v>
+      <c r="L13" s="1">
+        <v>1</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="N13" s="1">
+        <v>62</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O13" s="1">
         <v>8</v>
       </c>
-      <c r="O13" s="2"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="O14" s="2"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="O15" s="2"/>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="O16" s="2"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="O17" s="2"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="O18" s="2"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="O19" s="2"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="O20" s="2"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="O21" s="2"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="O22" s="2"/>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="O23" s="2"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="O24" s="2"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="O25" s="2"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="O26" s="2"/>
-    </row>
-    <row r="27" customFormat="1" customHeight="1" spans="1:15">
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P14" s="2"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P15" s="2"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P16" s="2"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P17" s="2"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P18" s="2"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P19" s="2"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P20" s="2"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P21" s="2"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P22" s="2"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P23" s="2"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P25" s="2"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P26" s="2"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="1:16">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -4971,9 +5285,10 @@
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
-      <c r="O27" s="2"/>
-    </row>
-    <row r="28" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O27" s="1"/>
+      <c r="P27" s="2"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="1:16">
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -4986,6 +5301,7 @@
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
     </row>
     <row r="29" customFormat="1" customHeight="1"/>
     <row r="30" customFormat="1" customHeight="1"/>
@@ -5018,7 +5334,676 @@
     <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O6:O27 C3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 P6:P27 C3:D5 F3:P5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P57"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5833333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.8333333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.4166666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5" style="1" customWidth="1"/>
+    <col min="11" max="12" width="13.75" style="1" customWidth="1"/>
+    <col min="13" max="13" width="42.75" style="1" customWidth="1"/>
+    <col min="14" max="14" width="21.4166666666667" style="1" customWidth="1"/>
+    <col min="15" max="15" width="19.625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5833333333333" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="2">
+        <v>5</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="2"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C6" s="1">
+        <v>11001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>11</v>
+      </c>
+      <c r="E6" s="1">
+        <v>11</v>
+      </c>
+      <c r="F6" s="1">
+        <v>301</v>
+      </c>
+      <c r="G6" s="1">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2"/>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P14" s="2"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P15" s="2"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P16" s="2"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P17" s="2"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P18" s="2"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P19" s="2"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P20" s="2"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P21" s="2"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P22" s="2"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P23" s="2"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P25" s="2"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P26" s="2"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="2"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="1:16">
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" customFormat="1" customHeight="1"/>
+    <row r="30" customFormat="1" customHeight="1"/>
+    <row r="31" customFormat="1" customHeight="1"/>
+    <row r="32" customFormat="1" customHeight="1"/>
+    <row r="33" customFormat="1" customHeight="1"/>
+    <row r="34" customFormat="1" customHeight="1"/>
+    <row r="35" customFormat="1" customHeight="1"/>
+    <row r="36" customFormat="1" customHeight="1"/>
+    <row r="37" customFormat="1" customHeight="1"/>
+    <row r="38" customFormat="1" customHeight="1"/>
+    <row r="39" customFormat="1" customHeight="1"/>
+    <row r="40" customFormat="1" customHeight="1"/>
+    <row r="41" customFormat="1" customHeight="1"/>
+    <row r="42" customFormat="1" customHeight="1"/>
+    <row r="43" customFormat="1" customHeight="1"/>
+    <row r="44" customFormat="1" customHeight="1"/>
+    <row r="45" customFormat="1" customHeight="1"/>
+    <row r="46" customFormat="1" customHeight="1"/>
+    <row r="47" customFormat="1" customHeight="1"/>
+    <row r="48" customFormat="1" customHeight="1"/>
+    <row r="49" customFormat="1" customHeight="1"/>
+    <row r="50" customFormat="1" customHeight="1"/>
+    <row r="51" customFormat="1" customHeight="1"/>
+    <row r="52" customFormat="1" customHeight="1"/>
+    <row r="53" customFormat="1" customHeight="1"/>
+    <row r="54" customFormat="1" customHeight="1"/>
+    <row r="55" customFormat="1" customHeight="1"/>
+    <row r="56" customFormat="1" customHeight="1"/>
+    <row r="57" customFormat="1" customHeight="1"/>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 P6:P27 C3:D5 F3:P5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P57"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="13.5833333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.8333333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.4166666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5" style="1" customWidth="1"/>
+    <col min="11" max="12" width="13.75" style="1" customWidth="1"/>
+    <col min="13" max="13" width="42.75" style="1" customWidth="1"/>
+    <col min="14" max="14" width="21.4166666666667" style="1" customWidth="1"/>
+    <col min="15" max="15" width="19.625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5833333333333" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="2">
+        <v>5</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="2"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C6" s="1">
+        <v>12001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>12</v>
+      </c>
+      <c r="E6" s="1">
+        <v>12</v>
+      </c>
+      <c r="F6" s="1">
+        <v>301</v>
+      </c>
+      <c r="G6" s="1">
+        <v>50000</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2"/>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P8" s="2"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P11" s="2"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P14" s="2"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P15" s="2"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P16" s="2"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P17" s="2"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P18" s="2"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P19" s="2"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P20" s="2"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P21" s="2"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P22" s="2"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P23" s="2"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P25" s="2"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P26" s="2"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="2"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="1:16">
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+    </row>
+    <row r="29" customFormat="1" customHeight="1"/>
+    <row r="30" customFormat="1" customHeight="1"/>
+    <row r="31" customFormat="1" customHeight="1"/>
+    <row r="32" customFormat="1" customHeight="1"/>
+    <row r="33" customFormat="1" customHeight="1"/>
+    <row r="34" customFormat="1" customHeight="1"/>
+    <row r="35" customFormat="1" customHeight="1"/>
+    <row r="36" customFormat="1" customHeight="1"/>
+    <row r="37" customFormat="1" customHeight="1"/>
+    <row r="38" customFormat="1" customHeight="1"/>
+    <row r="39" customFormat="1" customHeight="1"/>
+    <row r="40" customFormat="1" customHeight="1"/>
+    <row r="41" customFormat="1" customHeight="1"/>
+    <row r="42" customFormat="1" customHeight="1"/>
+    <row r="43" customFormat="1" customHeight="1"/>
+    <row r="44" customFormat="1" customHeight="1"/>
+    <row r="45" customFormat="1" customHeight="1"/>
+    <row r="46" customFormat="1" customHeight="1"/>
+    <row r="47" customFormat="1" customHeight="1"/>
+    <row r="48" customFormat="1" customHeight="1"/>
+    <row r="49" customFormat="1" customHeight="1"/>
+    <row r="50" customFormat="1" customHeight="1"/>
+    <row r="51" customFormat="1" customHeight="1"/>
+    <row r="52" customFormat="1" customHeight="1"/>
+    <row r="53" customFormat="1" customHeight="1"/>
+    <row r="54" customFormat="1" customHeight="1"/>
+    <row r="55" customFormat="1" customHeight="1"/>
+    <row r="56" customFormat="1" customHeight="1"/>
+    <row r="57" customFormat="1" customHeight="1"/>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 P6:P27 C3:D5 F3:P5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -216,7 +216,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="77">
   <si>
     <t>#</t>
   </si>
@@ -425,10 +425,28 @@
     <t>击杀1万个怪物，每日刷新</t>
   </si>
   <si>
-    <t>奖励10次抽奖次数</t>
-  </si>
-  <si>
-    <t>奖励5次抽奖次数</t>
+    <t>奖励10次抽奖</t>
+  </si>
+  <si>
+    <t>击杀5万个怪物（大佬福利1）</t>
+  </si>
+  <si>
+    <t>奖励5次抽奖</t>
+  </si>
+  <si>
+    <t>击杀5万个怪物（大佬福利2）</t>
+  </si>
+  <si>
+    <t>击杀5万个怪物（大佬福利3）</t>
+  </si>
+  <si>
+    <t>击杀5万个怪物（大佬福利4）</t>
+  </si>
+  <si>
+    <t>击杀5万个怪物（大佬福利5）</t>
+  </si>
+  <si>
+    <t>击杀5万个怪物（大佬福利6）</t>
   </si>
 </sst>
 </file>
@@ -2562,7 +2580,7 @@
     <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 P6:P27 C3:D5 F3:P5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="P6:P27 C3:P5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -4726,7 +4744,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 P11 C3:D5 F3:P5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="P11 C3:P5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -5334,7 +5352,7 @@
     <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 P6:P27 C3:D5 F3:P5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="P6:P27 C3:P5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -5517,7 +5535,7 @@
         <v>301</v>
       </c>
       <c r="G6" s="1">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -5669,7 +5687,7 @@
     <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 P6:P27 C3:D5 F3:P5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="P6:P27 C3:P5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -5731,8 +5749,8 @@
       <c r="I3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="2">
-        <v>5</v>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>9</v>
@@ -5851,7 +5869,7 @@
         <v>301</v>
       </c>
       <c r="G6" s="1">
-        <v>50000</v>
+        <v>50</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -5869,10 +5887,10 @@
         <v>0</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O6" s="1">
         <v>1</v>
@@ -5880,18 +5898,213 @@
       <c r="P6" s="2"/>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C7" s="1">
+        <v>12002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>12</v>
+      </c>
+      <c r="E7" s="1">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1">
+        <v>301</v>
+      </c>
+      <c r="G7" s="1">
+        <v>50</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O7" s="1">
+        <v>2</v>
+      </c>
       <c r="P7" s="2"/>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C8" s="1">
+        <v>12003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>12</v>
+      </c>
+      <c r="E8" s="1">
+        <v>12</v>
+      </c>
+      <c r="F8" s="1">
+        <v>301</v>
+      </c>
+      <c r="G8" s="1">
+        <v>50</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O8" s="1">
+        <v>3</v>
+      </c>
       <c r="P8" s="2"/>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C9" s="1">
+        <v>12004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>12</v>
+      </c>
+      <c r="E9" s="1">
+        <v>12</v>
+      </c>
+      <c r="F9" s="1">
+        <v>301</v>
+      </c>
+      <c r="G9" s="1">
+        <v>50</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O9" s="1">
+        <v>4</v>
+      </c>
       <c r="P9" s="2"/>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C10" s="1">
+        <v>12005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>12</v>
+      </c>
+      <c r="E10" s="1">
+        <v>12</v>
+      </c>
+      <c r="F10" s="1">
+        <v>301</v>
+      </c>
+      <c r="G10" s="1">
+        <v>50</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O10" s="1">
+        <v>5</v>
+      </c>
       <c r="P10" s="2"/>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="C11" s="1">
+        <v>12006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>12</v>
+      </c>
+      <c r="E11" s="1">
+        <v>12</v>
+      </c>
+      <c r="F11" s="1">
+        <v>301</v>
+      </c>
+      <c r="G11" s="1">
+        <v>50000</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>10000</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O11" s="1">
+        <v>6</v>
+      </c>
       <c r="P11" s="2"/>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
@@ -6003,7 +6216,7 @@
     <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 P6:P27 C3:D5 F3:P5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="P6:P27 C3:P5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="新入世界" sheetId="1" r:id="rId1"/>
@@ -38,10 +38,57 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
+    <author>Administrator</author>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="P3" authorId="0">
+    <comment ref="E3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+任务链Id</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0 指引累计任务
+1 福利杀怪任务
+2 每日循环任务</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -67,6 +114,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="E4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+任务链Id</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -77,7 +146,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="P3" authorId="0">
+    <comment ref="R3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -113,7 +182,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="P3" authorId="0">
+    <comment ref="R3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -149,7 +218,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="P3" authorId="0">
+    <comment ref="R3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -185,7 +254,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="P3" authorId="0">
+    <comment ref="R3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -216,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="87">
   <si>
     <t>#</t>
   </si>
@@ -227,7 +296,13 @@
     <t>GroupId</t>
   </si>
   <si>
-    <t>CalId</t>
+    <t>LinkId</t>
+  </si>
+  <si>
+    <t>TaskType</t>
+  </si>
+  <si>
+    <t>Net</t>
   </si>
   <si>
     <t>ConType</t>
@@ -416,10 +491,34 @@
     <t>奖励{1}个雄狮利爪</t>
   </si>
   <si>
+    <t>奖励{1}个虫卵</t>
+  </si>
+  <si>
     <t>奖励{1}个蛇皮</t>
   </si>
   <si>
     <t>奖励{1}个巨鳄之泪</t>
+  </si>
+  <si>
+    <t>奖励1个双减宠物</t>
+  </si>
+  <si>
+    <t>奖励{1}个乌鸦羽</t>
+  </si>
+  <si>
+    <t>奖励{1}个蝙蝠牙</t>
+  </si>
+  <si>
+    <t>奖励{1}个尸王之心</t>
+  </si>
+  <si>
+    <t>奖励{1}个树叶</t>
+  </si>
+  <si>
+    <t>奖励{1}个鱼鳞</t>
+  </si>
+  <si>
+    <t>奖励{1}个鹿血</t>
   </si>
   <si>
     <t>击杀1万个怪物，每日刷新</t>
@@ -1426,35 +1525,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P57"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5833333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.8333333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.4166666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" style="1" customWidth="1"/>
-    <col min="11" max="12" width="13.75" style="1" customWidth="1"/>
-    <col min="13" max="13" width="42.75" style="1" customWidth="1"/>
-    <col min="14" max="14" width="21.4166666666667" style="1" customWidth="1"/>
-    <col min="15" max="15" width="19.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5833333333333" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1"/>
+    <col min="5" max="7" width="11.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5833333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.8333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.4166666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5" style="1" customWidth="1"/>
+    <col min="13" max="14" width="13.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="42.75" style="1" customWidth="1"/>
+    <col min="16" max="16" width="21.4166666666667" style="1" customWidth="1"/>
+    <col min="17" max="17" width="19.625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5833333333333" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:16">
-      <c r="P1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:16">
-      <c r="P2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="3:16">
+    <row r="1" customHeight="1" spans="3:18">
+      <c r="R1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:18">
+      <c r="R2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="3:18">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1497,10 +1596,16 @@
       <c r="P3" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="3:16">
+      <c r="Q3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="3:18">
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -1538,51 +1643,63 @@
       <c r="O4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="2"/>
-    </row>
-    <row r="5" customHeight="1" spans="3:16">
+      <c r="P4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R4" s="2"/>
+    </row>
+    <row r="5" customHeight="1" spans="3:18">
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P5" s="2"/>
-    </row>
-    <row r="6" customHeight="1" spans="3:16">
+      <c r="R5" s="2"/>
+    </row>
+    <row r="6" customHeight="1" spans="3:18">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1593,38 +1710,44 @@
         <v>0</v>
       </c>
       <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
         <v>301</v>
       </c>
-      <c r="G6" s="1">
+      <c r="I6" s="1">
         <v>2</v>
       </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
       <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
         <v>20</v>
       </c>
-      <c r="K6" s="1">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1">
-        <v>1</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O6" s="1">
-        <v>1</v>
-      </c>
-      <c r="P6" s="2"/>
-    </row>
-    <row r="7" customHeight="1" spans="3:16">
+      <c r="M6" s="1">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
+      </c>
+      <c r="R6" s="2"/>
+    </row>
+    <row r="7" customHeight="1" spans="3:18">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1635,38 +1758,44 @@
         <v>0</v>
       </c>
       <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
         <v>4</v>
       </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
       <c r="I7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
         <v>20</v>
       </c>
-      <c r="K7" s="1">
+      <c r="M7" s="1">
         <v>2</v>
       </c>
-      <c r="L7" s="1">
-        <v>1</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O7" s="1">
+      <c r="N7" s="1">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q7" s="1">
         <v>2</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" customHeight="1" spans="3:16">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" customHeight="1" spans="3:18">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1677,38 +1806,44 @@
         <v>0</v>
       </c>
       <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
         <v>301</v>
       </c>
-      <c r="G8" s="1">
+      <c r="I8" s="1">
         <v>30</v>
       </c>
-      <c r="H8" s="1">
+      <c r="J8" s="1">
         <v>200000</v>
       </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1">
-        <v>5</v>
-      </c>
       <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>5</v>
+      </c>
+      <c r="M8" s="1">
         <v>5001</v>
       </c>
-      <c r="L8" s="1">
+      <c r="N8" s="1">
         <v>200</v>
       </c>
-      <c r="M8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O8" s="1">
+      <c r="O8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="1">
         <v>3</v>
       </c>
-      <c r="P8" s="2"/>
-    </row>
-    <row r="9" customHeight="1" spans="3:16">
+      <c r="R8" s="2"/>
+    </row>
+    <row r="9" customHeight="1" spans="3:18">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1719,38 +1854,44 @@
         <v>0</v>
       </c>
       <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
         <v>203</v>
       </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1">
         <v>200000</v>
       </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1">
-        <v>5</v>
-      </c>
       <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>5</v>
+      </c>
+      <c r="M9" s="1">
         <v>5002</v>
       </c>
-      <c r="L9" s="1">
+      <c r="N9" s="1">
         <v>10</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O9" s="1">
+      <c r="O9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q9" s="1">
         <v>4</v>
       </c>
-      <c r="P9" s="2"/>
-    </row>
-    <row r="10" customHeight="1" spans="3:16">
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" customHeight="1" spans="3:18">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1761,38 +1902,44 @@
         <v>0</v>
       </c>
       <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
         <v>202</v>
       </c>
-      <c r="G10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
       <c r="I10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
         <v>8</v>
       </c>
-      <c r="K10" s="1">
-        <v>1</v>
-      </c>
-      <c r="L10" s="1">
-        <v>1</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O10" s="1">
-        <v>5</v>
-      </c>
-      <c r="P10" s="2"/>
-    </row>
-    <row r="11" customHeight="1" spans="3:16">
+      <c r="M10" s="1">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1">
+        <v>1</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>5</v>
+      </c>
+      <c r="R10" s="2"/>
+    </row>
+    <row r="11" customHeight="1" spans="3:18">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1803,38 +1950,44 @@
         <v>0</v>
       </c>
       <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
         <v>10</v>
       </c>
-      <c r="G11" s="1">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
       <c r="I11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
         <v>8</v>
       </c>
-      <c r="K11" s="1">
+      <c r="M11" s="1">
         <v>10</v>
       </c>
-      <c r="L11" s="1">
-        <v>1</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O11" s="1">
+      <c r="N11" s="1">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q11" s="1">
         <v>6</v>
       </c>
-      <c r="P11" s="2"/>
-    </row>
-    <row r="12" customHeight="1" spans="3:16">
+      <c r="R11" s="2"/>
+    </row>
+    <row r="12" customHeight="1" spans="3:18">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1845,38 +1998,44 @@
         <v>0</v>
       </c>
       <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
         <v>100</v>
       </c>
-      <c r="G12" s="1">
-        <v>1</v>
-      </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1">
         <v>500000</v>
       </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>5</v>
-      </c>
       <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>5</v>
+      </c>
+      <c r="M12" s="1">
         <v>5001</v>
       </c>
-      <c r="L12" s="1">
+      <c r="N12" s="1">
         <v>500</v>
       </c>
-      <c r="M12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O12" s="1">
+      <c r="O12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="1">
         <v>7</v>
       </c>
-      <c r="P12" s="2"/>
-    </row>
-    <row r="13" customHeight="1" spans="3:16">
+      <c r="R12" s="2"/>
+    </row>
+    <row r="13" customHeight="1" spans="3:18">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1887,38 +2046,44 @@
         <v>0</v>
       </c>
       <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
         <v>102</v>
       </c>
-      <c r="G13" s="1">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1">
         <v>500000</v>
       </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>5</v>
-      </c>
       <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>5</v>
+      </c>
+      <c r="M13" s="1">
         <v>5001</v>
       </c>
-      <c r="L13" s="1">
+      <c r="N13" s="1">
         <v>500</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O13" s="1">
+      <c r="O13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q13" s="1">
         <v>8</v>
       </c>
-      <c r="P13" s="2"/>
-    </row>
-    <row r="14" customHeight="1" spans="3:16">
+      <c r="R13" s="2"/>
+    </row>
+    <row r="14" customHeight="1" spans="3:18">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1929,38 +2094,44 @@
         <v>0</v>
       </c>
       <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
         <v>301</v>
       </c>
-      <c r="G14" s="1">
+      <c r="I14" s="1">
         <v>100</v>
       </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
       <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
         <v>8</v>
       </c>
-      <c r="K14" s="1">
+      <c r="M14" s="1">
         <v>2</v>
       </c>
-      <c r="L14" s="1">
-        <v>1</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O14" s="1">
+      <c r="N14" s="1">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q14" s="1">
         <v>9</v>
       </c>
-      <c r="P14" s="2"/>
-    </row>
-    <row r="15" customHeight="1" spans="3:16">
+      <c r="R14" s="2"/>
+    </row>
+    <row r="15" customHeight="1" spans="3:18">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1971,38 +2142,44 @@
         <v>0</v>
       </c>
       <c r="F15" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1">
+        <v>5</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1">
         <v>500000</v>
       </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>5</v>
-      </c>
       <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>5</v>
+      </c>
+      <c r="M15" s="1">
         <v>5001</v>
       </c>
-      <c r="L15" s="1">
+      <c r="N15" s="1">
         <v>1000</v>
       </c>
-      <c r="M15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O15" s="1">
+      <c r="O15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q15" s="1">
         <v>10</v>
       </c>
-      <c r="P15" s="2"/>
-    </row>
-    <row r="16" customHeight="1" spans="3:16">
+      <c r="R15" s="2"/>
+    </row>
+    <row r="16" customHeight="1" spans="3:18">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -2013,38 +2190,44 @@
         <v>0</v>
       </c>
       <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
         <v>201</v>
       </c>
-      <c r="G16" s="1">
+      <c r="I16" s="1">
         <v>50</v>
       </c>
-      <c r="H16" s="1">
+      <c r="J16" s="1">
         <v>1000000</v>
       </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1">
-        <v>5</v>
-      </c>
       <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>5</v>
+      </c>
+      <c r="M16" s="1">
         <v>5002</v>
       </c>
-      <c r="L16" s="1">
+      <c r="N16" s="1">
         <v>20</v>
       </c>
-      <c r="M16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O16" s="1">
+      <c r="O16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q16" s="1">
         <v>11</v>
       </c>
-      <c r="P16" s="2"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:16">
+      <c r="R16" s="2"/>
+    </row>
+    <row r="17" customHeight="1" spans="1:18">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -2055,38 +2238,44 @@
         <v>0</v>
       </c>
       <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
         <v>300</v>
       </c>
-      <c r="G17" s="1">
-        <v>1</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
       <c r="I17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>5</v>
+      </c>
+      <c r="M17" s="1">
         <v>5002</v>
       </c>
-      <c r="L17" s="1">
+      <c r="N17" s="1">
         <v>30</v>
       </c>
-      <c r="M17" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O17" s="1">
+      <c r="O17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q17" s="1">
         <v>12</v>
       </c>
-      <c r="P17" s="2"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:16">
+      <c r="R17" s="2"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:18">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -2097,38 +2286,44 @@
         <v>0</v>
       </c>
       <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
         <v>301</v>
       </c>
-      <c r="G18" s="1">
+      <c r="I18" s="1">
         <v>500</v>
       </c>
-      <c r="H18" s="1">
+      <c r="J18" s="1">
         <v>1000000</v>
       </c>
-      <c r="I18" s="1">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1">
-        <v>5</v>
-      </c>
       <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>5</v>
+      </c>
+      <c r="M18" s="1">
         <v>5001</v>
       </c>
-      <c r="L18" s="1">
+      <c r="N18" s="1">
         <v>2000</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O18" s="1">
+      <c r="O18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q18" s="1">
         <v>13</v>
       </c>
-      <c r="P18" s="2"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:16">
+      <c r="R18" s="2"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:18">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -2139,38 +2334,44 @@
         <v>0</v>
       </c>
       <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
         <v>300</v>
       </c>
-      <c r="G19" s="1">
+      <c r="I19" s="1">
         <v>2</v>
       </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
-      <c r="I19" s="1">
-        <v>0</v>
-      </c>
       <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
         <v>8</v>
       </c>
-      <c r="K19" s="1">
+      <c r="M19" s="1">
         <v>3</v>
       </c>
-      <c r="L19" s="1">
-        <v>1</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O19" s="1">
+      <c r="N19" s="1">
+        <v>1</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q19" s="1">
         <v>14</v>
       </c>
-      <c r="P19" s="2"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:16">
+      <c r="R19" s="2"/>
+    </row>
+    <row r="20" customHeight="1" spans="1:18">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -2181,38 +2382,44 @@
         <v>0</v>
       </c>
       <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
         <v>301</v>
       </c>
-      <c r="G20" s="1">
+      <c r="I20" s="1">
         <v>1000</v>
       </c>
-      <c r="H20" s="1">
+      <c r="J20" s="1">
         <v>1000000</v>
       </c>
-      <c r="I20" s="1">
-        <v>0</v>
-      </c>
-      <c r="J20" s="1">
-        <v>5</v>
-      </c>
       <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>5</v>
+      </c>
+      <c r="M20" s="1">
         <v>5001</v>
       </c>
-      <c r="L20" s="1">
+      <c r="N20" s="1">
         <v>2000</v>
       </c>
-      <c r="M20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O20" s="1">
+      <c r="O20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q20" s="1">
         <v>15</v>
       </c>
-      <c r="P20" s="2"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:16">
+      <c r="R20" s="2"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:18">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -2223,38 +2430,44 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
         <v>300</v>
       </c>
-      <c r="G21" s="1">
+      <c r="I21" s="1">
         <v>3</v>
       </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0</v>
-      </c>
       <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
         <v>8</v>
       </c>
-      <c r="K21" s="1">
+      <c r="M21" s="1">
         <v>4</v>
       </c>
-      <c r="L21" s="1">
-        <v>1</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="O21" s="1">
+      <c r="N21" s="1">
+        <v>1</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q21" s="1">
         <v>16</v>
       </c>
-      <c r="P21" s="2"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:16">
+      <c r="R21" s="2"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:18">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -2265,38 +2478,44 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
         <v>301</v>
       </c>
-      <c r="G22" s="1">
+      <c r="I22" s="1">
         <v>3000</v>
       </c>
-      <c r="H22" s="1">
+      <c r="J22" s="1">
         <v>1000000</v>
       </c>
-      <c r="I22" s="1">
-        <v>0</v>
-      </c>
-      <c r="J22" s="1">
-        <v>5</v>
-      </c>
       <c r="K22" s="1">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>5</v>
+      </c>
+      <c r="M22" s="1">
         <v>5002</v>
       </c>
-      <c r="L22" s="1">
+      <c r="N22" s="1">
         <v>40</v>
       </c>
-      <c r="M22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O22" s="1">
+      <c r="O22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q22" s="1">
         <v>17</v>
       </c>
-      <c r="P22" s="2"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:16">
+      <c r="R22" s="2"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:18">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -2307,38 +2526,44 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
         <v>301</v>
       </c>
-      <c r="G23" s="1">
+      <c r="I23" s="1">
         <v>10000</v>
       </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
       <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
         <v>8</v>
       </c>
-      <c r="K23" s="1">
+      <c r="M23" s="1">
         <v>2</v>
       </c>
-      <c r="L23" s="1">
-        <v>1</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O23" s="1">
+      <c r="N23" s="1">
+        <v>1</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q23" s="1">
         <v>18</v>
       </c>
-      <c r="P23" s="2"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:16">
+      <c r="R23" s="2"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:18">
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -2349,38 +2574,44 @@
         <v>0</v>
       </c>
       <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
         <v>301</v>
       </c>
-      <c r="G24" s="1">
+      <c r="I24" s="1">
         <v>20000</v>
       </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="1">
-        <v>0</v>
-      </c>
       <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
         <v>8</v>
       </c>
-      <c r="K24" s="1">
+      <c r="M24" s="1">
         <v>3</v>
       </c>
-      <c r="L24" s="1">
-        <v>1</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O24" s="1">
+      <c r="N24" s="1">
+        <v>1</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q24" s="1">
         <v>19</v>
       </c>
-      <c r="P24" s="2"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:16">
+      <c r="R24" s="2"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:18">
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -2391,38 +2622,44 @@
         <v>0</v>
       </c>
       <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
         <v>301</v>
       </c>
-      <c r="G25" s="1">
+      <c r="I25" s="1">
         <v>30000</v>
       </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1">
-        <v>0</v>
-      </c>
       <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
         <v>8</v>
       </c>
-      <c r="K25" s="1">
+      <c r="M25" s="1">
         <v>4</v>
       </c>
-      <c r="L25" s="1">
-        <v>1</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="O25" s="1">
+      <c r="N25" s="1">
+        <v>1</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q25" s="1">
         <v>20</v>
       </c>
-      <c r="P25" s="2"/>
-    </row>
-    <row r="26" customHeight="1" spans="1:16">
+      <c r="R25" s="2"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:18">
       <c r="C26" s="1">
         <v>21</v>
       </c>
@@ -2433,38 +2670,44 @@
         <v>0</v>
       </c>
       <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
         <v>301</v>
       </c>
-      <c r="G26" s="1">
+      <c r="I26" s="1">
         <v>50000</v>
       </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="I26" s="1">
-        <v>0</v>
-      </c>
       <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
         <v>8</v>
       </c>
-      <c r="K26" s="1">
+      <c r="M26" s="1">
         <v>2</v>
       </c>
-      <c r="L26" s="1">
-        <v>1</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O26" s="1">
+      <c r="N26" s="1">
+        <v>1</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q26" s="1">
         <v>21</v>
       </c>
-      <c r="P26" s="2"/>
-    </row>
-    <row r="27" customFormat="1" customHeight="1" spans="1:16">
+      <c r="R26" s="2"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="1:18">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1">
@@ -2477,38 +2720,44 @@
         <v>0</v>
       </c>
       <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
         <v>301</v>
       </c>
-      <c r="G27" s="1">
+      <c r="I27" s="1">
         <v>100000</v>
       </c>
-      <c r="H27" s="1">
-        <v>0</v>
-      </c>
-      <c r="I27" s="1">
-        <v>0</v>
-      </c>
       <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
         <v>8</v>
       </c>
-      <c r="K27" s="1">
+      <c r="M27" s="1">
         <v>3</v>
       </c>
-      <c r="L27" s="1">
-        <v>1</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O27" s="1">
+      <c r="N27" s="1">
+        <v>1</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q27" s="1">
         <v>22</v>
       </c>
-      <c r="P27" s="2"/>
-    </row>
-    <row r="28" customFormat="1" customHeight="1" spans="1:16">
+      <c r="R27" s="2"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="1:18">
       <c r="C28" s="1">
         <v>23</v>
       </c>
@@ -2519,33 +2768,39 @@
         <v>0</v>
       </c>
       <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
         <v>301</v>
       </c>
-      <c r="G28" s="1">
+      <c r="I28" s="1">
         <v>150000</v>
       </c>
-      <c r="H28" s="1">
-        <v>0</v>
-      </c>
-      <c r="I28" s="1">
-        <v>0</v>
-      </c>
       <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
         <v>8</v>
       </c>
-      <c r="K28" s="1">
+      <c r="M28" s="1">
         <v>4</v>
       </c>
-      <c r="L28" s="1">
-        <v>1</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="O28" s="1">
+      <c r="N28" s="1">
+        <v>1</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q28" s="1">
         <v>23</v>
       </c>
     </row>
@@ -2580,7 +2835,7 @@
     <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="P6:P27 C3:P5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E3 F3 G3 C4:D4 E4 F4 G4 C5:E5 F5 G5 R6:R27 H3:R5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -2593,25 +2848,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P57"/>
+  <dimension ref="C1:R57"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5" customWidth="1"/>
-    <col min="14" max="14" width="23.9166666666667" customWidth="1"/>
+    <col min="5" max="7" width="11.5" style="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5" customWidth="1"/>
+    <col min="16" max="16" width="23.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -2654,10 +2909,16 @@
       <c r="P3" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -2695,51 +2956,63 @@
       <c r="O4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="2"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R4" s="2"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P5" s="2"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="R5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -2750,37 +3023,43 @@
         <v>0</v>
       </c>
       <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
         <v>301</v>
       </c>
-      <c r="G6" s="1">
+      <c r="I6" s="1">
         <v>500</v>
       </c>
-      <c r="H6" s="1">
+      <c r="J6" s="1">
         <v>1000000</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>5</v>
-      </c>
       <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>5</v>
+      </c>
+      <c r="M6" s="1">
         <v>5001</v>
       </c>
-      <c r="L6" s="1">
+      <c r="N6" s="1">
         <v>1000</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="O6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -2791,37 +3070,43 @@
         <v>0</v>
       </c>
       <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
         <v>301</v>
       </c>
-      <c r="G7" s="1">
+      <c r="I7" s="1">
         <v>1000</v>
       </c>
-      <c r="H7" s="1">
+      <c r="J7" s="1">
         <v>1000000</v>
       </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
-        <v>5</v>
-      </c>
       <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>5</v>
+      </c>
+      <c r="M7" s="1">
         <v>5001</v>
       </c>
-      <c r="L7" s="1">
+      <c r="N7" s="1">
         <v>1000</v>
       </c>
-      <c r="M7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O7" s="1">
+      <c r="O7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -2832,37 +3117,43 @@
         <v>0</v>
       </c>
       <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
         <v>301</v>
       </c>
-      <c r="G8" s="1">
+      <c r="I8" s="1">
         <v>2000</v>
       </c>
-      <c r="H8" s="1">
+      <c r="J8" s="1">
         <v>1000000</v>
       </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1">
-        <v>5</v>
-      </c>
       <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>5</v>
+      </c>
+      <c r="M8" s="1">
         <v>5001</v>
       </c>
-      <c r="L8" s="1">
+      <c r="N8" s="1">
         <v>1000</v>
       </c>
-      <c r="M8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O8" s="1">
+      <c r="O8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -2873,37 +3164,43 @@
         <v>0</v>
       </c>
       <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
         <v>301</v>
       </c>
-      <c r="G9" s="1">
+      <c r="I9" s="1">
         <v>3000</v>
       </c>
-      <c r="H9" s="1">
+      <c r="J9" s="1">
         <v>1000000</v>
       </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1">
-        <v>5</v>
-      </c>
       <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>5</v>
+      </c>
+      <c r="M9" s="1">
         <v>5001</v>
       </c>
-      <c r="L9" s="1">
+      <c r="N9" s="1">
         <v>1000</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O9" s="1">
+      <c r="O9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q9" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
@@ -2914,37 +3211,43 @@
         <v>0</v>
       </c>
       <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
         <v>301</v>
       </c>
-      <c r="G10" s="1">
+      <c r="I10" s="1">
         <v>5000</v>
       </c>
-      <c r="H10" s="1">
+      <c r="J10" s="1">
         <v>1000000</v>
       </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1">
-        <v>5</v>
-      </c>
       <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>5</v>
+      </c>
+      <c r="M10" s="1">
         <v>5001</v>
       </c>
-      <c r="L10" s="1">
+      <c r="N10" s="1">
         <v>1000</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O10" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="O10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
@@ -2955,38 +3258,44 @@
         <v>0</v>
       </c>
       <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
         <v>203</v>
       </c>
-      <c r="G11" s="1">
+      <c r="I11" s="1">
         <v>10</v>
       </c>
-      <c r="H11" s="1">
+      <c r="J11" s="1">
         <v>1000000</v>
       </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1">
-        <v>5</v>
-      </c>
       <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <v>5</v>
+      </c>
+      <c r="M11" s="1">
         <v>5001</v>
       </c>
-      <c r="L11" s="1">
+      <c r="N11" s="1">
         <v>2000</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O11" s="1">
+      <c r="O11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q11" s="1">
         <v>6</v>
       </c>
-      <c r="P11" s="2"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="R11" s="2"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
@@ -2997,37 +3306,43 @@
         <v>0</v>
       </c>
       <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
         <v>202</v>
       </c>
-      <c r="G12" s="1">
+      <c r="I12" s="1">
         <v>10</v>
       </c>
-      <c r="H12" s="1">
+      <c r="J12" s="1">
         <v>1000000</v>
       </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>5</v>
-      </c>
       <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>5</v>
+      </c>
+      <c r="M12" s="1">
         <v>5002</v>
       </c>
-      <c r="L12" s="1">
+      <c r="N12" s="1">
         <v>20</v>
       </c>
-      <c r="M12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O12" s="1">
+      <c r="O12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q12" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C13" s="1">
         <v>1008</v>
       </c>
@@ -3038,37 +3353,43 @@
         <v>0</v>
       </c>
       <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
         <v>301</v>
       </c>
-      <c r="G13" s="1">
+      <c r="I13" s="1">
         <v>7000</v>
       </c>
-      <c r="H13" s="1">
+      <c r="J13" s="1">
         <v>1000000</v>
       </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
         <v>8</v>
       </c>
-      <c r="K13" s="1">
+      <c r="M13" s="1">
         <v>11</v>
       </c>
-      <c r="L13" s="1">
+      <c r="N13" s="1">
         <v>10</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O13" s="1">
+      <c r="O13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q13" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C14" s="1">
         <v>1009</v>
       </c>
@@ -3079,37 +3400,43 @@
         <v>0</v>
       </c>
       <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
         <v>201</v>
       </c>
-      <c r="G14" s="1">
+      <c r="I14" s="1">
         <v>100</v>
       </c>
-      <c r="H14" s="1">
+      <c r="J14" s="1">
         <v>1000000</v>
       </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>5</v>
-      </c>
       <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>5</v>
+      </c>
+      <c r="M14" s="1">
         <v>5001</v>
       </c>
-      <c r="L14" s="1">
+      <c r="N14" s="1">
         <v>2000</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O14" s="1">
+      <c r="O14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C15" s="1">
         <v>1010</v>
       </c>
@@ -3120,37 +3447,43 @@
         <v>0</v>
       </c>
       <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
         <v>205</v>
       </c>
-      <c r="G15" s="1">
-        <v>1</v>
-      </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1">
         <v>1000000</v>
       </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>5</v>
-      </c>
       <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>5</v>
+      </c>
+      <c r="M15" s="1">
         <v>5002</v>
       </c>
-      <c r="L15" s="1">
+      <c r="N15" s="1">
         <v>20</v>
       </c>
-      <c r="M15" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="1">
+      <c r="O15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q15" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="16" s="3" customFormat="1" customHeight="1" spans="3:16">
+    <row r="16" s="3" customFormat="1" customHeight="1" spans="3:18">
       <c r="C16" s="1">
         <v>1011</v>
       </c>
@@ -3160,38 +3493,44 @@
       <c r="E16" s="1">
         <v>0</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3">
         <v>203</v>
       </c>
-      <c r="G16" s="3">
+      <c r="I16" s="3">
         <v>20</v>
       </c>
-      <c r="H16" s="1">
+      <c r="J16" s="1">
         <v>1500000</v>
       </c>
-      <c r="I16" s="3">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3">
-        <v>5</v>
-      </c>
-      <c r="K16" s="1">
+      <c r="K16" s="3">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3">
+        <v>5</v>
+      </c>
+      <c r="M16" s="1">
         <v>5001</v>
       </c>
-      <c r="L16" s="3">
+      <c r="N16" s="3">
         <v>3000</v>
       </c>
-      <c r="M16" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O16" s="1">
+      <c r="O16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q16" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C17" s="1">
         <v>1012</v>
       </c>
@@ -3202,37 +3541,43 @@
         <v>0</v>
       </c>
       <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
         <v>202</v>
       </c>
-      <c r="G17" s="1">
+      <c r="I17" s="1">
         <v>20</v>
       </c>
-      <c r="H17" s="1">
+      <c r="J17" s="1">
         <v>1500000</v>
       </c>
-      <c r="I17" s="1">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
-        <v>5</v>
-      </c>
       <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>5</v>
+      </c>
+      <c r="M17" s="1">
         <v>5002</v>
       </c>
-      <c r="L17" s="1">
+      <c r="N17" s="1">
         <v>30</v>
       </c>
-      <c r="M17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O17" s="1">
+      <c r="O17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q17" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C18" s="1">
         <v>1013</v>
       </c>
@@ -3243,37 +3588,43 @@
         <v>0</v>
       </c>
       <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
         <v>301</v>
       </c>
-      <c r="G18" s="1">
+      <c r="I18" s="1">
         <v>10000</v>
       </c>
-      <c r="H18" s="1">
+      <c r="J18" s="1">
         <v>1500000</v>
       </c>
-      <c r="I18" s="1">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1">
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
         <v>8</v>
       </c>
-      <c r="K18" s="1">
+      <c r="M18" s="1">
         <v>11</v>
       </c>
-      <c r="L18" s="1">
+      <c r="N18" s="1">
         <v>15</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O18" s="1">
+      <c r="O18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q18" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C19" s="1">
         <v>1014</v>
       </c>
@@ -3284,37 +3635,43 @@
         <v>0</v>
       </c>
       <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
         <v>201</v>
       </c>
-      <c r="G19" s="1">
+      <c r="I19" s="1">
         <v>800</v>
       </c>
-      <c r="H19" s="1">
+      <c r="J19" s="1">
         <v>1500000</v>
       </c>
-      <c r="I19" s="1">
-        <v>0</v>
-      </c>
-      <c r="J19" s="1">
-        <v>5</v>
-      </c>
       <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>5</v>
+      </c>
+      <c r="M19" s="1">
         <v>5001</v>
       </c>
-      <c r="L19" s="1">
+      <c r="N19" s="1">
         <v>3000</v>
       </c>
-      <c r="M19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O19" s="1">
+      <c r="O19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q19" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C20" s="1">
         <v>1015</v>
       </c>
@@ -3325,37 +3682,43 @@
         <v>0</v>
       </c>
       <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
         <v>101</v>
       </c>
-      <c r="G20" s="1">
-        <v>5</v>
-      </c>
-      <c r="H20" s="1">
+      <c r="I20" s="1">
+        <v>5</v>
+      </c>
+      <c r="J20" s="1">
         <v>1500000</v>
       </c>
-      <c r="I20" s="1">
-        <v>0</v>
-      </c>
-      <c r="J20" s="1">
-        <v>5</v>
-      </c>
       <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>5</v>
+      </c>
+      <c r="M20" s="1">
         <v>5002</v>
       </c>
-      <c r="L20" s="1">
+      <c r="N20" s="1">
         <v>30</v>
       </c>
-      <c r="M20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O20" s="1">
+      <c r="O20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q20" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="21" s="3" customFormat="1" customHeight="1" spans="3:15">
+    <row r="21" s="3" customFormat="1" customHeight="1" spans="3:17">
       <c r="C21" s="1">
         <v>1016</v>
       </c>
@@ -3365,38 +3728,44 @@
       <c r="E21" s="1">
         <v>0</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>203</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>35</v>
       </c>
-      <c r="H21" s="1">
+      <c r="J21" s="1">
         <v>1500000</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3">
-        <v>5</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
+        <v>5</v>
+      </c>
+      <c r="M21" s="1">
         <v>5001</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>4000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O21" s="1">
+      <c r="O21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q21" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C22" s="1">
         <v>1017</v>
       </c>
@@ -3407,37 +3776,43 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
         <v>202</v>
       </c>
-      <c r="G22" s="1">
+      <c r="I22" s="1">
         <v>35</v>
       </c>
-      <c r="H22" s="1">
+      <c r="J22" s="1">
         <v>1500000</v>
       </c>
-      <c r="I22" s="1">
-        <v>0</v>
-      </c>
-      <c r="J22" s="1">
-        <v>5</v>
-      </c>
       <c r="K22" s="1">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>5</v>
+      </c>
+      <c r="M22" s="1">
         <v>5002</v>
       </c>
-      <c r="L22" s="1">
+      <c r="N22" s="1">
         <v>40</v>
       </c>
-      <c r="M22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O22" s="1">
+      <c r="O22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q22" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C23" s="1">
         <v>1018</v>
       </c>
@@ -3448,37 +3823,43 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
         <v>301</v>
       </c>
-      <c r="G23" s="1">
+      <c r="I23" s="1">
         <v>20000</v>
       </c>
-      <c r="H23" s="1">
+      <c r="J23" s="1">
         <v>1500000</v>
       </c>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1">
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
         <v>8</v>
       </c>
-      <c r="K23" s="1">
+      <c r="M23" s="1">
         <v>11</v>
       </c>
-      <c r="L23" s="1">
+      <c r="N23" s="1">
         <v>20</v>
       </c>
-      <c r="M23" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O23" s="1">
+      <c r="O23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q23" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C24" s="1">
         <v>1019</v>
       </c>
@@ -3489,37 +3870,43 @@
         <v>0</v>
       </c>
       <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
         <v>201</v>
       </c>
-      <c r="G24" s="1">
+      <c r="I24" s="1">
         <v>2000</v>
       </c>
-      <c r="H24" s="1">
+      <c r="J24" s="1">
         <v>1500000</v>
       </c>
-      <c r="I24" s="1">
-        <v>0</v>
-      </c>
-      <c r="J24" s="1">
-        <v>5</v>
-      </c>
       <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>5</v>
+      </c>
+      <c r="M24" s="1">
         <v>5001</v>
       </c>
-      <c r="L24" s="1">
+      <c r="N24" s="1">
         <v>4000</v>
       </c>
-      <c r="M24" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O24" s="1">
+      <c r="O24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q24" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C25" s="1">
         <v>1020</v>
       </c>
@@ -3530,37 +3917,43 @@
         <v>0</v>
       </c>
       <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
         <v>205</v>
       </c>
-      <c r="G25" s="1">
+      <c r="I25" s="1">
         <v>3</v>
       </c>
-      <c r="H25" s="1">
+      <c r="J25" s="1">
         <v>1000000</v>
       </c>
-      <c r="I25" s="1">
-        <v>0</v>
-      </c>
-      <c r="J25" s="1">
-        <v>5</v>
-      </c>
       <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>5</v>
+      </c>
+      <c r="M25" s="1">
         <v>5002</v>
       </c>
-      <c r="L25" s="1">
+      <c r="N25" s="1">
         <v>40</v>
       </c>
-      <c r="M25" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O25" s="1">
+      <c r="O25" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q25" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="26" s="3" customFormat="1" customHeight="1" spans="3:15">
+    <row r="26" s="3" customFormat="1" customHeight="1" spans="3:17">
       <c r="C26" s="1">
         <v>1021</v>
       </c>
@@ -3570,38 +3963,44 @@
       <c r="E26" s="1">
         <v>0</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>203</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>55</v>
       </c>
-      <c r="H26" s="1">
+      <c r="J26" s="1">
         <v>1500000</v>
       </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3">
-        <v>5</v>
-      </c>
-      <c r="K26" s="1">
+      <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
+        <v>5</v>
+      </c>
+      <c r="M26" s="1">
         <v>5001</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>5000</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O26" s="1">
+      <c r="O26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q26" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C27" s="1">
         <v>1022</v>
       </c>
@@ -3612,37 +4011,43 @@
         <v>0</v>
       </c>
       <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
         <v>202</v>
       </c>
-      <c r="G27" s="1">
+      <c r="I27" s="1">
         <v>55</v>
       </c>
-      <c r="H27" s="5">
+      <c r="J27" s="5">
         <v>2000000</v>
       </c>
-      <c r="I27" s="1">
-        <v>0</v>
-      </c>
-      <c r="J27" s="1">
-        <v>5</v>
-      </c>
       <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>5</v>
+      </c>
+      <c r="M27" s="1">
         <v>5002</v>
       </c>
-      <c r="L27" s="1">
+      <c r="N27" s="1">
         <v>50</v>
       </c>
-      <c r="M27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O27" s="1">
+      <c r="O27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q27" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C28" s="1">
         <v>1023</v>
       </c>
@@ -3653,1098 +4058,1324 @@
         <v>0</v>
       </c>
       <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
         <v>301</v>
       </c>
-      <c r="G28" s="1">
+      <c r="I28" s="1">
         <v>50000</v>
       </c>
-      <c r="H28" s="5">
+      <c r="J28" s="5">
         <v>2000000</v>
       </c>
-      <c r="I28" s="1">
-        <v>0</v>
-      </c>
-      <c r="J28" s="1">
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
         <v>8</v>
       </c>
-      <c r="K28" s="1">
+      <c r="M28" s="1">
         <v>11</v>
       </c>
-      <c r="L28" s="1">
+      <c r="N28" s="1">
         <v>25</v>
       </c>
-      <c r="M28" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O28" s="1">
+      <c r="O28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q28" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C29" s="1">
         <v>1024</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
       </c>
-      <c r="E29"/>
+      <c r="E29" s="1">
+        <v>0</v>
+      </c>
       <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
         <v>201</v>
       </c>
-      <c r="G29" s="1">
+      <c r="I29" s="1">
         <v>5000</v>
       </c>
-      <c r="H29" s="5">
+      <c r="J29" s="5">
         <v>2000000</v>
       </c>
-      <c r="I29" s="1">
-        <v>0</v>
-      </c>
-      <c r="J29" s="1">
-        <v>5</v>
-      </c>
       <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>5</v>
+      </c>
+      <c r="M29" s="1">
         <v>5001</v>
       </c>
-      <c r="L29" s="1">
+      <c r="N29" s="1">
         <v>5000</v>
       </c>
-      <c r="M29" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O29" s="1">
+      <c r="O29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q29" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C30" s="1">
         <v>1025</v>
       </c>
       <c r="D30" s="1">
         <v>2</v>
       </c>
-      <c r="E30"/>
+      <c r="E30" s="1">
+        <v>0</v>
+      </c>
       <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
         <v>101</v>
       </c>
-      <c r="G30" s="1">
+      <c r="I30" s="1">
         <v>10</v>
       </c>
-      <c r="H30" s="5">
+      <c r="J30" s="5">
         <v>2000000</v>
       </c>
-      <c r="I30" s="1">
-        <v>0</v>
-      </c>
-      <c r="J30" s="1">
-        <v>5</v>
-      </c>
       <c r="K30" s="1">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1">
+        <v>5</v>
+      </c>
+      <c r="M30" s="1">
         <v>5002</v>
       </c>
-      <c r="L30" s="1">
+      <c r="N30" s="1">
         <v>50</v>
       </c>
-      <c r="M30" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O30" s="1">
+      <c r="O30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q30" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C31" s="1">
         <v>1026</v>
       </c>
       <c r="D31" s="3">
         <v>2</v>
       </c>
-      <c r="E31"/>
-      <c r="F31" s="3">
+      <c r="E31" s="1">
+        <v>0</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3">
         <v>203</v>
       </c>
-      <c r="G31" s="3">
+      <c r="I31" s="3">
         <v>85</v>
       </c>
-      <c r="H31" s="5">
+      <c r="J31" s="5">
         <v>2000000</v>
       </c>
-      <c r="I31" s="3">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3">
-        <v>5</v>
-      </c>
-      <c r="K31" s="1">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3">
+        <v>5</v>
+      </c>
+      <c r="M31" s="1">
         <v>5001</v>
       </c>
-      <c r="L31" s="3">
+      <c r="N31" s="3">
         <v>6000</v>
       </c>
-      <c r="M31" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O31" s="1">
+      <c r="O31" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q31" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C32" s="1">
         <v>1027</v>
       </c>
       <c r="D32" s="1">
         <v>2</v>
       </c>
-      <c r="E32"/>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
       <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
         <v>202</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>85</v>
       </c>
-      <c r="H32" s="5">
+      <c r="J32" s="5">
         <v>2000000</v>
       </c>
-      <c r="I32" s="1">
-        <v>0</v>
-      </c>
-      <c r="J32" s="1">
-        <v>5</v>
-      </c>
       <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1">
+        <v>5</v>
+      </c>
+      <c r="M32" s="1">
         <v>5002</v>
       </c>
-      <c r="L32" s="1">
+      <c r="N32" s="1">
         <v>50</v>
       </c>
-      <c r="M32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N32" s="1" t="s">
+      <c r="O32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q32" s="1">
         <v>27</v>
       </c>
-      <c r="O32" s="1">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:15">
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C33" s="1">
         <v>1028</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
       </c>
-      <c r="E33"/>
+      <c r="E33" s="1">
+        <v>0</v>
+      </c>
       <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
         <v>301</v>
       </c>
-      <c r="G33" s="1">
+      <c r="I33" s="1">
         <v>100000</v>
       </c>
-      <c r="H33" s="5">
+      <c r="J33" s="5">
         <v>2000000</v>
       </c>
-      <c r="I33" s="1">
-        <v>0</v>
-      </c>
-      <c r="J33" s="1">
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
         <v>8</v>
       </c>
-      <c r="K33" s="1">
+      <c r="M33" s="1">
         <v>11</v>
       </c>
-      <c r="L33" s="1">
+      <c r="N33" s="1">
         <v>30</v>
       </c>
-      <c r="M33" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O33" s="1">
+      <c r="O33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q33" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C34" s="1">
         <v>1029</v>
       </c>
       <c r="D34" s="1">
         <v>2</v>
       </c>
-      <c r="E34"/>
+      <c r="E34" s="1">
+        <v>0</v>
+      </c>
       <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
         <v>201</v>
       </c>
-      <c r="G34" s="1">
+      <c r="I34" s="1">
         <v>10000</v>
       </c>
-      <c r="H34" s="5">
+      <c r="J34" s="5">
         <v>2000000</v>
       </c>
-      <c r="I34" s="1">
-        <v>0</v>
-      </c>
-      <c r="J34" s="1">
-        <v>5</v>
-      </c>
       <c r="K34" s="1">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1">
+        <v>5</v>
+      </c>
+      <c r="M34" s="1">
         <v>5001</v>
       </c>
-      <c r="L34" s="1">
+      <c r="N34" s="1">
         <v>6000</v>
       </c>
-      <c r="M34" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O34" s="1">
+      <c r="O34" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q34" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C35" s="1">
         <v>1030</v>
       </c>
       <c r="D35" s="1">
         <v>2</v>
       </c>
-      <c r="E35"/>
+      <c r="E35" s="1">
+        <v>0</v>
+      </c>
       <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
         <v>205</v>
       </c>
-      <c r="G35" s="1">
-        <v>5</v>
-      </c>
-      <c r="H35" s="1">
+      <c r="I35" s="1">
+        <v>5</v>
+      </c>
+      <c r="J35" s="1">
         <v>1000000</v>
       </c>
-      <c r="I35" s="1">
-        <v>0</v>
-      </c>
-      <c r="J35" s="1">
-        <v>5</v>
-      </c>
       <c r="K35" s="1">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <v>5</v>
+      </c>
+      <c r="M35" s="1">
         <v>5002</v>
       </c>
-      <c r="L35" s="1">
+      <c r="N35" s="1">
         <v>50</v>
       </c>
-      <c r="M35" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O35" s="1">
+      <c r="O35" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q35" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C36" s="1">
         <v>1031</v>
       </c>
       <c r="D36" s="3">
         <v>2</v>
       </c>
-      <c r="E36"/>
-      <c r="F36" s="3">
+      <c r="E36" s="1">
+        <v>0</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3">
         <v>203</v>
       </c>
-      <c r="G36" s="3">
+      <c r="I36" s="3">
         <v>120</v>
       </c>
-      <c r="H36" s="5">
+      <c r="J36" s="5">
         <v>2000000</v>
       </c>
-      <c r="I36" s="3">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3">
-        <v>5</v>
-      </c>
-      <c r="K36" s="1">
+      <c r="K36" s="3">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3">
+        <v>5</v>
+      </c>
+      <c r="M36" s="1">
         <v>5001</v>
       </c>
-      <c r="L36" s="3">
+      <c r="N36" s="3">
         <v>7000</v>
       </c>
-      <c r="M36" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O36" s="1">
+      <c r="O36" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q36" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C37" s="1">
         <v>1032</v>
       </c>
       <c r="D37" s="1">
         <v>2</v>
       </c>
-      <c r="E37"/>
+      <c r="E37" s="1">
+        <v>0</v>
+      </c>
       <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
         <v>202</v>
       </c>
-      <c r="G37" s="1">
+      <c r="I37" s="1">
         <v>120</v>
       </c>
-      <c r="H37" s="5">
+      <c r="J37" s="5">
         <v>2000000</v>
       </c>
-      <c r="I37" s="1">
-        <v>0</v>
-      </c>
-      <c r="J37" s="1">
-        <v>5</v>
-      </c>
       <c r="K37" s="1">
+        <v>0</v>
+      </c>
+      <c r="L37" s="1">
+        <v>5</v>
+      </c>
+      <c r="M37" s="1">
         <v>5002</v>
       </c>
-      <c r="L37" s="1">
+      <c r="N37" s="1">
         <v>50</v>
       </c>
-      <c r="M37" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O37" s="1">
+      <c r="O37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q37" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C38" s="1">
         <v>1033</v>
       </c>
       <c r="D38" s="1">
         <v>2</v>
       </c>
-      <c r="E38"/>
+      <c r="E38" s="1">
+        <v>0</v>
+      </c>
       <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
         <v>301</v>
       </c>
-      <c r="G38" s="1">
+      <c r="I38" s="1">
         <v>200000</v>
       </c>
-      <c r="H38" s="5">
+      <c r="J38" s="5">
         <v>2000000</v>
       </c>
-      <c r="I38" s="1">
-        <v>0</v>
-      </c>
-      <c r="J38" s="1">
+      <c r="K38" s="1">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1">
         <v>8</v>
       </c>
-      <c r="K38" s="1">
+      <c r="M38" s="1">
         <v>11</v>
       </c>
-      <c r="L38" s="1">
+      <c r="N38" s="1">
         <v>35</v>
       </c>
-      <c r="M38" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O38" s="1">
+      <c r="O38" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q38" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C39" s="1">
         <v>1034</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
       </c>
-      <c r="E39"/>
+      <c r="E39" s="1">
+        <v>0</v>
+      </c>
       <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
         <v>201</v>
       </c>
-      <c r="G39" s="1">
+      <c r="I39" s="1">
         <v>20000</v>
       </c>
-      <c r="H39" s="5">
+      <c r="J39" s="5">
         <v>2000000</v>
       </c>
-      <c r="I39" s="1">
-        <v>0</v>
-      </c>
-      <c r="J39" s="1">
-        <v>5</v>
-      </c>
       <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1">
+        <v>5</v>
+      </c>
+      <c r="M39" s="1">
         <v>5001</v>
       </c>
-      <c r="L39" s="1">
+      <c r="N39" s="1">
         <v>7000</v>
       </c>
-      <c r="M39" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O39" s="1">
+      <c r="O39" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q39" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:17">
       <c r="C40" s="1">
         <v>1035</v>
       </c>
       <c r="D40" s="1">
         <v>2</v>
       </c>
-      <c r="E40"/>
+      <c r="E40" s="1">
+        <v>0</v>
+      </c>
       <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
         <v>101</v>
       </c>
-      <c r="G40" s="1">
+      <c r="I40" s="1">
         <v>50</v>
       </c>
-      <c r="H40" s="5">
+      <c r="J40" s="5">
         <v>2000000</v>
       </c>
-      <c r="I40" s="1">
-        <v>0</v>
-      </c>
-      <c r="J40" s="1">
-        <v>5</v>
-      </c>
       <c r="K40" s="1">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1">
+        <v>5</v>
+      </c>
+      <c r="M40" s="1">
         <v>5002</v>
       </c>
-      <c r="L40" s="1">
+      <c r="N40" s="1">
         <v>50</v>
       </c>
-      <c r="M40" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O40" s="1">
+      <c r="O40" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q40" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="3:15">
+    <row r="41" customHeight="1" spans="3:17">
       <c r="C41" s="1">
         <v>1036</v>
       </c>
       <c r="D41" s="3">
         <v>2</v>
       </c>
-      <c r="E41"/>
-      <c r="F41" s="3">
+      <c r="E41" s="1">
+        <v>0</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>203</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>160</v>
       </c>
-      <c r="H41" s="5">
+      <c r="J41" s="5">
         <v>2000000</v>
       </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3">
-        <v>5</v>
-      </c>
-      <c r="K41" s="1">
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
+        <v>5</v>
+      </c>
+      <c r="M41" s="1">
         <v>5001</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7000</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O41" s="1">
+      <c r="O41" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q41" s="1">
         <v>36</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="3:15">
+    <row r="42" customHeight="1" spans="3:17">
       <c r="C42" s="1">
         <v>1037</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
       </c>
-      <c r="E42"/>
+      <c r="E42" s="1">
+        <v>0</v>
+      </c>
       <c r="F42" s="1">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
         <v>202</v>
       </c>
-      <c r="G42" s="1">
+      <c r="I42" s="1">
         <v>160</v>
       </c>
-      <c r="H42" s="5">
+      <c r="J42" s="5">
         <v>2000000</v>
       </c>
-      <c r="I42" s="1">
-        <v>0</v>
-      </c>
-      <c r="J42" s="1">
-        <v>5</v>
-      </c>
       <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1">
+        <v>5</v>
+      </c>
+      <c r="M42" s="1">
         <v>5002</v>
       </c>
-      <c r="L42" s="1">
+      <c r="N42" s="1">
         <v>50</v>
       </c>
-      <c r="M42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O42" s="1">
+      <c r="O42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q42" s="1">
         <v>37</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="3:15">
+    <row r="43" customHeight="1" spans="3:17">
       <c r="C43" s="1">
         <v>1038</v>
       </c>
       <c r="D43" s="1">
         <v>2</v>
       </c>
-      <c r="E43"/>
+      <c r="E43" s="1">
+        <v>0</v>
+      </c>
       <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
         <v>301</v>
       </c>
-      <c r="G43" s="1">
+      <c r="I43" s="1">
         <v>350000</v>
       </c>
-      <c r="H43" s="5">
+      <c r="J43" s="5">
         <v>2000000</v>
       </c>
-      <c r="I43" s="1">
-        <v>0</v>
-      </c>
-      <c r="J43" s="1">
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1">
         <v>8</v>
       </c>
-      <c r="K43" s="1">
+      <c r="M43" s="1">
         <v>11</v>
       </c>
-      <c r="L43" s="1">
+      <c r="N43" s="1">
         <v>35</v>
       </c>
-      <c r="M43" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O43" s="1">
+      <c r="O43" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q43" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="3:15">
+    <row r="44" customHeight="1" spans="3:17">
       <c r="C44" s="1">
         <v>1039</v>
       </c>
       <c r="D44" s="1">
         <v>2</v>
       </c>
-      <c r="E44"/>
+      <c r="E44" s="1">
+        <v>0</v>
+      </c>
       <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
         <v>201</v>
       </c>
-      <c r="G44" s="1">
+      <c r="I44" s="1">
         <v>3500</v>
       </c>
-      <c r="H44" s="5">
+      <c r="J44" s="5">
         <v>2000000</v>
       </c>
-      <c r="I44" s="1">
-        <v>0</v>
-      </c>
-      <c r="J44" s="1">
-        <v>5</v>
-      </c>
       <c r="K44" s="1">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1">
+        <v>5</v>
+      </c>
+      <c r="M44" s="1">
         <v>5001</v>
       </c>
-      <c r="L44" s="1">
+      <c r="N44" s="1">
         <v>7000</v>
       </c>
-      <c r="M44" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O44" s="1">
+      <c r="O44" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q44" s="1">
         <v>39</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="3:15">
+    <row r="45" customHeight="1" spans="3:17">
       <c r="C45" s="1">
         <v>1040</v>
       </c>
       <c r="D45" s="1">
         <v>2</v>
       </c>
-      <c r="E45"/>
+      <c r="E45" s="1">
+        <v>0</v>
+      </c>
       <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
         <v>205</v>
       </c>
-      <c r="G45" s="1">
+      <c r="I45" s="1">
         <v>7</v>
       </c>
-      <c r="H45" s="1">
+      <c r="J45" s="1">
         <v>1000000</v>
       </c>
-      <c r="I45" s="1">
-        <v>0</v>
-      </c>
-      <c r="J45" s="1">
-        <v>5</v>
-      </c>
       <c r="K45" s="1">
+        <v>0</v>
+      </c>
+      <c r="L45" s="1">
+        <v>5</v>
+      </c>
+      <c r="M45" s="1">
         <v>5002</v>
       </c>
-      <c r="L45" s="1">
+      <c r="N45" s="1">
         <v>50</v>
       </c>
-      <c r="M45" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O45" s="1">
+      <c r="O45" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q45" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="3:15">
+    <row r="46" customHeight="1" spans="3:17">
       <c r="C46" s="1">
         <v>1041</v>
       </c>
       <c r="D46" s="3">
         <v>2</v>
       </c>
-      <c r="E46"/>
-      <c r="F46" s="3">
+      <c r="E46" s="1">
+        <v>0</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3">
         <v>203</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>200</v>
       </c>
-      <c r="H46" s="5">
+      <c r="J46" s="5">
         <v>2000000</v>
       </c>
-      <c r="I46" s="3">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3">
-        <v>5</v>
-      </c>
-      <c r="K46" s="1">
+      <c r="K46" s="3">
+        <v>0</v>
+      </c>
+      <c r="L46" s="3">
+        <v>5</v>
+      </c>
+      <c r="M46" s="1">
         <v>5001</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>7000</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O46" s="1">
+      <c r="O46" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q46" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="3:15">
+    <row r="47" customHeight="1" spans="3:17">
       <c r="C47" s="1">
         <v>1042</v>
       </c>
       <c r="D47" s="1">
         <v>2</v>
       </c>
-      <c r="E47"/>
+      <c r="E47" s="1">
+        <v>0</v>
+      </c>
       <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
         <v>202</v>
       </c>
-      <c r="G47" s="1">
+      <c r="I47" s="1">
         <v>200</v>
       </c>
-      <c r="H47" s="5">
+      <c r="J47" s="5">
         <v>2000000</v>
       </c>
-      <c r="I47" s="1">
-        <v>0</v>
-      </c>
-      <c r="J47" s="1">
-        <v>5</v>
-      </c>
       <c r="K47" s="1">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1">
+        <v>5</v>
+      </c>
+      <c r="M47" s="1">
         <v>5002</v>
       </c>
-      <c r="L47" s="1">
+      <c r="N47" s="1">
         <v>50</v>
       </c>
-      <c r="M47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O47" s="1">
+      <c r="O47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q47" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="3:15">
+    <row r="48" customHeight="1" spans="3:17">
       <c r="C48" s="1">
         <v>1043</v>
       </c>
       <c r="D48" s="1">
         <v>2</v>
       </c>
-      <c r="E48"/>
+      <c r="E48" s="1">
+        <v>0</v>
+      </c>
       <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
         <v>301</v>
       </c>
-      <c r="G48" s="1">
+      <c r="I48" s="1">
         <v>550000</v>
       </c>
-      <c r="H48" s="5">
+      <c r="J48" s="5">
         <v>2000000</v>
       </c>
-      <c r="I48" s="1">
-        <v>0</v>
-      </c>
-      <c r="J48" s="1">
+      <c r="K48" s="1">
+        <v>0</v>
+      </c>
+      <c r="L48" s="1">
         <v>8</v>
       </c>
-      <c r="K48" s="1">
+      <c r="M48" s="1">
         <v>11</v>
       </c>
-      <c r="L48" s="1">
+      <c r="N48" s="1">
         <v>35</v>
       </c>
-      <c r="M48" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N48" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O48" s="1">
+      <c r="O48" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q48" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="3:15">
+    <row r="49" customHeight="1" spans="3:17">
       <c r="C49" s="1">
         <v>1044</v>
       </c>
       <c r="D49" s="1">
         <v>2</v>
       </c>
-      <c r="E49"/>
+      <c r="E49" s="1">
+        <v>0</v>
+      </c>
       <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
         <v>201</v>
       </c>
-      <c r="G49" s="1">
+      <c r="I49" s="1">
         <v>55000</v>
       </c>
-      <c r="H49" s="5">
+      <c r="J49" s="5">
         <v>2000000</v>
       </c>
-      <c r="I49" s="1">
-        <v>0</v>
-      </c>
-      <c r="J49" s="1">
-        <v>5</v>
-      </c>
       <c r="K49" s="1">
+        <v>0</v>
+      </c>
+      <c r="L49" s="1">
+        <v>5</v>
+      </c>
+      <c r="M49" s="1">
         <v>5001</v>
       </c>
-      <c r="L49" s="1">
+      <c r="N49" s="1">
         <v>7000</v>
       </c>
-      <c r="M49" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N49" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O49" s="1">
+      <c r="O49" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q49" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="3:15">
+    <row r="50" customHeight="1" spans="3:17">
       <c r="C50" s="1">
         <v>1045</v>
       </c>
       <c r="D50" s="1">
         <v>2</v>
       </c>
-      <c r="E50"/>
+      <c r="E50" s="1">
+        <v>0</v>
+      </c>
       <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
         <v>101</v>
       </c>
-      <c r="G50" s="1">
+      <c r="I50" s="1">
         <v>200</v>
       </c>
-      <c r="H50" s="5">
+      <c r="J50" s="5">
         <v>2000000</v>
       </c>
-      <c r="I50" s="1">
-        <v>0</v>
-      </c>
-      <c r="J50" s="1">
-        <v>5</v>
-      </c>
       <c r="K50" s="1">
+        <v>0</v>
+      </c>
+      <c r="L50" s="1">
+        <v>5</v>
+      </c>
+      <c r="M50" s="1">
         <v>5002</v>
       </c>
-      <c r="L50" s="1">
+      <c r="N50" s="1">
         <v>50</v>
       </c>
-      <c r="M50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="N50" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O50" s="1">
+      <c r="O50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q50" s="1">
         <v>45</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="3:15">
+    <row r="51" customHeight="1" spans="3:17">
       <c r="C51" s="1">
         <v>1046</v>
       </c>
       <c r="D51" s="3">
         <v>2</v>
       </c>
-      <c r="E51"/>
-      <c r="F51" s="3">
+      <c r="E51" s="1">
+        <v>0</v>
+      </c>
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3">
         <v>203</v>
       </c>
-      <c r="G51" s="3">
+      <c r="I51" s="3">
         <v>240</v>
       </c>
-      <c r="H51" s="5">
+      <c r="J51" s="5">
         <v>2000000</v>
       </c>
-      <c r="I51" s="3">
-        <v>0</v>
-      </c>
-      <c r="J51" s="3">
-        <v>5</v>
-      </c>
-      <c r="K51" s="1">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3">
+        <v>5</v>
+      </c>
+      <c r="M51" s="1">
         <v>5001</v>
       </c>
-      <c r="L51" s="3">
+      <c r="N51" s="3">
         <v>7000</v>
       </c>
-      <c r="M51" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O51" s="1">
+      <c r="O51" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q51" s="1">
         <v>46</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="3:15">
+    <row r="52" customHeight="1" spans="3:17">
       <c r="C52" s="1">
         <v>1047</v>
       </c>
       <c r="D52" s="1">
         <v>2</v>
       </c>
-      <c r="E52"/>
+      <c r="E52" s="1">
+        <v>0</v>
+      </c>
       <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
         <v>202</v>
       </c>
-      <c r="G52" s="1">
+      <c r="I52" s="1">
         <v>240</v>
       </c>
-      <c r="H52" s="5">
+      <c r="J52" s="5">
         <v>2000000</v>
       </c>
-      <c r="I52" s="1">
-        <v>0</v>
-      </c>
-      <c r="J52" s="1">
-        <v>5</v>
-      </c>
       <c r="K52" s="1">
+        <v>0</v>
+      </c>
+      <c r="L52" s="1">
+        <v>5</v>
+      </c>
+      <c r="M52" s="1">
         <v>5002</v>
       </c>
-      <c r="L52" s="1">
+      <c r="N52" s="1">
         <v>50</v>
       </c>
-      <c r="M52" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N52" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O52" s="1">
+      <c r="O52" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q52" s="1">
         <v>47</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="3:15">
+    <row r="53" customHeight="1" spans="3:17">
       <c r="C53" s="1">
         <v>1048</v>
       </c>
       <c r="D53" s="1">
         <v>2</v>
       </c>
-      <c r="E53"/>
+      <c r="E53" s="1">
+        <v>0</v>
+      </c>
       <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
         <v>301</v>
       </c>
-      <c r="G53" s="1">
+      <c r="I53" s="1">
         <v>800000</v>
       </c>
-      <c r="H53" s="5">
+      <c r="J53" s="5">
         <v>2000000</v>
       </c>
-      <c r="I53" s="1">
-        <v>0</v>
-      </c>
-      <c r="J53" s="1">
+      <c r="K53" s="1">
+        <v>0</v>
+      </c>
+      <c r="L53" s="1">
         <v>8</v>
       </c>
-      <c r="K53" s="1">
+      <c r="M53" s="1">
         <v>11</v>
       </c>
-      <c r="L53" s="1">
+      <c r="N53" s="1">
         <v>35</v>
       </c>
-      <c r="M53" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O53" s="1">
+      <c r="O53" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q53" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="3:15">
+    <row r="54" customHeight="1" spans="3:17">
       <c r="C54" s="1">
         <v>1049</v>
       </c>
       <c r="D54" s="1">
         <v>2</v>
       </c>
-      <c r="E54"/>
+      <c r="E54" s="1">
+        <v>0</v>
+      </c>
       <c r="F54" s="1">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
         <v>201</v>
       </c>
-      <c r="G54" s="1">
+      <c r="I54" s="1">
         <v>80000</v>
       </c>
-      <c r="H54" s="5">
+      <c r="J54" s="5">
         <v>2000000</v>
       </c>
-      <c r="I54" s="1">
-        <v>0</v>
-      </c>
-      <c r="J54" s="1">
-        <v>5</v>
-      </c>
       <c r="K54" s="1">
+        <v>0</v>
+      </c>
+      <c r="L54" s="1">
+        <v>5</v>
+      </c>
+      <c r="M54" s="1">
         <v>5001</v>
       </c>
-      <c r="L54" s="1">
+      <c r="N54" s="1">
         <v>7000</v>
       </c>
-      <c r="M54" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O54" s="1">
+      <c r="O54" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q54" s="1">
         <v>49</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="3:15">
+    <row r="55" customHeight="1" spans="3:17">
       <c r="C55" s="1">
         <v>1050</v>
       </c>
       <c r="D55" s="1">
         <v>2</v>
       </c>
-      <c r="E55"/>
+      <c r="E55" s="1">
+        <v>0</v>
+      </c>
       <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
         <v>101</v>
       </c>
-      <c r="G55" s="1">
+      <c r="I55" s="1">
         <v>300</v>
       </c>
-      <c r="H55" s="5">
+      <c r="J55" s="5">
         <v>2000000</v>
       </c>
-      <c r="I55" s="1">
-        <v>0</v>
-      </c>
-      <c r="J55" s="1">
-        <v>5</v>
-      </c>
       <c r="K55" s="1">
+        <v>0</v>
+      </c>
+      <c r="L55" s="1">
+        <v>5</v>
+      </c>
+      <c r="M55" s="1">
         <v>5002</v>
       </c>
-      <c r="L55" s="1">
+      <c r="N55" s="1">
         <v>50</v>
       </c>
-      <c r="M55" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="N55" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O55" s="1">
+      <c r="O55" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q55" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="56" customHeight="1" spans="3:15">
+    <row r="56" customHeight="1" spans="3:17">
       <c r="E56"/>
-    </row>
-    <row r="57" customHeight="1" spans="3:15">
+      <c r="F56"/>
+      <c r="G56"/>
+    </row>
+    <row r="57" customHeight="1" spans="3:17">
       <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="P11 C3:P5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G3 G4 E5 F5 G5 R11 E3:E4 F3:F4 H3:R5 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -4757,35 +5388,35 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P57"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5833333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.8333333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.4166666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" style="1" customWidth="1"/>
-    <col min="11" max="12" width="13.75" style="1" customWidth="1"/>
-    <col min="13" max="13" width="42.75" style="1" customWidth="1"/>
-    <col min="14" max="14" width="21.4166666666667" style="1" customWidth="1"/>
-    <col min="15" max="15" width="19.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5833333333333" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1"/>
+    <col min="5" max="7" width="11.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5833333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.8333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.4166666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5" style="1" customWidth="1"/>
+    <col min="13" max="14" width="13.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="42.75" style="1" customWidth="1"/>
+    <col min="16" max="16" width="21.4166666666667" style="1" customWidth="1"/>
+    <col min="17" max="17" width="19.625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5833333333333" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -4807,14 +5438,14 @@
       <c r="I3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="2">
-        <v>5</v>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>10</v>
+      <c r="L3" s="2">
+        <v>5</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>11</v>
@@ -4828,10 +5459,16 @@
       <c r="P3" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -4869,51 +5506,63 @@
       <c r="O4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="2"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R4" s="2"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P5" s="2"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="R5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C6" s="1">
         <v>3001</v>
       </c>
@@ -4924,38 +5573,44 @@
         <v>3</v>
       </c>
       <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
         <v>301</v>
       </c>
-      <c r="G6" s="1">
+      <c r="I6" s="1">
         <v>10000</v>
       </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
       <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
         <v>8</v>
       </c>
-      <c r="K6" s="1">
+      <c r="M6" s="1">
         <v>14</v>
       </c>
-      <c r="L6" s="1">
-        <v>1</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="O6" s="1">
-        <v>1</v>
-      </c>
-      <c r="P6" s="2"/>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N6" s="1">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
+      </c>
+      <c r="R6" s="2"/>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C7" s="1">
         <v>3002</v>
       </c>
@@ -4966,38 +5621,44 @@
         <v>3</v>
       </c>
       <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
         <v>301</v>
       </c>
-      <c r="G7" s="1">
+      <c r="I7" s="1">
         <v>100000</v>
       </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
       <c r="J7" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>5</v>
+      </c>
+      <c r="M7" s="1">
         <v>10004</v>
       </c>
-      <c r="L7" s="1">
-        <v>1</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="O7" s="1">
+      <c r="N7" s="1">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q7" s="1">
         <v>2</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C8" s="1">
         <v>3003</v>
       </c>
@@ -5008,38 +5669,44 @@
         <v>3</v>
       </c>
       <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
         <v>301</v>
       </c>
-      <c r="G8" s="1">
+      <c r="I8" s="1">
         <v>50000</v>
       </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
       <c r="J8" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>5</v>
+      </c>
+      <c r="M8" s="1">
         <v>40000001</v>
       </c>
-      <c r="L8" s="1">
+      <c r="N8" s="1">
         <v>25</v>
       </c>
-      <c r="M8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="O8" s="1">
+      <c r="O8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="1">
         <v>3</v>
       </c>
-      <c r="P8" s="2"/>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="R8" s="2"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C9" s="1">
         <v>3004</v>
       </c>
@@ -5050,38 +5717,44 @@
         <v>3</v>
       </c>
       <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
         <v>301</v>
       </c>
-      <c r="G9" s="1">
+      <c r="I9" s="1">
         <v>50000</v>
       </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
       <c r="J9" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>5</v>
+      </c>
+      <c r="M9" s="1">
         <v>40000002</v>
       </c>
-      <c r="L9" s="1">
+      <c r="N9" s="1">
         <v>3</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N9" s="1" t="s">
+      <c r="O9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="O9" s="1">
+      <c r="P9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q9" s="1">
         <v>4</v>
       </c>
-      <c r="P9" s="2"/>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C10" s="1">
         <v>3005</v>
       </c>
@@ -5092,38 +5765,44 @@
         <v>3</v>
       </c>
       <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
         <v>301</v>
       </c>
-      <c r="G10" s="1">
+      <c r="I10" s="1">
         <v>50000</v>
       </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
       <c r="J10" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>5</v>
+      </c>
+      <c r="M10" s="1">
         <v>40000003</v>
       </c>
-      <c r="L10" s="1">
-        <v>1</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="O10" s="1">
-        <v>5</v>
-      </c>
-      <c r="P10" s="2"/>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="N10" s="1">
+        <v>1</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>5</v>
+      </c>
+      <c r="R10" s="2"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C11" s="1">
         <v>3006</v>
       </c>
@@ -5134,38 +5813,44 @@
         <v>3</v>
       </c>
       <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
         <v>301</v>
       </c>
-      <c r="G11" s="1">
+      <c r="I11" s="1">
         <v>50000</v>
       </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
       <c r="J11" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <v>5</v>
+      </c>
+      <c r="M11" s="1">
         <v>40000004</v>
       </c>
-      <c r="L11" s="1">
+      <c r="N11" s="1">
         <v>25</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O11" s="1">
+      <c r="O11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q11" s="1">
         <v>6</v>
       </c>
-      <c r="P11" s="2"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="R11" s="2"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C12" s="1">
         <v>3007</v>
       </c>
@@ -5176,38 +5861,44 @@
         <v>3</v>
       </c>
       <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
         <v>301</v>
       </c>
-      <c r="G12" s="1">
+      <c r="I12" s="1">
         <v>50000</v>
       </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
       <c r="J12" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>5</v>
+      </c>
+      <c r="M12" s="1">
         <v>40000005</v>
       </c>
-      <c r="L12" s="1">
+      <c r="N12" s="1">
         <v>3</v>
       </c>
-      <c r="M12" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="O12" s="1">
+      <c r="O12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q12" s="1">
         <v>7</v>
       </c>
-      <c r="P12" s="2"/>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="R12" s="2"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C13" s="1">
         <v>3008</v>
       </c>
@@ -5218,77 +5909,398 @@
         <v>3</v>
       </c>
       <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
         <v>301</v>
       </c>
-      <c r="G13" s="1">
+      <c r="I13" s="1">
         <v>50000</v>
       </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
       <c r="J13" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>5</v>
+      </c>
+      <c r="M13" s="1">
         <v>40000006</v>
       </c>
-      <c r="L13" s="1">
-        <v>1</v>
-      </c>
-      <c r="M13" s="1" t="s">
+      <c r="N13" s="1">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C14" s="1">
+        <v>3009</v>
+      </c>
+      <c r="D14" s="1">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1">
+        <v>3</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>301</v>
+      </c>
+      <c r="I14" s="1">
+        <v>200000</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>8</v>
+      </c>
+      <c r="M14" s="1">
+        <v>15</v>
+      </c>
+      <c r="N14" s="1">
+        <v>1</v>
+      </c>
+      <c r="O14" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="N13" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="O13" s="1">
-        <v>8</v>
-      </c>
-      <c r="P13" s="2"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P14" s="2"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P15" s="2"/>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P16" s="2"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P17" s="2"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P18" s="2"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P19" s="2"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P20" s="2"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P21" s="2"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P22" s="2"/>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P23" s="2"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P24" s="2"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P25" s="2"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P26" s="2"/>
-    </row>
-    <row r="27" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P14" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>9</v>
+      </c>
+      <c r="R14" s="2"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C15" s="1">
+        <v>3010</v>
+      </c>
+      <c r="D15" s="1">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1">
+        <v>3</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>301</v>
+      </c>
+      <c r="I15" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>5</v>
+      </c>
+      <c r="M15" s="1">
+        <v>40000007</v>
+      </c>
+      <c r="N15" s="1">
+        <v>25</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>10</v>
+      </c>
+      <c r="R15" s="2"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C16" s="1">
+        <v>3011</v>
+      </c>
+      <c r="D16" s="1">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>301</v>
+      </c>
+      <c r="I16" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>5</v>
+      </c>
+      <c r="M16" s="1">
+        <v>40000008</v>
+      </c>
+      <c r="N16" s="1">
+        <v>3</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>11</v>
+      </c>
+      <c r="R16" s="2"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C17" s="1">
+        <v>3012</v>
+      </c>
+      <c r="D17" s="1">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1">
+        <v>3</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>301</v>
+      </c>
+      <c r="I17" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>5</v>
+      </c>
+      <c r="M17" s="1">
+        <v>40000009</v>
+      </c>
+      <c r="N17" s="1">
+        <v>1</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>12</v>
+      </c>
+      <c r="R17" s="2"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C18" s="1">
+        <v>3013</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>301</v>
+      </c>
+      <c r="I18" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>5</v>
+      </c>
+      <c r="M18" s="1">
+        <v>40000010</v>
+      </c>
+      <c r="N18" s="1">
+        <v>25</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>13</v>
+      </c>
+      <c r="R18" s="2"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C19" s="1">
+        <v>3014</v>
+      </c>
+      <c r="D19" s="1">
+        <v>3</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>301</v>
+      </c>
+      <c r="I19" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>5</v>
+      </c>
+      <c r="M19" s="1">
+        <v>40000011</v>
+      </c>
+      <c r="N19" s="1">
+        <v>3</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>14</v>
+      </c>
+      <c r="R19" s="2"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C20" s="1">
+        <v>3015</v>
+      </c>
+      <c r="D20" s="1">
+        <v>3</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>301</v>
+      </c>
+      <c r="I20" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>5</v>
+      </c>
+      <c r="M20" s="1">
+        <v>40000012</v>
+      </c>
+      <c r="N20" s="1">
+        <v>1</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>15</v>
+      </c>
+      <c r="R20" s="2"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R21" s="2"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R22" s="2"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R23" s="2"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R24" s="2"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R25" s="2"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R26" s="2"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="1:18">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -5304,9 +6316,11 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
-      <c r="P27" s="2"/>
-    </row>
-    <row r="28" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="2"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="1:18">
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -5320,6 +6334,8 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
     </row>
     <row r="29" customFormat="1" customHeight="1"/>
     <row r="30" customFormat="1" customHeight="1"/>
@@ -5352,7 +6368,7 @@
     <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="P6:P27 C3:P5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G3 G4 E5 F5 G5 E3:E4 F3:F4 R6:R27 H3:R5 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -5365,35 +6381,35 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P57"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="11.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5833333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.8333333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.4166666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" style="1" customWidth="1"/>
-    <col min="11" max="12" width="13.75" style="1" customWidth="1"/>
-    <col min="13" max="13" width="42.75" style="1" customWidth="1"/>
-    <col min="14" max="14" width="21.4166666666667" style="1" customWidth="1"/>
-    <col min="15" max="15" width="19.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5833333333333" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1"/>
+    <col min="5" max="7" width="11.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5833333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.8333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.4166666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5" style="1" customWidth="1"/>
+    <col min="13" max="14" width="13.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="42.75" style="1" customWidth="1"/>
+    <col min="16" max="16" width="21.4166666666667" style="1" customWidth="1"/>
+    <col min="17" max="17" width="19.625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5833333333333" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -5415,14 +6431,14 @@
       <c r="I3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="2">
-        <v>5</v>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>10</v>
+      <c r="L3" s="2">
+        <v>5</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>11</v>
@@ -5436,10 +6452,16 @@
       <c r="P3" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -5477,51 +6499,63 @@
       <c r="O4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="2"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R4" s="2"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P5" s="2"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="R5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C6" s="1">
         <v>11001</v>
       </c>
@@ -5532,98 +6566,104 @@
         <v>11</v>
       </c>
       <c r="F6" s="1">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
         <v>301</v>
       </c>
-      <c r="G6" s="1">
+      <c r="I6" s="1">
         <v>100</v>
       </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
       <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
         <v>10000</v>
       </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1">
-        <v>0</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="O6" s="1">
-        <v>1</v>
-      </c>
-      <c r="P6" s="2"/>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P8" s="2"/>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P9" s="2"/>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P10" s="2"/>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P11" s="2"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P12" s="2"/>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P13" s="2"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P14" s="2"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P15" s="2"/>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P16" s="2"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P17" s="2"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P18" s="2"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P19" s="2"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P20" s="2"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P21" s="2"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P22" s="2"/>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P23" s="2"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P24" s="2"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P25" s="2"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P26" s="2"/>
-    </row>
-    <row r="27" customFormat="1" customHeight="1" spans="1:16">
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
+      </c>
+      <c r="R6" s="2"/>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R8" s="2"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R10" s="2"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R11" s="2"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R12" s="2"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R13" s="2"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R14" s="2"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R15" s="2"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R16" s="2"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R17" s="2"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R18" s="2"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R19" s="2"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R20" s="2"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R21" s="2"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R22" s="2"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R23" s="2"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R24" s="2"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R25" s="2"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R26" s="2"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="1:18">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -5639,9 +6679,11 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
-      <c r="P27" s="2"/>
-    </row>
-    <row r="28" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="2"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="1:18">
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -5655,6 +6697,8 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
     </row>
     <row r="29" customFormat="1" customHeight="1"/>
     <row r="30" customFormat="1" customHeight="1"/>
@@ -5687,7 +6731,7 @@
     <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="P6:P27 C3:P5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G3 G4 E5 F5 G5 E3:E4 F3:F4 R6:R27 H3:R5 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -5700,34 +6744,36 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P57"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="13.5833333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.8333333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.4166666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" style="1" customWidth="1"/>
-    <col min="11" max="12" width="13.75" style="1" customWidth="1"/>
-    <col min="13" max="13" width="42.75" style="1" customWidth="1"/>
-    <col min="14" max="14" width="21.4166666666667" style="1" customWidth="1"/>
-    <col min="15" max="15" width="19.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5833333333333" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="10.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.0833333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5833333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.8333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.4166666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5" style="1" customWidth="1"/>
+    <col min="13" max="14" width="13.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="42.75" style="1" customWidth="1"/>
+    <col min="16" max="16" width="21.4166666666667" style="1" customWidth="1"/>
+    <col min="17" max="17" width="19.625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5833333333333" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:16">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -5770,10 +6816,16 @@
       <c r="P3" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="Q3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -5811,51 +6863,63 @@
       <c r="O4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="2"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="P4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R4" s="2"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P5" s="2"/>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="R5" s="2"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C6" s="1">
         <v>12001</v>
       </c>
@@ -5866,38 +6930,44 @@
         <v>12</v>
       </c>
       <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
         <v>301</v>
       </c>
-      <c r="G6" s="1">
+      <c r="I6" s="1">
         <v>50</v>
       </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
       <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
         <v>10000</v>
       </c>
-      <c r="K6" s="1">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1">
-        <v>0</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O6" s="1">
-        <v>1</v>
-      </c>
-      <c r="P6" s="2"/>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="M6" s="1">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
+      </c>
+      <c r="R6" s="2"/>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C7" s="1">
         <v>12002</v>
       </c>
@@ -5908,38 +6978,44 @@
         <v>12</v>
       </c>
       <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
         <v>301</v>
       </c>
-      <c r="G7" s="1">
+      <c r="I7" s="1">
         <v>50</v>
       </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
       <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
         <v>10000</v>
       </c>
-      <c r="K7" s="1">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O7" s="1">
+      <c r="M7" s="1">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q7" s="1">
         <v>2</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C8" s="1">
         <v>12003</v>
       </c>
@@ -5950,38 +7026,44 @@
         <v>12</v>
       </c>
       <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
         <v>301</v>
       </c>
-      <c r="G8" s="1">
+      <c r="I8" s="1">
         <v>50</v>
       </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
       <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
         <v>10000</v>
       </c>
-      <c r="K8" s="1">
-        <v>1</v>
-      </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O8" s="1">
+      <c r="M8" s="1">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q8" s="1">
         <v>3</v>
       </c>
-      <c r="P8" s="2"/>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="R8" s="2"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C9" s="1">
         <v>12004</v>
       </c>
@@ -5992,38 +7074,44 @@
         <v>12</v>
       </c>
       <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
         <v>301</v>
       </c>
-      <c r="G9" s="1">
+      <c r="I9" s="1">
         <v>50</v>
       </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
       <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
         <v>10000</v>
       </c>
-      <c r="K9" s="1">
-        <v>1</v>
-      </c>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O9" s="1">
+      <c r="M9" s="1">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q9" s="1">
         <v>4</v>
       </c>
-      <c r="P9" s="2"/>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="R9" s="2"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C10" s="1">
         <v>12005</v>
       </c>
@@ -6034,38 +7122,44 @@
         <v>12</v>
       </c>
       <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1">
         <v>301</v>
       </c>
-      <c r="G10" s="1">
+      <c r="I10" s="1">
         <v>50</v>
       </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
       <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
         <v>10000</v>
       </c>
-      <c r="K10" s="1">
-        <v>1</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O10" s="1">
-        <v>5</v>
-      </c>
-      <c r="P10" s="2"/>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:16">
+      <c r="M10" s="1">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>5</v>
+      </c>
+      <c r="R10" s="2"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C11" s="1">
         <v>12006</v>
       </c>
@@ -6076,83 +7170,89 @@
         <v>12</v>
       </c>
       <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
         <v>301</v>
       </c>
-      <c r="G11" s="1">
+      <c r="I11" s="1">
         <v>50000</v>
       </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
       <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
         <v>10000</v>
       </c>
-      <c r="K11" s="1">
-        <v>1</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O11" s="1">
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q11" s="1">
         <v>6</v>
       </c>
-      <c r="P11" s="2"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P12" s="2"/>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P13" s="2"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P14" s="2"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P15" s="2"/>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:16">
-      <c r="P16" s="2"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P17" s="2"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P18" s="2"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P19" s="2"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P20" s="2"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P21" s="2"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P22" s="2"/>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P23" s="2"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P24" s="2"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P25" s="2"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="P26" s="2"/>
-    </row>
-    <row r="27" customFormat="1" customHeight="1" spans="1:16">
+      <c r="R11" s="2"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R12" s="2"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R13" s="2"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R14" s="2"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R15" s="2"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="R16" s="2"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R17" s="2"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R18" s="2"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R19" s="2"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R20" s="2"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R21" s="2"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R22" s="2"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R23" s="2"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R24" s="2"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R25" s="2"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R26" s="2"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="1:18">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -6168,9 +7268,11 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
-      <c r="P27" s="2"/>
-    </row>
-    <row r="28" customFormat="1" customHeight="1" spans="1:16">
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="2"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="1:18">
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -6184,6 +7286,8 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
     </row>
     <row r="29" customFormat="1" customHeight="1"/>
     <row r="30" customFormat="1" customHeight="1"/>
@@ -6216,7 +7320,7 @@
     <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="P6:P27 C3:P5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G3 G4 E5 F5 G5 E3:E4 F3:F4 R6:R27 H3:R5 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="新入世界" sheetId="1" r:id="rId1"/>
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="83">
   <si>
     <t>#</t>
   </si>
@@ -467,21 +467,12 @@
     <t>获得{0}个宠物</t>
   </si>
   <si>
-    <t>击杀1万个怪物</t>
-  </si>
-  <si>
     <t>奖励1个多重宠物</t>
   </si>
   <si>
-    <t>击杀10万个怪物</t>
-  </si>
-  <si>
     <t>奖励1个天下无双皮肤</t>
   </si>
   <si>
-    <t>击杀5万个怪物</t>
-  </si>
-  <si>
     <t>奖励{1}个狼毛</t>
   </si>
   <si>
@@ -521,31 +512,28 @@
     <t>奖励{1}个鹿血</t>
   </si>
   <si>
-    <t>击杀1万个怪物，每日刷新</t>
-  </si>
-  <si>
     <t>奖励10次抽奖</t>
   </si>
   <si>
-    <t>击杀5万个怪物（大佬福利1）</t>
+    <t>击杀{0}个怪物（大佬福利1）</t>
   </si>
   <si>
     <t>奖励5次抽奖</t>
   </si>
   <si>
-    <t>击杀5万个怪物（大佬福利2）</t>
-  </si>
-  <si>
-    <t>击杀5万个怪物（大佬福利3）</t>
-  </si>
-  <si>
-    <t>击杀5万个怪物（大佬福利4）</t>
-  </si>
-  <si>
-    <t>击杀5万个怪物（大佬福利5）</t>
-  </si>
-  <si>
-    <t>击杀5万个怪物（大佬福利6）</t>
+    <t>击杀{0}个怪物（大佬福利2）</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物（大佬福利3）</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物（大佬福利4）</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物（大佬福利5）</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物（大佬福利6）</t>
   </si>
 </sst>
 </file>
@@ -5600,10 +5588,10 @@
         <v>1</v>
       </c>
       <c r="O6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P6" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
@@ -5648,10 +5636,10 @@
         <v>1</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Q7" s="1">
         <v>2</v>
@@ -5696,10 +5684,10 @@
         <v>25</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="Q8" s="1">
         <v>3</v>
@@ -5744,10 +5732,10 @@
         <v>3</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="Q9" s="1">
         <v>4</v>
@@ -5792,10 +5780,10 @@
         <v>1</v>
       </c>
       <c r="O10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P10" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="Q10" s="1">
         <v>5</v>
@@ -5840,10 +5828,10 @@
         <v>25</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="Q11" s="1">
         <v>6</v>
@@ -5888,10 +5876,10 @@
         <v>3</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="Q12" s="1">
         <v>7</v>
@@ -5936,10 +5924,10 @@
         <v>1</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="Q13" s="1">
         <v>8</v>
@@ -5984,10 +5972,10 @@
         <v>1</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q14" s="1">
         <v>9</v>
@@ -6032,10 +6020,10 @@
         <v>25</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Q15" s="1">
         <v>10</v>
@@ -6080,10 +6068,10 @@
         <v>3</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="1">
         <v>11</v>
@@ -6128,10 +6116,10 @@
         <v>1</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q17" s="1">
         <v>12</v>
@@ -6176,10 +6164,10 @@
         <v>25</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="Q18" s="1">
         <v>13</v>
@@ -6224,10 +6212,10 @@
         <v>3</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q19" s="1">
         <v>14</v>
@@ -6272,10 +6260,10 @@
         <v>1</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="Q20" s="1">
         <v>15</v>
@@ -6575,7 +6563,7 @@
         <v>301</v>
       </c>
       <c r="I6" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -6593,10 +6581,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
@@ -6763,17 +6751,17 @@
     <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="R1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="R2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -6823,7 +6811,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
@@ -6871,7 +6859,7 @@
       </c>
       <c r="R4" s="2"/>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
@@ -6919,7 +6907,13 @@
       </c>
       <c r="R5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C6" s="1">
         <v>12001</v>
       </c>
@@ -6939,7 +6933,7 @@
         <v>301</v>
       </c>
       <c r="I6" s="1">
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -6957,17 +6951,23 @@
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
       </c>
       <c r="R6" s="2"/>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C7" s="1">
         <v>12002</v>
       </c>
@@ -6987,7 +6987,7 @@
         <v>301</v>
       </c>
       <c r="I7" s="1">
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
@@ -7005,17 +7005,23 @@
         <v>0</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q7" s="1">
         <v>2</v>
       </c>
       <c r="R7" s="2"/>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C8" s="1">
         <v>12003</v>
       </c>
@@ -7035,7 +7041,7 @@
         <v>301</v>
       </c>
       <c r="I8" s="1">
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="J8" s="1">
         <v>0</v>
@@ -7053,17 +7059,23 @@
         <v>0</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q8" s="1">
         <v>3</v>
       </c>
       <c r="R8" s="2"/>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C9" s="1">
         <v>12004</v>
       </c>
@@ -7083,7 +7095,7 @@
         <v>301</v>
       </c>
       <c r="I9" s="1">
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
@@ -7101,17 +7113,23 @@
         <v>0</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q9" s="1">
         <v>4</v>
       </c>
       <c r="R9" s="2"/>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C10" s="1">
         <v>12005</v>
       </c>
@@ -7131,7 +7149,7 @@
         <v>301</v>
       </c>
       <c r="I10" s="1">
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="J10" s="1">
         <v>0</v>
@@ -7149,17 +7167,23 @@
         <v>0</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q10" s="1">
         <v>5</v>
       </c>
       <c r="R10" s="2"/>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C11" s="1">
         <v>12006</v>
       </c>
@@ -7197,29 +7221,29 @@
         <v>0</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q11" s="1">
         <v>6</v>
       </c>
       <c r="R11" s="2"/>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="R12" s="2"/>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="R13" s="2"/>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="R14" s="2"/>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="R15" s="2"/>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="R16" s="2"/>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:18">

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="新入世界" sheetId="1" r:id="rId1"/>
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="91">
   <si>
     <t>#</t>
   </si>
@@ -512,28 +512,52 @@
     <t>奖励{1}个鹿血</t>
   </si>
   <si>
+    <t>奖励1阶神兵符{1}</t>
+  </si>
+  <si>
+    <t>奖励2阶神兵符{1}</t>
+  </si>
+  <si>
+    <t>奖励3阶神兵符{1}</t>
+  </si>
+  <si>
+    <t>奖励4阶神兵符{1}</t>
+  </si>
+  <si>
+    <t>奖励5阶神兵符{1}</t>
+  </si>
+  <si>
+    <t>奖励{1}个骨弓</t>
+  </si>
+  <si>
+    <t>奖励{1}个骨杖</t>
+  </si>
+  <si>
+    <t>奖励{1}个骨龙核心</t>
+  </si>
+  <si>
     <t>奖励10次抽奖</t>
   </si>
   <si>
-    <t>击杀{0}个怪物（大佬福利1）</t>
+    <t>击杀{0}个怪物，福利1（Z）</t>
   </si>
   <si>
     <t>奖励5次抽奖</t>
   </si>
   <si>
-    <t>击杀{0}个怪物（大佬福利2）</t>
-  </si>
-  <si>
-    <t>击杀{0}个怪物（大佬福利3）</t>
-  </si>
-  <si>
-    <t>击杀{0}个怪物（大佬福利4）</t>
-  </si>
-  <si>
-    <t>击杀{0}个怪物（大佬福利5）</t>
-  </si>
-  <si>
-    <t>击杀{0}个怪物（大佬福利6）</t>
+    <t>击杀{0}个怪物，福利2（Z）</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，福利3（Z）</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，福利4（Z）</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，福利5（Z）</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，福利6（Z）</t>
   </si>
 </sst>
 </file>
@@ -712,12 +736,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1183,11 +1207,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2823,7 +2850,7 @@
     <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:E3 F3 G3 C4:D4 E4 F4 G4 C5:E5 F5 G5 R6:R27 H3:R5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R6:R27 C3:R5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -3461,7 +3488,7 @@
       <c r="N15" s="1">
         <v>20</v>
       </c>
-      <c r="O15" s="4" t="s">
+      <c r="O15" s="5" t="s">
         <v>58</v>
       </c>
       <c r="P15" s="1" t="s">
@@ -3471,11 +3498,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" s="3" customFormat="1" customHeight="1" spans="3:18">
+    <row r="16" s="4" customFormat="1" customHeight="1" spans="3:18">
       <c r="C16" s="1">
         <v>1011</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="4">
         <v>2</v>
       </c>
       <c r="E16" s="1">
@@ -3487,31 +3514,31 @@
       <c r="G16" s="1">
         <v>0</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="4">
         <v>203</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="4">
         <v>20</v>
       </c>
       <c r="J16" s="1">
         <v>1500000</v>
       </c>
-      <c r="K16" s="3">
-        <v>0</v>
-      </c>
-      <c r="L16" s="3">
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4">
         <v>5</v>
       </c>
       <c r="M16" s="1">
         <v>5001</v>
       </c>
-      <c r="N16" s="3">
+      <c r="N16" s="4">
         <v>3000</v>
       </c>
-      <c r="O16" s="3" t="s">
+      <c r="O16" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="P16" s="3" t="s">
+      <c r="P16" s="4" t="s">
         <v>27</v>
       </c>
       <c r="Q16" s="1">
@@ -3706,11 +3733,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" s="3" customFormat="1" customHeight="1" spans="3:17">
+    <row r="21" s="4" customFormat="1" customHeight="1" spans="3:17">
       <c r="C21" s="1">
         <v>1016</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="4">
         <v>2</v>
       </c>
       <c r="E21" s="1">
@@ -3722,31 +3749,31 @@
       <c r="G21" s="1">
         <v>0</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="4">
         <v>203</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="4">
         <v>35</v>
       </c>
       <c r="J21" s="1">
         <v>1500000</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="K21" s="4">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4">
         <v>5</v>
       </c>
       <c r="M21" s="1">
         <v>5001</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="4">
         <v>4000</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="O21" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="P21" s="4" t="s">
         <v>27</v>
       </c>
       <c r="Q21" s="1">
@@ -3931,7 +3958,7 @@
       <c r="N25" s="1">
         <v>40</v>
       </c>
-      <c r="O25" s="4" t="s">
+      <c r="O25" s="5" t="s">
         <v>58</v>
       </c>
       <c r="P25" s="1" t="s">
@@ -3941,11 +3968,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" s="3" customFormat="1" customHeight="1" spans="3:17">
+    <row r="26" s="4" customFormat="1" customHeight="1" spans="3:17">
       <c r="C26" s="1">
         <v>1021</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="4">
         <v>2</v>
       </c>
       <c r="E26" s="1">
@@ -3957,31 +3984,31 @@
       <c r="G26" s="1">
         <v>0</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26" s="4">
         <v>203</v>
       </c>
-      <c r="I26" s="3">
+      <c r="I26" s="4">
         <v>55</v>
       </c>
       <c r="J26" s="1">
         <v>1500000</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="K26" s="4">
+        <v>0</v>
+      </c>
+      <c r="L26" s="4">
         <v>5</v>
       </c>
       <c r="M26" s="1">
         <v>5001</v>
       </c>
-      <c r="N26" s="3">
+      <c r="N26" s="4">
         <v>5000</v>
       </c>
-      <c r="O26" s="3" t="s">
+      <c r="O26" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="P26" s="3" t="s">
+      <c r="P26" s="4" t="s">
         <v>27</v>
       </c>
       <c r="Q26" s="1">
@@ -4010,7 +4037,7 @@
       <c r="I27" s="1">
         <v>55</v>
       </c>
-      <c r="J27" s="5">
+      <c r="J27" s="6">
         <v>2000000</v>
       </c>
       <c r="K27" s="1">
@@ -4057,7 +4084,7 @@
       <c r="I28" s="1">
         <v>50000</v>
       </c>
-      <c r="J28" s="5">
+      <c r="J28" s="6">
         <v>2000000</v>
       </c>
       <c r="K28" s="1">
@@ -4104,7 +4131,7 @@
       <c r="I29" s="1">
         <v>5000</v>
       </c>
-      <c r="J29" s="5">
+      <c r="J29" s="6">
         <v>2000000</v>
       </c>
       <c r="K29" s="1">
@@ -4151,7 +4178,7 @@
       <c r="I30" s="1">
         <v>10</v>
       </c>
-      <c r="J30" s="5">
+      <c r="J30" s="6">
         <v>2000000</v>
       </c>
       <c r="K30" s="1">
@@ -4180,7 +4207,7 @@
       <c r="C31" s="1">
         <v>1026</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="4">
         <v>2</v>
       </c>
       <c r="E31" s="1">
@@ -4192,31 +4219,31 @@
       <c r="G31" s="1">
         <v>0</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H31" s="4">
         <v>203</v>
       </c>
-      <c r="I31" s="3">
+      <c r="I31" s="4">
         <v>85</v>
       </c>
-      <c r="J31" s="5">
+      <c r="J31" s="6">
         <v>2000000</v>
       </c>
-      <c r="K31" s="3">
-        <v>0</v>
-      </c>
-      <c r="L31" s="3">
+      <c r="K31" s="4">
+        <v>0</v>
+      </c>
+      <c r="L31" s="4">
         <v>5</v>
       </c>
       <c r="M31" s="1">
         <v>5001</v>
       </c>
-      <c r="N31" s="3">
+      <c r="N31" s="4">
         <v>6000</v>
       </c>
-      <c r="O31" s="3" t="s">
+      <c r="O31" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="P31" s="3" t="s">
+      <c r="P31" s="4" t="s">
         <v>27</v>
       </c>
       <c r="Q31" s="1">
@@ -4242,10 +4269,10 @@
       <c r="H32" s="1">
         <v>202</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="4">
         <v>85</v>
       </c>
-      <c r="J32" s="5">
+      <c r="J32" s="6">
         <v>2000000</v>
       </c>
       <c r="K32" s="1">
@@ -4292,7 +4319,7 @@
       <c r="I33" s="1">
         <v>100000</v>
       </c>
-      <c r="J33" s="5">
+      <c r="J33" s="6">
         <v>2000000</v>
       </c>
       <c r="K33" s="1">
@@ -4339,7 +4366,7 @@
       <c r="I34" s="1">
         <v>10000</v>
       </c>
-      <c r="J34" s="5">
+      <c r="J34" s="6">
         <v>2000000</v>
       </c>
       <c r="K34" s="1">
@@ -4401,7 +4428,7 @@
       <c r="N35" s="1">
         <v>50</v>
       </c>
-      <c r="O35" s="4" t="s">
+      <c r="O35" s="5" t="s">
         <v>58</v>
       </c>
       <c r="P35" s="1" t="s">
@@ -4415,7 +4442,7 @@
       <c r="C36" s="1">
         <v>1031</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="4">
         <v>2</v>
       </c>
       <c r="E36" s="1">
@@ -4427,31 +4454,31 @@
       <c r="G36" s="1">
         <v>0</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H36" s="4">
         <v>203</v>
       </c>
-      <c r="I36" s="3">
+      <c r="I36" s="4">
         <v>120</v>
       </c>
-      <c r="J36" s="5">
+      <c r="J36" s="6">
         <v>2000000</v>
       </c>
-      <c r="K36" s="3">
-        <v>0</v>
-      </c>
-      <c r="L36" s="3">
+      <c r="K36" s="4">
+        <v>0</v>
+      </c>
+      <c r="L36" s="4">
         <v>5</v>
       </c>
       <c r="M36" s="1">
         <v>5001</v>
       </c>
-      <c r="N36" s="3">
+      <c r="N36" s="4">
         <v>7000</v>
       </c>
-      <c r="O36" s="3" t="s">
+      <c r="O36" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="P36" s="3" t="s">
+      <c r="P36" s="4" t="s">
         <v>27</v>
       </c>
       <c r="Q36" s="1">
@@ -4480,7 +4507,7 @@
       <c r="I37" s="1">
         <v>120</v>
       </c>
-      <c r="J37" s="5">
+      <c r="J37" s="6">
         <v>2000000</v>
       </c>
       <c r="K37" s="1">
@@ -4527,7 +4554,7 @@
       <c r="I38" s="1">
         <v>200000</v>
       </c>
-      <c r="J38" s="5">
+      <c r="J38" s="6">
         <v>2000000</v>
       </c>
       <c r="K38" s="1">
@@ -4574,7 +4601,7 @@
       <c r="I39" s="1">
         <v>20000</v>
       </c>
-      <c r="J39" s="5">
+      <c r="J39" s="6">
         <v>2000000</v>
       </c>
       <c r="K39" s="1">
@@ -4621,7 +4648,7 @@
       <c r="I40" s="1">
         <v>50</v>
       </c>
-      <c r="J40" s="5">
+      <c r="J40" s="6">
         <v>2000000</v>
       </c>
       <c r="K40" s="1">
@@ -4650,7 +4677,7 @@
       <c r="C41" s="1">
         <v>1036</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="4">
         <v>2</v>
       </c>
       <c r="E41" s="1">
@@ -4662,31 +4689,31 @@
       <c r="G41" s="1">
         <v>0</v>
       </c>
-      <c r="H41" s="3">
+      <c r="H41" s="4">
         <v>203</v>
       </c>
-      <c r="I41" s="3">
+      <c r="I41" s="4">
         <v>160</v>
       </c>
-      <c r="J41" s="5">
+      <c r="J41" s="6">
         <v>2000000</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="K41" s="4">
+        <v>0</v>
+      </c>
+      <c r="L41" s="4">
         <v>5</v>
       </c>
       <c r="M41" s="1">
         <v>5001</v>
       </c>
-      <c r="N41" s="3">
+      <c r="N41" s="4">
         <v>7000</v>
       </c>
-      <c r="O41" s="3" t="s">
+      <c r="O41" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="P41" s="3" t="s">
+      <c r="P41" s="4" t="s">
         <v>27</v>
       </c>
       <c r="Q41" s="1">
@@ -4715,7 +4742,7 @@
       <c r="I42" s="1">
         <v>160</v>
       </c>
-      <c r="J42" s="5">
+      <c r="J42" s="6">
         <v>2000000</v>
       </c>
       <c r="K42" s="1">
@@ -4762,7 +4789,7 @@
       <c r="I43" s="1">
         <v>350000</v>
       </c>
-      <c r="J43" s="5">
+      <c r="J43" s="6">
         <v>2000000</v>
       </c>
       <c r="K43" s="1">
@@ -4809,7 +4836,7 @@
       <c r="I44" s="1">
         <v>3500</v>
       </c>
-      <c r="J44" s="5">
+      <c r="J44" s="6">
         <v>2000000</v>
       </c>
       <c r="K44" s="1">
@@ -4871,7 +4898,7 @@
       <c r="N45" s="1">
         <v>50</v>
       </c>
-      <c r="O45" s="4" t="s">
+      <c r="O45" s="5" t="s">
         <v>58</v>
       </c>
       <c r="P45" s="1" t="s">
@@ -4885,7 +4912,7 @@
       <c r="C46" s="1">
         <v>1041</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="4">
         <v>2</v>
       </c>
       <c r="E46" s="1">
@@ -4897,31 +4924,31 @@
       <c r="G46" s="1">
         <v>0</v>
       </c>
-      <c r="H46" s="3">
+      <c r="H46" s="4">
         <v>203</v>
       </c>
-      <c r="I46" s="3">
+      <c r="I46" s="4">
         <v>200</v>
       </c>
-      <c r="J46" s="5">
+      <c r="J46" s="6">
         <v>2000000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3">
+      <c r="K46" s="4">
+        <v>0</v>
+      </c>
+      <c r="L46" s="4">
         <v>5</v>
       </c>
       <c r="M46" s="1">
         <v>5001</v>
       </c>
-      <c r="N46" s="3">
+      <c r="N46" s="4">
         <v>7000</v>
       </c>
-      <c r="O46" s="3" t="s">
+      <c r="O46" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="P46" s="3" t="s">
+      <c r="P46" s="4" t="s">
         <v>27</v>
       </c>
       <c r="Q46" s="1">
@@ -4950,7 +4977,7 @@
       <c r="I47" s="1">
         <v>200</v>
       </c>
-      <c r="J47" s="5">
+      <c r="J47" s="6">
         <v>2000000</v>
       </c>
       <c r="K47" s="1">
@@ -4997,7 +5024,7 @@
       <c r="I48" s="1">
         <v>550000</v>
       </c>
-      <c r="J48" s="5">
+      <c r="J48" s="6">
         <v>2000000</v>
       </c>
       <c r="K48" s="1">
@@ -5044,7 +5071,7 @@
       <c r="I49" s="1">
         <v>55000</v>
       </c>
-      <c r="J49" s="5">
+      <c r="J49" s="6">
         <v>2000000</v>
       </c>
       <c r="K49" s="1">
@@ -5091,7 +5118,7 @@
       <c r="I50" s="1">
         <v>200</v>
       </c>
-      <c r="J50" s="5">
+      <c r="J50" s="6">
         <v>2000000</v>
       </c>
       <c r="K50" s="1">
@@ -5120,7 +5147,7 @@
       <c r="C51" s="1">
         <v>1046</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D51" s="4">
         <v>2</v>
       </c>
       <c r="E51" s="1">
@@ -5132,31 +5159,31 @@
       <c r="G51" s="1">
         <v>0</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H51" s="4">
         <v>203</v>
       </c>
-      <c r="I51" s="3">
+      <c r="I51" s="4">
         <v>240</v>
       </c>
-      <c r="J51" s="5">
+      <c r="J51" s="6">
         <v>2000000</v>
       </c>
-      <c r="K51" s="3">
-        <v>0</v>
-      </c>
-      <c r="L51" s="3">
+      <c r="K51" s="4">
+        <v>0</v>
+      </c>
+      <c r="L51" s="4">
         <v>5</v>
       </c>
       <c r="M51" s="1">
         <v>5001</v>
       </c>
-      <c r="N51" s="3">
+      <c r="N51" s="4">
         <v>7000</v>
       </c>
-      <c r="O51" s="3" t="s">
+      <c r="O51" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="P51" s="3" t="s">
+      <c r="P51" s="4" t="s">
         <v>27</v>
       </c>
       <c r="Q51" s="1">
@@ -5185,7 +5212,7 @@
       <c r="I52" s="1">
         <v>240</v>
       </c>
-      <c r="J52" s="5">
+      <c r="J52" s="6">
         <v>2000000</v>
       </c>
       <c r="K52" s="1">
@@ -5232,7 +5259,7 @@
       <c r="I53" s="1">
         <v>800000</v>
       </c>
-      <c r="J53" s="5">
+      <c r="J53" s="6">
         <v>2000000</v>
       </c>
       <c r="K53" s="1">
@@ -5279,7 +5306,7 @@
       <c r="I54" s="1">
         <v>80000</v>
       </c>
-      <c r="J54" s="5">
+      <c r="J54" s="6">
         <v>2000000</v>
       </c>
       <c r="K54" s="1">
@@ -5326,7 +5353,7 @@
       <c r="I55" s="1">
         <v>300</v>
       </c>
-      <c r="J55" s="5">
+      <c r="J55" s="6">
         <v>2000000</v>
       </c>
       <c r="K55" s="1">
@@ -5363,7 +5390,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G3 G4 E5 F5 G5 R11 E3:E4 F3:F4 H3:R5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R11 C3:R5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -5376,7 +5403,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R57"/>
+  <dimension ref="A1:R62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -6271,65 +6298,435 @@
       <c r="R20" s="2"/>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C21" s="1">
+        <v>3016</v>
+      </c>
+      <c r="D21" s="1">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>301</v>
+      </c>
+      <c r="I21" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>5</v>
+      </c>
+      <c r="M21" s="3">
+        <v>5015</v>
+      </c>
+      <c r="N21" s="1">
+        <v>50</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>16</v>
+      </c>
       <c r="R21" s="2"/>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C22" s="1">
+        <v>3017</v>
+      </c>
+      <c r="D22" s="1">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1">
+        <v>3</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>301</v>
+      </c>
+      <c r="I22" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>5</v>
+      </c>
+      <c r="M22" s="3">
+        <v>5016</v>
+      </c>
+      <c r="N22" s="1">
+        <v>40</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>17</v>
+      </c>
       <c r="R22" s="2"/>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C23" s="1">
+        <v>3018</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3</v>
+      </c>
+      <c r="E23" s="1">
+        <v>3</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>301</v>
+      </c>
+      <c r="I23" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
+        <v>5</v>
+      </c>
+      <c r="M23" s="3">
+        <v>5017</v>
+      </c>
+      <c r="N23" s="1">
+        <v>30</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>18</v>
+      </c>
       <c r="R23" s="2"/>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C24" s="1">
+        <v>3019</v>
+      </c>
+      <c r="D24" s="1">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1">
+        <v>3</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>301</v>
+      </c>
+      <c r="I24" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>5</v>
+      </c>
+      <c r="M24" s="3">
+        <v>5018</v>
+      </c>
+      <c r="N24" s="1">
+        <v>20</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>19</v>
+      </c>
       <c r="R24" s="2"/>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C25" s="1">
+        <v>3020</v>
+      </c>
+      <c r="D25" s="1">
+        <v>3</v>
+      </c>
+      <c r="E25" s="1">
+        <v>3</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>301</v>
+      </c>
+      <c r="I25" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>5</v>
+      </c>
+      <c r="M25" s="3">
+        <v>5019</v>
+      </c>
+      <c r="N25" s="1">
+        <v>10</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>20</v>
+      </c>
       <c r="R25" s="2"/>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C26" s="1">
+        <v>3021</v>
+      </c>
+      <c r="D26" s="1">
+        <v>3</v>
+      </c>
+      <c r="E26" s="1">
+        <v>3</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>301</v>
+      </c>
+      <c r="I26" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>5</v>
+      </c>
+      <c r="M26" s="1">
+        <v>40000013</v>
+      </c>
+      <c r="N26" s="1">
+        <v>25</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>21</v>
+      </c>
       <c r="R26" s="2"/>
     </row>
-    <row r="27" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C27" s="1">
+        <v>3022</v>
+      </c>
+      <c r="D27" s="1">
+        <v>3</v>
+      </c>
+      <c r="E27" s="1">
+        <v>3</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>301</v>
+      </c>
+      <c r="I27" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>5</v>
+      </c>
+      <c r="M27" s="1">
+        <v>40000014</v>
+      </c>
+      <c r="N27" s="1">
+        <v>3</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>22</v>
+      </c>
       <c r="R27" s="2"/>
     </row>
-    <row r="28" customFormat="1" customHeight="1" spans="1:18">
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-    </row>
-    <row r="29" customFormat="1" customHeight="1"/>
-    <row r="30" customFormat="1" customHeight="1"/>
-    <row r="31" customFormat="1" customHeight="1"/>
-    <row r="32" customFormat="1" customHeight="1"/>
-    <row r="33" customFormat="1" customHeight="1"/>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C28" s="1">
+        <v>3023</v>
+      </c>
+      <c r="D28" s="1">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1">
+        <v>3</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>301</v>
+      </c>
+      <c r="I28" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <v>5</v>
+      </c>
+      <c r="M28" s="1">
+        <v>40000015</v>
+      </c>
+      <c r="N28" s="1">
+        <v>1</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>23</v>
+      </c>
+      <c r="R28" s="2"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R29" s="2"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R30" s="2"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="R31" s="2"/>
+    </row>
+    <row r="32" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="2"/>
+    </row>
+    <row r="33" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+    </row>
     <row r="34" customFormat="1" customHeight="1"/>
     <row r="35" customFormat="1" customHeight="1"/>
     <row r="36" customFormat="1" customHeight="1"/>
@@ -6354,9 +6751,14 @@
     <row r="55" customFormat="1" customHeight="1"/>
     <row r="56" customFormat="1" customHeight="1"/>
     <row r="57" customFormat="1" customHeight="1"/>
+    <row r="58" customFormat="1" customHeight="1"/>
+    <row r="59" customFormat="1" customHeight="1"/>
+    <row r="60" customFormat="1" customHeight="1"/>
+    <row r="61" customFormat="1" customHeight="1"/>
+    <row r="62" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G3 G4 E5 F5 G5 E3:E4 F3:F4 R6:R27 H3:R5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M21:M25 R6:R32 C3:R5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -6584,7 +6986,7 @@
         <v>53</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
@@ -6719,7 +7121,7 @@
     <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G3 G4 E5 F5 G5 E3:E4 F3:F4 R6:R27 H3:R5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R6:R27 C3:R5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -6908,12 +7310,6 @@
       <c r="R5" s="2"/>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C6" s="1">
         <v>12001</v>
       </c>
@@ -6951,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
@@ -7005,10 +7401,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="Q7" s="1">
         <v>2</v>
@@ -7059,10 +7455,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="Q8" s="1">
         <v>3</v>
@@ -7113,10 +7509,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="Q9" s="1">
         <v>4</v>
@@ -7167,10 +7563,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="Q10" s="1">
         <v>5</v>
@@ -7221,10 +7617,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="Q11" s="1">
         <v>6</v>
@@ -7344,7 +7740,7 @@
     <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="G3 G4 E5 F5 G5 E3:E4 F3:F4 R6:R27 H3:R5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R6:R27 C3:R5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="91">
   <si>
     <t>#</t>
   </si>
@@ -736,12 +736,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5645,7 +5645,7 @@
         <v>301</v>
       </c>
       <c r="I7" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
@@ -5981,7 +5981,7 @@
         <v>301</v>
       </c>
       <c r="I14" s="1">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="J14" s="1">
         <v>0</v>
@@ -6682,54 +6682,387 @@
       <c r="R28" s="2"/>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C29" s="1">
+        <v>3024</v>
+      </c>
+      <c r="D29" s="1">
+        <v>3</v>
+      </c>
+      <c r="E29" s="1">
+        <v>3</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>301</v>
+      </c>
+      <c r="I29" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>5</v>
+      </c>
+      <c r="M29" s="1">
+        <v>40000003</v>
+      </c>
+      <c r="N29" s="1">
+        <v>2</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>24</v>
+      </c>
       <c r="R29" s="2"/>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C30" s="1">
+        <v>3025</v>
+      </c>
+      <c r="D30" s="1">
+        <v>3</v>
+      </c>
+      <c r="E30" s="1">
+        <v>3</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>301</v>
+      </c>
+      <c r="I30" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1">
+        <v>5</v>
+      </c>
+      <c r="M30" s="1">
+        <v>40000006</v>
+      </c>
+      <c r="N30" s="1">
+        <v>2</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>25</v>
+      </c>
       <c r="R30" s="2"/>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C31" s="1">
+        <v>3026</v>
+      </c>
+      <c r="D31" s="1">
+        <v>3</v>
+      </c>
+      <c r="E31" s="1">
+        <v>3</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>301</v>
+      </c>
+      <c r="I31" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J31" s="1">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
+        <v>5</v>
+      </c>
+      <c r="M31" s="1">
+        <v>40000009</v>
+      </c>
+      <c r="N31" s="1">
+        <v>2</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>26</v>
+      </c>
       <c r="R31" s="2"/>
     </row>
     <row r="32" customFormat="1" customHeight="1" spans="1:18">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
+      <c r="C32" s="1">
+        <v>3027</v>
+      </c>
+      <c r="D32" s="1">
+        <v>3</v>
+      </c>
+      <c r="E32" s="1">
+        <v>3</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>301</v>
+      </c>
+      <c r="I32" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1">
+        <v>5</v>
+      </c>
+      <c r="M32" s="1">
+        <v>40000015</v>
+      </c>
+      <c r="N32" s="1">
+        <v>2</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>27</v>
+      </c>
       <c r="R32" s="2"/>
     </row>
     <row r="33" customFormat="1" customHeight="1" spans="3:17">
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-    </row>
-    <row r="34" customFormat="1" customHeight="1"/>
-    <row r="35" customFormat="1" customHeight="1"/>
-    <row r="36" customFormat="1" customHeight="1"/>
+      <c r="C33" s="1">
+        <v>3028</v>
+      </c>
+      <c r="D33" s="1">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1">
+        <v>3</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>301</v>
+      </c>
+      <c r="I33" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <v>5</v>
+      </c>
+      <c r="M33" s="1">
+        <v>40000003</v>
+      </c>
+      <c r="N33" s="1">
+        <v>2</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C34" s="1">
+        <v>3029</v>
+      </c>
+      <c r="D34" s="1">
+        <v>3</v>
+      </c>
+      <c r="E34" s="1">
+        <v>3</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>301</v>
+      </c>
+      <c r="I34" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0</v>
+      </c>
+      <c r="K34" s="1">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1">
+        <v>5</v>
+      </c>
+      <c r="M34" s="1">
+        <v>40000006</v>
+      </c>
+      <c r="N34" s="1">
+        <v>2</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C35" s="1">
+        <v>3030</v>
+      </c>
+      <c r="D35" s="1">
+        <v>3</v>
+      </c>
+      <c r="E35" s="1">
+        <v>3</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>301</v>
+      </c>
+      <c r="I35" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <v>5</v>
+      </c>
+      <c r="M35" s="1">
+        <v>40000009</v>
+      </c>
+      <c r="N35" s="1">
+        <v>2</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C36" s="1">
+        <v>3031</v>
+      </c>
+      <c r="D36" s="1">
+        <v>3</v>
+      </c>
+      <c r="E36" s="1">
+        <v>3</v>
+      </c>
+      <c r="F36" s="1">
+        <v>1</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>301</v>
+      </c>
+      <c r="I36" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0</v>
+      </c>
+      <c r="K36" s="1">
+        <v>0</v>
+      </c>
+      <c r="L36" s="1">
+        <v>5</v>
+      </c>
+      <c r="M36" s="1">
+        <v>40000015</v>
+      </c>
+      <c r="N36" s="1">
+        <v>2</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>31</v>
+      </c>
+    </row>
     <row r="37" customFormat="1" customHeight="1"/>
     <row r="38" customFormat="1" customHeight="1"/>
     <row r="39" customFormat="1" customHeight="1"/>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="91">
   <si>
     <t>#</t>
   </si>
@@ -5403,7 +5403,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R62"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -7048,7 +7048,7 @@
         <v>5</v>
       </c>
       <c r="M36" s="1">
-        <v>40000015</v>
+        <v>40000012</v>
       </c>
       <c r="N36" s="1">
         <v>2</v>
@@ -7057,38 +7057,1281 @@
         <v>53</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="Q36" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="37" customFormat="1" customHeight="1"/>
-    <row r="38" customFormat="1" customHeight="1"/>
-    <row r="39" customFormat="1" customHeight="1"/>
-    <row r="40" customFormat="1" customHeight="1"/>
-    <row r="41" customFormat="1" customHeight="1"/>
-    <row r="42" customFormat="1" customHeight="1"/>
-    <row r="43" customFormat="1" customHeight="1"/>
-    <row r="44" customFormat="1" customHeight="1"/>
-    <row r="45" customFormat="1" customHeight="1"/>
-    <row r="46" customFormat="1" customHeight="1"/>
-    <row r="47" customFormat="1" customHeight="1"/>
-    <row r="48" customFormat="1" customHeight="1"/>
-    <row r="49" customFormat="1" customHeight="1"/>
-    <row r="50" customFormat="1" customHeight="1"/>
-    <row r="51" customFormat="1" customHeight="1"/>
-    <row r="52" customFormat="1" customHeight="1"/>
-    <row r="53" customFormat="1" customHeight="1"/>
-    <row r="54" customFormat="1" customHeight="1"/>
-    <row r="55" customFormat="1" customHeight="1"/>
-    <row r="56" customFormat="1" customHeight="1"/>
-    <row r="57" customFormat="1" customHeight="1"/>
-    <row r="58" customFormat="1" customHeight="1"/>
-    <row r="59" customFormat="1" customHeight="1"/>
-    <row r="60" customFormat="1" customHeight="1"/>
-    <row r="61" customFormat="1" customHeight="1"/>
-    <row r="62" customFormat="1" customHeight="1"/>
+    <row r="37" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C37" s="1">
+        <v>3032</v>
+      </c>
+      <c r="D37" s="1">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1">
+        <v>3</v>
+      </c>
+      <c r="F37" s="1">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>301</v>
+      </c>
+      <c r="I37" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1">
+        <v>0</v>
+      </c>
+      <c r="L37" s="1">
+        <v>5</v>
+      </c>
+      <c r="M37" s="1">
+        <v>40000006</v>
+      </c>
+      <c r="N37" s="1">
+        <v>2</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C38" s="1">
+        <v>3033</v>
+      </c>
+      <c r="D38" s="1">
+        <v>3</v>
+      </c>
+      <c r="E38" s="1">
+        <v>3</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>301</v>
+      </c>
+      <c r="I38" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1">
+        <v>5</v>
+      </c>
+      <c r="M38" s="1">
+        <v>40000009</v>
+      </c>
+      <c r="N38" s="1">
+        <v>2</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C39" s="1">
+        <v>3034</v>
+      </c>
+      <c r="D39" s="1">
+        <v>3</v>
+      </c>
+      <c r="E39" s="1">
+        <v>3</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>301</v>
+      </c>
+      <c r="I39" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J39" s="1">
+        <v>0</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1">
+        <v>5</v>
+      </c>
+      <c r="M39" s="1">
+        <v>40000012</v>
+      </c>
+      <c r="N39" s="1">
+        <v>2</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C40" s="1">
+        <v>3035</v>
+      </c>
+      <c r="D40" s="1">
+        <v>3</v>
+      </c>
+      <c r="E40" s="1">
+        <v>3</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>301</v>
+      </c>
+      <c r="I40" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J40" s="1">
+        <v>0</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1">
+        <v>5</v>
+      </c>
+      <c r="M40" s="1">
+        <v>40000006</v>
+      </c>
+      <c r="N40" s="1">
+        <v>2</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C41" s="1">
+        <v>3036</v>
+      </c>
+      <c r="D41" s="1">
+        <v>3</v>
+      </c>
+      <c r="E41" s="1">
+        <v>3</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>301</v>
+      </c>
+      <c r="I41" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J41" s="1">
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1">
+        <v>5</v>
+      </c>
+      <c r="M41" s="1">
+        <v>40000009</v>
+      </c>
+      <c r="N41" s="1">
+        <v>2</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C42" s="1">
+        <v>3037</v>
+      </c>
+      <c r="D42" s="1">
+        <v>3</v>
+      </c>
+      <c r="E42" s="1">
+        <v>3</v>
+      </c>
+      <c r="F42" s="1">
+        <v>1</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>301</v>
+      </c>
+      <c r="I42" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1">
+        <v>5</v>
+      </c>
+      <c r="M42" s="1">
+        <v>40000012</v>
+      </c>
+      <c r="N42" s="1">
+        <v>2</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C43" s="1">
+        <v>3038</v>
+      </c>
+      <c r="D43" s="1">
+        <v>3</v>
+      </c>
+      <c r="E43" s="1">
+        <v>3</v>
+      </c>
+      <c r="F43" s="1">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>301</v>
+      </c>
+      <c r="I43" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1">
+        <v>5</v>
+      </c>
+      <c r="M43" s="1">
+        <v>40000006</v>
+      </c>
+      <c r="N43" s="1">
+        <v>2</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C44" s="1">
+        <v>3039</v>
+      </c>
+      <c r="D44" s="1">
+        <v>3</v>
+      </c>
+      <c r="E44" s="1">
+        <v>3</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>301</v>
+      </c>
+      <c r="I44" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0</v>
+      </c>
+      <c r="K44" s="1">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1">
+        <v>5</v>
+      </c>
+      <c r="M44" s="1">
+        <v>40000009</v>
+      </c>
+      <c r="N44" s="1">
+        <v>2</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C45" s="1">
+        <v>3040</v>
+      </c>
+      <c r="D45" s="1">
+        <v>3</v>
+      </c>
+      <c r="E45" s="1">
+        <v>3</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>301</v>
+      </c>
+      <c r="I45" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J45" s="1">
+        <v>0</v>
+      </c>
+      <c r="K45" s="1">
+        <v>0</v>
+      </c>
+      <c r="L45" s="1">
+        <v>5</v>
+      </c>
+      <c r="M45" s="1">
+        <v>40000012</v>
+      </c>
+      <c r="N45" s="1">
+        <v>2</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C46" s="1">
+        <v>3041</v>
+      </c>
+      <c r="D46" s="1">
+        <v>3</v>
+      </c>
+      <c r="E46" s="1">
+        <v>3</v>
+      </c>
+      <c r="F46" s="1">
+        <v>1</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>301</v>
+      </c>
+      <c r="I46" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J46" s="1">
+        <v>0</v>
+      </c>
+      <c r="K46" s="1">
+        <v>0</v>
+      </c>
+      <c r="L46" s="1">
+        <v>5</v>
+      </c>
+      <c r="M46" s="1">
+        <v>40000006</v>
+      </c>
+      <c r="N46" s="1">
+        <v>2</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C47" s="1">
+        <v>3042</v>
+      </c>
+      <c r="D47" s="1">
+        <v>3</v>
+      </c>
+      <c r="E47" s="1">
+        <v>3</v>
+      </c>
+      <c r="F47" s="1">
+        <v>1</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>301</v>
+      </c>
+      <c r="I47" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1">
+        <v>5</v>
+      </c>
+      <c r="M47" s="1">
+        <v>40000009</v>
+      </c>
+      <c r="N47" s="1">
+        <v>2</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C48" s="1">
+        <v>3043</v>
+      </c>
+      <c r="D48" s="1">
+        <v>3</v>
+      </c>
+      <c r="E48" s="1">
+        <v>3</v>
+      </c>
+      <c r="F48" s="1">
+        <v>1</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>301</v>
+      </c>
+      <c r="I48" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J48" s="1">
+        <v>0</v>
+      </c>
+      <c r="K48" s="1">
+        <v>0</v>
+      </c>
+      <c r="L48" s="1">
+        <v>5</v>
+      </c>
+      <c r="M48" s="1">
+        <v>40000012</v>
+      </c>
+      <c r="N48" s="1">
+        <v>2</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C49" s="1">
+        <v>3044</v>
+      </c>
+      <c r="D49" s="1">
+        <v>3</v>
+      </c>
+      <c r="E49" s="1">
+        <v>3</v>
+      </c>
+      <c r="F49" s="1">
+        <v>1</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>301</v>
+      </c>
+      <c r="I49" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J49" s="1">
+        <v>0</v>
+      </c>
+      <c r="K49" s="1">
+        <v>0</v>
+      </c>
+      <c r="L49" s="1">
+        <v>5</v>
+      </c>
+      <c r="M49" s="1">
+        <v>40000006</v>
+      </c>
+      <c r="N49" s="1">
+        <v>2</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q49" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C50" s="1">
+        <v>3045</v>
+      </c>
+      <c r="D50" s="1">
+        <v>3</v>
+      </c>
+      <c r="E50" s="1">
+        <v>3</v>
+      </c>
+      <c r="F50" s="1">
+        <v>1</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>301</v>
+      </c>
+      <c r="I50" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
+        <v>0</v>
+      </c>
+      <c r="L50" s="1">
+        <v>5</v>
+      </c>
+      <c r="M50" s="1">
+        <v>40000009</v>
+      </c>
+      <c r="N50" s="1">
+        <v>2</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C51" s="1">
+        <v>3046</v>
+      </c>
+      <c r="D51" s="1">
+        <v>3</v>
+      </c>
+      <c r="E51" s="1">
+        <v>3</v>
+      </c>
+      <c r="F51" s="1">
+        <v>1</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>301</v>
+      </c>
+      <c r="I51" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0</v>
+      </c>
+      <c r="K51" s="1">
+        <v>0</v>
+      </c>
+      <c r="L51" s="1">
+        <v>5</v>
+      </c>
+      <c r="M51" s="1">
+        <v>40000012</v>
+      </c>
+      <c r="N51" s="1">
+        <v>2</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q51" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C52" s="1">
+        <v>3047</v>
+      </c>
+      <c r="D52" s="1">
+        <v>3</v>
+      </c>
+      <c r="E52" s="1">
+        <v>3</v>
+      </c>
+      <c r="F52" s="1">
+        <v>1</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>301</v>
+      </c>
+      <c r="I52" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J52" s="1">
+        <v>0</v>
+      </c>
+      <c r="K52" s="1">
+        <v>0</v>
+      </c>
+      <c r="L52" s="1">
+        <v>5</v>
+      </c>
+      <c r="M52" s="1">
+        <v>40000006</v>
+      </c>
+      <c r="N52" s="1">
+        <v>2</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q52" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C53" s="1">
+        <v>3048</v>
+      </c>
+      <c r="D53" s="1">
+        <v>3</v>
+      </c>
+      <c r="E53" s="1">
+        <v>3</v>
+      </c>
+      <c r="F53" s="1">
+        <v>1</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>301</v>
+      </c>
+      <c r="I53" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J53" s="1">
+        <v>0</v>
+      </c>
+      <c r="K53" s="1">
+        <v>0</v>
+      </c>
+      <c r="L53" s="1">
+        <v>5</v>
+      </c>
+      <c r="M53" s="1">
+        <v>40000009</v>
+      </c>
+      <c r="N53" s="1">
+        <v>2</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C54" s="1">
+        <v>3049</v>
+      </c>
+      <c r="D54" s="1">
+        <v>3</v>
+      </c>
+      <c r="E54" s="1">
+        <v>3</v>
+      </c>
+      <c r="F54" s="1">
+        <v>1</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>301</v>
+      </c>
+      <c r="I54" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J54" s="1">
+        <v>0</v>
+      </c>
+      <c r="K54" s="1">
+        <v>0</v>
+      </c>
+      <c r="L54" s="1">
+        <v>5</v>
+      </c>
+      <c r="M54" s="1">
+        <v>40000012</v>
+      </c>
+      <c r="N54" s="1">
+        <v>2</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q54" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C55" s="1">
+        <v>3050</v>
+      </c>
+      <c r="D55" s="1">
+        <v>3</v>
+      </c>
+      <c r="E55" s="1">
+        <v>3</v>
+      </c>
+      <c r="F55" s="1">
+        <v>1</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>301</v>
+      </c>
+      <c r="I55" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J55" s="1">
+        <v>0</v>
+      </c>
+      <c r="K55" s="1">
+        <v>0</v>
+      </c>
+      <c r="L55" s="1">
+        <v>5</v>
+      </c>
+      <c r="M55" s="1">
+        <v>40000003</v>
+      </c>
+      <c r="N55" s="1">
+        <v>2</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C56" s="1">
+        <v>3051</v>
+      </c>
+      <c r="D56" s="1">
+        <v>3</v>
+      </c>
+      <c r="E56" s="1">
+        <v>3</v>
+      </c>
+      <c r="F56" s="1">
+        <v>1</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>301</v>
+      </c>
+      <c r="I56" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
+        <v>0</v>
+      </c>
+      <c r="L56" s="1">
+        <v>5</v>
+      </c>
+      <c r="M56" s="1">
+        <v>40000006</v>
+      </c>
+      <c r="N56" s="1">
+        <v>2</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C57" s="1">
+        <v>3052</v>
+      </c>
+      <c r="D57" s="1">
+        <v>3</v>
+      </c>
+      <c r="E57" s="1">
+        <v>3</v>
+      </c>
+      <c r="F57" s="1">
+        <v>1</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>301</v>
+      </c>
+      <c r="I57" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0</v>
+      </c>
+      <c r="K57" s="1">
+        <v>0</v>
+      </c>
+      <c r="L57" s="1">
+        <v>5</v>
+      </c>
+      <c r="M57" s="1">
+        <v>40000009</v>
+      </c>
+      <c r="N57" s="1">
+        <v>2</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:17">
+      <c r="C58" s="1">
+        <v>3053</v>
+      </c>
+      <c r="D58" s="1">
+        <v>3</v>
+      </c>
+      <c r="E58" s="1">
+        <v>3</v>
+      </c>
+      <c r="F58" s="1">
+        <v>1</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>301</v>
+      </c>
+      <c r="I58" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J58" s="1">
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
+        <v>0</v>
+      </c>
+      <c r="L58" s="1">
+        <v>5</v>
+      </c>
+      <c r="M58" s="1">
+        <v>40000003</v>
+      </c>
+      <c r="N58" s="1">
+        <v>2</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C59" s="1">
+        <v>3054</v>
+      </c>
+      <c r="D59" s="1">
+        <v>3</v>
+      </c>
+      <c r="E59" s="1">
+        <v>3</v>
+      </c>
+      <c r="F59" s="1">
+        <v>1</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <v>301</v>
+      </c>
+      <c r="I59" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J59" s="1">
+        <v>0</v>
+      </c>
+      <c r="K59" s="1">
+        <v>0</v>
+      </c>
+      <c r="L59" s="1">
+        <v>5</v>
+      </c>
+      <c r="M59" s="1">
+        <v>40000006</v>
+      </c>
+      <c r="N59" s="1">
+        <v>2</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q59" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C60" s="1">
+        <v>3055</v>
+      </c>
+      <c r="D60" s="1">
+        <v>3</v>
+      </c>
+      <c r="E60" s="1">
+        <v>3</v>
+      </c>
+      <c r="F60" s="1">
+        <v>1</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>301</v>
+      </c>
+      <c r="I60" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J60" s="1">
+        <v>0</v>
+      </c>
+      <c r="K60" s="1">
+        <v>0</v>
+      </c>
+      <c r="L60" s="1">
+        <v>5</v>
+      </c>
+      <c r="M60" s="1">
+        <v>40000009</v>
+      </c>
+      <c r="N60" s="1">
+        <v>2</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C61" s="1">
+        <v>3056</v>
+      </c>
+      <c r="D61" s="1">
+        <v>3</v>
+      </c>
+      <c r="E61" s="1">
+        <v>3</v>
+      </c>
+      <c r="F61" s="1">
+        <v>1</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>301</v>
+      </c>
+      <c r="I61" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J61" s="1">
+        <v>0</v>
+      </c>
+      <c r="K61" s="1">
+        <v>0</v>
+      </c>
+      <c r="L61" s="1">
+        <v>5</v>
+      </c>
+      <c r="M61" s="1">
+        <v>40000003</v>
+      </c>
+      <c r="N61" s="1">
+        <v>2</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C62" s="1">
+        <v>3057</v>
+      </c>
+      <c r="D62" s="1">
+        <v>3</v>
+      </c>
+      <c r="E62" s="1">
+        <v>3</v>
+      </c>
+      <c r="F62" s="1">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>301</v>
+      </c>
+      <c r="I62" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J62" s="1">
+        <v>0</v>
+      </c>
+      <c r="K62" s="1">
+        <v>0</v>
+      </c>
+      <c r="L62" s="1">
+        <v>5</v>
+      </c>
+      <c r="M62" s="1">
+        <v>40000006</v>
+      </c>
+      <c r="N62" s="1">
+        <v>2</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:17">
+      <c r="C63" s="1">
+        <v>3058</v>
+      </c>
+      <c r="D63" s="1">
+        <v>3</v>
+      </c>
+      <c r="E63" s="1">
+        <v>3</v>
+      </c>
+      <c r="F63" s="1">
+        <v>1</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1">
+        <v>301</v>
+      </c>
+      <c r="I63" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J63" s="1">
+        <v>0</v>
+      </c>
+      <c r="K63" s="1">
+        <v>0</v>
+      </c>
+      <c r="L63" s="1">
+        <v>5</v>
+      </c>
+      <c r="M63" s="1">
+        <v>40000009</v>
+      </c>
+      <c r="N63" s="1">
+        <v>2</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P63" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M21:M25 R6:R32 C3:R5" errorStyle="warning">

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -6859,7 +6859,7 @@
         <v>5</v>
       </c>
       <c r="M32" s="1">
-        <v>40000015</v>
+        <v>40000012</v>
       </c>
       <c r="N32" s="1">
         <v>2</v>
@@ -6868,7 +6868,7 @@
         <v>53</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="Q32" s="1">
         <v>27</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="新入世界" sheetId="1" r:id="rId1"/>
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="91">
   <si>
     <t>#</t>
   </si>
@@ -542,13 +542,13 @@
     <t>击杀{0}个怪物，福利1（Z）</t>
   </si>
   <si>
-    <t>奖励5次抽奖</t>
-  </si>
-  <si>
-    <t>击杀{0}个怪物，福利2（Z）</t>
+    <t>击杀{0}个怪物，福利2（泽泽）</t>
   </si>
   <si>
     <t>击杀{0}个怪物，福利3（Z）</t>
+  </si>
+  <si>
+    <t>奖励5次抽奖</t>
   </si>
   <si>
     <t>击杀{0}个怪物，福利4（Z）</t>
@@ -8926,7 +8926,7 @@
         <v>84</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
@@ -8934,12 +8934,6 @@
       <c r="R6" s="2"/>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C7" s="1">
         <v>12002</v>
       </c>
@@ -8977,10 +8971,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Q7" s="1">
         <v>2</v>
@@ -9031,10 +9025,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P8" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="Q8" s="1">
         <v>3</v>
@@ -9088,7 +9082,7 @@
         <v>88</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Q9" s="1">
         <v>4</v>
@@ -9142,7 +9136,7 @@
         <v>89</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Q10" s="1">
         <v>5</v>
@@ -9196,7 +9190,7 @@
         <v>90</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Q11" s="1">
         <v>6</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="新入世界" sheetId="1" r:id="rId1"/>
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="102">
   <si>
     <t>#</t>
   </si>
@@ -446,6 +446,24 @@
     <t>击杀150000个怪物</t>
   </si>
   <si>
+    <t>击杀250000个怪物</t>
+  </si>
+  <si>
+    <t>奖励1本5阶技能自选</t>
+  </si>
+  <si>
+    <t>击杀350000个怪物</t>
+  </si>
+  <si>
+    <t>奖励1本6阶技能自选</t>
+  </si>
+  <si>
+    <t>击杀450000个怪物</t>
+  </si>
+  <si>
+    <t>击杀550000个怪物</t>
+  </si>
+  <si>
     <t>击杀{0}个怪物</t>
   </si>
   <si>
@@ -545,19 +563,34 @@
     <t>击杀{0}个怪物，福利2（泽泽）</t>
   </si>
   <si>
-    <t>击杀{0}个怪物，福利3（Z）</t>
-  </si>
-  <si>
-    <t>奖励5次抽奖</t>
-  </si>
-  <si>
-    <t>击杀{0}个怪物，福利4（Z）</t>
-  </si>
-  <si>
-    <t>击杀{0}个怪物，福利5（Z）</t>
-  </si>
-  <si>
-    <t>击杀{0}个怪物，福利6（Z）</t>
+    <t>击杀{0}个怪物，新手十抽1</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，新手十抽2</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，新手十抽3</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，新手十抽4</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，新手十抽5</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，新手十抽6</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，新手十抽7</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，新手十抽8</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，新手十抽9</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，新手十抽10</t>
   </si>
 </sst>
 </file>
@@ -1207,12 +1240,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2819,10 +2853,194 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" customFormat="1" customHeight="1"/>
-    <row r="30" customFormat="1" customHeight="1"/>
-    <row r="31" customFormat="1" customHeight="1"/>
-    <row r="32" customFormat="1" customHeight="1"/>
+    <row r="29" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>301</v>
+      </c>
+      <c r="I29" s="1">
+        <v>250000</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>8</v>
+      </c>
+      <c r="M29" s="1">
+        <v>5</v>
+      </c>
+      <c r="N29" s="1">
+        <v>1</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>301</v>
+      </c>
+      <c r="I30" s="1">
+        <v>350000</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1">
+        <v>8</v>
+      </c>
+      <c r="M30" s="1">
+        <v>6</v>
+      </c>
+      <c r="N30" s="1">
+        <v>1</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>301</v>
+      </c>
+      <c r="I31" s="1">
+        <v>450000</v>
+      </c>
+      <c r="J31" s="1">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
+        <v>8</v>
+      </c>
+      <c r="M31" s="1">
+        <v>5</v>
+      </c>
+      <c r="N31" s="1">
+        <v>1</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C32" s="1">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>301</v>
+      </c>
+      <c r="I32" s="1">
+        <v>550000</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1">
+        <v>8</v>
+      </c>
+      <c r="M32" s="1">
+        <v>6</v>
+      </c>
+      <c r="N32" s="1">
+        <v>1</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>27</v>
+      </c>
+    </row>
     <row r="33" customFormat="1" customHeight="1"/>
     <row r="34" customFormat="1" customHeight="1"/>
     <row r="35" customFormat="1" customHeight="1"/>
@@ -3065,7 +3283,7 @@
         <v>1000</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>27</v>
@@ -3112,7 +3330,7 @@
         <v>1000</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>27</v>
@@ -3159,7 +3377,7 @@
         <v>1000</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>27</v>
@@ -3206,7 +3424,7 @@
         <v>1000</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>27</v>
@@ -3253,7 +3471,7 @@
         <v>1000</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>27</v>
@@ -3300,7 +3518,7 @@
         <v>2000</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>27</v>
@@ -3348,7 +3566,7 @@
         <v>20</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>29</v>
@@ -3395,10 +3613,10 @@
         <v>10</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="Q13" s="1">
         <v>8</v>
@@ -3442,7 +3660,7 @@
         <v>2000</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>27</v>
@@ -3488,8 +3706,8 @@
       <c r="N15" s="1">
         <v>20</v>
       </c>
-      <c r="O15" s="5" t="s">
-        <v>58</v>
+      <c r="O15" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>29</v>
@@ -3498,11 +3716,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" s="4" customFormat="1" customHeight="1" spans="3:18">
+    <row r="16" s="5" customFormat="1" customHeight="1" spans="3:18">
       <c r="C16" s="1">
         <v>1011</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <v>2</v>
       </c>
       <c r="E16" s="1">
@@ -3514,31 +3732,31 @@
       <c r="G16" s="1">
         <v>0</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="5">
         <v>203</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="5">
         <v>20</v>
       </c>
       <c r="J16" s="1">
         <v>1500000</v>
       </c>
-      <c r="K16" s="4">
-        <v>0</v>
-      </c>
-      <c r="L16" s="4">
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
         <v>5</v>
       </c>
       <c r="M16" s="1">
         <v>5001</v>
       </c>
-      <c r="N16" s="4">
+      <c r="N16" s="5">
         <v>3000</v>
       </c>
-      <c r="O16" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="P16" s="4" t="s">
+      <c r="O16" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P16" s="5" t="s">
         <v>27</v>
       </c>
       <c r="Q16" s="1">
@@ -3583,7 +3801,7 @@
         <v>30</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>29</v>
@@ -3630,10 +3848,10 @@
         <v>15</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="Q18" s="1">
         <v>13</v>
@@ -3677,7 +3895,7 @@
         <v>3000</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>27</v>
@@ -3724,7 +3942,7 @@
         <v>30</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>29</v>
@@ -3733,11 +3951,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" s="4" customFormat="1" customHeight="1" spans="3:17">
+    <row r="21" s="5" customFormat="1" customHeight="1" spans="3:17">
       <c r="C21" s="1">
         <v>1016</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="5">
         <v>2</v>
       </c>
       <c r="E21" s="1">
@@ -3749,31 +3967,31 @@
       <c r="G21" s="1">
         <v>0</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="5">
         <v>203</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="5">
         <v>35</v>
       </c>
       <c r="J21" s="1">
         <v>1500000</v>
       </c>
-      <c r="K21" s="4">
-        <v>0</v>
-      </c>
-      <c r="L21" s="4">
+      <c r="K21" s="5">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5">
         <v>5</v>
       </c>
       <c r="M21" s="1">
         <v>5001</v>
       </c>
-      <c r="N21" s="4">
+      <c r="N21" s="5">
         <v>4000</v>
       </c>
-      <c r="O21" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="P21" s="4" t="s">
+      <c r="O21" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P21" s="5" t="s">
         <v>27</v>
       </c>
       <c r="Q21" s="1">
@@ -3818,7 +4036,7 @@
         <v>40</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>29</v>
@@ -3865,10 +4083,10 @@
         <v>20</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="Q23" s="1">
         <v>18</v>
@@ -3912,7 +4130,7 @@
         <v>4000</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>27</v>
@@ -3958,8 +4176,8 @@
       <c r="N25" s="1">
         <v>40</v>
       </c>
-      <c r="O25" s="5" t="s">
-        <v>58</v>
+      <c r="O25" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>29</v>
@@ -3968,11 +4186,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" s="4" customFormat="1" customHeight="1" spans="3:17">
+    <row r="26" s="5" customFormat="1" customHeight="1" spans="3:17">
       <c r="C26" s="1">
         <v>1021</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="5">
         <v>2</v>
       </c>
       <c r="E26" s="1">
@@ -3984,31 +4202,31 @@
       <c r="G26" s="1">
         <v>0</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H26" s="5">
         <v>203</v>
       </c>
-      <c r="I26" s="4">
+      <c r="I26" s="5">
         <v>55</v>
       </c>
       <c r="J26" s="1">
         <v>1500000</v>
       </c>
-      <c r="K26" s="4">
-        <v>0</v>
-      </c>
-      <c r="L26" s="4">
+      <c r="K26" s="5">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5">
         <v>5</v>
       </c>
       <c r="M26" s="1">
         <v>5001</v>
       </c>
-      <c r="N26" s="4">
+      <c r="N26" s="5">
         <v>5000</v>
       </c>
-      <c r="O26" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="P26" s="4" t="s">
+      <c r="O26" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P26" s="5" t="s">
         <v>27</v>
       </c>
       <c r="Q26" s="1">
@@ -4037,7 +4255,7 @@
       <c r="I27" s="1">
         <v>55</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27" s="7">
         <v>2000000</v>
       </c>
       <c r="K27" s="1">
@@ -4053,7 +4271,7 @@
         <v>50</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>29</v>
@@ -4084,7 +4302,7 @@
       <c r="I28" s="1">
         <v>50000</v>
       </c>
-      <c r="J28" s="6">
+      <c r="J28" s="7">
         <v>2000000</v>
       </c>
       <c r="K28" s="1">
@@ -4100,10 +4318,10 @@
         <v>25</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="Q28" s="1">
         <v>23</v>
@@ -4131,7 +4349,7 @@
       <c r="I29" s="1">
         <v>5000</v>
       </c>
-      <c r="J29" s="6">
+      <c r="J29" s="7">
         <v>2000000</v>
       </c>
       <c r="K29" s="1">
@@ -4147,7 +4365,7 @@
         <v>5000</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>27</v>
@@ -4178,7 +4396,7 @@
       <c r="I30" s="1">
         <v>10</v>
       </c>
-      <c r="J30" s="6">
+      <c r="J30" s="7">
         <v>2000000</v>
       </c>
       <c r="K30" s="1">
@@ -4194,7 +4412,7 @@
         <v>50</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>29</v>
@@ -4207,7 +4425,7 @@
       <c r="C31" s="1">
         <v>1026</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="5">
         <v>2</v>
       </c>
       <c r="E31" s="1">
@@ -4219,31 +4437,31 @@
       <c r="G31" s="1">
         <v>0</v>
       </c>
-      <c r="H31" s="4">
+      <c r="H31" s="5">
         <v>203</v>
       </c>
-      <c r="I31" s="4">
+      <c r="I31" s="5">
         <v>85</v>
       </c>
-      <c r="J31" s="6">
+      <c r="J31" s="7">
         <v>2000000</v>
       </c>
-      <c r="K31" s="4">
-        <v>0</v>
-      </c>
-      <c r="L31" s="4">
+      <c r="K31" s="5">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5">
         <v>5</v>
       </c>
       <c r="M31" s="1">
         <v>5001</v>
       </c>
-      <c r="N31" s="4">
+      <c r="N31" s="5">
         <v>6000</v>
       </c>
-      <c r="O31" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="P31" s="4" t="s">
+      <c r="O31" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P31" s="5" t="s">
         <v>27</v>
       </c>
       <c r="Q31" s="1">
@@ -4269,10 +4487,10 @@
       <c r="H32" s="1">
         <v>202</v>
       </c>
-      <c r="I32" s="4">
+      <c r="I32" s="5">
         <v>85</v>
       </c>
-      <c r="J32" s="6">
+      <c r="J32" s="7">
         <v>2000000</v>
       </c>
       <c r="K32" s="1">
@@ -4288,7 +4506,7 @@
         <v>50</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>29</v>
@@ -4319,7 +4537,7 @@
       <c r="I33" s="1">
         <v>100000</v>
       </c>
-      <c r="J33" s="6">
+      <c r="J33" s="7">
         <v>2000000</v>
       </c>
       <c r="K33" s="1">
@@ -4335,10 +4553,10 @@
         <v>30</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="Q33" s="1">
         <v>28</v>
@@ -4366,7 +4584,7 @@
       <c r="I34" s="1">
         <v>10000</v>
       </c>
-      <c r="J34" s="6">
+      <c r="J34" s="7">
         <v>2000000</v>
       </c>
       <c r="K34" s="1">
@@ -4382,7 +4600,7 @@
         <v>6000</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>27</v>
@@ -4428,8 +4646,8 @@
       <c r="N35" s="1">
         <v>50</v>
       </c>
-      <c r="O35" s="5" t="s">
-        <v>58</v>
+      <c r="O35" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>29</v>
@@ -4442,7 +4660,7 @@
       <c r="C36" s="1">
         <v>1031</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="5">
         <v>2</v>
       </c>
       <c r="E36" s="1">
@@ -4454,31 +4672,31 @@
       <c r="G36" s="1">
         <v>0</v>
       </c>
-      <c r="H36" s="4">
+      <c r="H36" s="5">
         <v>203</v>
       </c>
-      <c r="I36" s="4">
+      <c r="I36" s="5">
         <v>120</v>
       </c>
-      <c r="J36" s="6">
+      <c r="J36" s="7">
         <v>2000000</v>
       </c>
-      <c r="K36" s="4">
-        <v>0</v>
-      </c>
-      <c r="L36" s="4">
+      <c r="K36" s="5">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5">
         <v>5</v>
       </c>
       <c r="M36" s="1">
         <v>5001</v>
       </c>
-      <c r="N36" s="4">
+      <c r="N36" s="5">
         <v>7000</v>
       </c>
-      <c r="O36" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="P36" s="4" t="s">
+      <c r="O36" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P36" s="5" t="s">
         <v>27</v>
       </c>
       <c r="Q36" s="1">
@@ -4507,7 +4725,7 @@
       <c r="I37" s="1">
         <v>120</v>
       </c>
-      <c r="J37" s="6">
+      <c r="J37" s="7">
         <v>2000000</v>
       </c>
       <c r="K37" s="1">
@@ -4523,7 +4741,7 @@
         <v>50</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>29</v>
@@ -4554,7 +4772,7 @@
       <c r="I38" s="1">
         <v>200000</v>
       </c>
-      <c r="J38" s="6">
+      <c r="J38" s="7">
         <v>2000000</v>
       </c>
       <c r="K38" s="1">
@@ -4570,10 +4788,10 @@
         <v>35</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="Q38" s="1">
         <v>33</v>
@@ -4601,7 +4819,7 @@
       <c r="I39" s="1">
         <v>20000</v>
       </c>
-      <c r="J39" s="6">
+      <c r="J39" s="7">
         <v>2000000</v>
       </c>
       <c r="K39" s="1">
@@ -4617,7 +4835,7 @@
         <v>7000</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>27</v>
@@ -4648,7 +4866,7 @@
       <c r="I40" s="1">
         <v>50</v>
       </c>
-      <c r="J40" s="6">
+      <c r="J40" s="7">
         <v>2000000</v>
       </c>
       <c r="K40" s="1">
@@ -4664,7 +4882,7 @@
         <v>50</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>29</v>
@@ -4677,7 +4895,7 @@
       <c r="C41" s="1">
         <v>1036</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="5">
         <v>2</v>
       </c>
       <c r="E41" s="1">
@@ -4689,31 +4907,31 @@
       <c r="G41" s="1">
         <v>0</v>
       </c>
-      <c r="H41" s="4">
+      <c r="H41" s="5">
         <v>203</v>
       </c>
-      <c r="I41" s="4">
+      <c r="I41" s="5">
         <v>160</v>
       </c>
-      <c r="J41" s="6">
+      <c r="J41" s="7">
         <v>2000000</v>
       </c>
-      <c r="K41" s="4">
-        <v>0</v>
-      </c>
-      <c r="L41" s="4">
+      <c r="K41" s="5">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5">
         <v>5</v>
       </c>
       <c r="M41" s="1">
         <v>5001</v>
       </c>
-      <c r="N41" s="4">
+      <c r="N41" s="5">
         <v>7000</v>
       </c>
-      <c r="O41" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="P41" s="4" t="s">
+      <c r="O41" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P41" s="5" t="s">
         <v>27</v>
       </c>
       <c r="Q41" s="1">
@@ -4742,7 +4960,7 @@
       <c r="I42" s="1">
         <v>160</v>
       </c>
-      <c r="J42" s="6">
+      <c r="J42" s="7">
         <v>2000000</v>
       </c>
       <c r="K42" s="1">
@@ -4758,7 +4976,7 @@
         <v>50</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>29</v>
@@ -4789,7 +5007,7 @@
       <c r="I43" s="1">
         <v>350000</v>
       </c>
-      <c r="J43" s="6">
+      <c r="J43" s="7">
         <v>2000000</v>
       </c>
       <c r="K43" s="1">
@@ -4805,10 +5023,10 @@
         <v>35</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="Q43" s="1">
         <v>38</v>
@@ -4836,7 +5054,7 @@
       <c r="I44" s="1">
         <v>3500</v>
       </c>
-      <c r="J44" s="6">
+      <c r="J44" s="7">
         <v>2000000</v>
       </c>
       <c r="K44" s="1">
@@ -4852,7 +5070,7 @@
         <v>7000</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>27</v>
@@ -4898,8 +5116,8 @@
       <c r="N45" s="1">
         <v>50</v>
       </c>
-      <c r="O45" s="5" t="s">
-        <v>58</v>
+      <c r="O45" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>29</v>
@@ -4912,7 +5130,7 @@
       <c r="C46" s="1">
         <v>1041</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="5">
         <v>2</v>
       </c>
       <c r="E46" s="1">
@@ -4924,31 +5142,31 @@
       <c r="G46" s="1">
         <v>0</v>
       </c>
-      <c r="H46" s="4">
+      <c r="H46" s="5">
         <v>203</v>
       </c>
-      <c r="I46" s="4">
+      <c r="I46" s="5">
         <v>200</v>
       </c>
-      <c r="J46" s="6">
+      <c r="J46" s="7">
         <v>2000000</v>
       </c>
-      <c r="K46" s="4">
-        <v>0</v>
-      </c>
-      <c r="L46" s="4">
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5">
         <v>5</v>
       </c>
       <c r="M46" s="1">
         <v>5001</v>
       </c>
-      <c r="N46" s="4">
+      <c r="N46" s="5">
         <v>7000</v>
       </c>
-      <c r="O46" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="P46" s="4" t="s">
+      <c r="O46" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P46" s="5" t="s">
         <v>27</v>
       </c>
       <c r="Q46" s="1">
@@ -4977,7 +5195,7 @@
       <c r="I47" s="1">
         <v>200</v>
       </c>
-      <c r="J47" s="6">
+      <c r="J47" s="7">
         <v>2000000</v>
       </c>
       <c r="K47" s="1">
@@ -4993,7 +5211,7 @@
         <v>50</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>29</v>
@@ -5024,7 +5242,7 @@
       <c r="I48" s="1">
         <v>550000</v>
       </c>
-      <c r="J48" s="6">
+      <c r="J48" s="7">
         <v>2000000</v>
       </c>
       <c r="K48" s="1">
@@ -5040,10 +5258,10 @@
         <v>35</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="Q48" s="1">
         <v>43</v>
@@ -5071,7 +5289,7 @@
       <c r="I49" s="1">
         <v>55000</v>
       </c>
-      <c r="J49" s="6">
+      <c r="J49" s="7">
         <v>2000000</v>
       </c>
       <c r="K49" s="1">
@@ -5087,7 +5305,7 @@
         <v>7000</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>27</v>
@@ -5118,7 +5336,7 @@
       <c r="I50" s="1">
         <v>200</v>
       </c>
-      <c r="J50" s="6">
+      <c r="J50" s="7">
         <v>2000000</v>
       </c>
       <c r="K50" s="1">
@@ -5134,7 +5352,7 @@
         <v>50</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>29</v>
@@ -5147,7 +5365,7 @@
       <c r="C51" s="1">
         <v>1046</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="5">
         <v>2</v>
       </c>
       <c r="E51" s="1">
@@ -5159,31 +5377,31 @@
       <c r="G51" s="1">
         <v>0</v>
       </c>
-      <c r="H51" s="4">
+      <c r="H51" s="5">
         <v>203</v>
       </c>
-      <c r="I51" s="4">
+      <c r="I51" s="5">
         <v>240</v>
       </c>
-      <c r="J51" s="6">
+      <c r="J51" s="7">
         <v>2000000</v>
       </c>
-      <c r="K51" s="4">
-        <v>0</v>
-      </c>
-      <c r="L51" s="4">
+      <c r="K51" s="5">
+        <v>0</v>
+      </c>
+      <c r="L51" s="5">
         <v>5</v>
       </c>
       <c r="M51" s="1">
         <v>5001</v>
       </c>
-      <c r="N51" s="4">
+      <c r="N51" s="5">
         <v>7000</v>
       </c>
-      <c r="O51" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="P51" s="4" t="s">
+      <c r="O51" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P51" s="5" t="s">
         <v>27</v>
       </c>
       <c r="Q51" s="1">
@@ -5212,7 +5430,7 @@
       <c r="I52" s="1">
         <v>240</v>
       </c>
-      <c r="J52" s="6">
+      <c r="J52" s="7">
         <v>2000000</v>
       </c>
       <c r="K52" s="1">
@@ -5228,7 +5446,7 @@
         <v>50</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>29</v>
@@ -5259,7 +5477,7 @@
       <c r="I53" s="1">
         <v>800000</v>
       </c>
-      <c r="J53" s="6">
+      <c r="J53" s="7">
         <v>2000000</v>
       </c>
       <c r="K53" s="1">
@@ -5275,10 +5493,10 @@
         <v>35</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="Q53" s="1">
         <v>48</v>
@@ -5306,7 +5524,7 @@
       <c r="I54" s="1">
         <v>80000</v>
       </c>
-      <c r="J54" s="6">
+      <c r="J54" s="7">
         <v>2000000</v>
       </c>
       <c r="K54" s="1">
@@ -5322,7 +5540,7 @@
         <v>7000</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>27</v>
@@ -5353,7 +5571,7 @@
       <c r="I55" s="1">
         <v>300</v>
       </c>
-      <c r="J55" s="6">
+      <c r="J55" s="7">
         <v>2000000</v>
       </c>
       <c r="K55" s="1">
@@ -5369,7 +5587,7 @@
         <v>50</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>29</v>
@@ -5615,10 +5833,10 @@
         <v>1</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
@@ -5663,10 +5881,10 @@
         <v>1</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="Q7" s="1">
         <v>2</v>
@@ -5711,10 +5929,10 @@
         <v>25</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="Q8" s="1">
         <v>3</v>
@@ -5759,10 +5977,10 @@
         <v>3</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="Q9" s="1">
         <v>4</v>
@@ -5807,10 +6025,10 @@
         <v>1</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="Q10" s="1">
         <v>5</v>
@@ -5855,10 +6073,10 @@
         <v>25</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="Q11" s="1">
         <v>6</v>
@@ -5903,10 +6121,10 @@
         <v>3</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Q12" s="1">
         <v>7</v>
@@ -5951,10 +6169,10 @@
         <v>1</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Q13" s="1">
         <v>8</v>
@@ -5999,10 +6217,10 @@
         <v>1</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="Q14" s="1">
         <v>9</v>
@@ -6047,10 +6265,10 @@
         <v>25</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="Q15" s="1">
         <v>10</v>
@@ -6095,10 +6313,10 @@
         <v>3</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="Q16" s="1">
         <v>11</v>
@@ -6143,10 +6361,10 @@
         <v>1</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q17" s="1">
         <v>12</v>
@@ -6191,10 +6409,10 @@
         <v>25</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="1">
         <v>13</v>
@@ -6239,10 +6457,10 @@
         <v>3</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="Q19" s="1">
         <v>14</v>
@@ -6287,10 +6505,10 @@
         <v>1</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q20" s="1">
         <v>15</v>
@@ -6328,17 +6546,17 @@
       <c r="L21" s="1">
         <v>5</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="4">
         <v>5015</v>
       </c>
       <c r="N21" s="1">
         <v>50</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q21" s="1">
         <v>16</v>
@@ -6376,17 +6594,17 @@
       <c r="L22" s="1">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="4">
         <v>5016</v>
       </c>
       <c r="N22" s="1">
         <v>40</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="Q22" s="1">
         <v>17</v>
@@ -6424,17 +6642,17 @@
       <c r="L23" s="1">
         <v>5</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="4">
         <v>5017</v>
       </c>
       <c r="N23" s="1">
         <v>30</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="Q23" s="1">
         <v>18</v>
@@ -6472,17 +6690,17 @@
       <c r="L24" s="1">
         <v>5</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="4">
         <v>5018</v>
       </c>
       <c r="N24" s="1">
         <v>20</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="Q24" s="1">
         <v>19</v>
@@ -6520,17 +6738,17 @@
       <c r="L25" s="1">
         <v>5</v>
       </c>
-      <c r="M25" s="3">
+      <c r="M25" s="4">
         <v>5019</v>
       </c>
       <c r="N25" s="1">
         <v>10</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="Q25" s="1">
         <v>20</v>
@@ -6575,10 +6793,10 @@
         <v>25</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="Q26" s="1">
         <v>21</v>
@@ -6623,10 +6841,10 @@
         <v>3</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="Q27" s="1">
         <v>22</v>
@@ -6671,10 +6889,10 @@
         <v>1</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="Q28" s="1">
         <v>23</v>
@@ -6719,10 +6937,10 @@
         <v>2</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="Q29" s="1">
         <v>24</v>
@@ -6767,10 +6985,10 @@
         <v>2</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Q30" s="1">
         <v>25</v>
@@ -6815,10 +7033,10 @@
         <v>2</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q31" s="1">
         <v>26</v>
@@ -6865,10 +7083,10 @@
         <v>2</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q32" s="1">
         <v>27</v>
@@ -6913,10 +7131,10 @@
         <v>2</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="Q33" s="1">
         <v>28</v>
@@ -6960,10 +7178,10 @@
         <v>2</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Q34" s="1">
         <v>29</v>
@@ -7007,10 +7225,10 @@
         <v>2</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q35" s="1">
         <v>30</v>
@@ -7054,10 +7272,10 @@
         <v>2</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q36" s="1">
         <v>31</v>
@@ -7101,10 +7319,10 @@
         <v>2</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Q37" s="1">
         <v>32</v>
@@ -7148,10 +7366,10 @@
         <v>2</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q38" s="1">
         <v>33</v>
@@ -7195,10 +7413,10 @@
         <v>2</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q39" s="1">
         <v>34</v>
@@ -7242,10 +7460,10 @@
         <v>2</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Q40" s="1">
         <v>35</v>
@@ -7289,10 +7507,10 @@
         <v>2</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q41" s="1">
         <v>36</v>
@@ -7336,10 +7554,10 @@
         <v>2</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q42" s="1">
         <v>37</v>
@@ -7383,10 +7601,10 @@
         <v>2</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Q43" s="1">
         <v>38</v>
@@ -7430,10 +7648,10 @@
         <v>2</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q44" s="1">
         <v>39</v>
@@ -7477,10 +7695,10 @@
         <v>2</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q45" s="1">
         <v>40</v>
@@ -7524,10 +7742,10 @@
         <v>2</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Q46" s="1">
         <v>41</v>
@@ -7571,10 +7789,10 @@
         <v>2</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q47" s="1">
         <v>42</v>
@@ -7618,10 +7836,10 @@
         <v>2</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q48" s="1">
         <v>43</v>
@@ -7665,10 +7883,10 @@
         <v>2</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Q49" s="1">
         <v>44</v>
@@ -7712,10 +7930,10 @@
         <v>2</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q50" s="1">
         <v>45</v>
@@ -7759,10 +7977,10 @@
         <v>2</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q51" s="1">
         <v>46</v>
@@ -7806,10 +8024,10 @@
         <v>2</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Q52" s="1">
         <v>47</v>
@@ -7853,10 +8071,10 @@
         <v>2</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q53" s="1">
         <v>48</v>
@@ -7900,10 +8118,10 @@
         <v>2</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q54" s="1">
         <v>49</v>
@@ -7947,10 +8165,10 @@
         <v>2</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="Q55" s="1">
         <v>50</v>
@@ -7994,10 +8212,10 @@
         <v>2</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Q56" s="1">
         <v>51</v>
@@ -8041,10 +8259,10 @@
         <v>2</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q57" s="1">
         <v>52</v>
@@ -8088,10 +8306,10 @@
         <v>2</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="Q58" s="1">
         <v>53</v>
@@ -8135,10 +8353,10 @@
         <v>2</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Q59" s="1">
         <v>54</v>
@@ -8182,10 +8400,10 @@
         <v>2</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q60" s="1">
         <v>55</v>
@@ -8229,10 +8447,10 @@
         <v>2</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="Q61" s="1">
         <v>56</v>
@@ -8276,10 +8494,10 @@
         <v>2</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Q62" s="1">
         <v>57</v>
@@ -8323,10 +8541,10 @@
         <v>2</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q63" s="1">
         <v>58</v>
@@ -8559,10 +8777,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
@@ -8729,17 +8947,17 @@
     <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="R1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="R2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -8789,7 +9007,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
@@ -8837,7 +9055,7 @@
       </c>
       <c r="R4" s="2"/>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
@@ -8885,7 +9103,7 @@
       </c>
       <c r="R5" s="2"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C6" s="1">
         <v>12001</v>
       </c>
@@ -8923,17 +9141,17 @@
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="Q6" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R6" s="2"/>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C7" s="1">
         <v>12002</v>
       </c>
@@ -8971,23 +9189,17 @@
         <v>0</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="Q7" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R7" s="2"/>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C8" s="1">
         <v>12003</v>
       </c>
@@ -9025,23 +9237,17 @@
         <v>0</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="Q8" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R8" s="2"/>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C9" s="1">
         <v>12004</v>
       </c>
@@ -9079,23 +9285,17 @@
         <v>0</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="Q9" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R9" s="2"/>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C10" s="1">
         <v>12005</v>
       </c>
@@ -9133,23 +9333,17 @@
         <v>0</v>
       </c>
       <c r="O10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="P10" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="Q10" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R10" s="2"/>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C11" s="1">
         <v>12006</v>
       </c>
@@ -9187,32 +9381,302 @@
         <v>0</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="Q11" s="1">
+        <v>4</v>
+      </c>
+      <c r="R11" s="2"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C12" s="1">
+        <v>12007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>12</v>
+      </c>
+      <c r="E12" s="1">
+        <v>12</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1">
+        <v>301</v>
+      </c>
+      <c r="I12" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>5</v>
+      </c>
+      <c r="R12" s="2"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C13" s="1">
+        <v>12008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>12</v>
+      </c>
+      <c r="E13" s="1">
+        <v>12</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1">
+        <v>301</v>
+      </c>
+      <c r="I13" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q13" s="1">
         <v>6</v>
       </c>
-      <c r="R11" s="2"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="R12" s="2"/>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="R13" s="2"/>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C14" s="1">
+        <v>12009</v>
+      </c>
+      <c r="D14" s="1">
+        <v>12</v>
+      </c>
+      <c r="E14" s="1">
+        <v>12</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>301</v>
+      </c>
+      <c r="I14" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M14" s="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>7</v>
+      </c>
       <c r="R14" s="2"/>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C15" s="1">
+        <v>12010</v>
+      </c>
+      <c r="D15" s="1">
+        <v>12</v>
+      </c>
+      <c r="E15" s="1">
+        <v>12</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
+        <v>301</v>
+      </c>
+      <c r="I15" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>8</v>
+      </c>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C16" s="1">
+        <v>12011</v>
+      </c>
+      <c r="D16" s="1">
+        <v>12</v>
+      </c>
+      <c r="E16" s="1">
+        <v>12</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1">
+        <v>301</v>
+      </c>
+      <c r="I16" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M16" s="1">
+        <v>1</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>9</v>
+      </c>
       <c r="R16" s="2"/>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C17" s="1">
+        <v>12012</v>
+      </c>
+      <c r="D17" s="1">
+        <v>12</v>
+      </c>
+      <c r="E17" s="1">
+        <v>12</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1">
+        <v>301</v>
+      </c>
+      <c r="I17" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M17" s="1">
+        <v>1</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>10</v>
+      </c>
       <c r="R17" s="2"/>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:18">

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="25600" windowHeight="11480" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="新入世界" sheetId="1" r:id="rId1"/>
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="103">
   <si>
     <t>#</t>
   </si>
@@ -591,6 +591,9 @@
   </si>
   <si>
     <t>击杀{0}个怪物，新手十抽10</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，新手十抽11</t>
   </si>
 </sst>
 </file>
@@ -8928,7 +8931,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R57"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
@@ -9680,6 +9683,51 @@
       <c r="R17" s="2"/>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C18" s="1">
+        <v>12013</v>
+      </c>
+      <c r="D18" s="1">
+        <v>12</v>
+      </c>
+      <c r="E18" s="1">
+        <v>12</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
+        <v>301</v>
+      </c>
+      <c r="I18" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M18" s="1">
+        <v>1</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>13</v>
+      </c>
       <c r="R18" s="2"/>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:18">
@@ -9703,12 +9751,27 @@
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="R25" s="2"/>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="26" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
       <c r="R26" s="2"/>
     </row>
     <row r="27" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -9724,25 +9787,8 @@
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
-      <c r="R27" s="2"/>
-    </row>
-    <row r="28" customFormat="1" customHeight="1" spans="1:18">
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-    </row>
+    </row>
+    <row r="28" customFormat="1" customHeight="1"/>
     <row r="29" customFormat="1" customHeight="1"/>
     <row r="30" customFormat="1" customHeight="1"/>
     <row r="31" customFormat="1" customHeight="1"/>
@@ -9771,10 +9817,9 @@
     <row r="54" customFormat="1" customHeight="1"/>
     <row r="55" customFormat="1" customHeight="1"/>
     <row r="56" customFormat="1" customHeight="1"/>
-    <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R6:R27 C3:R5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R6:R18 R19:R26 C3:R5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11480" activeTab="4"/>
+    <workbookView windowWidth="25600" windowHeight="11480" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="新入世界" sheetId="1" r:id="rId1"/>
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="103">
   <si>
     <t>#</t>
   </si>
@@ -5624,7 +5624,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R63"/>
+  <dimension ref="A1:R68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -7848,7 +7848,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="49" customFormat="1" customHeight="1" spans="3:17">
+    <row r="49" customFormat="1" customHeight="1" spans="3:18">
       <c r="C49" s="1">
         <v>3044</v>
       </c>
@@ -7895,7 +7895,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" customFormat="1" customHeight="1" spans="3:17">
+    <row r="50" customFormat="1" customHeight="1" spans="3:18">
       <c r="C50" s="1">
         <v>3045</v>
       </c>
@@ -7942,7 +7942,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="51" customFormat="1" customHeight="1" spans="3:17">
+    <row r="51" customFormat="1" customHeight="1" spans="3:18">
       <c r="C51" s="1">
         <v>3046</v>
       </c>
@@ -7989,7 +7989,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="52" customFormat="1" customHeight="1" spans="3:17">
+    <row r="52" customFormat="1" customHeight="1" spans="3:18">
       <c r="C52" s="1">
         <v>3047</v>
       </c>
@@ -8036,7 +8036,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="53" customFormat="1" customHeight="1" spans="3:17">
+    <row r="53" customFormat="1" customHeight="1" spans="3:18">
       <c r="C53" s="1">
         <v>3048</v>
       </c>
@@ -8083,7 +8083,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54" customFormat="1" customHeight="1" spans="3:17">
+    <row r="54" customFormat="1" customHeight="1" spans="3:18">
       <c r="C54" s="1">
         <v>3049</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" customFormat="1" customHeight="1" spans="3:17">
+    <row r="55" customFormat="1" customHeight="1" spans="3:18">
       <c r="C55" s="1">
         <v>3050</v>
       </c>
@@ -8177,7 +8177,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="56" customFormat="1" customHeight="1" spans="3:17">
+    <row r="56" customFormat="1" customHeight="1" spans="3:18">
       <c r="C56" s="1">
         <v>3051</v>
       </c>
@@ -8224,7 +8224,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="57" customFormat="1" customHeight="1" spans="3:17">
+    <row r="57" customFormat="1" customHeight="1" spans="3:18">
       <c r="C57" s="1">
         <v>3052</v>
       </c>
@@ -8271,7 +8271,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="3:17">
+    <row r="58" customHeight="1" spans="3:18">
       <c r="C58" s="1">
         <v>3053</v>
       </c>
@@ -8318,7 +8318,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="59" customFormat="1" customHeight="1" spans="3:17">
+    <row r="59" customFormat="1" customHeight="1" spans="3:18">
       <c r="C59" s="1">
         <v>3054</v>
       </c>
@@ -8365,7 +8365,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="60" customFormat="1" customHeight="1" spans="3:17">
+    <row r="60" customFormat="1" customHeight="1" spans="3:18">
       <c r="C60" s="1">
         <v>3055</v>
       </c>
@@ -8412,7 +8412,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="61" customFormat="1" customHeight="1" spans="3:17">
+    <row r="61" customFormat="1" customHeight="1" spans="3:18">
       <c r="C61" s="1">
         <v>3056</v>
       </c>
@@ -8459,7 +8459,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="62" customFormat="1" customHeight="1" spans="3:17">
+    <row r="62" customFormat="1" customHeight="1" spans="3:18">
       <c r="C62" s="1">
         <v>3057</v>
       </c>
@@ -8506,7 +8506,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="3:17">
+    <row r="63" customHeight="1" spans="3:18">
       <c r="C63" s="1">
         <v>3058</v>
       </c>
@@ -8553,9 +8553,249 @@
         <v>58</v>
       </c>
     </row>
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C64" s="1">
+        <v>3059</v>
+      </c>
+      <c r="D64" s="1">
+        <v>3</v>
+      </c>
+      <c r="E64" s="1">
+        <v>3</v>
+      </c>
+      <c r="F64" s="1">
+        <v>1</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1">
+        <v>301</v>
+      </c>
+      <c r="I64" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J64" s="1">
+        <v>0</v>
+      </c>
+      <c r="K64" s="1">
+        <v>0</v>
+      </c>
+      <c r="L64" s="1">
+        <v>5</v>
+      </c>
+      <c r="M64" s="4">
+        <v>5015</v>
+      </c>
+      <c r="N64" s="1">
+        <v>25</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P64" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>59</v>
+      </c>
+      <c r="R64" s="2"/>
+    </row>
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C65" s="1">
+        <v>3060</v>
+      </c>
+      <c r="D65" s="1">
+        <v>3</v>
+      </c>
+      <c r="E65" s="1">
+        <v>3</v>
+      </c>
+      <c r="F65" s="1">
+        <v>1</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0</v>
+      </c>
+      <c r="H65" s="1">
+        <v>301</v>
+      </c>
+      <c r="I65" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J65" s="1">
+        <v>0</v>
+      </c>
+      <c r="K65" s="1">
+        <v>0</v>
+      </c>
+      <c r="L65" s="1">
+        <v>5</v>
+      </c>
+      <c r="M65" s="4">
+        <v>5016</v>
+      </c>
+      <c r="N65" s="1">
+        <v>20</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>60</v>
+      </c>
+      <c r="R65" s="2"/>
+    </row>
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C66" s="1">
+        <v>3061</v>
+      </c>
+      <c r="D66" s="1">
+        <v>3</v>
+      </c>
+      <c r="E66" s="1">
+        <v>3</v>
+      </c>
+      <c r="F66" s="1">
+        <v>1</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1">
+        <v>301</v>
+      </c>
+      <c r="I66" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J66" s="1">
+        <v>0</v>
+      </c>
+      <c r="K66" s="1">
+        <v>0</v>
+      </c>
+      <c r="L66" s="1">
+        <v>5</v>
+      </c>
+      <c r="M66" s="4">
+        <v>5017</v>
+      </c>
+      <c r="N66" s="1">
+        <v>15</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q66" s="1">
+        <v>61</v>
+      </c>
+      <c r="R66" s="2"/>
+    </row>
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C67" s="1">
+        <v>3062</v>
+      </c>
+      <c r="D67" s="1">
+        <v>3</v>
+      </c>
+      <c r="E67" s="1">
+        <v>3</v>
+      </c>
+      <c r="F67" s="1">
+        <v>1</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1">
+        <v>301</v>
+      </c>
+      <c r="I67" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J67" s="1">
+        <v>0</v>
+      </c>
+      <c r="K67" s="1">
+        <v>0</v>
+      </c>
+      <c r="L67" s="1">
+        <v>5</v>
+      </c>
+      <c r="M67" s="4">
+        <v>5018</v>
+      </c>
+      <c r="N67" s="1">
+        <v>10</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P67" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q67" s="1">
+        <v>62</v>
+      </c>
+      <c r="R67" s="2"/>
+    </row>
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C68" s="1">
+        <v>3063</v>
+      </c>
+      <c r="D68" s="1">
+        <v>3</v>
+      </c>
+      <c r="E68" s="1">
+        <v>3</v>
+      </c>
+      <c r="F68" s="1">
+        <v>1</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1">
+        <v>301</v>
+      </c>
+      <c r="I68" s="1">
+        <v>100000</v>
+      </c>
+      <c r="J68" s="1">
+        <v>0</v>
+      </c>
+      <c r="K68" s="1">
+        <v>0</v>
+      </c>
+      <c r="L68" s="1">
+        <v>5</v>
+      </c>
+      <c r="M68" s="4">
+        <v>5019</v>
+      </c>
+      <c r="N68" s="1">
+        <v>5</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P68" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>63</v>
+      </c>
+      <c r="R68" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M21:M25 R6:R32 C3:R5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M21:M25 M64:M68 R6:R32 R64:R68 C3:R5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -9819,7 +10059,7 @@
     <row r="56" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R6:R18 R19:R26 C3:R5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R6:R26 C3:R5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11480" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="新入世界" sheetId="1" r:id="rId1"/>
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="104">
   <si>
     <t>#</t>
   </si>
@@ -594,6 +594,9 @@
   </si>
   <si>
     <t>击杀{0}个怪物，新手十抽11</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，新手十抽12</t>
   </si>
 </sst>
 </file>
@@ -9971,6 +9974,51 @@
       <c r="R18" s="2"/>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C19" s="1">
+        <v>12014</v>
+      </c>
+      <c r="D19" s="1">
+        <v>12</v>
+      </c>
+      <c r="E19" s="1">
+        <v>12</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1">
+        <v>301</v>
+      </c>
+      <c r="I19" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M19" s="1">
+        <v>1</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>14</v>
+      </c>
       <c r="R19" s="2"/>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:18">

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="新入世界" sheetId="1" r:id="rId1"/>
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="106">
   <si>
     <t>#</t>
   </si>
@@ -462,6 +462,12 @@
   </si>
   <si>
     <t>击杀550000个怪物</t>
+  </si>
+  <si>
+    <t>击杀1000000个怪物</t>
+  </si>
+  <si>
+    <t>奖励1本7阶技能自选</t>
   </si>
   <si>
     <t>击杀{0}个怪物</t>
@@ -3047,7 +3053,53 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" customFormat="1" customHeight="1"/>
+    <row r="33" customFormat="1" customHeight="1" spans="3:17">
+      <c r="C33" s="1">
+        <v>28</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>301</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <v>8</v>
+      </c>
+      <c r="M33" s="1">
+        <v>7</v>
+      </c>
+      <c r="N33" s="1">
+        <v>1</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>28</v>
+      </c>
+    </row>
     <row r="34" customFormat="1" customHeight="1"/>
     <row r="35" customFormat="1" customHeight="1"/>
     <row r="36" customFormat="1" customHeight="1"/>
@@ -3289,7 +3341,7 @@
         <v>1000</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>27</v>
@@ -3336,7 +3388,7 @@
         <v>1000</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>27</v>
@@ -3383,7 +3435,7 @@
         <v>1000</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>27</v>
@@ -3430,7 +3482,7 @@
         <v>1000</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>27</v>
@@ -3477,7 +3529,7 @@
         <v>1000</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>27</v>
@@ -3524,7 +3576,7 @@
         <v>2000</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>27</v>
@@ -3572,7 +3624,7 @@
         <v>20</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>29</v>
@@ -3619,10 +3671,10 @@
         <v>10</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q13" s="1">
         <v>8</v>
@@ -3666,7 +3718,7 @@
         <v>2000</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>27</v>
@@ -3713,7 +3765,7 @@
         <v>20</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>29</v>
@@ -3760,7 +3812,7 @@
         <v>3000</v>
       </c>
       <c r="O16" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P16" s="5" t="s">
         <v>27</v>
@@ -3807,7 +3859,7 @@
         <v>30</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P17" s="1" t="s">
         <v>29</v>
@@ -3854,10 +3906,10 @@
         <v>15</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q18" s="1">
         <v>13</v>
@@ -3901,7 +3953,7 @@
         <v>3000</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P19" s="1" t="s">
         <v>27</v>
@@ -3948,7 +4000,7 @@
         <v>30</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>29</v>
@@ -3995,7 +4047,7 @@
         <v>4000</v>
       </c>
       <c r="O21" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P21" s="5" t="s">
         <v>27</v>
@@ -4042,7 +4094,7 @@
         <v>40</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>29</v>
@@ -4089,10 +4141,10 @@
         <v>20</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q23" s="1">
         <v>18</v>
@@ -4136,7 +4188,7 @@
         <v>4000</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>27</v>
@@ -4183,7 +4235,7 @@
         <v>40</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P25" s="1" t="s">
         <v>29</v>
@@ -4230,7 +4282,7 @@
         <v>5000</v>
       </c>
       <c r="O26" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P26" s="5" t="s">
         <v>27</v>
@@ -4277,7 +4329,7 @@
         <v>50</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>29</v>
@@ -4324,10 +4376,10 @@
         <v>25</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q28" s="1">
         <v>23</v>
@@ -4371,7 +4423,7 @@
         <v>5000</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>27</v>
@@ -4418,7 +4470,7 @@
         <v>50</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>29</v>
@@ -4465,7 +4517,7 @@
         <v>6000</v>
       </c>
       <c r="O31" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P31" s="5" t="s">
         <v>27</v>
@@ -4512,7 +4564,7 @@
         <v>50</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>29</v>
@@ -4559,10 +4611,10 @@
         <v>30</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q33" s="1">
         <v>28</v>
@@ -4606,7 +4658,7 @@
         <v>6000</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P34" s="1" t="s">
         <v>27</v>
@@ -4653,7 +4705,7 @@
         <v>50</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>29</v>
@@ -4700,7 +4752,7 @@
         <v>7000</v>
       </c>
       <c r="O36" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P36" s="5" t="s">
         <v>27</v>
@@ -4747,7 +4799,7 @@
         <v>50</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>29</v>
@@ -4794,10 +4846,10 @@
         <v>35</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q38" s="1">
         <v>33</v>
@@ -4841,7 +4893,7 @@
         <v>7000</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P39" s="1" t="s">
         <v>27</v>
@@ -4888,7 +4940,7 @@
         <v>50</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>29</v>
@@ -4935,7 +4987,7 @@
         <v>7000</v>
       </c>
       <c r="O41" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P41" s="5" t="s">
         <v>27</v>
@@ -4982,7 +5034,7 @@
         <v>50</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>29</v>
@@ -5029,10 +5081,10 @@
         <v>35</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q43" s="1">
         <v>38</v>
@@ -5076,7 +5128,7 @@
         <v>7000</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>27</v>
@@ -5123,7 +5175,7 @@
         <v>50</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>29</v>
@@ -5170,7 +5222,7 @@
         <v>7000</v>
       </c>
       <c r="O46" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P46" s="5" t="s">
         <v>27</v>
@@ -5217,7 +5269,7 @@
         <v>50</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P47" s="1" t="s">
         <v>29</v>
@@ -5264,10 +5316,10 @@
         <v>35</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q48" s="1">
         <v>43</v>
@@ -5311,7 +5363,7 @@
         <v>7000</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>27</v>
@@ -5358,7 +5410,7 @@
         <v>50</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P50" s="1" t="s">
         <v>29</v>
@@ -5405,7 +5457,7 @@
         <v>7000</v>
       </c>
       <c r="O51" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P51" s="5" t="s">
         <v>27</v>
@@ -5452,7 +5504,7 @@
         <v>50</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>29</v>
@@ -5499,10 +5551,10 @@
         <v>35</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q53" s="1">
         <v>48</v>
@@ -5546,7 +5598,7 @@
         <v>7000</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>27</v>
@@ -5593,7 +5645,7 @@
         <v>50</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>29</v>
@@ -5839,10 +5891,10 @@
         <v>1</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
@@ -5887,10 +5939,10 @@
         <v>1</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Q7" s="1">
         <v>2</v>
@@ -5935,10 +5987,10 @@
         <v>25</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q8" s="1">
         <v>3</v>
@@ -5983,10 +6035,10 @@
         <v>3</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Q9" s="1">
         <v>4</v>
@@ -6031,10 +6083,10 @@
         <v>1</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q10" s="1">
         <v>5</v>
@@ -6079,10 +6131,10 @@
         <v>25</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Q11" s="1">
         <v>6</v>
@@ -6127,10 +6179,10 @@
         <v>3</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q12" s="1">
         <v>7</v>
@@ -6175,10 +6227,10 @@
         <v>1</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q13" s="1">
         <v>8</v>
@@ -6223,10 +6275,10 @@
         <v>1</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q14" s="1">
         <v>9</v>
@@ -6271,10 +6323,10 @@
         <v>25</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q15" s="1">
         <v>10</v>
@@ -6319,10 +6371,10 @@
         <v>3</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q16" s="1">
         <v>11</v>
@@ -6367,10 +6419,10 @@
         <v>1</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q17" s="1">
         <v>12</v>
@@ -6415,10 +6467,10 @@
         <v>25</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="1">
         <v>13</v>
@@ -6463,10 +6515,10 @@
         <v>3</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q19" s="1">
         <v>14</v>
@@ -6511,10 +6563,10 @@
         <v>1</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q20" s="1">
         <v>15</v>
@@ -6559,10 +6611,10 @@
         <v>50</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q21" s="1">
         <v>16</v>
@@ -6607,10 +6659,10 @@
         <v>40</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Q22" s="1">
         <v>17</v>
@@ -6655,10 +6707,10 @@
         <v>30</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q23" s="1">
         <v>18</v>
@@ -6703,10 +6755,10 @@
         <v>20</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Q24" s="1">
         <v>19</v>
@@ -6751,10 +6803,10 @@
         <v>10</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Q25" s="1">
         <v>20</v>
@@ -6799,10 +6851,10 @@
         <v>25</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q26" s="1">
         <v>21</v>
@@ -6847,10 +6899,10 @@
         <v>3</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Q27" s="1">
         <v>22</v>
@@ -6895,10 +6947,10 @@
         <v>1</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q28" s="1">
         <v>23</v>
@@ -6943,10 +6995,10 @@
         <v>2</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q29" s="1">
         <v>24</v>
@@ -6991,10 +7043,10 @@
         <v>2</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q30" s="1">
         <v>25</v>
@@ -7039,10 +7091,10 @@
         <v>2</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q31" s="1">
         <v>26</v>
@@ -7089,10 +7141,10 @@
         <v>2</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q32" s="1">
         <v>27</v>
@@ -7137,10 +7189,10 @@
         <v>2</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q33" s="1">
         <v>28</v>
@@ -7184,10 +7236,10 @@
         <v>2</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q34" s="1">
         <v>29</v>
@@ -7231,10 +7283,10 @@
         <v>2</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q35" s="1">
         <v>30</v>
@@ -7278,10 +7330,10 @@
         <v>2</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q36" s="1">
         <v>31</v>
@@ -7325,10 +7377,10 @@
         <v>2</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q37" s="1">
         <v>32</v>
@@ -7372,10 +7424,10 @@
         <v>2</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q38" s="1">
         <v>33</v>
@@ -7419,10 +7471,10 @@
         <v>2</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q39" s="1">
         <v>34</v>
@@ -7466,10 +7518,10 @@
         <v>2</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q40" s="1">
         <v>35</v>
@@ -7513,10 +7565,10 @@
         <v>2</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q41" s="1">
         <v>36</v>
@@ -7560,10 +7612,10 @@
         <v>2</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q42" s="1">
         <v>37</v>
@@ -7607,10 +7659,10 @@
         <v>2</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q43" s="1">
         <v>38</v>
@@ -7654,10 +7706,10 @@
         <v>2</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q44" s="1">
         <v>39</v>
@@ -7701,10 +7753,10 @@
         <v>2</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q45" s="1">
         <v>40</v>
@@ -7748,10 +7800,10 @@
         <v>2</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q46" s="1">
         <v>41</v>
@@ -7795,10 +7847,10 @@
         <v>2</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q47" s="1">
         <v>42</v>
@@ -7842,10 +7894,10 @@
         <v>2</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q48" s="1">
         <v>43</v>
@@ -7889,10 +7941,10 @@
         <v>2</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q49" s="1">
         <v>44</v>
@@ -7936,10 +7988,10 @@
         <v>2</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q50" s="1">
         <v>45</v>
@@ -7983,10 +8035,10 @@
         <v>2</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q51" s="1">
         <v>46</v>
@@ -8030,10 +8082,10 @@
         <v>2</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q52" s="1">
         <v>47</v>
@@ -8077,10 +8129,10 @@
         <v>2</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q53" s="1">
         <v>48</v>
@@ -8124,10 +8176,10 @@
         <v>2</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q54" s="1">
         <v>49</v>
@@ -8171,10 +8223,10 @@
         <v>2</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q55" s="1">
         <v>50</v>
@@ -8218,10 +8270,10 @@
         <v>2</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q56" s="1">
         <v>51</v>
@@ -8265,10 +8317,10 @@
         <v>2</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q57" s="1">
         <v>52</v>
@@ -8312,10 +8364,10 @@
         <v>2</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q58" s="1">
         <v>53</v>
@@ -8359,10 +8411,10 @@
         <v>2</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q59" s="1">
         <v>54</v>
@@ -8406,10 +8458,10 @@
         <v>2</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q60" s="1">
         <v>55</v>
@@ -8453,10 +8505,10 @@
         <v>2</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q61" s="1">
         <v>56</v>
@@ -8500,10 +8552,10 @@
         <v>2</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q62" s="1">
         <v>57</v>
@@ -8547,10 +8599,10 @@
         <v>2</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q63" s="1">
         <v>58</v>
@@ -8594,10 +8646,10 @@
         <v>25</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q64" s="1">
         <v>59</v>
@@ -8642,10 +8694,10 @@
         <v>20</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Q65" s="1">
         <v>60</v>
@@ -8690,10 +8742,10 @@
         <v>15</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q66" s="1">
         <v>61</v>
@@ -8738,10 +8790,10 @@
         <v>10</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Q67" s="1">
         <v>62</v>
@@ -8786,10 +8838,10 @@
         <v>5</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Q68" s="1">
         <v>63</v>
@@ -9023,10 +9075,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
@@ -9387,10 +9439,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q6" s="1">
         <v>11</v>
@@ -9435,10 +9487,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P7" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="Q7" s="1">
         <v>12</v>
@@ -9483,10 +9535,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q8" s="1">
         <v>1</v>
@@ -9531,10 +9583,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q9" s="1">
         <v>2</v>
@@ -9579,10 +9631,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q10" s="1">
         <v>3</v>
@@ -9627,10 +9679,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q11" s="1">
         <v>4</v>
@@ -9675,10 +9727,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q12" s="1">
         <v>5</v>
@@ -9723,10 +9775,10 @@
         <v>0</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q13" s="1">
         <v>6</v>
@@ -9771,10 +9823,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q14" s="1">
         <v>7</v>
@@ -9819,10 +9871,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q15" s="1">
         <v>8</v>
@@ -9867,10 +9919,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q16" s="1">
         <v>9</v>
@@ -9915,10 +9967,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q17" s="1">
         <v>10</v>
@@ -9963,10 +10015,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q18" s="1">
         <v>13</v>
@@ -10011,10 +10063,10 @@
         <v>0</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q19" s="1">
         <v>14</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="新入世界" sheetId="1" r:id="rId1"/>
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="108">
   <si>
     <t>#</t>
   </si>
@@ -603,6 +603,12 @@
   </si>
   <si>
     <t>击杀{0}个怪物，新手十抽12</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，福利3（泽泽）</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，福利4（泽泽）</t>
   </si>
 </sst>
 </file>
@@ -10074,9 +10080,99 @@
       <c r="R19" s="2"/>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C20" s="1">
+        <v>12015</v>
+      </c>
+      <c r="D20" s="1">
+        <v>12</v>
+      </c>
+      <c r="E20" s="1">
+        <v>12</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1">
+        <v>301</v>
+      </c>
+      <c r="I20" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M20" s="1">
+        <v>1</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>15</v>
+      </c>
       <c r="R20" s="2"/>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C21" s="1">
+        <v>12016</v>
+      </c>
+      <c r="D21" s="1">
+        <v>12</v>
+      </c>
+      <c r="E21" s="1">
+        <v>12</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1">
+        <v>301</v>
+      </c>
+      <c r="I21" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M21" s="1">
+        <v>1</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>16</v>
+      </c>
       <c r="R21" s="2"/>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:18">

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="新入世界" sheetId="1" r:id="rId1"/>
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="110">
   <si>
     <t>#</t>
   </si>
@@ -609,6 +609,12 @@
   </si>
   <si>
     <t>击杀{0}个怪物，福利4（泽泽）</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，奖励50抽</t>
+  </si>
+  <si>
+    <t>奖励50次抽奖</t>
   </si>
 </sst>
 </file>
@@ -10176,9 +10182,99 @@
       <c r="R21" s="2"/>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C22" s="1">
+        <v>12017</v>
+      </c>
+      <c r="D22" s="1">
+        <v>12</v>
+      </c>
+      <c r="E22" s="1">
+        <v>12</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
+        <v>301</v>
+      </c>
+      <c r="I22" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M22" s="1">
+        <v>1</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>17</v>
+      </c>
       <c r="R22" s="2"/>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C23" s="1">
+        <v>12018</v>
+      </c>
+      <c r="D23" s="1">
+        <v>12</v>
+      </c>
+      <c r="E23" s="1">
+        <v>12</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1</v>
+      </c>
+      <c r="H23" s="1">
+        <v>301</v>
+      </c>
+      <c r="I23" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M23" s="1">
+        <v>1</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>18</v>
+      </c>
       <c r="R23" s="2"/>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:18">

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="新入世界" sheetId="1" r:id="rId1"/>
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="112">
   <si>
     <t>#</t>
   </si>
@@ -558,6 +558,12 @@
   </si>
   <si>
     <t>奖励{1}个骨龙核心</t>
+  </si>
+  <si>
+    <t>奖励{1}铜矿石</t>
+  </si>
+  <si>
+    <t>奖励{1}黑铁矿</t>
   </si>
   <si>
     <t>奖励10次抽奖</t>
@@ -5691,7 +5697,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R68"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -8860,9 +8866,105 @@
       </c>
       <c r="R68" s="2"/>
     </row>
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C69" s="1">
+        <v>3064</v>
+      </c>
+      <c r="D69" s="1">
+        <v>3</v>
+      </c>
+      <c r="E69" s="1">
+        <v>3</v>
+      </c>
+      <c r="F69" s="1">
+        <v>1</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1">
+        <v>301</v>
+      </c>
+      <c r="I69" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J69" s="1">
+        <v>0</v>
+      </c>
+      <c r="K69" s="1">
+        <v>0</v>
+      </c>
+      <c r="L69" s="1">
+        <v>5</v>
+      </c>
+      <c r="M69" s="1">
+        <v>5001</v>
+      </c>
+      <c r="N69" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P69" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q69" s="1">
+        <v>63</v>
+      </c>
+      <c r="R69" s="2"/>
+    </row>
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C70" s="1">
+        <v>3065</v>
+      </c>
+      <c r="D70" s="1">
+        <v>3</v>
+      </c>
+      <c r="E70" s="1">
+        <v>3</v>
+      </c>
+      <c r="F70" s="1">
+        <v>1</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1">
+        <v>301</v>
+      </c>
+      <c r="I70" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J70" s="1">
+        <v>0</v>
+      </c>
+      <c r="K70" s="1">
+        <v>0</v>
+      </c>
+      <c r="L70" s="1">
+        <v>5</v>
+      </c>
+      <c r="M70" s="1">
+        <v>5002</v>
+      </c>
+      <c r="N70" s="1">
+        <v>1000</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P70" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q70" s="1">
+        <v>63</v>
+      </c>
+      <c r="R70" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M21:M25 M64:M68 R6:R32 R64:R68 C3:R5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R69 R70 M21:M25 M64:M68 R6:R32 R64:R68 C3:R5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -9090,7 +9192,7 @@
         <v>61</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
@@ -9451,10 +9553,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q6" s="1">
         <v>11</v>
@@ -9499,10 +9601,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="P7" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="Q7" s="1">
         <v>12</v>
@@ -9547,10 +9649,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q8" s="1">
         <v>1</v>
@@ -9595,10 +9697,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q9" s="1">
         <v>2</v>
@@ -9643,10 +9745,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q10" s="1">
         <v>3</v>
@@ -9691,10 +9793,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q11" s="1">
         <v>4</v>
@@ -9739,10 +9841,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q12" s="1">
         <v>5</v>
@@ -9787,10 +9889,10 @@
         <v>0</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q13" s="1">
         <v>6</v>
@@ -9835,10 +9937,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q14" s="1">
         <v>7</v>
@@ -9883,10 +9985,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q15" s="1">
         <v>8</v>
@@ -9931,10 +10033,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q16" s="1">
         <v>9</v>
@@ -9979,10 +10081,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q17" s="1">
         <v>10</v>
@@ -10027,10 +10129,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q18" s="1">
         <v>13</v>
@@ -10075,10 +10177,10 @@
         <v>0</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q19" s="1">
         <v>14</v>
@@ -10123,10 +10225,10 @@
         <v>0</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q20" s="1">
         <v>15</v>
@@ -10171,10 +10273,10 @@
         <v>0</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q21" s="1">
         <v>16</v>
@@ -10219,10 +10321,10 @@
         <v>0</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q22" s="1">
         <v>17</v>
@@ -10267,10 +10369,10 @@
         <v>0</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q23" s="1">
         <v>18</v>

--- a/Excel/AchievementTaskConfig.xlsx
+++ b/Excel/AchievementTaskConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="新入世界" sheetId="1" r:id="rId1"/>
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="114">
   <si>
     <t>#</t>
   </si>
@@ -566,6 +566,9 @@
     <t>奖励{1}黑铁矿</t>
   </si>
   <si>
+    <t>奖励{1}四格碎片</t>
+  </si>
+  <si>
     <t>奖励10次抽奖</t>
   </si>
   <si>
@@ -621,6 +624,9 @@
   </si>
   <si>
     <t>奖励50次抽奖</t>
+  </si>
+  <si>
+    <t>击杀{0}个怪物，福利5（彼此）</t>
   </si>
 </sst>
 </file>
@@ -5697,7 +5703,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -8910,7 +8916,7 @@
         <v>91</v>
       </c>
       <c r="Q69" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R69" s="2"/>
     </row>
@@ -8958,13 +8964,154 @@
         <v>92</v>
       </c>
       <c r="Q70" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R70" s="2"/>
+    </row>
+    <row r="71" customHeight="1" spans="3:18">
+      <c r="C71" s="1">
+        <v>3066</v>
+      </c>
+      <c r="D71" s="1">
+        <v>3</v>
+      </c>
+      <c r="E71" s="1">
+        <v>3</v>
+      </c>
+      <c r="F71" s="1">
+        <v>1</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0</v>
+      </c>
+      <c r="H71" s="1">
+        <v>301</v>
+      </c>
+      <c r="I71" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J71" s="1">
+        <v>0</v>
+      </c>
+      <c r="K71" s="1">
+        <v>0</v>
+      </c>
+      <c r="L71" s="1">
+        <v>5</v>
+      </c>
+      <c r="M71" s="1">
+        <v>5001</v>
+      </c>
+      <c r="N71" s="1">
+        <v>100000</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P71" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q71" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:18">
+      <c r="C72" s="1">
+        <v>3067</v>
+      </c>
+      <c r="D72" s="1">
+        <v>3</v>
+      </c>
+      <c r="E72" s="1">
+        <v>3</v>
+      </c>
+      <c r="F72" s="1">
+        <v>1</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1">
+        <v>301</v>
+      </c>
+      <c r="I72" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J72" s="1">
+        <v>0</v>
+      </c>
+      <c r="K72" s="1">
+        <v>0</v>
+      </c>
+      <c r="L72" s="1">
+        <v>5</v>
+      </c>
+      <c r="M72" s="1">
+        <v>5002</v>
+      </c>
+      <c r="N72" s="1">
+        <v>1000</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P72" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q72" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:18">
+      <c r="C73" s="1">
+        <v>3068</v>
+      </c>
+      <c r="D73" s="1">
+        <v>3</v>
+      </c>
+      <c r="E73" s="1">
+        <v>3</v>
+      </c>
+      <c r="F73" s="1">
+        <v>1</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+      <c r="H73" s="1">
+        <v>301</v>
+      </c>
+      <c r="I73" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J73" s="1">
+        <v>0</v>
+      </c>
+      <c r="K73" s="1">
+        <v>0</v>
+      </c>
+      <c r="L73" s="1">
+        <v>8</v>
+      </c>
+      <c r="M73" s="1">
+        <v>11</v>
+      </c>
+      <c r="N73" s="1">
+        <v>200</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P73" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q73" s="1">
+        <v>68</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R69 R70 M21:M25 M64:M68 R6:R32 R64:R68 C3:R5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M21:M25 M64:M68 R6:R32 R64:R70 C3:R5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -9192,7 +9339,7 @@
         <v>61</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
@@ -9340,7 +9487,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
@@ -9553,10 +9700,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="P6" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="Q6" s="1">
         <v>11</v>
@@ -9601,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q7" s="1">
         <v>12</v>
@@ -9649,10 +9796,10 @@
         <v>0</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q8" s="1">
         <v>1</v>
@@ -9697,10 +9844,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q9" s="1">
         <v>2</v>
@@ -9745,10 +9892,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q10" s="1">
         <v>3</v>
@@ -9793,10 +9940,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q11" s="1">
         <v>4</v>
@@ -9841,10 +9988,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q12" s="1">
         <v>5</v>
@@ -9889,10 +10036,10 @@
         <v>0</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q13" s="1">
         <v>6</v>
@@ -9937,10 +10084,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q14" s="1">
         <v>7</v>
@@ -9985,10 +10132,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q15" s="1">
         <v>8</v>
@@ -10033,10 +10180,10 @@
         <v>0</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q16" s="1">
         <v>9</v>
@@ -10081,10 +10228,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q17" s="1">
         <v>10</v>
@@ -10129,10 +10276,10 @@
         <v>0</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q18" s="1">
         <v>13</v>
@@ -10177,10 +10324,10 @@
         <v>0</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q19" s="1">
         <v>14</v>
@@ -10225,10 +10372,10 @@
         <v>0</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q20" s="1">
         <v>15</v>
@@ -10273,10 +10420,10 @@
         <v>0</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q21" s="1">
         <v>16</v>
@@ -10321,10 +10468,10 @@
         <v>0</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q22" s="1">
         <v>17</v>
@@ -10369,10 +10516,10 @@
         <v>0</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q23" s="1">
         <v>18</v>
@@ -10380,32 +10527,107 @@
       <c r="R23" s="2"/>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C24" s="1">
+        <v>12019</v>
+      </c>
+      <c r="D24" s="1">
+        <v>12</v>
+      </c>
+      <c r="E24" s="1">
+        <v>12</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1">
+        <v>301</v>
+      </c>
+      <c r="I24" s="1">
+        <v>50000</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M24" s="1">
+        <v>1</v>
+      </c>
+      <c r="N24" s="1">
+        <v>0</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>19</v>
+      </c>
       <c r="R24" s="2"/>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C25" s="1">
+        <v>12020</v>
+      </c>
+      <c r="D25" s="1">
+        <v>12</v>
+      </c>
+      <c r="E25" s="1">
+        <v>12</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1">
+        <v>301</v>
+      </c>
+      <c r="I25" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M25" s="1">
+        <v>1</v>
+      </c>
+      <c r="N25" s="1">
+        <v>0</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>20</v>
+      </c>
       <c r="R25" s="2"/>
     </row>
-    <row r="26" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:18">
       <c r="R26" s="2"/>
     </row>
     <row r="27" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -10421,8 +10643,25 @@
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
-    </row>
-    <row r="28" customFormat="1" customHeight="1"/>
+      <c r="R27" s="2"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="1:18">
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+    </row>
     <row r="29" customFormat="1" customHeight="1"/>
     <row r="30" customFormat="1" customHeight="1"/>
     <row r="31" customFormat="1" customHeight="1"/>
@@ -10451,9 +10690,10 @@
     <row r="54" customFormat="1" customHeight="1"/>
     <row r="55" customFormat="1" customHeight="1"/>
     <row r="56" customFormat="1" customHeight="1"/>
+    <row r="57" customFormat="1" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R6:R26 C3:R5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R24 R25 R6:R23 R26:R27 C3:R5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
